--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
@@ -28411,7 +28411,7 @@
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
@@ -30767,7 +30767,7 @@
       </c>
       <c r="B490" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C490" s="2" t="inlineStr">
@@ -31821,7 +31821,7 @@
       </c>
       <c r="B507" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C507" s="2" t="inlineStr">
@@ -35665,7 +35665,7 @@
       </c>
       <c r="B569" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C569" s="2" t="inlineStr">
@@ -37897,7 +37897,7 @@
       </c>
       <c r="B605" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C605" s="2" t="inlineStr">
@@ -38021,7 +38021,7 @@
       </c>
       <c r="B607" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C607" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -47445,7 +47445,7 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
@@ -51041,7 +51041,7 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
@@ -51599,7 +51599,7 @@
       </c>
       <c r="B826" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C826" s="2" t="inlineStr">
@@ -56001,7 +56001,7 @@
       </c>
       <c r="B897" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C897" s="2" t="inlineStr">
@@ -58171,7 +58171,7 @@
       </c>
       <c r="B932" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C932" s="2" t="inlineStr">
@@ -63193,7 +63193,7 @@
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
@@ -70261,7 +70261,7 @@
       </c>
       <c r="B1127" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1127" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -73609,7 +73609,7 @@
       </c>
       <c r="B1181" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1181" s="2" t="inlineStr">
@@ -74663,7 +74663,7 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
@@ -74725,7 +74725,7 @@
       </c>
       <c r="B1199" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1199" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -76213,7 +76213,7 @@
       </c>
       <c r="B1223" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1223" s="2" t="inlineStr">
@@ -77577,7 +77577,7 @@
       </c>
       <c r="B1245" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1245" s="2" t="inlineStr">
@@ -79375,7 +79375,7 @@
       </c>
       <c r="B1274" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1274" s="2" t="inlineStr">
@@ -79561,7 +79561,7 @@
       </c>
       <c r="B1277" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1277" s="2" t="inlineStr">
@@ -83591,7 +83591,7 @@
       </c>
       <c r="B1342" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1342" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -83963,7 +83963,7 @@
       </c>
       <c r="B1348" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1348" s="2" t="inlineStr">
@@ -84397,7 +84397,7 @@
       </c>
       <c r="B1355" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1355" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -87993,7 +87993,7 @@
       </c>
       <c r="B1413" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1413" s="2" t="inlineStr">
@@ -88551,7 +88551,7 @@
       </c>
       <c r="B1422" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1422" s="2" t="inlineStr">
@@ -90349,7 +90349,7 @@
       </c>
       <c r="B1451" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1451" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">
@@ -92643,7 +92643,7 @@
       </c>
       <c r="B1488" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1488" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
@@ -28411,7 +28411,7 @@
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
@@ -31821,7 +31821,7 @@
       </c>
       <c r="B507" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C507" s="2" t="inlineStr">
@@ -33185,7 +33185,7 @@
       </c>
       <c r="B529" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C529" s="2" t="inlineStr">
@@ -37897,7 +37897,7 @@
       </c>
       <c r="B605" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C605" s="2" t="inlineStr">
@@ -38331,7 +38331,7 @@
       </c>
       <c r="B612" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C612" s="2" t="inlineStr">
@@ -40315,7 +40315,7 @@
       </c>
       <c r="B644" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C644" s="2" t="inlineStr">
@@ -42485,7 +42485,7 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
@@ -42919,7 +42919,7 @@
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
@@ -42981,7 +42981,7 @@
       </c>
       <c r="B687" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C687" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -47445,7 +47445,7 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
@@ -51041,7 +51041,7 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
@@ -51537,7 +51537,7 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -56001,7 +56001,7 @@
       </c>
       <c r="B897" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C897" s="2" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="B971" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C971" s="2" t="inlineStr">
@@ -66789,7 +66789,7 @@
       </c>
       <c r="B1071" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1071" s="2" t="inlineStr">
@@ -71191,7 +71191,7 @@
       </c>
       <c r="B1142" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1142" s="2" t="inlineStr">
@@ -74663,7 +74663,7 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -75035,7 +75035,7 @@
       </c>
       <c r="B1204" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1204" s="2" t="inlineStr">
@@ -76213,7 +76213,7 @@
       </c>
       <c r="B1223" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1223" s="2" t="inlineStr">
@@ -77577,7 +77577,7 @@
       </c>
       <c r="B1245" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1245" s="2" t="inlineStr">
@@ -77701,7 +77701,7 @@
       </c>
       <c r="B1247" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1247" s="2" t="inlineStr">
@@ -78879,7 +78879,7 @@
       </c>
       <c r="B1266" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1266" s="2" t="inlineStr">
@@ -83467,7 +83467,7 @@
       </c>
       <c r="B1340" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1340" s="2" t="inlineStr">
@@ -83591,7 +83591,7 @@
       </c>
       <c r="B1342" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1342" s="2" t="inlineStr">
@@ -83715,7 +83715,7 @@
       </c>
       <c r="B1344" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1344" s="2" t="inlineStr">
@@ -83963,7 +83963,7 @@
       </c>
       <c r="B1348" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1348" s="2" t="inlineStr">
@@ -84273,7 +84273,7 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
@@ -84397,7 +84397,7 @@
       </c>
       <c r="B1355" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1355" s="2" t="inlineStr">
@@ -88489,7 +88489,7 @@
       </c>
       <c r="B1421" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1421" s="2" t="inlineStr">
@@ -90225,7 +90225,7 @@
       </c>
       <c r="B1449" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1449" s="2" t="inlineStr">
@@ -92643,7 +92643,7 @@
       </c>
       <c r="B1488" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1488" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
@@ -31635,7 +31635,7 @@
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
@@ -31821,7 +31821,7 @@
       </c>
       <c r="B507" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C507" s="2" t="inlineStr">
@@ -33185,7 +33185,7 @@
       </c>
       <c r="B529" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C529" s="2" t="inlineStr">
@@ -42485,7 +42485,7 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -42981,7 +42981,7 @@
       </c>
       <c r="B687" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C687" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="B971" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C971" s="2" t="inlineStr">
@@ -63193,7 +63193,7 @@
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
@@ -69641,7 +69641,7 @@
       </c>
       <c r="B1117" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1117" s="2" t="inlineStr">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
@@ -71191,7 +71191,7 @@
       </c>
       <c r="B1142" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1142" s="2" t="inlineStr">
@@ -71687,7 +71687,7 @@
       </c>
       <c r="B1150" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1150" s="2" t="inlineStr">
@@ -74663,7 +74663,7 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
@@ -75035,7 +75035,7 @@
       </c>
       <c r="B1204" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1204" s="2" t="inlineStr">
@@ -79375,7 +79375,7 @@
       </c>
       <c r="B1274" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1274" s="2" t="inlineStr">
@@ -83467,7 +83467,7 @@
       </c>
       <c r="B1340" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1340" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -83715,7 +83715,7 @@
       </c>
       <c r="B1344" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1344" s="2" t="inlineStr">
@@ -83963,7 +83963,7 @@
       </c>
       <c r="B1348" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1348" s="2" t="inlineStr">
@@ -84273,7 +84273,7 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
@@ -84397,7 +84397,7 @@
       </c>
       <c r="B1355" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1355" s="2" t="inlineStr">
@@ -84707,7 +84707,7 @@
       </c>
       <c r="B1360" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1360" s="2" t="inlineStr">
@@ -84769,7 +84769,7 @@
       </c>
       <c r="B1361" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1361" s="2" t="inlineStr">
@@ -84893,7 +84893,7 @@
       </c>
       <c r="B1363" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1363" s="2" t="inlineStr">
@@ -87993,7 +87993,7 @@
       </c>
       <c r="B1413" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1413" s="2" t="inlineStr">
@@ -88489,7 +88489,7 @@
       </c>
       <c r="B1421" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1421" s="2" t="inlineStr">
@@ -88551,7 +88551,7 @@
       </c>
       <c r="B1422" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1422" s="2" t="inlineStr">
@@ -90287,7 +90287,7 @@
       </c>
       <c r="B1450" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1450" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">
@@ -91961,7 +91961,7 @@
       </c>
       <c r="B1477" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1477" s="2" t="inlineStr">
@@ -92643,7 +92643,7 @@
       </c>
       <c r="B1488" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1488" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -2557,7 +2557,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="B527" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C527" s="2" t="inlineStr">
@@ -38021,7 +38021,7 @@
       </c>
       <c r="B607" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C607" s="2" t="inlineStr">
@@ -42609,7 +42609,7 @@
       </c>
       <c r="B681" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C681" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -47445,7 +47445,7 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
@@ -51041,7 +51041,7 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
@@ -51103,7 +51103,7 @@
       </c>
       <c r="B818" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C818" s="2" t="inlineStr">
@@ -51413,7 +51413,7 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
@@ -58171,7 +58171,7 @@
       </c>
       <c r="B932" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C932" s="2" t="inlineStr">
@@ -58233,7 +58233,7 @@
       </c>
       <c r="B933" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C933" s="2" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="B971" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C971" s="2" t="inlineStr">
@@ -63193,7 +63193,7 @@
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
@@ -66789,7 +66789,7 @@
       </c>
       <c r="B1071" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1071" s="2" t="inlineStr">
@@ -69641,7 +69641,7 @@
       </c>
       <c r="B1117" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1117" s="2" t="inlineStr">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -75035,7 +75035,7 @@
       </c>
       <c r="B1204" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1204" s="2" t="inlineStr">
@@ -76213,7 +76213,7 @@
       </c>
       <c r="B1223" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1223" s="2" t="inlineStr">
@@ -77763,7 +77763,7 @@
       </c>
       <c r="B1248" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1248" s="2" t="inlineStr">
@@ -79375,7 +79375,7 @@
       </c>
       <c r="B1274" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1274" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -84087,7 +84087,7 @@
       </c>
       <c r="B1350" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1350" s="2" t="inlineStr">
@@ -84273,7 +84273,7 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
@@ -84397,7 +84397,7 @@
       </c>
       <c r="B1355" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1355" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84769,7 +84769,7 @@
       </c>
       <c r="B1361" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1361" s="2" t="inlineStr">
@@ -84893,7 +84893,7 @@
       </c>
       <c r="B1363" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1363" s="2" t="inlineStr">
@@ -87993,7 +87993,7 @@
       </c>
       <c r="B1413" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1413" s="2" t="inlineStr">
@@ -88551,7 +88551,7 @@
       </c>
       <c r="B1422" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1422" s="2" t="inlineStr">
@@ -90287,7 +90287,7 @@
       </c>
       <c r="B1450" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1450" s="2" t="inlineStr">
@@ -92643,7 +92643,7 @@
       </c>
       <c r="B1488" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1488" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
@@ -31635,7 +31635,7 @@
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
@@ -32937,7 +32937,7 @@
       </c>
       <c r="B525" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C525" s="2" t="inlineStr">
@@ -34921,7 +34921,7 @@
       </c>
       <c r="B557" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C557" s="2" t="inlineStr">
@@ -37897,7 +37897,7 @@
       </c>
       <c r="B605" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C605" s="2" t="inlineStr">
@@ -38021,7 +38021,7 @@
       </c>
       <c r="B607" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C607" s="2" t="inlineStr">
@@ -40315,7 +40315,7 @@
       </c>
       <c r="B644" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C644" s="2" t="inlineStr">
@@ -42609,7 +42609,7 @@
       </c>
       <c r="B681" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C681" s="2" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -47445,7 +47445,7 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
@@ -48933,7 +48933,7 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
@@ -51041,7 +51041,7 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
@@ -51103,7 +51103,7 @@
       </c>
       <c r="B818" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C818" s="2" t="inlineStr">
@@ -51413,7 +51413,7 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
@@ -51537,7 +51537,7 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -58171,7 +58171,7 @@
       </c>
       <c r="B932" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C932" s="2" t="inlineStr">
@@ -66789,7 +66789,7 @@
       </c>
       <c r="B1071" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1071" s="2" t="inlineStr">
@@ -69703,7 +69703,7 @@
       </c>
       <c r="B1118" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1118" s="2" t="inlineStr">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
@@ -71191,7 +71191,7 @@
       </c>
       <c r="B1142" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1142" s="2" t="inlineStr">
@@ -71687,7 +71687,7 @@
       </c>
       <c r="B1150" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1150" s="2" t="inlineStr">
@@ -71749,7 +71749,7 @@
       </c>
       <c r="B1151" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1151" s="2" t="inlineStr">
@@ -73609,7 +73609,7 @@
       </c>
       <c r="B1181" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1181" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -75035,7 +75035,7 @@
       </c>
       <c r="B1204" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1204" s="2" t="inlineStr">
@@ -76213,7 +76213,7 @@
       </c>
       <c r="B1223" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1223" s="2" t="inlineStr">
@@ -77701,7 +77701,7 @@
       </c>
       <c r="B1247" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1247" s="2" t="inlineStr">
@@ -77763,7 +77763,7 @@
       </c>
       <c r="B1248" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1248" s="2" t="inlineStr">
@@ -83591,7 +83591,7 @@
       </c>
       <c r="B1342" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1342" s="2" t="inlineStr">
@@ -83715,7 +83715,7 @@
       </c>
       <c r="B1344" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1344" s="2" t="inlineStr">
@@ -84273,7 +84273,7 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84707,7 +84707,7 @@
       </c>
       <c r="B1360" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1360" s="2" t="inlineStr">
@@ -84769,7 +84769,7 @@
       </c>
       <c r="B1361" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1361" s="2" t="inlineStr">
@@ -84893,7 +84893,7 @@
       </c>
       <c r="B1363" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1363" s="2" t="inlineStr">
@@ -88551,7 +88551,7 @@
       </c>
       <c r="B1422" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1422" s="2" t="inlineStr">
@@ -90225,7 +90225,7 @@
       </c>
       <c r="B1449" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1449" s="2" t="inlineStr">
@@ -90349,7 +90349,7 @@
       </c>
       <c r="B1451" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1451" s="2" t="inlineStr">
@@ -91961,7 +91961,7 @@
       </c>
       <c r="B1477" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1477" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
@@ -31635,7 +31635,7 @@
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="B527" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C527" s="2" t="inlineStr">
@@ -34921,7 +34921,7 @@
       </c>
       <c r="B557" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C557" s="2" t="inlineStr">
@@ -35665,7 +35665,7 @@
       </c>
       <c r="B569" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C569" s="2" t="inlineStr">
@@ -37897,7 +37897,7 @@
       </c>
       <c r="B605" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C605" s="2" t="inlineStr">
@@ -38331,7 +38331,7 @@
       </c>
       <c r="B612" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C612" s="2" t="inlineStr">
@@ -47445,7 +47445,7 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
@@ -48933,7 +48933,7 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
@@ -51537,7 +51537,7 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
@@ -51599,7 +51599,7 @@
       </c>
       <c r="B826" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C826" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -58171,7 +58171,7 @@
       </c>
       <c r="B932" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C932" s="2" t="inlineStr">
@@ -58233,7 +58233,7 @@
       </c>
       <c r="B933" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C933" s="2" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="B971" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C971" s="2" t="inlineStr">
@@ -69641,7 +69641,7 @@
       </c>
       <c r="B1117" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1117" s="2" t="inlineStr">
@@ -69703,7 +69703,7 @@
       </c>
       <c r="B1118" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1118" s="2" t="inlineStr">
@@ -70261,7 +70261,7 @@
       </c>
       <c r="B1127" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1127" s="2" t="inlineStr">
@@ -71191,7 +71191,7 @@
       </c>
       <c r="B1142" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1142" s="2" t="inlineStr">
@@ -71749,7 +71749,7 @@
       </c>
       <c r="B1151" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1151" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -76213,7 +76213,7 @@
       </c>
       <c r="B1223" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1223" s="2" t="inlineStr">
@@ -77639,7 +77639,7 @@
       </c>
       <c r="B1246" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1246" s="2" t="inlineStr">
@@ -78879,7 +78879,7 @@
       </c>
       <c r="B1266" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1266" s="2" t="inlineStr">
@@ -79561,7 +79561,7 @@
       </c>
       <c r="B1277" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1277" s="2" t="inlineStr">
@@ -79747,7 +79747,7 @@
       </c>
       <c r="B1280" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1280" s="2" t="inlineStr">
@@ -83467,7 +83467,7 @@
       </c>
       <c r="B1340" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1340" s="2" t="inlineStr">
@@ -83591,7 +83591,7 @@
       </c>
       <c r="B1342" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1342" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -83715,7 +83715,7 @@
       </c>
       <c r="B1344" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1344" s="2" t="inlineStr">
@@ -83963,7 +83963,7 @@
       </c>
       <c r="B1348" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1348" s="2" t="inlineStr">
@@ -84087,7 +84087,7 @@
       </c>
       <c r="B1350" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1350" s="2" t="inlineStr">
@@ -84707,7 +84707,7 @@
       </c>
       <c r="B1360" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1360" s="2" t="inlineStr">
@@ -84769,7 +84769,7 @@
       </c>
       <c r="B1361" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1361" s="2" t="inlineStr">
@@ -84831,7 +84831,7 @@
       </c>
       <c r="B1362" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1362" s="2" t="inlineStr">
@@ -84893,7 +84893,7 @@
       </c>
       <c r="B1363" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1363" s="2" t="inlineStr">
@@ -87931,7 +87931,7 @@
       </c>
       <c r="B1412" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1412" s="2" t="inlineStr">
@@ -87993,7 +87993,7 @@
       </c>
       <c r="B1413" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1413" s="2" t="inlineStr">
@@ -90225,7 +90225,7 @@
       </c>
       <c r="B1449" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1449" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">
@@ -91961,7 +91961,7 @@
       </c>
       <c r="B1477" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1477" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -2557,7 +2557,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
@@ -29713,7 +29713,7 @@
       </c>
       <c r="B473" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C473" s="2" t="inlineStr">
@@ -31635,7 +31635,7 @@
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
@@ -35665,7 +35665,7 @@
       </c>
       <c r="B569" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C569" s="2" t="inlineStr">
@@ -38331,7 +38331,7 @@
       </c>
       <c r="B612" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C612" s="2" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -63193,7 +63193,7 @@
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
@@ -69641,7 +69641,7 @@
       </c>
       <c r="B1117" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1117" s="2" t="inlineStr">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
@@ -70261,7 +70261,7 @@
       </c>
       <c r="B1127" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1127" s="2" t="inlineStr">
@@ -71191,7 +71191,7 @@
       </c>
       <c r="B1142" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1142" s="2" t="inlineStr">
@@ -73609,7 +73609,7 @@
       </c>
       <c r="B1181" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1181" s="2" t="inlineStr">
@@ -74663,7 +74663,7 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -77639,7 +77639,7 @@
       </c>
       <c r="B1246" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1246" s="2" t="inlineStr">
@@ -77701,7 +77701,7 @@
       </c>
       <c r="B1247" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1247" s="2" t="inlineStr">
@@ -79561,7 +79561,7 @@
       </c>
       <c r="B1277" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1277" s="2" t="inlineStr">
@@ -79747,7 +79747,7 @@
       </c>
       <c r="B1280" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1280" s="2" t="inlineStr">
@@ -83591,7 +83591,7 @@
       </c>
       <c r="B1342" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1342" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -83715,7 +83715,7 @@
       </c>
       <c r="B1344" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1344" s="2" t="inlineStr">
@@ -83963,7 +83963,7 @@
       </c>
       <c r="B1348" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1348" s="2" t="inlineStr">
@@ -84273,7 +84273,7 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
@@ -84397,7 +84397,7 @@
       </c>
       <c r="B1355" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1355" s="2" t="inlineStr">
@@ -84707,7 +84707,7 @@
       </c>
       <c r="B1360" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1360" s="2" t="inlineStr">
@@ -84769,7 +84769,7 @@
       </c>
       <c r="B1361" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1361" s="2" t="inlineStr">
@@ -84831,7 +84831,7 @@
       </c>
       <c r="B1362" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1362" s="2" t="inlineStr">
@@ -84893,7 +84893,7 @@
       </c>
       <c r="B1363" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1363" s="2" t="inlineStr">
@@ -87931,7 +87931,7 @@
       </c>
       <c r="B1412" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1412" s="2" t="inlineStr">
@@ -87993,7 +87993,7 @@
       </c>
       <c r="B1413" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1413" s="2" t="inlineStr">
@@ -88551,7 +88551,7 @@
       </c>
       <c r="B1422" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1422" s="2" t="inlineStr">
@@ -90225,7 +90225,7 @@
       </c>
       <c r="B1449" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1449" s="2" t="inlineStr">
@@ -90349,7 +90349,7 @@
       </c>
       <c r="B1451" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1451" s="2" t="inlineStr">
@@ -91961,7 +91961,7 @@
       </c>
       <c r="B1477" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1477" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -29713,7 +29713,7 @@
       </c>
       <c r="B473" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C473" s="2" t="inlineStr">
@@ -30767,7 +30767,7 @@
       </c>
       <c r="B490" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C490" s="2" t="inlineStr">
@@ -31635,7 +31635,7 @@
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
@@ -33185,7 +33185,7 @@
       </c>
       <c r="B529" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C529" s="2" t="inlineStr">
@@ -35665,7 +35665,7 @@
       </c>
       <c r="B569" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C569" s="2" t="inlineStr">
@@ -38331,7 +38331,7 @@
       </c>
       <c r="B612" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C612" s="2" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -51041,7 +51041,7 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
@@ -51537,7 +51537,7 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
@@ -51599,7 +51599,7 @@
       </c>
       <c r="B826" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C826" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -69641,7 +69641,7 @@
       </c>
       <c r="B1117" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1117" s="2" t="inlineStr">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
@@ -71191,7 +71191,7 @@
       </c>
       <c r="B1142" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1142" s="2" t="inlineStr">
@@ -71687,7 +71687,7 @@
       </c>
       <c r="B1150" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1150" s="2" t="inlineStr">
@@ -73609,7 +73609,7 @@
       </c>
       <c r="B1181" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1181" s="2" t="inlineStr">
@@ -74663,7 +74663,7 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -75035,7 +75035,7 @@
       </c>
       <c r="B1204" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1204" s="2" t="inlineStr">
@@ -77701,7 +77701,7 @@
       </c>
       <c r="B1247" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1247" s="2" t="inlineStr">
@@ -79747,7 +79747,7 @@
       </c>
       <c r="B1280" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1280" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -83715,7 +83715,7 @@
       </c>
       <c r="B1344" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1344" s="2" t="inlineStr">
@@ -84273,7 +84273,7 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
@@ -84707,7 +84707,7 @@
       </c>
       <c r="B1360" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1360" s="2" t="inlineStr">
@@ -84831,7 +84831,7 @@
       </c>
       <c r="B1362" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1362" s="2" t="inlineStr">
@@ -87993,7 +87993,7 @@
       </c>
       <c r="B1413" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1413" s="2" t="inlineStr">
@@ -88551,7 +88551,7 @@
       </c>
       <c r="B1422" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1422" s="2" t="inlineStr">
@@ -90225,7 +90225,7 @@
       </c>
       <c r="B1449" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1449" s="2" t="inlineStr">
@@ -90287,7 +90287,7 @@
       </c>
       <c r="B1450" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1450" s="2" t="inlineStr">
@@ -91961,7 +91961,7 @@
       </c>
       <c r="B1477" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1477" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
@@ -31635,7 +31635,7 @@
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
@@ -33185,7 +33185,7 @@
       </c>
       <c r="B529" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C529" s="2" t="inlineStr">
@@ -35665,7 +35665,7 @@
       </c>
       <c r="B569" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C569" s="2" t="inlineStr">
@@ -37897,7 +37897,7 @@
       </c>
       <c r="B605" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C605" s="2" t="inlineStr">
@@ -42485,7 +42485,7 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -47445,7 +47445,7 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
@@ -51413,7 +51413,7 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
@@ -51537,7 +51537,7 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
@@ -56001,7 +56001,7 @@
       </c>
       <c r="B897" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C897" s="2" t="inlineStr">
@@ -63193,7 +63193,7 @@
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
@@ -69641,7 +69641,7 @@
       </c>
       <c r="B1117" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1117" s="2" t="inlineStr">
@@ -69703,7 +69703,7 @@
       </c>
       <c r="B1118" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1118" s="2" t="inlineStr">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -74725,7 +74725,7 @@
       </c>
       <c r="B1199" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1199" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -76213,7 +76213,7 @@
       </c>
       <c r="B1223" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1223" s="2" t="inlineStr">
@@ -77577,7 +77577,7 @@
       </c>
       <c r="B1245" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1245" s="2" t="inlineStr">
@@ -77701,7 +77701,7 @@
       </c>
       <c r="B1247" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1247" s="2" t="inlineStr">
@@ -79375,7 +79375,7 @@
       </c>
       <c r="B1274" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1274" s="2" t="inlineStr">
@@ -83467,7 +83467,7 @@
       </c>
       <c r="B1340" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1340" s="2" t="inlineStr">
@@ -83591,7 +83591,7 @@
       </c>
       <c r="B1342" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1342" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -83963,7 +83963,7 @@
       </c>
       <c r="B1348" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1348" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84707,7 +84707,7 @@
       </c>
       <c r="B1360" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1360" s="2" t="inlineStr">
@@ -84769,7 +84769,7 @@
       </c>
       <c r="B1361" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1361" s="2" t="inlineStr">
@@ -90287,7 +90287,7 @@
       </c>
       <c r="B1450" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1450" s="2" t="inlineStr">
@@ -90349,7 +90349,7 @@
       </c>
       <c r="B1451" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1451" s="2" t="inlineStr">
@@ -91031,7 +91031,7 @@
       </c>
       <c r="B1462" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1462" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -28411,7 +28411,7 @@
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
@@ -30767,7 +30767,7 @@
       </c>
       <c r="B490" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C490" s="2" t="inlineStr">
@@ -31821,7 +31821,7 @@
       </c>
       <c r="B507" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C507" s="2" t="inlineStr">
@@ -34921,7 +34921,7 @@
       </c>
       <c r="B557" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C557" s="2" t="inlineStr">
@@ -35541,7 +35541,7 @@
       </c>
       <c r="B567" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C567" s="2" t="inlineStr">
@@ -35665,7 +35665,7 @@
       </c>
       <c r="B569" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C569" s="2" t="inlineStr">
@@ -38331,7 +38331,7 @@
       </c>
       <c r="B612" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C612" s="2" t="inlineStr">
@@ -40315,7 +40315,7 @@
       </c>
       <c r="B644" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C644" s="2" t="inlineStr">
@@ -42485,7 +42485,7 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
@@ -42609,7 +42609,7 @@
       </c>
       <c r="B681" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C681" s="2" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -51041,7 +51041,7 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
@@ -51413,7 +51413,7 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
@@ -56001,7 +56001,7 @@
       </c>
       <c r="B897" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C897" s="2" t="inlineStr">
@@ -60279,7 +60279,7 @@
       </c>
       <c r="B966" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C966" s="2" t="inlineStr">
@@ -69703,7 +69703,7 @@
       </c>
       <c r="B1118" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1118" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -71749,7 +71749,7 @@
       </c>
       <c r="B1151" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1151" s="2" t="inlineStr">
@@ -74725,7 +74725,7 @@
       </c>
       <c r="B1199" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1199" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -74973,7 +74973,7 @@
       </c>
       <c r="B1203" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1203" s="2" t="inlineStr">
@@ -75035,7 +75035,7 @@
       </c>
       <c r="B1204" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1204" s="2" t="inlineStr">
@@ -76213,7 +76213,7 @@
       </c>
       <c r="B1223" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1223" s="2" t="inlineStr">
@@ -77577,7 +77577,7 @@
       </c>
       <c r="B1245" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1245" s="2" t="inlineStr">
@@ -78879,7 +78879,7 @@
       </c>
       <c r="B1266" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1266" s="2" t="inlineStr">
@@ -79375,7 +79375,7 @@
       </c>
       <c r="B1274" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1274" s="2" t="inlineStr">
@@ -79747,7 +79747,7 @@
       </c>
       <c r="B1280" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1280" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -83963,7 +83963,7 @@
       </c>
       <c r="B1348" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1348" s="2" t="inlineStr">
@@ -84273,7 +84273,7 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84707,7 +84707,7 @@
       </c>
       <c r="B1360" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1360" s="2" t="inlineStr">
@@ -84769,7 +84769,7 @@
       </c>
       <c r="B1361" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1361" s="2" t="inlineStr">
@@ -84893,7 +84893,7 @@
       </c>
       <c r="B1363" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1363" s="2" t="inlineStr">
@@ -87993,7 +87993,7 @@
       </c>
       <c r="B1413" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1413" s="2" t="inlineStr">
@@ -88551,7 +88551,7 @@
       </c>
       <c r="B1422" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1422" s="2" t="inlineStr">
@@ -90349,7 +90349,7 @@
       </c>
       <c r="B1451" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1451" s="2" t="inlineStr">
@@ -91031,7 +91031,7 @@
       </c>
       <c r="B1462" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1462" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">
@@ -91961,7 +91961,7 @@
       </c>
       <c r="B1477" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1477" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
@@ -28411,7 +28411,7 @@
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
@@ -31821,7 +31821,7 @@
       </c>
       <c r="B507" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C507" s="2" t="inlineStr">
@@ -34921,7 +34921,7 @@
       </c>
       <c r="B557" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C557" s="2" t="inlineStr">
@@ -35541,7 +35541,7 @@
       </c>
       <c r="B567" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C567" s="2" t="inlineStr">
@@ -35665,7 +35665,7 @@
       </c>
       <c r="B569" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C569" s="2" t="inlineStr">
@@ -37897,7 +37897,7 @@
       </c>
       <c r="B605" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C605" s="2" t="inlineStr">
@@ -42609,7 +42609,7 @@
       </c>
       <c r="B681" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C681" s="2" t="inlineStr">
@@ -42919,7 +42919,7 @@
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
@@ -42981,7 +42981,7 @@
       </c>
       <c r="B687" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C687" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -47445,7 +47445,7 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
@@ -51041,7 +51041,7 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -56001,7 +56001,7 @@
       </c>
       <c r="B897" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C897" s="2" t="inlineStr">
@@ -60279,7 +60279,7 @@
       </c>
       <c r="B966" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C966" s="2" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="B971" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C971" s="2" t="inlineStr">
@@ -66789,7 +66789,7 @@
       </c>
       <c r="B1071" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1071" s="2" t="inlineStr">
@@ -69641,7 +69641,7 @@
       </c>
       <c r="B1117" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1117" s="2" t="inlineStr">
@@ -69703,7 +69703,7 @@
       </c>
       <c r="B1118" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1118" s="2" t="inlineStr">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
@@ -71749,7 +71749,7 @@
       </c>
       <c r="B1151" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1151" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -74973,7 +74973,7 @@
       </c>
       <c r="B1203" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1203" s="2" t="inlineStr">
@@ -77639,7 +77639,7 @@
       </c>
       <c r="B1246" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1246" s="2" t="inlineStr">
@@ -77701,7 +77701,7 @@
       </c>
       <c r="B1247" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1247" s="2" t="inlineStr">
@@ -78879,7 +78879,7 @@
       </c>
       <c r="B1266" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1266" s="2" t="inlineStr">
@@ -79561,7 +79561,7 @@
       </c>
       <c r="B1277" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1277" s="2" t="inlineStr">
@@ -83467,7 +83467,7 @@
       </c>
       <c r="B1340" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1340" s="2" t="inlineStr">
@@ -83591,7 +83591,7 @@
       </c>
       <c r="B1342" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1342" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -83963,7 +83963,7 @@
       </c>
       <c r="B1348" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1348" s="2" t="inlineStr">
@@ -84273,7 +84273,7 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84707,7 +84707,7 @@
       </c>
       <c r="B1360" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1360" s="2" t="inlineStr">
@@ -84769,7 +84769,7 @@
       </c>
       <c r="B1361" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1361" s="2" t="inlineStr">
@@ -84831,7 +84831,7 @@
       </c>
       <c r="B1362" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1362" s="2" t="inlineStr">
@@ -84893,7 +84893,7 @@
       </c>
       <c r="B1363" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1363" s="2" t="inlineStr">
@@ -86629,7 +86629,7 @@
       </c>
       <c r="B1391" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1391" s="2" t="inlineStr">
@@ -88489,7 +88489,7 @@
       </c>
       <c r="B1421" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1421" s="2" t="inlineStr">
@@ -88551,7 +88551,7 @@
       </c>
       <c r="B1422" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1422" s="2" t="inlineStr">
@@ -90349,7 +90349,7 @@
       </c>
       <c r="B1451" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1451" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -2557,7 +2557,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
@@ -28411,7 +28411,7 @@
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
@@ -35541,7 +35541,7 @@
       </c>
       <c r="B567" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C567" s="2" t="inlineStr">
@@ -35665,7 +35665,7 @@
       </c>
       <c r="B569" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C569" s="2" t="inlineStr">
@@ -40315,7 +40315,7 @@
       </c>
       <c r="B644" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C644" s="2" t="inlineStr">
@@ -42609,7 +42609,7 @@
       </c>
       <c r="B681" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C681" s="2" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -42919,7 +42919,7 @@
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
@@ -42981,7 +42981,7 @@
       </c>
       <c r="B687" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C687" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -47445,7 +47445,7 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
@@ -51041,7 +51041,7 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -56001,7 +56001,7 @@
       </c>
       <c r="B897" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C897" s="2" t="inlineStr">
@@ -58233,7 +58233,7 @@
       </c>
       <c r="B933" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C933" s="2" t="inlineStr">
@@ -63193,7 +63193,7 @@
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
@@ -69703,7 +69703,7 @@
       </c>
       <c r="B1118" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1118" s="2" t="inlineStr">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
@@ -71191,7 +71191,7 @@
       </c>
       <c r="B1142" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1142" s="2" t="inlineStr">
@@ -71687,7 +71687,7 @@
       </c>
       <c r="B1150" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1150" s="2" t="inlineStr">
@@ -74601,7 +74601,7 @@
       </c>
       <c r="B1197" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1197" s="2" t="inlineStr">
@@ -74663,7 +74663,7 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -75035,7 +75035,7 @@
       </c>
       <c r="B1204" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1204" s="2" t="inlineStr">
@@ -77763,7 +77763,7 @@
       </c>
       <c r="B1248" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1248" s="2" t="inlineStr">
@@ -78879,7 +78879,7 @@
       </c>
       <c r="B1266" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1266" s="2" t="inlineStr">
@@ -79561,7 +79561,7 @@
       </c>
       <c r="B1277" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1277" s="2" t="inlineStr">
@@ -79747,7 +79747,7 @@
       </c>
       <c r="B1280" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1280" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -84087,7 +84087,7 @@
       </c>
       <c r="B1350" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1350" s="2" t="inlineStr">
@@ -84397,7 +84397,7 @@
       </c>
       <c r="B1355" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1355" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84831,7 +84831,7 @@
       </c>
       <c r="B1362" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1362" s="2" t="inlineStr">
@@ -86629,7 +86629,7 @@
       </c>
       <c r="B1391" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1391" s="2" t="inlineStr">
@@ -87931,7 +87931,7 @@
       </c>
       <c r="B1412" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1412" s="2" t="inlineStr">
@@ -87993,7 +87993,7 @@
       </c>
       <c r="B1413" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1413" s="2" t="inlineStr">
@@ -88489,7 +88489,7 @@
       </c>
       <c r="B1421" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1421" s="2" t="inlineStr">
@@ -88551,7 +88551,7 @@
       </c>
       <c r="B1422" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1422" s="2" t="inlineStr">
@@ -90349,7 +90349,7 @@
       </c>
       <c r="B1451" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1451" s="2" t="inlineStr">
@@ -92643,7 +92643,7 @@
       </c>
       <c r="B1488" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1488" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -31821,7 +31821,7 @@
       </c>
       <c r="B507" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C507" s="2" t="inlineStr">
@@ -35541,7 +35541,7 @@
       </c>
       <c r="B567" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C567" s="2" t="inlineStr">
@@ -35665,7 +35665,7 @@
       </c>
       <c r="B569" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C569" s="2" t="inlineStr">
@@ -37897,7 +37897,7 @@
       </c>
       <c r="B605" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C605" s="2" t="inlineStr">
@@ -42609,7 +42609,7 @@
       </c>
       <c r="B681" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C681" s="2" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -47445,7 +47445,7 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
@@ -51041,7 +51041,7 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
@@ -51599,7 +51599,7 @@
       </c>
       <c r="B826" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C826" s="2" t="inlineStr">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
@@ -58233,7 +58233,7 @@
       </c>
       <c r="B933" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C933" s="2" t="inlineStr">
@@ -63193,7 +63193,7 @@
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
@@ -66789,7 +66789,7 @@
       </c>
       <c r="B1071" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1071" s="2" t="inlineStr">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
@@ -70261,7 +70261,7 @@
       </c>
       <c r="B1127" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1127" s="2" t="inlineStr">
@@ -71191,7 +71191,7 @@
       </c>
       <c r="B1142" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1142" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -75035,7 +75035,7 @@
       </c>
       <c r="B1204" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1204" s="2" t="inlineStr">
@@ -77639,7 +77639,7 @@
       </c>
       <c r="B1246" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1246" s="2" t="inlineStr">
@@ -77763,7 +77763,7 @@
       </c>
       <c r="B1248" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1248" s="2" t="inlineStr">
@@ -79747,7 +79747,7 @@
       </c>
       <c r="B1280" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1280" s="2" t="inlineStr">
@@ -83591,7 +83591,7 @@
       </c>
       <c r="B1342" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1342" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -84087,7 +84087,7 @@
       </c>
       <c r="B1350" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1350" s="2" t="inlineStr">
@@ -84273,7 +84273,7 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84769,7 +84769,7 @@
       </c>
       <c r="B1361" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1361" s="2" t="inlineStr">
@@ -84831,7 +84831,7 @@
       </c>
       <c r="B1362" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1362" s="2" t="inlineStr">
@@ -87993,7 +87993,7 @@
       </c>
       <c r="B1413" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1413" s="2" t="inlineStr">
@@ -90287,7 +90287,7 @@
       </c>
       <c r="B1450" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1450" s="2" t="inlineStr">
@@ -90349,7 +90349,7 @@
       </c>
       <c r="B1451" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1451" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">
@@ -91961,7 +91961,7 @@
       </c>
       <c r="B1477" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1477" s="2" t="inlineStr">
@@ -92643,7 +92643,7 @@
       </c>
       <c r="B1488" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1488" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
@@ -30767,7 +30767,7 @@
       </c>
       <c r="B490" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C490" s="2" t="inlineStr">
@@ -32937,7 +32937,7 @@
       </c>
       <c r="B525" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C525" s="2" t="inlineStr">
@@ -38331,7 +38331,7 @@
       </c>
       <c r="B612" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C612" s="2" t="inlineStr">
@@ -40315,7 +40315,7 @@
       </c>
       <c r="B644" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C644" s="2" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -42919,7 +42919,7 @@
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
@@ -42981,7 +42981,7 @@
       </c>
       <c r="B687" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C687" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -47445,7 +47445,7 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
@@ -48933,7 +48933,7 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
@@ -51041,7 +51041,7 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
@@ -51537,7 +51537,7 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
@@ -51599,7 +51599,7 @@
       </c>
       <c r="B826" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C826" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -58171,7 +58171,7 @@
       </c>
       <c r="B932" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C932" s="2" t="inlineStr">
@@ -58233,7 +58233,7 @@
       </c>
       <c r="B933" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C933" s="2" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="B971" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C971" s="2" t="inlineStr">
@@ -63193,7 +63193,7 @@
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
@@ -66789,7 +66789,7 @@
       </c>
       <c r="B1071" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1071" s="2" t="inlineStr">
@@ -69703,7 +69703,7 @@
       </c>
       <c r="B1118" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1118" s="2" t="inlineStr">
@@ -71191,7 +71191,7 @@
       </c>
       <c r="B1142" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1142" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -71687,7 +71687,7 @@
       </c>
       <c r="B1150" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1150" s="2" t="inlineStr">
@@ -74601,7 +74601,7 @@
       </c>
       <c r="B1197" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1197" s="2" t="inlineStr">
@@ -74663,7 +74663,7 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -74973,7 +74973,7 @@
       </c>
       <c r="B1203" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1203" s="2" t="inlineStr">
@@ -75035,7 +75035,7 @@
       </c>
       <c r="B1204" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1204" s="2" t="inlineStr">
@@ -76213,7 +76213,7 @@
       </c>
       <c r="B1223" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1223" s="2" t="inlineStr">
@@ -77763,7 +77763,7 @@
       </c>
       <c r="B1248" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1248" s="2" t="inlineStr">
@@ -79561,7 +79561,7 @@
       </c>
       <c r="B1277" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1277" s="2" t="inlineStr">
@@ -79747,7 +79747,7 @@
       </c>
       <c r="B1280" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1280" s="2" t="inlineStr">
@@ -83963,7 +83963,7 @@
       </c>
       <c r="B1348" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1348" s="2" t="inlineStr">
@@ -84273,7 +84273,7 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
@@ -84397,7 +84397,7 @@
       </c>
       <c r="B1355" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1355" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84831,7 +84831,7 @@
       </c>
       <c r="B1362" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1362" s="2" t="inlineStr">
@@ -84893,7 +84893,7 @@
       </c>
       <c r="B1363" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1363" s="2" t="inlineStr">
@@ -87931,7 +87931,7 @@
       </c>
       <c r="B1412" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1412" s="2" t="inlineStr">
@@ -88551,7 +88551,7 @@
       </c>
       <c r="B1422" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1422" s="2" t="inlineStr">
@@ -90225,7 +90225,7 @@
       </c>
       <c r="B1449" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1449" s="2" t="inlineStr">
@@ -90349,7 +90349,7 @@
       </c>
       <c r="B1451" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1451" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -30767,7 +30767,7 @@
       </c>
       <c r="B490" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C490" s="2" t="inlineStr">
@@ -31635,7 +31635,7 @@
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
@@ -32937,7 +32937,7 @@
       </c>
       <c r="B525" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C525" s="2" t="inlineStr">
@@ -42609,7 +42609,7 @@
       </c>
       <c r="B681" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C681" s="2" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -42919,7 +42919,7 @@
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
@@ -42981,7 +42981,7 @@
       </c>
       <c r="B687" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C687" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -48933,7 +48933,7 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
@@ -51041,7 +51041,7 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
@@ -51537,7 +51537,7 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -56001,7 +56001,7 @@
       </c>
       <c r="B897" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C897" s="2" t="inlineStr">
@@ -58171,7 +58171,7 @@
       </c>
       <c r="B932" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C932" s="2" t="inlineStr">
@@ -58233,7 +58233,7 @@
       </c>
       <c r="B933" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C933" s="2" t="inlineStr">
@@ -60279,7 +60279,7 @@
       </c>
       <c r="B966" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C966" s="2" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="B971" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C971" s="2" t="inlineStr">
@@ -63193,7 +63193,7 @@
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
@@ -69641,7 +69641,7 @@
       </c>
       <c r="B1117" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1117" s="2" t="inlineStr">
@@ -69703,7 +69703,7 @@
       </c>
       <c r="B1118" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1118" s="2" t="inlineStr">
@@ -70261,7 +70261,7 @@
       </c>
       <c r="B1127" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1127" s="2" t="inlineStr">
@@ -71191,7 +71191,7 @@
       </c>
       <c r="B1142" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1142" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -71687,7 +71687,7 @@
       </c>
       <c r="B1150" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1150" s="2" t="inlineStr">
@@ -73609,7 +73609,7 @@
       </c>
       <c r="B1181" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1181" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -74973,7 +74973,7 @@
       </c>
       <c r="B1203" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1203" s="2" t="inlineStr">
@@ -75035,7 +75035,7 @@
       </c>
       <c r="B1204" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1204" s="2" t="inlineStr">
@@ -76213,7 +76213,7 @@
       </c>
       <c r="B1223" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1223" s="2" t="inlineStr">
@@ -77763,7 +77763,7 @@
       </c>
       <c r="B1248" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1248" s="2" t="inlineStr">
@@ -79561,7 +79561,7 @@
       </c>
       <c r="B1277" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1277" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -83963,7 +83963,7 @@
       </c>
       <c r="B1348" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1348" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84707,7 +84707,7 @@
       </c>
       <c r="B1360" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1360" s="2" t="inlineStr">
@@ -84769,7 +84769,7 @@
       </c>
       <c r="B1361" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1361" s="2" t="inlineStr">
@@ -84831,7 +84831,7 @@
       </c>
       <c r="B1362" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1362" s="2" t="inlineStr">
@@ -86629,7 +86629,7 @@
       </c>
       <c r="B1391" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1391" s="2" t="inlineStr">
@@ -87931,7 +87931,7 @@
       </c>
       <c r="B1412" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1412" s="2" t="inlineStr">
@@ -88489,7 +88489,7 @@
       </c>
       <c r="B1421" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1421" s="2" t="inlineStr">
@@ -90225,7 +90225,7 @@
       </c>
       <c r="B1449" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1449" s="2" t="inlineStr">
@@ -90287,7 +90287,7 @@
       </c>
       <c r="B1450" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1450" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -28411,7 +28411,7 @@
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
@@ -31821,7 +31821,7 @@
       </c>
       <c r="B507" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C507" s="2" t="inlineStr">
@@ -35541,7 +35541,7 @@
       </c>
       <c r="B567" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C567" s="2" t="inlineStr">
@@ -35665,7 +35665,7 @@
       </c>
       <c r="B569" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C569" s="2" t="inlineStr">
@@ -40315,7 +40315,7 @@
       </c>
       <c r="B644" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C644" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -51103,7 +51103,7 @@
       </c>
       <c r="B818" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C818" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -58171,7 +58171,7 @@
       </c>
       <c r="B932" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C932" s="2" t="inlineStr">
@@ -60279,7 +60279,7 @@
       </c>
       <c r="B966" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C966" s="2" t="inlineStr">
@@ -63193,7 +63193,7 @@
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
@@ -69703,7 +69703,7 @@
       </c>
       <c r="B1118" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1118" s="2" t="inlineStr">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
@@ -74663,7 +74663,7 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -77701,7 +77701,7 @@
       </c>
       <c r="B1247" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1247" s="2" t="inlineStr">
@@ -79747,7 +79747,7 @@
       </c>
       <c r="B1280" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1280" s="2" t="inlineStr">
@@ -83467,7 +83467,7 @@
       </c>
       <c r="B1340" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1340" s="2" t="inlineStr">
@@ -83591,7 +83591,7 @@
       </c>
       <c r="B1342" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1342" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -83963,7 +83963,7 @@
       </c>
       <c r="B1348" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1348" s="2" t="inlineStr">
@@ -84397,7 +84397,7 @@
       </c>
       <c r="B1355" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1355" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84707,7 +84707,7 @@
       </c>
       <c r="B1360" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1360" s="2" t="inlineStr">
@@ -84769,7 +84769,7 @@
       </c>
       <c r="B1361" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1361" s="2" t="inlineStr">
@@ -84831,7 +84831,7 @@
       </c>
       <c r="B1362" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1362" s="2" t="inlineStr">
@@ -86629,7 +86629,7 @@
       </c>
       <c r="B1391" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1391" s="2" t="inlineStr">
@@ -87931,7 +87931,7 @@
       </c>
       <c r="B1412" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1412" s="2" t="inlineStr">
@@ -87993,7 +87993,7 @@
       </c>
       <c r="B1413" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1413" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -2557,7 +2557,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -28411,7 +28411,7 @@
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
@@ -30767,7 +30767,7 @@
       </c>
       <c r="B490" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C490" s="2" t="inlineStr">
@@ -31635,7 +31635,7 @@
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
@@ -32937,7 +32937,7 @@
       </c>
       <c r="B525" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C525" s="2" t="inlineStr">
@@ -34921,7 +34921,7 @@
       </c>
       <c r="B557" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C557" s="2" t="inlineStr">
@@ -35541,7 +35541,7 @@
       </c>
       <c r="B567" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C567" s="2" t="inlineStr">
@@ -38331,7 +38331,7 @@
       </c>
       <c r="B612" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C612" s="2" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
@@ -42919,7 +42919,7 @@
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -48933,7 +48933,7 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
@@ -51041,7 +51041,7 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
@@ -51103,7 +51103,7 @@
       </c>
       <c r="B818" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C818" s="2" t="inlineStr">
@@ -51599,7 +51599,7 @@
       </c>
       <c r="B826" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C826" s="2" t="inlineStr">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
@@ -56001,7 +56001,7 @@
       </c>
       <c r="B897" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C897" s="2" t="inlineStr">
@@ -58171,7 +58171,7 @@
       </c>
       <c r="B932" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C932" s="2" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="B971" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C971" s="2" t="inlineStr">
@@ -63193,7 +63193,7 @@
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
@@ -71191,7 +71191,7 @@
       </c>
       <c r="B1142" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1142" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -71687,7 +71687,7 @@
       </c>
       <c r="B1150" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1150" s="2" t="inlineStr">
@@ -73609,7 +73609,7 @@
       </c>
       <c r="B1181" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1181" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -76213,7 +76213,7 @@
       </c>
       <c r="B1223" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1223" s="2" t="inlineStr">
@@ -83467,7 +83467,7 @@
       </c>
       <c r="B1340" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1340" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -84397,7 +84397,7 @@
       </c>
       <c r="B1355" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1355" s="2" t="inlineStr">
@@ -84831,7 +84831,7 @@
       </c>
       <c r="B1362" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1362" s="2" t="inlineStr">
@@ -87993,7 +87993,7 @@
       </c>
       <c r="B1413" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1413" s="2" t="inlineStr">
@@ -88489,7 +88489,7 @@
       </c>
       <c r="B1421" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1421" s="2" t="inlineStr">
@@ -88551,7 +88551,7 @@
       </c>
       <c r="B1422" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1422" s="2" t="inlineStr">
@@ -90349,7 +90349,7 @@
       </c>
       <c r="B1451" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1451" s="2" t="inlineStr">
@@ -91031,7 +91031,7 @@
       </c>
       <c r="B1462" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1462" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -28411,7 +28411,7 @@
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
@@ -30767,7 +30767,7 @@
       </c>
       <c r="B490" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C490" s="2" t="inlineStr">
@@ -32937,7 +32937,7 @@
       </c>
       <c r="B525" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C525" s="2" t="inlineStr">
@@ -33185,7 +33185,7 @@
       </c>
       <c r="B529" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C529" s="2" t="inlineStr">
@@ -34921,7 +34921,7 @@
       </c>
       <c r="B557" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C557" s="2" t="inlineStr">
@@ -35665,7 +35665,7 @@
       </c>
       <c r="B569" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C569" s="2" t="inlineStr">
@@ -37897,7 +37897,7 @@
       </c>
       <c r="B605" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C605" s="2" t="inlineStr">
@@ -40315,7 +40315,7 @@
       </c>
       <c r="B644" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C644" s="2" t="inlineStr">
@@ -42609,7 +42609,7 @@
       </c>
       <c r="B681" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C681" s="2" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
@@ -42919,7 +42919,7 @@
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -48933,7 +48933,7 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
@@ -51041,7 +51041,7 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
@@ -51103,7 +51103,7 @@
       </c>
       <c r="B818" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C818" s="2" t="inlineStr">
@@ -51537,7 +51537,7 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
@@ -51599,7 +51599,7 @@
       </c>
       <c r="B826" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C826" s="2" t="inlineStr">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -58171,7 +58171,7 @@
       </c>
       <c r="B932" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C932" s="2" t="inlineStr">
@@ -60279,7 +60279,7 @@
       </c>
       <c r="B966" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C966" s="2" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="B971" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C971" s="2" t="inlineStr">
@@ -63193,7 +63193,7 @@
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
@@ -66789,7 +66789,7 @@
       </c>
       <c r="B1071" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1071" s="2" t="inlineStr">
@@ -69703,7 +69703,7 @@
       </c>
       <c r="B1118" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1118" s="2" t="inlineStr">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
@@ -70261,7 +70261,7 @@
       </c>
       <c r="B1127" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1127" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -71687,7 +71687,7 @@
       </c>
       <c r="B1150" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1150" s="2" t="inlineStr">
@@ -74663,7 +74663,7 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -76213,7 +76213,7 @@
       </c>
       <c r="B1223" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1223" s="2" t="inlineStr">
@@ -77577,7 +77577,7 @@
       </c>
       <c r="B1245" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1245" s="2" t="inlineStr">
@@ -77639,7 +77639,7 @@
       </c>
       <c r="B1246" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1246" s="2" t="inlineStr">
@@ -79747,7 +79747,7 @@
       </c>
       <c r="B1280" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1280" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -83963,7 +83963,7 @@
       </c>
       <c r="B1348" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1348" s="2" t="inlineStr">
@@ -84273,7 +84273,7 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
@@ -84397,7 +84397,7 @@
       </c>
       <c r="B1355" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1355" s="2" t="inlineStr">
@@ -84707,7 +84707,7 @@
       </c>
       <c r="B1360" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1360" s="2" t="inlineStr">
@@ -84769,7 +84769,7 @@
       </c>
       <c r="B1361" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1361" s="2" t="inlineStr">
@@ -84831,7 +84831,7 @@
       </c>
       <c r="B1362" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1362" s="2" t="inlineStr">
@@ -88489,7 +88489,7 @@
       </c>
       <c r="B1421" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1421" s="2" t="inlineStr">
@@ -90287,7 +90287,7 @@
       </c>
       <c r="B1450" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1450" s="2" t="inlineStr">
@@ -91031,7 +91031,7 @@
       </c>
       <c r="B1462" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1462" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">
@@ -92643,7 +92643,7 @@
       </c>
       <c r="B1488" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1488" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
@@ -28411,7 +28411,7 @@
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
@@ -30767,7 +30767,7 @@
       </c>
       <c r="B490" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C490" s="2" t="inlineStr">
@@ -31635,7 +31635,7 @@
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
@@ -32937,7 +32937,7 @@
       </c>
       <c r="B525" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C525" s="2" t="inlineStr">
@@ -37897,7 +37897,7 @@
       </c>
       <c r="B605" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C605" s="2" t="inlineStr">
@@ -40315,7 +40315,7 @@
       </c>
       <c r="B644" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C644" s="2" t="inlineStr">
@@ -42485,7 +42485,7 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -42919,7 +42919,7 @@
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -51041,7 +51041,7 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
@@ -51103,7 +51103,7 @@
       </c>
       <c r="B818" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C818" s="2" t="inlineStr">
@@ -51537,7 +51537,7 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
@@ -51599,7 +51599,7 @@
       </c>
       <c r="B826" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C826" s="2" t="inlineStr">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -58171,7 +58171,7 @@
       </c>
       <c r="B932" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C932" s="2" t="inlineStr">
@@ -60279,7 +60279,7 @@
       </c>
       <c r="B966" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C966" s="2" t="inlineStr">
@@ -63193,7 +63193,7 @@
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
@@ -66789,7 +66789,7 @@
       </c>
       <c r="B1071" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1071" s="2" t="inlineStr">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -73609,7 +73609,7 @@
       </c>
       <c r="B1181" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1181" s="2" t="inlineStr">
@@ -74663,7 +74663,7 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
@@ -74725,7 +74725,7 @@
       </c>
       <c r="B1199" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1199" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -75035,7 +75035,7 @@
       </c>
       <c r="B1204" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1204" s="2" t="inlineStr">
@@ -76213,7 +76213,7 @@
       </c>
       <c r="B1223" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1223" s="2" t="inlineStr">
@@ -77577,7 +77577,7 @@
       </c>
       <c r="B1245" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1245" s="2" t="inlineStr">
@@ -77639,7 +77639,7 @@
       </c>
       <c r="B1246" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1246" s="2" t="inlineStr">
@@ -79561,7 +79561,7 @@
       </c>
       <c r="B1277" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1277" s="2" t="inlineStr">
@@ -79747,7 +79747,7 @@
       </c>
       <c r="B1280" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1280" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -84273,7 +84273,7 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84893,7 +84893,7 @@
       </c>
       <c r="B1363" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1363" s="2" t="inlineStr">
@@ -87993,7 +87993,7 @@
       </c>
       <c r="B1413" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1413" s="2" t="inlineStr">
@@ -88489,7 +88489,7 @@
       </c>
       <c r="B1421" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1421" s="2" t="inlineStr">
@@ -90287,7 +90287,7 @@
       </c>
       <c r="B1450" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1450" s="2" t="inlineStr">
@@ -90349,7 +90349,7 @@
       </c>
       <c r="B1451" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1451" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">
@@ -92643,7 +92643,7 @@
       </c>
       <c r="B1488" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1488" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
@@ -30767,7 +30767,7 @@
       </c>
       <c r="B490" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C490" s="2" t="inlineStr">
@@ -31635,7 +31635,7 @@
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
@@ -33185,7 +33185,7 @@
       </c>
       <c r="B529" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C529" s="2" t="inlineStr">
@@ -35541,7 +35541,7 @@
       </c>
       <c r="B567" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C567" s="2" t="inlineStr">
@@ -37897,7 +37897,7 @@
       </c>
       <c r="B605" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C605" s="2" t="inlineStr">
@@ -40315,7 +40315,7 @@
       </c>
       <c r="B644" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C644" s="2" t="inlineStr">
@@ -42919,7 +42919,7 @@
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -48933,7 +48933,7 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -66789,7 +66789,7 @@
       </c>
       <c r="B1071" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1071" s="2" t="inlineStr">
@@ -69703,7 +69703,7 @@
       </c>
       <c r="B1118" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1118" s="2" t="inlineStr">
@@ -70261,7 +70261,7 @@
       </c>
       <c r="B1127" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1127" s="2" t="inlineStr">
@@ -71191,7 +71191,7 @@
       </c>
       <c r="B1142" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1142" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -71687,7 +71687,7 @@
       </c>
       <c r="B1150" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1150" s="2" t="inlineStr">
@@ -74663,7 +74663,7 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
@@ -74725,7 +74725,7 @@
       </c>
       <c r="B1199" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1199" s="2" t="inlineStr">
@@ -75035,7 +75035,7 @@
       </c>
       <c r="B1204" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1204" s="2" t="inlineStr">
@@ -77639,7 +77639,7 @@
       </c>
       <c r="B1246" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1246" s="2" t="inlineStr">
@@ -79747,7 +79747,7 @@
       </c>
       <c r="B1280" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1280" s="2" t="inlineStr">
@@ -83591,7 +83591,7 @@
       </c>
       <c r="B1342" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1342" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -84707,7 +84707,7 @@
       </c>
       <c r="B1360" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1360" s="2" t="inlineStr">
@@ -87931,7 +87931,7 @@
       </c>
       <c r="B1412" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1412" s="2" t="inlineStr">
@@ -90225,7 +90225,7 @@
       </c>
       <c r="B1449" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1449" s="2" t="inlineStr">
@@ -90349,7 +90349,7 @@
       </c>
       <c r="B1451" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1451" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">
@@ -92643,7 +92643,7 @@
       </c>
       <c r="B1488" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1488" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -35665,7 +35665,7 @@
       </c>
       <c r="B569" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C569" s="2" t="inlineStr">
@@ -37897,7 +37897,7 @@
       </c>
       <c r="B605" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C605" s="2" t="inlineStr">
@@ -38021,7 +38021,7 @@
       </c>
       <c r="B607" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C607" s="2" t="inlineStr">
@@ -38331,7 +38331,7 @@
       </c>
       <c r="B612" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C612" s="2" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
@@ -42981,7 +42981,7 @@
       </c>
       <c r="B687" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C687" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -47445,7 +47445,7 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
@@ -48933,7 +48933,7 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -58171,7 +58171,7 @@
       </c>
       <c r="B932" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C932" s="2" t="inlineStr">
@@ -58233,7 +58233,7 @@
       </c>
       <c r="B933" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C933" s="2" t="inlineStr">
@@ -63193,7 +63193,7 @@
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
@@ -69703,7 +69703,7 @@
       </c>
       <c r="B1118" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1118" s="2" t="inlineStr">
@@ -70261,7 +70261,7 @@
       </c>
       <c r="B1127" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1127" s="2" t="inlineStr">
@@ -71191,7 +71191,7 @@
       </c>
       <c r="B1142" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1142" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -74663,7 +74663,7 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
@@ -74725,7 +74725,7 @@
       </c>
       <c r="B1199" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1199" s="2" t="inlineStr">
@@ -76213,7 +76213,7 @@
       </c>
       <c r="B1223" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1223" s="2" t="inlineStr">
@@ -77763,7 +77763,7 @@
       </c>
       <c r="B1248" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1248" s="2" t="inlineStr">
@@ -79561,7 +79561,7 @@
       </c>
       <c r="B1277" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1277" s="2" t="inlineStr">
@@ -79747,7 +79747,7 @@
       </c>
       <c r="B1280" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1280" s="2" t="inlineStr">
@@ -83467,7 +83467,7 @@
       </c>
       <c r="B1340" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1340" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -83963,7 +83963,7 @@
       </c>
       <c r="B1348" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1348" s="2" t="inlineStr">
@@ -84087,7 +84087,7 @@
       </c>
       <c r="B1350" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1350" s="2" t="inlineStr">
@@ -84273,7 +84273,7 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84707,7 +84707,7 @@
       </c>
       <c r="B1360" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1360" s="2" t="inlineStr">
@@ -86629,7 +86629,7 @@
       </c>
       <c r="B1391" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1391" s="2" t="inlineStr">
@@ -87931,7 +87931,7 @@
       </c>
       <c r="B1412" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1412" s="2" t="inlineStr">
@@ -87993,7 +87993,7 @@
       </c>
       <c r="B1413" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1413" s="2" t="inlineStr">
@@ -90349,7 +90349,7 @@
       </c>
       <c r="B1451" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1451" s="2" t="inlineStr">
@@ -91031,7 +91031,7 @@
       </c>
       <c r="B1462" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1462" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">
@@ -91961,7 +91961,7 @@
       </c>
       <c r="B1477" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1477" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
@@ -28411,7 +28411,7 @@
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
@@ -31635,7 +31635,7 @@
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
@@ -32937,7 +32937,7 @@
       </c>
       <c r="B525" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C525" s="2" t="inlineStr">
@@ -35541,7 +35541,7 @@
       </c>
       <c r="B567" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C567" s="2" t="inlineStr">
@@ -38021,7 +38021,7 @@
       </c>
       <c r="B607" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C607" s="2" t="inlineStr">
@@ -40315,7 +40315,7 @@
       </c>
       <c r="B644" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C644" s="2" t="inlineStr">
@@ -42609,7 +42609,7 @@
       </c>
       <c r="B681" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C681" s="2" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
@@ -42981,7 +42981,7 @@
       </c>
       <c r="B687" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C687" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -47445,7 +47445,7 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
@@ -51599,7 +51599,7 @@
       </c>
       <c r="B826" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C826" s="2" t="inlineStr">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -58171,7 +58171,7 @@
       </c>
       <c r="B932" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C932" s="2" t="inlineStr">
@@ -58233,7 +58233,7 @@
       </c>
       <c r="B933" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C933" s="2" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="B971" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C971" s="2" t="inlineStr">
@@ -63193,7 +63193,7 @@
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
@@ -66789,7 +66789,7 @@
       </c>
       <c r="B1071" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1071" s="2" t="inlineStr">
@@ -69641,7 +69641,7 @@
       </c>
       <c r="B1117" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1117" s="2" t="inlineStr">
@@ -70261,7 +70261,7 @@
       </c>
       <c r="B1127" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1127" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -71687,7 +71687,7 @@
       </c>
       <c r="B1150" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1150" s="2" t="inlineStr">
@@ -74725,7 +74725,7 @@
       </c>
       <c r="B1199" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1199" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -75035,7 +75035,7 @@
       </c>
       <c r="B1204" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1204" s="2" t="inlineStr">
@@ -77639,7 +77639,7 @@
       </c>
       <c r="B1246" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1246" s="2" t="inlineStr">
@@ -77763,7 +77763,7 @@
       </c>
       <c r="B1248" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1248" s="2" t="inlineStr">
@@ -79561,7 +79561,7 @@
       </c>
       <c r="B1277" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1277" s="2" t="inlineStr">
@@ -83467,7 +83467,7 @@
       </c>
       <c r="B1340" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1340" s="2" t="inlineStr">
@@ -83591,7 +83591,7 @@
       </c>
       <c r="B1342" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1342" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -84397,7 +84397,7 @@
       </c>
       <c r="B1355" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1355" s="2" t="inlineStr">
@@ -84707,7 +84707,7 @@
       </c>
       <c r="B1360" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1360" s="2" t="inlineStr">
@@ -84893,7 +84893,7 @@
       </c>
       <c r="B1363" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1363" s="2" t="inlineStr">
@@ -86629,7 +86629,7 @@
       </c>
       <c r="B1391" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1391" s="2" t="inlineStr">
@@ -87931,7 +87931,7 @@
       </c>
       <c r="B1412" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1412" s="2" t="inlineStr">
@@ -87993,7 +87993,7 @@
       </c>
       <c r="B1413" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1413" s="2" t="inlineStr">
@@ -88489,7 +88489,7 @@
       </c>
       <c r="B1421" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1421" s="2" t="inlineStr">
@@ -88551,7 +88551,7 @@
       </c>
       <c r="B1422" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1422" s="2" t="inlineStr">
@@ -90287,7 +90287,7 @@
       </c>
       <c r="B1450" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1450" s="2" t="inlineStr">
@@ -91031,7 +91031,7 @@
       </c>
       <c r="B1462" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1462" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">
@@ -92643,7 +92643,7 @@
       </c>
       <c r="B1488" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1488" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -35541,7 +35541,7 @@
       </c>
       <c r="B567" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C567" s="2" t="inlineStr">
@@ -38331,7 +38331,7 @@
       </c>
       <c r="B612" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C612" s="2" t="inlineStr">
@@ -42485,7 +42485,7 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
@@ -42609,7 +42609,7 @@
       </c>
       <c r="B681" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C681" s="2" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -42919,7 +42919,7 @@
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -47445,7 +47445,7 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
@@ -51537,7 +51537,7 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -66789,7 +66789,7 @@
       </c>
       <c r="B1071" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1071" s="2" t="inlineStr">
@@ -69703,7 +69703,7 @@
       </c>
       <c r="B1118" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1118" s="2" t="inlineStr">
@@ -71191,7 +71191,7 @@
       </c>
       <c r="B1142" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1142" s="2" t="inlineStr">
@@ -71687,7 +71687,7 @@
       </c>
       <c r="B1150" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1150" s="2" t="inlineStr">
@@ -73609,7 +73609,7 @@
       </c>
       <c r="B1181" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1181" s="2" t="inlineStr">
@@ -77701,7 +77701,7 @@
       </c>
       <c r="B1247" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1247" s="2" t="inlineStr">
@@ -77763,7 +77763,7 @@
       </c>
       <c r="B1248" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1248" s="2" t="inlineStr">
@@ -78879,7 +78879,7 @@
       </c>
       <c r="B1266" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1266" s="2" t="inlineStr">
@@ -83467,7 +83467,7 @@
       </c>
       <c r="B1340" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1340" s="2" t="inlineStr">
@@ -83591,7 +83591,7 @@
       </c>
       <c r="B1342" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1342" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -84087,7 +84087,7 @@
       </c>
       <c r="B1350" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1350" s="2" t="inlineStr">
@@ -84273,7 +84273,7 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
@@ -84397,7 +84397,7 @@
       </c>
       <c r="B1355" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1355" s="2" t="inlineStr">
@@ -84893,7 +84893,7 @@
       </c>
       <c r="B1363" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1363" s="2" t="inlineStr">
@@ -87931,7 +87931,7 @@
       </c>
       <c r="B1412" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1412" s="2" t="inlineStr">
@@ -87993,7 +87993,7 @@
       </c>
       <c r="B1413" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1413" s="2" t="inlineStr">
@@ -88489,7 +88489,7 @@
       </c>
       <c r="B1421" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1421" s="2" t="inlineStr">
@@ -90225,7 +90225,7 @@
       </c>
       <c r="B1449" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1449" s="2" t="inlineStr">
@@ -90287,7 +90287,7 @@
       </c>
       <c r="B1450" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1450" s="2" t="inlineStr">
@@ -91031,7 +91031,7 @@
       </c>
       <c r="B1462" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1462" s="2" t="inlineStr">
@@ -91961,7 +91961,7 @@
       </c>
       <c r="B1477" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1477" s="2" t="inlineStr">
@@ -92643,7 +92643,7 @@
       </c>
       <c r="B1488" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1488" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -31635,7 +31635,7 @@
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
@@ -32937,7 +32937,7 @@
       </c>
       <c r="B525" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C525" s="2" t="inlineStr">
@@ -34921,7 +34921,7 @@
       </c>
       <c r="B557" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C557" s="2" t="inlineStr">
@@ -35665,7 +35665,7 @@
       </c>
       <c r="B569" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C569" s="2" t="inlineStr">
@@ -37897,7 +37897,7 @@
       </c>
       <c r="B605" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C605" s="2" t="inlineStr">
@@ -38331,7 +38331,7 @@
       </c>
       <c r="B612" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C612" s="2" t="inlineStr">
@@ -42485,7 +42485,7 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
@@ -42609,7 +42609,7 @@
       </c>
       <c r="B681" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C681" s="2" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -42919,7 +42919,7 @@
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -51103,7 +51103,7 @@
       </c>
       <c r="B818" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C818" s="2" t="inlineStr">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
@@ -56001,7 +56001,7 @@
       </c>
       <c r="B897" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C897" s="2" t="inlineStr">
@@ -58233,7 +58233,7 @@
       </c>
       <c r="B933" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C933" s="2" t="inlineStr">
@@ -69641,7 +69641,7 @@
       </c>
       <c r="B1117" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1117" s="2" t="inlineStr">
@@ -69703,7 +69703,7 @@
       </c>
       <c r="B1118" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1118" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -74725,7 +74725,7 @@
       </c>
       <c r="B1199" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1199" s="2" t="inlineStr">
@@ -76213,7 +76213,7 @@
       </c>
       <c r="B1223" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1223" s="2" t="inlineStr">
@@ -77577,7 +77577,7 @@
       </c>
       <c r="B1245" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1245" s="2" t="inlineStr">
@@ -77639,7 +77639,7 @@
       </c>
       <c r="B1246" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1246" s="2" t="inlineStr">
@@ -79561,7 +79561,7 @@
       </c>
       <c r="B1277" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1277" s="2" t="inlineStr">
@@ -83467,7 +83467,7 @@
       </c>
       <c r="B1340" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1340" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -83963,7 +83963,7 @@
       </c>
       <c r="B1348" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1348" s="2" t="inlineStr">
@@ -84087,7 +84087,7 @@
       </c>
       <c r="B1350" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1350" s="2" t="inlineStr">
@@ -84273,7 +84273,7 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
@@ -84893,7 +84893,7 @@
       </c>
       <c r="B1363" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1363" s="2" t="inlineStr">
@@ -87993,7 +87993,7 @@
       </c>
       <c r="B1413" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1413" s="2" t="inlineStr">
@@ -90225,7 +90225,7 @@
       </c>
       <c r="B1449" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1449" s="2" t="inlineStr">
@@ -90287,7 +90287,7 @@
       </c>
       <c r="B1450" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1450" s="2" t="inlineStr">
@@ -90349,7 +90349,7 @@
       </c>
       <c r="B1451" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1451" s="2" t="inlineStr">
@@ -91031,7 +91031,7 @@
       </c>
       <c r="B1462" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1462" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">
@@ -91961,7 +91961,7 @@
       </c>
       <c r="B1477" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1477" s="2" t="inlineStr">
@@ -92643,7 +92643,7 @@
       </c>
       <c r="B1488" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1488" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
@@ -28411,7 +28411,7 @@
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
@@ -31635,7 +31635,7 @@
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
@@ -34921,7 +34921,7 @@
       </c>
       <c r="B557" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C557" s="2" t="inlineStr">
@@ -37897,7 +37897,7 @@
       </c>
       <c r="B605" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C605" s="2" t="inlineStr">
@@ -40315,7 +40315,7 @@
       </c>
       <c r="B644" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C644" s="2" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
@@ -42981,7 +42981,7 @@
       </c>
       <c r="B687" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C687" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -51041,7 +51041,7 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
@@ -51103,7 +51103,7 @@
       </c>
       <c r="B818" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C818" s="2" t="inlineStr">
@@ -51413,7 +51413,7 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -56001,7 +56001,7 @@
       </c>
       <c r="B897" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C897" s="2" t="inlineStr">
@@ -58233,7 +58233,7 @@
       </c>
       <c r="B933" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C933" s="2" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="B971" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C971" s="2" t="inlineStr">
@@ -69703,7 +69703,7 @@
       </c>
       <c r="B1118" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1118" s="2" t="inlineStr">
@@ -71191,7 +71191,7 @@
       </c>
       <c r="B1142" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1142" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -73609,7 +73609,7 @@
       </c>
       <c r="B1181" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1181" s="2" t="inlineStr">
@@ -74663,7 +74663,7 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -76213,7 +76213,7 @@
       </c>
       <c r="B1223" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1223" s="2" t="inlineStr">
@@ -77577,7 +77577,7 @@
       </c>
       <c r="B1245" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1245" s="2" t="inlineStr">
@@ -77639,7 +77639,7 @@
       </c>
       <c r="B1246" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1246" s="2" t="inlineStr">
@@ -77763,7 +77763,7 @@
       </c>
       <c r="B1248" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1248" s="2" t="inlineStr">
@@ -78879,7 +78879,7 @@
       </c>
       <c r="B1266" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1266" s="2" t="inlineStr">
@@ -79561,7 +79561,7 @@
       </c>
       <c r="B1277" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1277" s="2" t="inlineStr">
@@ -83467,7 +83467,7 @@
       </c>
       <c r="B1340" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1340" s="2" t="inlineStr">
@@ -83591,7 +83591,7 @@
       </c>
       <c r="B1342" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1342" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -84087,7 +84087,7 @@
       </c>
       <c r="B1350" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1350" s="2" t="inlineStr">
@@ -84397,7 +84397,7 @@
       </c>
       <c r="B1355" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1355" s="2" t="inlineStr">
@@ -84831,7 +84831,7 @@
       </c>
       <c r="B1362" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1362" s="2" t="inlineStr">
@@ -84893,7 +84893,7 @@
       </c>
       <c r="B1363" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1363" s="2" t="inlineStr">
@@ -87931,7 +87931,7 @@
       </c>
       <c r="B1412" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1412" s="2" t="inlineStr">
@@ -90225,7 +90225,7 @@
       </c>
       <c r="B1449" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1449" s="2" t="inlineStr">
@@ -90287,7 +90287,7 @@
       </c>
       <c r="B1450" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1450" s="2" t="inlineStr">
@@ -90349,7 +90349,7 @@
       </c>
       <c r="B1451" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1451" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
@@ -28411,7 +28411,7 @@
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
@@ -29713,7 +29713,7 @@
       </c>
       <c r="B473" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C473" s="2" t="inlineStr">
@@ -35665,7 +35665,7 @@
       </c>
       <c r="B569" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C569" s="2" t="inlineStr">
@@ -38021,7 +38021,7 @@
       </c>
       <c r="B607" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C607" s="2" t="inlineStr">
@@ -40315,7 +40315,7 @@
       </c>
       <c r="B644" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C644" s="2" t="inlineStr">
@@ -42485,7 +42485,7 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
@@ -42609,7 +42609,7 @@
       </c>
       <c r="B681" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C681" s="2" t="inlineStr">
@@ -42919,7 +42919,7 @@
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
@@ -42981,7 +42981,7 @@
       </c>
       <c r="B687" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C687" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -48933,7 +48933,7 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
@@ -51103,7 +51103,7 @@
       </c>
       <c r="B818" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C818" s="2" t="inlineStr">
@@ -51413,7 +51413,7 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
@@ -51537,7 +51537,7 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -63193,7 +63193,7 @@
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
@@ -69641,7 +69641,7 @@
       </c>
       <c r="B1117" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1117" s="2" t="inlineStr">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
@@ -70261,7 +70261,7 @@
       </c>
       <c r="B1127" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1127" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -71687,7 +71687,7 @@
       </c>
       <c r="B1150" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1150" s="2" t="inlineStr">
@@ -73609,7 +73609,7 @@
       </c>
       <c r="B1181" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1181" s="2" t="inlineStr">
@@ -74663,7 +74663,7 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
@@ -74725,7 +74725,7 @@
       </c>
       <c r="B1199" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1199" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -77701,7 +77701,7 @@
       </c>
       <c r="B1247" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1247" s="2" t="inlineStr">
@@ -78879,7 +78879,7 @@
       </c>
       <c r="B1266" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1266" s="2" t="inlineStr">
@@ -79375,7 +79375,7 @@
       </c>
       <c r="B1274" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1274" s="2" t="inlineStr">
@@ -79561,7 +79561,7 @@
       </c>
       <c r="B1277" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1277" s="2" t="inlineStr">
@@ -79747,7 +79747,7 @@
       </c>
       <c r="B1280" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1280" s="2" t="inlineStr">
@@ -83467,7 +83467,7 @@
       </c>
       <c r="B1340" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1340" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -84087,7 +84087,7 @@
       </c>
       <c r="B1350" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1350" s="2" t="inlineStr">
@@ -84273,7 +84273,7 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
@@ -84707,7 +84707,7 @@
       </c>
       <c r="B1360" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1360" s="2" t="inlineStr">
@@ -87931,7 +87931,7 @@
       </c>
       <c r="B1412" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1412" s="2" t="inlineStr">
@@ -90225,7 +90225,7 @@
       </c>
       <c r="B1449" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1449" s="2" t="inlineStr">
@@ -90287,7 +90287,7 @@
       </c>
       <c r="B1450" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1450" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -28411,7 +28411,7 @@
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
@@ -29713,7 +29713,7 @@
       </c>
       <c r="B473" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C473" s="2" t="inlineStr">
@@ -30767,7 +30767,7 @@
       </c>
       <c r="B490" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C490" s="2" t="inlineStr">
@@ -35541,7 +35541,7 @@
       </c>
       <c r="B567" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C567" s="2" t="inlineStr">
@@ -38021,7 +38021,7 @@
       </c>
       <c r="B607" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C607" s="2" t="inlineStr">
@@ -38331,7 +38331,7 @@
       </c>
       <c r="B612" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C612" s="2" t="inlineStr">
@@ -40315,7 +40315,7 @@
       </c>
       <c r="B644" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C644" s="2" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -42919,7 +42919,7 @@
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
@@ -42981,7 +42981,7 @@
       </c>
       <c r="B687" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C687" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -47445,7 +47445,7 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
@@ -48933,7 +48933,7 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
@@ -51103,7 +51103,7 @@
       </c>
       <c r="B818" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C818" s="2" t="inlineStr">
@@ -51537,7 +51537,7 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
@@ -51599,7 +51599,7 @@
       </c>
       <c r="B826" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C826" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -56001,7 +56001,7 @@
       </c>
       <c r="B897" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C897" s="2" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="B971" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C971" s="2" t="inlineStr">
@@ -63193,7 +63193,7 @@
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
@@ -66789,7 +66789,7 @@
       </c>
       <c r="B1071" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1071" s="2" t="inlineStr">
@@ -69641,7 +69641,7 @@
       </c>
       <c r="B1117" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1117" s="2" t="inlineStr">
@@ -69703,7 +69703,7 @@
       </c>
       <c r="B1118" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1118" s="2" t="inlineStr">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
@@ -70261,7 +70261,7 @@
       </c>
       <c r="B1127" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1127" s="2" t="inlineStr">
@@ -71191,7 +71191,7 @@
       </c>
       <c r="B1142" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1142" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -73609,7 +73609,7 @@
       </c>
       <c r="B1181" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1181" s="2" t="inlineStr">
@@ -74663,7 +74663,7 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
@@ -74725,7 +74725,7 @@
       </c>
       <c r="B1199" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1199" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -77701,7 +77701,7 @@
       </c>
       <c r="B1247" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1247" s="2" t="inlineStr">
@@ -79375,7 +79375,7 @@
       </c>
       <c r="B1274" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1274" s="2" t="inlineStr">
@@ -79747,7 +79747,7 @@
       </c>
       <c r="B1280" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1280" s="2" t="inlineStr">
@@ -83591,7 +83591,7 @@
       </c>
       <c r="B1342" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1342" s="2" t="inlineStr">
@@ -83963,7 +83963,7 @@
       </c>
       <c r="B1348" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1348" s="2" t="inlineStr">
@@ -84087,7 +84087,7 @@
       </c>
       <c r="B1350" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1350" s="2" t="inlineStr">
@@ -84273,7 +84273,7 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84707,7 +84707,7 @@
       </c>
       <c r="B1360" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1360" s="2" t="inlineStr">
@@ -84831,7 +84831,7 @@
       </c>
       <c r="B1362" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1362" s="2" t="inlineStr">
@@ -87993,7 +87993,7 @@
       </c>
       <c r="B1413" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1413" s="2" t="inlineStr">
@@ -88551,7 +88551,7 @@
       </c>
       <c r="B1422" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1422" s="2" t="inlineStr">
@@ -90225,7 +90225,7 @@
       </c>
       <c r="B1449" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1449" s="2" t="inlineStr">
@@ -90287,7 +90287,7 @@
       </c>
       <c r="B1450" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1450" s="2" t="inlineStr">
@@ -91961,7 +91961,7 @@
       </c>
       <c r="B1477" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1477" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
@@ -29713,7 +29713,7 @@
       </c>
       <c r="B473" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C473" s="2" t="inlineStr">
@@ -38331,7 +38331,7 @@
       </c>
       <c r="B612" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C612" s="2" t="inlineStr">
@@ -40315,7 +40315,7 @@
       </c>
       <c r="B644" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C644" s="2" t="inlineStr">
@@ -42485,7 +42485,7 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -48933,7 +48933,7 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
@@ -51103,7 +51103,7 @@
       </c>
       <c r="B818" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C818" s="2" t="inlineStr">
@@ -51413,7 +51413,7 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
@@ -51537,7 +51537,7 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -56001,7 +56001,7 @@
       </c>
       <c r="B897" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C897" s="2" t="inlineStr">
@@ -58171,7 +58171,7 @@
       </c>
       <c r="B932" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C932" s="2" t="inlineStr">
@@ -58233,7 +58233,7 @@
       </c>
       <c r="B933" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C933" s="2" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="B971" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C971" s="2" t="inlineStr">
@@ -71191,7 +71191,7 @@
       </c>
       <c r="B1142" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1142" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -77639,7 +77639,7 @@
       </c>
       <c r="B1246" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1246" s="2" t="inlineStr">
@@ -78879,7 +78879,7 @@
       </c>
       <c r="B1266" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1266" s="2" t="inlineStr">
@@ -79747,7 +79747,7 @@
       </c>
       <c r="B1280" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1280" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -83963,7 +83963,7 @@
       </c>
       <c r="B1348" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1348" s="2" t="inlineStr">
@@ -84273,7 +84273,7 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
@@ -84397,7 +84397,7 @@
       </c>
       <c r="B1355" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1355" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84707,7 +84707,7 @@
       </c>
       <c r="B1360" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1360" s="2" t="inlineStr">
@@ -84893,7 +84893,7 @@
       </c>
       <c r="B1363" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1363" s="2" t="inlineStr">
@@ -86629,7 +86629,7 @@
       </c>
       <c r="B1391" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1391" s="2" t="inlineStr">
@@ -87993,7 +87993,7 @@
       </c>
       <c r="B1413" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1413" s="2" t="inlineStr">
@@ -90225,7 +90225,7 @@
       </c>
       <c r="B1449" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1449" s="2" t="inlineStr">
@@ -90349,7 +90349,7 @@
       </c>
       <c r="B1451" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1451" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
@@ -29713,7 +29713,7 @@
       </c>
       <c r="B473" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C473" s="2" t="inlineStr">
@@ -31635,7 +31635,7 @@
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
@@ -32937,7 +32937,7 @@
       </c>
       <c r="B525" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C525" s="2" t="inlineStr">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="B527" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C527" s="2" t="inlineStr">
@@ -35665,7 +35665,7 @@
       </c>
       <c r="B569" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C569" s="2" t="inlineStr">
@@ -40315,7 +40315,7 @@
       </c>
       <c r="B644" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C644" s="2" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -47445,7 +47445,7 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
@@ -48933,7 +48933,7 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
@@ -51041,7 +51041,7 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
@@ -51103,7 +51103,7 @@
       </c>
       <c r="B818" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C818" s="2" t="inlineStr">
@@ -51537,7 +51537,7 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
@@ -51599,7 +51599,7 @@
       </c>
       <c r="B826" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C826" s="2" t="inlineStr">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
@@ -60279,7 +60279,7 @@
       </c>
       <c r="B966" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C966" s="2" t="inlineStr">
@@ -66789,7 +66789,7 @@
       </c>
       <c r="B1071" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1071" s="2" t="inlineStr">
@@ -69641,7 +69641,7 @@
       </c>
       <c r="B1117" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1117" s="2" t="inlineStr">
@@ -69703,7 +69703,7 @@
       </c>
       <c r="B1118" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1118" s="2" t="inlineStr">
@@ -70261,7 +70261,7 @@
       </c>
       <c r="B1127" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1127" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -71687,7 +71687,7 @@
       </c>
       <c r="B1150" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1150" s="2" t="inlineStr">
@@ -74663,7 +74663,7 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
@@ -74725,7 +74725,7 @@
       </c>
       <c r="B1199" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1199" s="2" t="inlineStr">
@@ -75035,7 +75035,7 @@
       </c>
       <c r="B1204" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1204" s="2" t="inlineStr">
@@ -77639,7 +77639,7 @@
       </c>
       <c r="B1246" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1246" s="2" t="inlineStr">
@@ -77701,7 +77701,7 @@
       </c>
       <c r="B1247" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1247" s="2" t="inlineStr">
@@ -77763,7 +77763,7 @@
       </c>
       <c r="B1248" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1248" s="2" t="inlineStr">
@@ -78879,7 +78879,7 @@
       </c>
       <c r="B1266" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1266" s="2" t="inlineStr">
@@ -79375,7 +79375,7 @@
       </c>
       <c r="B1274" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1274" s="2" t="inlineStr">
@@ -79561,7 +79561,7 @@
       </c>
       <c r="B1277" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1277" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -83715,7 +83715,7 @@
       </c>
       <c r="B1344" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1344" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84893,7 +84893,7 @@
       </c>
       <c r="B1363" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1363" s="2" t="inlineStr">
@@ -86629,7 +86629,7 @@
       </c>
       <c r="B1391" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1391" s="2" t="inlineStr">
@@ -87993,7 +87993,7 @@
       </c>
       <c r="B1413" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1413" s="2" t="inlineStr">
@@ -88551,7 +88551,7 @@
       </c>
       <c r="B1422" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1422" s="2" t="inlineStr">
@@ -90349,7 +90349,7 @@
       </c>
       <c r="B1451" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1451" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">
@@ -92643,7 +92643,7 @@
       </c>
       <c r="B1488" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1488" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -28411,7 +28411,7 @@
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
@@ -31635,7 +31635,7 @@
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
@@ -32937,7 +32937,7 @@
       </c>
       <c r="B525" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C525" s="2" t="inlineStr">
@@ -37897,7 +37897,7 @@
       </c>
       <c r="B605" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C605" s="2" t="inlineStr">
@@ -40315,7 +40315,7 @@
       </c>
       <c r="B644" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C644" s="2" t="inlineStr">
@@ -42485,7 +42485,7 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -48933,7 +48933,7 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
@@ -51041,7 +51041,7 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
@@ -51413,7 +51413,7 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
@@ -51537,7 +51537,7 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -58171,7 +58171,7 @@
       </c>
       <c r="B932" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C932" s="2" t="inlineStr">
@@ -58233,7 +58233,7 @@
       </c>
       <c r="B933" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C933" s="2" t="inlineStr">
@@ -60279,7 +60279,7 @@
       </c>
       <c r="B966" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C966" s="2" t="inlineStr">
@@ -66789,7 +66789,7 @@
       </c>
       <c r="B1071" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1071" s="2" t="inlineStr">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
@@ -71191,7 +71191,7 @@
       </c>
       <c r="B1142" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1142" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -71749,7 +71749,7 @@
       </c>
       <c r="B1151" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1151" s="2" t="inlineStr">
@@ -73609,7 +73609,7 @@
       </c>
       <c r="B1181" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1181" s="2" t="inlineStr">
@@ -74663,7 +74663,7 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
@@ -74725,7 +74725,7 @@
       </c>
       <c r="B1199" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1199" s="2" t="inlineStr">
@@ -74973,7 +74973,7 @@
       </c>
       <c r="B1203" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1203" s="2" t="inlineStr">
@@ -75035,7 +75035,7 @@
       </c>
       <c r="B1204" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1204" s="2" t="inlineStr">
@@ -76213,7 +76213,7 @@
       </c>
       <c r="B1223" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1223" s="2" t="inlineStr">
@@ -77639,7 +77639,7 @@
       </c>
       <c r="B1246" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1246" s="2" t="inlineStr">
@@ -77701,7 +77701,7 @@
       </c>
       <c r="B1247" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1247" s="2" t="inlineStr">
@@ -78879,7 +78879,7 @@
       </c>
       <c r="B1266" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1266" s="2" t="inlineStr">
@@ -79375,7 +79375,7 @@
       </c>
       <c r="B1274" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1274" s="2" t="inlineStr">
@@ -79561,7 +79561,7 @@
       </c>
       <c r="B1277" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1277" s="2" t="inlineStr">
@@ -83467,7 +83467,7 @@
       </c>
       <c r="B1340" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1340" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -83715,7 +83715,7 @@
       </c>
       <c r="B1344" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1344" s="2" t="inlineStr">
@@ -83963,7 +83963,7 @@
       </c>
       <c r="B1348" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1348" s="2" t="inlineStr">
@@ -84273,7 +84273,7 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
@@ -84397,7 +84397,7 @@
       </c>
       <c r="B1355" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1355" s="2" t="inlineStr">
@@ -84831,7 +84831,7 @@
       </c>
       <c r="B1362" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1362" s="2" t="inlineStr">
@@ -88551,7 +88551,7 @@
       </c>
       <c r="B1422" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1422" s="2" t="inlineStr">
@@ -90225,7 +90225,7 @@
       </c>
       <c r="B1449" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1449" s="2" t="inlineStr">
@@ -90287,7 +90287,7 @@
       </c>
       <c r="B1450" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1450" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
@@ -28411,7 +28411,7 @@
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
@@ -30767,7 +30767,7 @@
       </c>
       <c r="B490" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C490" s="2" t="inlineStr">
@@ -31635,7 +31635,7 @@
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
@@ -32937,7 +32937,7 @@
       </c>
       <c r="B525" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C525" s="2" t="inlineStr">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="B527" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C527" s="2" t="inlineStr">
@@ -42485,7 +42485,7 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -42981,7 +42981,7 @@
       </c>
       <c r="B687" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C687" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -48933,7 +48933,7 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
@@ -51041,7 +51041,7 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
@@ -51103,7 +51103,7 @@
       </c>
       <c r="B818" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C818" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="B971" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C971" s="2" t="inlineStr">
@@ -63193,7 +63193,7 @@
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
@@ -66789,7 +66789,7 @@
       </c>
       <c r="B1071" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1071" s="2" t="inlineStr">
@@ -69641,7 +69641,7 @@
       </c>
       <c r="B1117" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1117" s="2" t="inlineStr">
@@ -69703,7 +69703,7 @@
       </c>
       <c r="B1118" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1118" s="2" t="inlineStr">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
@@ -70261,7 +70261,7 @@
       </c>
       <c r="B1127" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1127" s="2" t="inlineStr">
@@ -71191,7 +71191,7 @@
       </c>
       <c r="B1142" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1142" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -71687,7 +71687,7 @@
       </c>
       <c r="B1150" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1150" s="2" t="inlineStr">
@@ -74601,7 +74601,7 @@
       </c>
       <c r="B1197" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1197" s="2" t="inlineStr">
@@ -74663,7 +74663,7 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
@@ -74725,7 +74725,7 @@
       </c>
       <c r="B1199" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1199" s="2" t="inlineStr">
@@ -74973,7 +74973,7 @@
       </c>
       <c r="B1203" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1203" s="2" t="inlineStr">
@@ -76213,7 +76213,7 @@
       </c>
       <c r="B1223" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1223" s="2" t="inlineStr">
@@ -77639,7 +77639,7 @@
       </c>
       <c r="B1246" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1246" s="2" t="inlineStr">
@@ -77763,7 +77763,7 @@
       </c>
       <c r="B1248" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1248" s="2" t="inlineStr">
@@ -79561,7 +79561,7 @@
       </c>
       <c r="B1277" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1277" s="2" t="inlineStr">
@@ -83467,7 +83467,7 @@
       </c>
       <c r="B1340" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1340" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -83963,7 +83963,7 @@
       </c>
       <c r="B1348" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1348" s="2" t="inlineStr">
@@ -84273,7 +84273,7 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84893,7 +84893,7 @@
       </c>
       <c r="B1363" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1363" s="2" t="inlineStr">
@@ -86629,7 +86629,7 @@
       </c>
       <c r="B1391" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1391" s="2" t="inlineStr">
@@ -90225,7 +90225,7 @@
       </c>
       <c r="B1449" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1449" s="2" t="inlineStr">
@@ -90287,7 +90287,7 @@
       </c>
       <c r="B1450" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1450" s="2" t="inlineStr">
@@ -90349,7 +90349,7 @@
       </c>
       <c r="B1451" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1451" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">
@@ -91961,7 +91961,7 @@
       </c>
       <c r="B1477" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1477" s="2" t="inlineStr">
@@ -92643,7 +92643,7 @@
       </c>
       <c r="B1488" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1488" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
@@ -28411,7 +28411,7 @@
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
@@ -35665,7 +35665,7 @@
       </c>
       <c r="B569" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C569" s="2" t="inlineStr">
@@ -37897,7 +37897,7 @@
       </c>
       <c r="B605" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C605" s="2" t="inlineStr">
@@ -42485,7 +42485,7 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -47445,7 +47445,7 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
@@ -51041,7 +51041,7 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
@@ -51537,7 +51537,7 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -63193,7 +63193,7 @@
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
@@ -66789,7 +66789,7 @@
       </c>
       <c r="B1071" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1071" s="2" t="inlineStr">
@@ -69641,7 +69641,7 @@
       </c>
       <c r="B1117" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1117" s="2" t="inlineStr">
@@ -70261,7 +70261,7 @@
       </c>
       <c r="B1127" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1127" s="2" t="inlineStr">
@@ -71749,7 +71749,7 @@
       </c>
       <c r="B1151" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1151" s="2" t="inlineStr">
@@ -73609,7 +73609,7 @@
       </c>
       <c r="B1181" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1181" s="2" t="inlineStr">
@@ -74601,7 +74601,7 @@
       </c>
       <c r="B1197" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1197" s="2" t="inlineStr">
@@ -74725,7 +74725,7 @@
       </c>
       <c r="B1199" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1199" s="2" t="inlineStr">
@@ -75035,7 +75035,7 @@
       </c>
       <c r="B1204" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1204" s="2" t="inlineStr">
@@ -83591,7 +83591,7 @@
       </c>
       <c r="B1342" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1342" s="2" t="inlineStr">
@@ -83963,7 +83963,7 @@
       </c>
       <c r="B1348" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1348" s="2" t="inlineStr">
@@ -84273,7 +84273,7 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
@@ -84769,7 +84769,7 @@
       </c>
       <c r="B1361" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1361" s="2" t="inlineStr">
@@ -84893,7 +84893,7 @@
       </c>
       <c r="B1363" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1363" s="2" t="inlineStr">
@@ -86629,7 +86629,7 @@
       </c>
       <c r="B1391" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1391" s="2" t="inlineStr">
@@ -87931,7 +87931,7 @@
       </c>
       <c r="B1412" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1412" s="2" t="inlineStr">
@@ -87993,7 +87993,7 @@
       </c>
       <c r="B1413" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1413" s="2" t="inlineStr">
@@ -88551,7 +88551,7 @@
       </c>
       <c r="B1422" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1422" s="2" t="inlineStr">
@@ -90225,7 +90225,7 @@
       </c>
       <c r="B1449" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1449" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">
@@ -91961,7 +91961,7 @@
       </c>
       <c r="B1477" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1477" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
@@ -28411,7 +28411,7 @@
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
@@ -31635,7 +31635,7 @@
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
@@ -32937,7 +32937,7 @@
       </c>
       <c r="B525" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C525" s="2" t="inlineStr">
@@ -35665,7 +35665,7 @@
       </c>
       <c r="B569" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C569" s="2" t="inlineStr">
@@ -37897,7 +37897,7 @@
       </c>
       <c r="B605" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C605" s="2" t="inlineStr">
@@ -40315,7 +40315,7 @@
       </c>
       <c r="B644" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C644" s="2" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -48933,7 +48933,7 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
@@ -51103,7 +51103,7 @@
       </c>
       <c r="B818" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C818" s="2" t="inlineStr">
@@ -51537,7 +51537,7 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -56001,7 +56001,7 @@
       </c>
       <c r="B897" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C897" s="2" t="inlineStr">
@@ -58233,7 +58233,7 @@
       </c>
       <c r="B933" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C933" s="2" t="inlineStr">
@@ -66789,7 +66789,7 @@
       </c>
       <c r="B1071" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1071" s="2" t="inlineStr">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
@@ -70261,7 +70261,7 @@
       </c>
       <c r="B1127" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1127" s="2" t="inlineStr">
@@ -71191,7 +71191,7 @@
       </c>
       <c r="B1142" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1142" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -73609,7 +73609,7 @@
       </c>
       <c r="B1181" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1181" s="2" t="inlineStr">
@@ -74601,7 +74601,7 @@
       </c>
       <c r="B1197" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1197" s="2" t="inlineStr">
@@ -74663,7 +74663,7 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
@@ -77577,7 +77577,7 @@
       </c>
       <c r="B1245" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1245" s="2" t="inlineStr">
@@ -77701,7 +77701,7 @@
       </c>
       <c r="B1247" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1247" s="2" t="inlineStr">
@@ -79375,7 +79375,7 @@
       </c>
       <c r="B1274" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1274" s="2" t="inlineStr">
@@ -79561,7 +79561,7 @@
       </c>
       <c r="B1277" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1277" s="2" t="inlineStr">
@@ -79747,7 +79747,7 @@
       </c>
       <c r="B1280" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1280" s="2" t="inlineStr">
@@ -83467,7 +83467,7 @@
       </c>
       <c r="B1340" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1340" s="2" t="inlineStr">
@@ -83591,7 +83591,7 @@
       </c>
       <c r="B1342" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1342" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -84707,7 +84707,7 @@
       </c>
       <c r="B1360" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1360" s="2" t="inlineStr">
@@ -84893,7 +84893,7 @@
       </c>
       <c r="B1363" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1363" s="2" t="inlineStr">
@@ -87931,7 +87931,7 @@
       </c>
       <c r="B1412" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1412" s="2" t="inlineStr">
@@ -88551,7 +88551,7 @@
       </c>
       <c r="B1422" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1422" s="2" t="inlineStr">
@@ -90225,7 +90225,7 @@
       </c>
       <c r="B1449" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1449" s="2" t="inlineStr">
@@ -90287,7 +90287,7 @@
       </c>
       <c r="B1450" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1450" s="2" t="inlineStr">
@@ -90349,7 +90349,7 @@
       </c>
       <c r="B1451" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1451" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -28411,7 +28411,7 @@
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
@@ -31635,7 +31635,7 @@
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
@@ -34921,7 +34921,7 @@
       </c>
       <c r="B557" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C557" s="2" t="inlineStr">
@@ -37897,7 +37897,7 @@
       </c>
       <c r="B605" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C605" s="2" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
@@ -42981,7 +42981,7 @@
       </c>
       <c r="B687" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C687" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -48933,7 +48933,7 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
@@ -51537,7 +51537,7 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
@@ -56001,7 +56001,7 @@
       </c>
       <c r="B897" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C897" s="2" t="inlineStr">
@@ -58233,7 +58233,7 @@
       </c>
       <c r="B933" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C933" s="2" t="inlineStr">
@@ -63193,7 +63193,7 @@
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
@@ -66789,7 +66789,7 @@
       </c>
       <c r="B1071" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1071" s="2" t="inlineStr">
@@ -69641,7 +69641,7 @@
       </c>
       <c r="B1117" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1117" s="2" t="inlineStr">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
@@ -71687,7 +71687,7 @@
       </c>
       <c r="B1150" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1150" s="2" t="inlineStr">
@@ -74601,7 +74601,7 @@
       </c>
       <c r="B1197" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1197" s="2" t="inlineStr">
@@ -74663,7 +74663,7 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
@@ -74725,7 +74725,7 @@
       </c>
       <c r="B1199" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1199" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -74973,7 +74973,7 @@
       </c>
       <c r="B1203" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1203" s="2" t="inlineStr">
@@ -75035,7 +75035,7 @@
       </c>
       <c r="B1204" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1204" s="2" t="inlineStr">
@@ -77701,7 +77701,7 @@
       </c>
       <c r="B1247" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1247" s="2" t="inlineStr">
@@ -79375,7 +79375,7 @@
       </c>
       <c r="B1274" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1274" s="2" t="inlineStr">
@@ -83467,7 +83467,7 @@
       </c>
       <c r="B1340" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1340" s="2" t="inlineStr">
@@ -83963,7 +83963,7 @@
       </c>
       <c r="B1348" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1348" s="2" t="inlineStr">
@@ -84707,7 +84707,7 @@
       </c>
       <c r="B1360" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1360" s="2" t="inlineStr">
@@ -84769,7 +84769,7 @@
       </c>
       <c r="B1361" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1361" s="2" t="inlineStr">
@@ -84893,7 +84893,7 @@
       </c>
       <c r="B1363" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1363" s="2" t="inlineStr">
@@ -87931,7 +87931,7 @@
       </c>
       <c r="B1412" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1412" s="2" t="inlineStr">
@@ -88489,7 +88489,7 @@
       </c>
       <c r="B1421" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1421" s="2" t="inlineStr">
@@ -88551,7 +88551,7 @@
       </c>
       <c r="B1422" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1422" s="2" t="inlineStr">
@@ -90225,7 +90225,7 @@
       </c>
       <c r="B1449" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1449" s="2" t="inlineStr">
@@ -90287,7 +90287,7 @@
       </c>
       <c r="B1450" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1450" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">
@@ -91961,7 +91961,7 @@
       </c>
       <c r="B1477" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1477" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -29713,7 +29713,7 @@
       </c>
       <c r="B473" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C473" s="2" t="inlineStr">
@@ -31821,7 +31821,7 @@
       </c>
       <c r="B507" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C507" s="2" t="inlineStr">
@@ -34425,7 +34425,7 @@
       </c>
       <c r="B549" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C549" s="2" t="inlineStr">
@@ -34921,7 +34921,7 @@
       </c>
       <c r="B557" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C557" s="2" t="inlineStr">
@@ -42609,7 +42609,7 @@
       </c>
       <c r="B681" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C681" s="2" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -42981,7 +42981,7 @@
       </c>
       <c r="B687" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C687" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -47445,7 +47445,7 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
@@ -51537,7 +51537,7 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -56001,7 +56001,7 @@
       </c>
       <c r="B897" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C897" s="2" t="inlineStr">
@@ -69641,7 +69641,7 @@
       </c>
       <c r="B1117" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1117" s="2" t="inlineStr">
@@ -69703,7 +69703,7 @@
       </c>
       <c r="B1118" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1118" s="2" t="inlineStr">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
@@ -74601,7 +74601,7 @@
       </c>
       <c r="B1197" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1197" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -74973,7 +74973,7 @@
       </c>
       <c r="B1203" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1203" s="2" t="inlineStr">
@@ -75035,7 +75035,7 @@
       </c>
       <c r="B1204" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1204" s="2" t="inlineStr">
@@ -77577,7 +77577,7 @@
       </c>
       <c r="B1245" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1245" s="2" t="inlineStr">
@@ -83467,7 +83467,7 @@
       </c>
       <c r="B1340" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1340" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -84273,7 +84273,7 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
@@ -84397,7 +84397,7 @@
       </c>
       <c r="B1355" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1355" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84893,7 +84893,7 @@
       </c>
       <c r="B1363" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1363" s="2" t="inlineStr">
@@ -87931,7 +87931,7 @@
       </c>
       <c r="B1412" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1412" s="2" t="inlineStr">
@@ -87993,7 +87993,7 @@
       </c>
       <c r="B1413" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1413" s="2" t="inlineStr">
@@ -88489,7 +88489,7 @@
       </c>
       <c r="B1421" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1421" s="2" t="inlineStr">
@@ -90349,7 +90349,7 @@
       </c>
       <c r="B1451" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1451" s="2" t="inlineStr">
@@ -91031,7 +91031,7 @@
       </c>
       <c r="B1462" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1462" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
@@ -29713,7 +29713,7 @@
       </c>
       <c r="B473" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C473" s="2" t="inlineStr">
@@ -31635,7 +31635,7 @@
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
@@ -32937,7 +32937,7 @@
       </c>
       <c r="B525" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C525" s="2" t="inlineStr">
@@ -33185,7 +33185,7 @@
       </c>
       <c r="B529" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C529" s="2" t="inlineStr">
@@ -34425,7 +34425,7 @@
       </c>
       <c r="B549" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C549" s="2" t="inlineStr">
@@ -35541,7 +35541,7 @@
       </c>
       <c r="B567" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C567" s="2" t="inlineStr">
@@ -42609,7 +42609,7 @@
       </c>
       <c r="B681" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C681" s="2" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -47445,7 +47445,7 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
@@ -51041,7 +51041,7 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
@@ -51413,7 +51413,7 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
@@ -51537,7 +51537,7 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
@@ -56001,7 +56001,7 @@
       </c>
       <c r="B897" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C897" s="2" t="inlineStr">
@@ -58171,7 +58171,7 @@
       </c>
       <c r="B932" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C932" s="2" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="B971" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C971" s="2" t="inlineStr">
@@ -63193,7 +63193,7 @@
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
@@ -69703,7 +69703,7 @@
       </c>
       <c r="B1118" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1118" s="2" t="inlineStr">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -74601,7 +74601,7 @@
       </c>
       <c r="B1197" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1197" s="2" t="inlineStr">
@@ -77639,7 +77639,7 @@
       </c>
       <c r="B1246" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1246" s="2" t="inlineStr">
@@ -77701,7 +77701,7 @@
       </c>
       <c r="B1247" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1247" s="2" t="inlineStr">
@@ -79561,7 +79561,7 @@
       </c>
       <c r="B1277" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1277" s="2" t="inlineStr">
@@ -79747,7 +79747,7 @@
       </c>
       <c r="B1280" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1280" s="2" t="inlineStr">
@@ -83467,7 +83467,7 @@
       </c>
       <c r="B1340" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1340" s="2" t="inlineStr">
@@ -83591,7 +83591,7 @@
       </c>
       <c r="B1342" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1342" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -83963,7 +83963,7 @@
       </c>
       <c r="B1348" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1348" s="2" t="inlineStr">
@@ -84397,7 +84397,7 @@
       </c>
       <c r="B1355" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1355" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84707,7 +84707,7 @@
       </c>
       <c r="B1360" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1360" s="2" t="inlineStr">
@@ -84831,7 +84831,7 @@
       </c>
       <c r="B1362" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1362" s="2" t="inlineStr">
@@ -84893,7 +84893,7 @@
       </c>
       <c r="B1363" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1363" s="2" t="inlineStr">
@@ -87993,7 +87993,7 @@
       </c>
       <c r="B1413" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1413" s="2" t="inlineStr">
@@ -88551,7 +88551,7 @@
       </c>
       <c r="B1422" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1422" s="2" t="inlineStr">
@@ -91031,7 +91031,7 @@
       </c>
       <c r="B1462" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1462" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
@@ -28411,7 +28411,7 @@
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
@@ -30767,7 +30767,7 @@
       </c>
       <c r="B490" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C490" s="2" t="inlineStr">
@@ -31821,7 +31821,7 @@
       </c>
       <c r="B507" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C507" s="2" t="inlineStr">
@@ -32937,7 +32937,7 @@
       </c>
       <c r="B525" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C525" s="2" t="inlineStr">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="B527" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C527" s="2" t="inlineStr">
@@ -33185,7 +33185,7 @@
       </c>
       <c r="B529" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C529" s="2" t="inlineStr">
@@ -34425,7 +34425,7 @@
       </c>
       <c r="B549" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C549" s="2" t="inlineStr">
@@ -35541,7 +35541,7 @@
       </c>
       <c r="B567" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C567" s="2" t="inlineStr">
@@ -35665,7 +35665,7 @@
       </c>
       <c r="B569" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C569" s="2" t="inlineStr">
@@ -38331,7 +38331,7 @@
       </c>
       <c r="B612" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C612" s="2" t="inlineStr">
@@ -40315,7 +40315,7 @@
       </c>
       <c r="B644" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C644" s="2" t="inlineStr">
@@ -42485,7 +42485,7 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -42981,7 +42981,7 @@
       </c>
       <c r="B687" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C687" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -51413,7 +51413,7 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
@@ -51537,7 +51537,7 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -58171,7 +58171,7 @@
       </c>
       <c r="B932" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C932" s="2" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="B971" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C971" s="2" t="inlineStr">
@@ -63193,7 +63193,7 @@
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
@@ -66789,7 +66789,7 @@
       </c>
       <c r="B1071" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1071" s="2" t="inlineStr">
@@ -69641,7 +69641,7 @@
       </c>
       <c r="B1117" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1117" s="2" t="inlineStr">
@@ -70261,7 +70261,7 @@
       </c>
       <c r="B1127" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1127" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -71687,7 +71687,7 @@
       </c>
       <c r="B1150" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1150" s="2" t="inlineStr">
@@ -74663,7 +74663,7 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
@@ -74725,7 +74725,7 @@
       </c>
       <c r="B1199" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1199" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -75035,7 +75035,7 @@
       </c>
       <c r="B1204" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1204" s="2" t="inlineStr">
@@ -76213,7 +76213,7 @@
       </c>
       <c r="B1223" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1223" s="2" t="inlineStr">
@@ -77577,7 +77577,7 @@
       </c>
       <c r="B1245" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1245" s="2" t="inlineStr">
@@ -77701,7 +77701,7 @@
       </c>
       <c r="B1247" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1247" s="2" t="inlineStr">
@@ -78879,7 +78879,7 @@
       </c>
       <c r="B1266" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1266" s="2" t="inlineStr">
@@ -83467,7 +83467,7 @@
       </c>
       <c r="B1340" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1340" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -83963,7 +83963,7 @@
       </c>
       <c r="B1348" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1348" s="2" t="inlineStr">
@@ -84397,7 +84397,7 @@
       </c>
       <c r="B1355" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1355" s="2" t="inlineStr">
@@ -84707,7 +84707,7 @@
       </c>
       <c r="B1360" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1360" s="2" t="inlineStr">
@@ -84893,7 +84893,7 @@
       </c>
       <c r="B1363" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1363" s="2" t="inlineStr">
@@ -87993,7 +87993,7 @@
       </c>
       <c r="B1413" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1413" s="2" t="inlineStr">
@@ -88551,7 +88551,7 @@
       </c>
       <c r="B1422" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1422" s="2" t="inlineStr">
@@ -90225,7 +90225,7 @@
       </c>
       <c r="B1449" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1449" s="2" t="inlineStr">
@@ -90349,7 +90349,7 @@
       </c>
       <c r="B1451" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1451" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -31635,7 +31635,7 @@
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="B527" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C527" s="2" t="inlineStr">
@@ -34425,7 +34425,7 @@
       </c>
       <c r="B549" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C549" s="2" t="inlineStr">
@@ -35665,7 +35665,7 @@
       </c>
       <c r="B569" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C569" s="2" t="inlineStr">
@@ -38331,7 +38331,7 @@
       </c>
       <c r="B612" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C612" s="2" t="inlineStr">
@@ -42485,7 +42485,7 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
@@ -42609,7 +42609,7 @@
       </c>
       <c r="B681" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C681" s="2" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -51041,7 +51041,7 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -58171,7 +58171,7 @@
       </c>
       <c r="B932" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C932" s="2" t="inlineStr">
@@ -58233,7 +58233,7 @@
       </c>
       <c r="B933" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C933" s="2" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="B971" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C971" s="2" t="inlineStr">
@@ -66789,7 +66789,7 @@
       </c>
       <c r="B1071" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1071" s="2" t="inlineStr">
@@ -70261,7 +70261,7 @@
       </c>
       <c r="B1127" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1127" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -71687,7 +71687,7 @@
       </c>
       <c r="B1150" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1150" s="2" t="inlineStr">
@@ -74663,7 +74663,7 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
@@ -74725,7 +74725,7 @@
       </c>
       <c r="B1199" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1199" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -77577,7 +77577,7 @@
       </c>
       <c r="B1245" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1245" s="2" t="inlineStr">
@@ -77639,7 +77639,7 @@
       </c>
       <c r="B1246" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1246" s="2" t="inlineStr">
@@ -78879,7 +78879,7 @@
       </c>
       <c r="B1266" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1266" s="2" t="inlineStr">
@@ -79561,7 +79561,7 @@
       </c>
       <c r="B1277" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1277" s="2" t="inlineStr">
@@ -79747,7 +79747,7 @@
       </c>
       <c r="B1280" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1280" s="2" t="inlineStr">
@@ -83467,7 +83467,7 @@
       </c>
       <c r="B1340" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1340" s="2" t="inlineStr">
@@ -83591,7 +83591,7 @@
       </c>
       <c r="B1342" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1342" s="2" t="inlineStr">
@@ -83963,7 +83963,7 @@
       </c>
       <c r="B1348" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1348" s="2" t="inlineStr">
@@ -84273,7 +84273,7 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84831,7 +84831,7 @@
       </c>
       <c r="B1362" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1362" s="2" t="inlineStr">
@@ -84893,7 +84893,7 @@
       </c>
       <c r="B1363" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1363" s="2" t="inlineStr">
@@ -86629,7 +86629,7 @@
       </c>
       <c r="B1391" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1391" s="2" t="inlineStr">
@@ -88551,7 +88551,7 @@
       </c>
       <c r="B1422" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1422" s="2" t="inlineStr">
@@ -90287,7 +90287,7 @@
       </c>
       <c r="B1450" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1450" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">
@@ -91961,7 +91961,7 @@
       </c>
       <c r="B1477" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1477" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
@@ -28411,7 +28411,7 @@
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
@@ -30767,7 +30767,7 @@
       </c>
       <c r="B490" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C490" s="2" t="inlineStr">
@@ -31635,7 +31635,7 @@
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
@@ -31821,7 +31821,7 @@
       </c>
       <c r="B507" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C507" s="2" t="inlineStr">
@@ -35541,7 +35541,7 @@
       </c>
       <c r="B567" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C567" s="2" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
@@ -42919,7 +42919,7 @@
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -47445,7 +47445,7 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
@@ -48933,7 +48933,7 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
@@ -51041,7 +51041,7 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
@@ -51413,7 +51413,7 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
@@ -58233,7 +58233,7 @@
       </c>
       <c r="B933" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C933" s="2" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="B971" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C971" s="2" t="inlineStr">
@@ -63193,7 +63193,7 @@
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
@@ -69641,7 +69641,7 @@
       </c>
       <c r="B1117" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1117" s="2" t="inlineStr">
@@ -69703,7 +69703,7 @@
       </c>
       <c r="B1118" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1118" s="2" t="inlineStr">
@@ -71191,7 +71191,7 @@
       </c>
       <c r="B1142" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1142" s="2" t="inlineStr">
@@ -71687,7 +71687,7 @@
       </c>
       <c r="B1150" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1150" s="2" t="inlineStr">
@@ -74663,7 +74663,7 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
@@ -74725,7 +74725,7 @@
       </c>
       <c r="B1199" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1199" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -76213,7 +76213,7 @@
       </c>
       <c r="B1223" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1223" s="2" t="inlineStr">
@@ -77639,7 +77639,7 @@
       </c>
       <c r="B1246" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1246" s="2" t="inlineStr">
@@ -78879,7 +78879,7 @@
       </c>
       <c r="B1266" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1266" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -83963,7 +83963,7 @@
       </c>
       <c r="B1348" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1348" s="2" t="inlineStr">
@@ -84397,7 +84397,7 @@
       </c>
       <c r="B1355" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1355" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84831,7 +84831,7 @@
       </c>
       <c r="B1362" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1362" s="2" t="inlineStr">
@@ -86629,7 +86629,7 @@
       </c>
       <c r="B1391" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1391" s="2" t="inlineStr">
@@ -87931,7 +87931,7 @@
       </c>
       <c r="B1412" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1412" s="2" t="inlineStr">
@@ -90225,7 +90225,7 @@
       </c>
       <c r="B1449" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1449" s="2" t="inlineStr">
@@ -90287,7 +90287,7 @@
       </c>
       <c r="B1450" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1450" s="2" t="inlineStr">
@@ -91031,7 +91031,7 @@
       </c>
       <c r="B1462" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1462" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -28411,7 +28411,7 @@
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
@@ -31635,7 +31635,7 @@
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
@@ -31821,7 +31821,7 @@
       </c>
       <c r="B507" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C507" s="2" t="inlineStr">
@@ -32937,7 +32937,7 @@
       </c>
       <c r="B525" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C525" s="2" t="inlineStr">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="B527" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C527" s="2" t="inlineStr">
@@ -35541,7 +35541,7 @@
       </c>
       <c r="B567" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C567" s="2" t="inlineStr">
@@ -37897,7 +37897,7 @@
       </c>
       <c r="B605" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C605" s="2" t="inlineStr">
@@ -42609,7 +42609,7 @@
       </c>
       <c r="B681" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C681" s="2" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -42919,7 +42919,7 @@
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
@@ -42981,7 +42981,7 @@
       </c>
       <c r="B687" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C687" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -48933,7 +48933,7 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
@@ -51413,7 +51413,7 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
@@ -51537,7 +51537,7 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
@@ -58171,7 +58171,7 @@
       </c>
       <c r="B932" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C932" s="2" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="B971" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C971" s="2" t="inlineStr">
@@ -66789,7 +66789,7 @@
       </c>
       <c r="B1071" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1071" s="2" t="inlineStr">
@@ -69641,7 +69641,7 @@
       </c>
       <c r="B1117" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1117" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -71749,7 +71749,7 @@
       </c>
       <c r="B1151" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1151" s="2" t="inlineStr">
@@ -73609,7 +73609,7 @@
       </c>
       <c r="B1181" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1181" s="2" t="inlineStr">
@@ -74663,7 +74663,7 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
@@ -74725,7 +74725,7 @@
       </c>
       <c r="B1199" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1199" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -76213,7 +76213,7 @@
       </c>
       <c r="B1223" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1223" s="2" t="inlineStr">
@@ -77639,7 +77639,7 @@
       </c>
       <c r="B1246" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1246" s="2" t="inlineStr">
@@ -84273,7 +84273,7 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
@@ -84893,7 +84893,7 @@
       </c>
       <c r="B1363" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1363" s="2" t="inlineStr">
@@ -87931,7 +87931,7 @@
       </c>
       <c r="B1412" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1412" s="2" t="inlineStr">
@@ -90225,7 +90225,7 @@
       </c>
       <c r="B1449" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1449" s="2" t="inlineStr">
@@ -91031,7 +91031,7 @@
       </c>
       <c r="B1462" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1462" s="2" t="inlineStr">
@@ -91961,7 +91961,7 @@
       </c>
       <c r="B1477" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1477" s="2" t="inlineStr">
@@ -92643,7 +92643,7 @@
       </c>
       <c r="B1488" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1488" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
@@ -29713,7 +29713,7 @@
       </c>
       <c r="B473" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C473" s="2" t="inlineStr">
@@ -30767,7 +30767,7 @@
       </c>
       <c r="B490" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C490" s="2" t="inlineStr">
@@ -31821,7 +31821,7 @@
       </c>
       <c r="B507" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C507" s="2" t="inlineStr">
@@ -32937,7 +32937,7 @@
       </c>
       <c r="B525" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C525" s="2" t="inlineStr">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="B527" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C527" s="2" t="inlineStr">
@@ -34921,7 +34921,7 @@
       </c>
       <c r="B557" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C557" s="2" t="inlineStr">
@@ -37897,7 +37897,7 @@
       </c>
       <c r="B605" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C605" s="2" t="inlineStr">
@@ -38021,7 +38021,7 @@
       </c>
       <c r="B607" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C607" s="2" t="inlineStr">
@@ -38331,7 +38331,7 @@
       </c>
       <c r="B612" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C612" s="2" t="inlineStr">
@@ -42609,7 +42609,7 @@
       </c>
       <c r="B681" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C681" s="2" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -47445,7 +47445,7 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
@@ -51041,7 +51041,7 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
@@ -63193,7 +63193,7 @@
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
@@ -66789,7 +66789,7 @@
       </c>
       <c r="B1071" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1071" s="2" t="inlineStr">
@@ -69641,7 +69641,7 @@
       </c>
       <c r="B1117" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1117" s="2" t="inlineStr">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
@@ -71191,7 +71191,7 @@
       </c>
       <c r="B1142" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1142" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -71749,7 +71749,7 @@
       </c>
       <c r="B1151" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1151" s="2" t="inlineStr">
@@ -74601,7 +74601,7 @@
       </c>
       <c r="B1197" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1197" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -75035,7 +75035,7 @@
       </c>
       <c r="B1204" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1204" s="2" t="inlineStr">
@@ -77577,7 +77577,7 @@
       </c>
       <c r="B1245" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1245" s="2" t="inlineStr">
@@ -77639,7 +77639,7 @@
       </c>
       <c r="B1246" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1246" s="2" t="inlineStr">
@@ -77701,7 +77701,7 @@
       </c>
       <c r="B1247" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1247" s="2" t="inlineStr">
@@ -77763,7 +77763,7 @@
       </c>
       <c r="B1248" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1248" s="2" t="inlineStr">
@@ -83715,7 +83715,7 @@
       </c>
       <c r="B1344" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1344" s="2" t="inlineStr">
@@ -83963,7 +83963,7 @@
       </c>
       <c r="B1348" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1348" s="2" t="inlineStr">
@@ -84273,7 +84273,7 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
@@ -84707,7 +84707,7 @@
       </c>
       <c r="B1360" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1360" s="2" t="inlineStr">
@@ -84893,7 +84893,7 @@
       </c>
       <c r="B1363" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1363" s="2" t="inlineStr">
@@ -87993,7 +87993,7 @@
       </c>
       <c r="B1413" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1413" s="2" t="inlineStr">
@@ -90225,7 +90225,7 @@
       </c>
       <c r="B1449" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1449" s="2" t="inlineStr">
@@ -90287,7 +90287,7 @@
       </c>
       <c r="B1450" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1450" s="2" t="inlineStr">
@@ -91961,7 +91961,7 @@
       </c>
       <c r="B1477" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1477" s="2" t="inlineStr">
@@ -92643,7 +92643,7 @@
       </c>
       <c r="B1488" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1488" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
@@ -31821,7 +31821,7 @@
       </c>
       <c r="B507" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C507" s="2" t="inlineStr">
@@ -34921,7 +34921,7 @@
       </c>
       <c r="B557" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C557" s="2" t="inlineStr">
@@ -35665,7 +35665,7 @@
       </c>
       <c r="B569" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C569" s="2" t="inlineStr">
@@ -38021,7 +38021,7 @@
       </c>
       <c r="B607" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C607" s="2" t="inlineStr">
@@ -38331,7 +38331,7 @@
       </c>
       <c r="B612" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C612" s="2" t="inlineStr">
@@ -42609,7 +42609,7 @@
       </c>
       <c r="B681" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C681" s="2" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -48933,7 +48933,7 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
@@ -51041,7 +51041,7 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
@@ -51537,7 +51537,7 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -56001,7 +56001,7 @@
       </c>
       <c r="B897" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C897" s="2" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="B971" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C971" s="2" t="inlineStr">
@@ -63193,7 +63193,7 @@
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
@@ -69703,7 +69703,7 @@
       </c>
       <c r="B1118" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1118" s="2" t="inlineStr">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -71687,7 +71687,7 @@
       </c>
       <c r="B1150" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1150" s="2" t="inlineStr">
@@ -74601,7 +74601,7 @@
       </c>
       <c r="B1197" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1197" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -75035,7 +75035,7 @@
       </c>
       <c r="B1204" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1204" s="2" t="inlineStr">
@@ -76213,7 +76213,7 @@
       </c>
       <c r="B1223" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1223" s="2" t="inlineStr">
@@ -77577,7 +77577,7 @@
       </c>
       <c r="B1245" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1245" s="2" t="inlineStr">
@@ -77639,7 +77639,7 @@
       </c>
       <c r="B1246" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1246" s="2" t="inlineStr">
@@ -77763,7 +77763,7 @@
       </c>
       <c r="B1248" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1248" s="2" t="inlineStr">
@@ -79747,7 +79747,7 @@
       </c>
       <c r="B1280" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1280" s="2" t="inlineStr">
@@ -83467,7 +83467,7 @@
       </c>
       <c r="B1340" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1340" s="2" t="inlineStr">
@@ -83715,7 +83715,7 @@
       </c>
       <c r="B1344" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1344" s="2" t="inlineStr">
@@ -83963,7 +83963,7 @@
       </c>
       <c r="B1348" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1348" s="2" t="inlineStr">
@@ -84397,7 +84397,7 @@
       </c>
       <c r="B1355" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1355" s="2" t="inlineStr">
@@ -84769,7 +84769,7 @@
       </c>
       <c r="B1361" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1361" s="2" t="inlineStr">
@@ -84831,7 +84831,7 @@
       </c>
       <c r="B1362" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1362" s="2" t="inlineStr">
@@ -84893,7 +84893,7 @@
       </c>
       <c r="B1363" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1363" s="2" t="inlineStr">
@@ -87993,7 +87993,7 @@
       </c>
       <c r="B1413" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1413" s="2" t="inlineStr">
@@ -90225,7 +90225,7 @@
       </c>
       <c r="B1449" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1449" s="2" t="inlineStr">
@@ -90287,7 +90287,7 @@
       </c>
       <c r="B1450" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1450" s="2" t="inlineStr">
@@ -90349,7 +90349,7 @@
       </c>
       <c r="B1451" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1451" s="2" t="inlineStr">
@@ -91031,7 +91031,7 @@
       </c>
       <c r="B1462" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1462" s="2" t="inlineStr">
@@ -91961,7 +91961,7 @@
       </c>
       <c r="B1477" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1477" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
@@ -30767,7 +30767,7 @@
       </c>
       <c r="B490" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C490" s="2" t="inlineStr">
@@ -31821,7 +31821,7 @@
       </c>
       <c r="B507" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C507" s="2" t="inlineStr">
@@ -40315,7 +40315,7 @@
       </c>
       <c r="B644" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C644" s="2" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -48933,7 +48933,7 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
@@ -51041,7 +51041,7 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
@@ -51413,7 +51413,7 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
@@ -56001,7 +56001,7 @@
       </c>
       <c r="B897" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C897" s="2" t="inlineStr">
@@ -58233,7 +58233,7 @@
       </c>
       <c r="B933" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C933" s="2" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="B971" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C971" s="2" t="inlineStr">
@@ -63193,7 +63193,7 @@
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
@@ -69641,7 +69641,7 @@
       </c>
       <c r="B1117" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1117" s="2" t="inlineStr">
@@ -71687,7 +71687,7 @@
       </c>
       <c r="B1150" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1150" s="2" t="inlineStr">
@@ -73609,7 +73609,7 @@
       </c>
       <c r="B1181" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1181" s="2" t="inlineStr">
@@ -74663,7 +74663,7 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -74973,7 +74973,7 @@
       </c>
       <c r="B1203" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1203" s="2" t="inlineStr">
@@ -75035,7 +75035,7 @@
       </c>
       <c r="B1204" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1204" s="2" t="inlineStr">
@@ -77639,7 +77639,7 @@
       </c>
       <c r="B1246" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1246" s="2" t="inlineStr">
@@ -77701,7 +77701,7 @@
       </c>
       <c r="B1247" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1247" s="2" t="inlineStr">
@@ -78879,7 +78879,7 @@
       </c>
       <c r="B1266" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1266" s="2" t="inlineStr">
@@ -79375,7 +79375,7 @@
       </c>
       <c r="B1274" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1274" s="2" t="inlineStr">
@@ -83467,7 +83467,7 @@
       </c>
       <c r="B1340" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1340" s="2" t="inlineStr">
@@ -83591,7 +83591,7 @@
       </c>
       <c r="B1342" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1342" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -83963,7 +83963,7 @@
       </c>
       <c r="B1348" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1348" s="2" t="inlineStr">
@@ -84273,7 +84273,7 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84707,7 +84707,7 @@
       </c>
       <c r="B1360" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1360" s="2" t="inlineStr">
@@ -84769,7 +84769,7 @@
       </c>
       <c r="B1361" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1361" s="2" t="inlineStr">
@@ -84831,7 +84831,7 @@
       </c>
       <c r="B1362" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1362" s="2" t="inlineStr">
@@ -86629,7 +86629,7 @@
       </c>
       <c r="B1391" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1391" s="2" t="inlineStr">
@@ -87993,7 +87993,7 @@
       </c>
       <c r="B1413" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1413" s="2" t="inlineStr">
@@ -88551,7 +88551,7 @@
       </c>
       <c r="B1422" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1422" s="2" t="inlineStr">
@@ -91031,7 +91031,7 @@
       </c>
       <c r="B1462" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1462" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">
@@ -91961,7 +91961,7 @@
       </c>
       <c r="B1477" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1477" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
@@ -29713,7 +29713,7 @@
       </c>
       <c r="B473" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C473" s="2" t="inlineStr">
@@ -31821,7 +31821,7 @@
       </c>
       <c r="B507" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C507" s="2" t="inlineStr">
@@ -32937,7 +32937,7 @@
       </c>
       <c r="B525" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C525" s="2" t="inlineStr">
@@ -37897,7 +37897,7 @@
       </c>
       <c r="B605" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C605" s="2" t="inlineStr">
@@ -40315,7 +40315,7 @@
       </c>
       <c r="B644" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C644" s="2" t="inlineStr">
@@ -42485,7 +42485,7 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -47445,7 +47445,7 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
@@ -48933,7 +48933,7 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
@@ -51041,7 +51041,7 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
@@ -51413,7 +51413,7 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
@@ -51537,7 +51537,7 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
@@ -58171,7 +58171,7 @@
       </c>
       <c r="B932" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C932" s="2" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="B971" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C971" s="2" t="inlineStr">
@@ -66789,7 +66789,7 @@
       </c>
       <c r="B1071" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1071" s="2" t="inlineStr">
@@ -69703,7 +69703,7 @@
       </c>
       <c r="B1118" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1118" s="2" t="inlineStr">
@@ -71687,7 +71687,7 @@
       </c>
       <c r="B1150" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1150" s="2" t="inlineStr">
@@ -74973,7 +74973,7 @@
       </c>
       <c r="B1203" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1203" s="2" t="inlineStr">
@@ -75035,7 +75035,7 @@
       </c>
       <c r="B1204" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1204" s="2" t="inlineStr">
@@ -76213,7 +76213,7 @@
       </c>
       <c r="B1223" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1223" s="2" t="inlineStr">
@@ -77639,7 +77639,7 @@
       </c>
       <c r="B1246" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1246" s="2" t="inlineStr">
@@ -78879,7 +78879,7 @@
       </c>
       <c r="B1266" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1266" s="2" t="inlineStr">
@@ -79375,7 +79375,7 @@
       </c>
       <c r="B1274" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1274" s="2" t="inlineStr">
@@ -79561,7 +79561,7 @@
       </c>
       <c r="B1277" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1277" s="2" t="inlineStr">
@@ -83591,7 +83591,7 @@
       </c>
       <c r="B1342" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1342" s="2" t="inlineStr">
@@ -83963,7 +83963,7 @@
       </c>
       <c r="B1348" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1348" s="2" t="inlineStr">
@@ -84397,7 +84397,7 @@
       </c>
       <c r="B1355" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1355" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84707,7 +84707,7 @@
       </c>
       <c r="B1360" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1360" s="2" t="inlineStr">
@@ -84831,7 +84831,7 @@
       </c>
       <c r="B1362" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1362" s="2" t="inlineStr">
@@ -86629,7 +86629,7 @@
       </c>
       <c r="B1391" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1391" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">
@@ -91961,7 +91961,7 @@
       </c>
       <c r="B1477" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1477" s="2" t="inlineStr">
@@ -92643,7 +92643,7 @@
       </c>
       <c r="B1488" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1488" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
@@ -30767,7 +30767,7 @@
       </c>
       <c r="B490" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C490" s="2" t="inlineStr">
@@ -31635,7 +31635,7 @@
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
@@ -32937,7 +32937,7 @@
       </c>
       <c r="B525" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C525" s="2" t="inlineStr">
@@ -35665,7 +35665,7 @@
       </c>
       <c r="B569" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C569" s="2" t="inlineStr">
@@ -38021,7 +38021,7 @@
       </c>
       <c r="B607" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C607" s="2" t="inlineStr">
@@ -42485,7 +42485,7 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
@@ -42981,7 +42981,7 @@
       </c>
       <c r="B687" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C687" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -47445,7 +47445,7 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
@@ -48933,7 +48933,7 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
@@ -51103,7 +51103,7 @@
       </c>
       <c r="B818" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C818" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="B971" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C971" s="2" t="inlineStr">
@@ -66789,7 +66789,7 @@
       </c>
       <c r="B1071" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1071" s="2" t="inlineStr">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
@@ -73609,7 +73609,7 @@
       </c>
       <c r="B1181" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1181" s="2" t="inlineStr">
@@ -74663,7 +74663,7 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
@@ -74973,7 +74973,7 @@
       </c>
       <c r="B1203" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1203" s="2" t="inlineStr">
@@ -77701,7 +77701,7 @@
       </c>
       <c r="B1247" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1247" s="2" t="inlineStr">
@@ -77763,7 +77763,7 @@
       </c>
       <c r="B1248" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1248" s="2" t="inlineStr">
@@ -83467,7 +83467,7 @@
       </c>
       <c r="B1340" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1340" s="2" t="inlineStr">
@@ -83591,7 +83591,7 @@
       </c>
       <c r="B1342" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1342" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -84273,7 +84273,7 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
@@ -84831,7 +84831,7 @@
       </c>
       <c r="B1362" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1362" s="2" t="inlineStr">
@@ -87931,7 +87931,7 @@
       </c>
       <c r="B1412" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1412" s="2" t="inlineStr">
@@ -87993,7 +87993,7 @@
       </c>
       <c r="B1413" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1413" s="2" t="inlineStr">
@@ -88551,7 +88551,7 @@
       </c>
       <c r="B1422" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1422" s="2" t="inlineStr">
@@ -90349,7 +90349,7 @@
       </c>
       <c r="B1451" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1451" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">
@@ -91961,7 +91961,7 @@
       </c>
       <c r="B1477" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1477" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -28411,7 +28411,7 @@
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
@@ -30767,7 +30767,7 @@
       </c>
       <c r="B490" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C490" s="2" t="inlineStr">
@@ -31635,7 +31635,7 @@
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
@@ -32937,7 +32937,7 @@
       </c>
       <c r="B525" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C525" s="2" t="inlineStr">
@@ -35665,7 +35665,7 @@
       </c>
       <c r="B569" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C569" s="2" t="inlineStr">
@@ -37897,7 +37897,7 @@
       </c>
       <c r="B605" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C605" s="2" t="inlineStr">
@@ -38021,7 +38021,7 @@
       </c>
       <c r="B607" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C607" s="2" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -42919,7 +42919,7 @@
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
@@ -42981,7 +42981,7 @@
       </c>
       <c r="B687" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C687" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -48933,7 +48933,7 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
@@ -51103,7 +51103,7 @@
       </c>
       <c r="B818" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C818" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -58171,7 +58171,7 @@
       </c>
       <c r="B932" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C932" s="2" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="B971" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C971" s="2" t="inlineStr">
@@ -66789,7 +66789,7 @@
       </c>
       <c r="B1071" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1071" s="2" t="inlineStr">
@@ -69641,7 +69641,7 @@
       </c>
       <c r="B1117" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1117" s="2" t="inlineStr">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
@@ -70261,7 +70261,7 @@
       </c>
       <c r="B1127" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1127" s="2" t="inlineStr">
@@ -73609,7 +73609,7 @@
       </c>
       <c r="B1181" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1181" s="2" t="inlineStr">
@@ -74725,7 +74725,7 @@
       </c>
       <c r="B1199" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1199" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -74973,7 +74973,7 @@
       </c>
       <c r="B1203" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1203" s="2" t="inlineStr">
@@ -76213,7 +76213,7 @@
       </c>
       <c r="B1223" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1223" s="2" t="inlineStr">
@@ -77701,7 +77701,7 @@
       </c>
       <c r="B1247" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1247" s="2" t="inlineStr">
@@ -77763,7 +77763,7 @@
       </c>
       <c r="B1248" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1248" s="2" t="inlineStr">
@@ -78879,7 +78879,7 @@
       </c>
       <c r="B1266" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1266" s="2" t="inlineStr">
@@ -83467,7 +83467,7 @@
       </c>
       <c r="B1340" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1340" s="2" t="inlineStr">
@@ -83591,7 +83591,7 @@
       </c>
       <c r="B1342" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1342" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -84087,7 +84087,7 @@
       </c>
       <c r="B1350" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1350" s="2" t="inlineStr">
@@ -84273,7 +84273,7 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
@@ -84397,7 +84397,7 @@
       </c>
       <c r="B1355" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1355" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84707,7 +84707,7 @@
       </c>
       <c r="B1360" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1360" s="2" t="inlineStr">
@@ -84831,7 +84831,7 @@
       </c>
       <c r="B1362" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1362" s="2" t="inlineStr">
@@ -87931,7 +87931,7 @@
       </c>
       <c r="B1412" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1412" s="2" t="inlineStr">
@@ -88489,7 +88489,7 @@
       </c>
       <c r="B1421" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1421" s="2" t="inlineStr">
@@ -88551,7 +88551,7 @@
       </c>
       <c r="B1422" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1422" s="2" t="inlineStr">
@@ -90225,7 +90225,7 @@
       </c>
       <c r="B1449" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1449" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -31635,7 +31635,7 @@
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
@@ -34425,7 +34425,7 @@
       </c>
       <c r="B549" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C549" s="2" t="inlineStr">
@@ -34921,7 +34921,7 @@
       </c>
       <c r="B557" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C557" s="2" t="inlineStr">
@@ -35541,7 +35541,7 @@
       </c>
       <c r="B567" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C567" s="2" t="inlineStr">
@@ -35665,7 +35665,7 @@
       </c>
       <c r="B569" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C569" s="2" t="inlineStr">
@@ -37897,7 +37897,7 @@
       </c>
       <c r="B605" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C605" s="2" t="inlineStr">
@@ -38331,7 +38331,7 @@
       </c>
       <c r="B612" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C612" s="2" t="inlineStr">
@@ -40315,7 +40315,7 @@
       </c>
       <c r="B644" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C644" s="2" t="inlineStr">
@@ -42609,7 +42609,7 @@
       </c>
       <c r="B681" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C681" s="2" t="inlineStr">
@@ -42919,7 +42919,7 @@
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
@@ -42981,7 +42981,7 @@
       </c>
       <c r="B687" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C687" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -47445,7 +47445,7 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
@@ -48933,7 +48933,7 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
@@ -51599,7 +51599,7 @@
       </c>
       <c r="B826" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C826" s="2" t="inlineStr">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -58233,7 +58233,7 @@
       </c>
       <c r="B933" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C933" s="2" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="B971" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C971" s="2" t="inlineStr">
@@ -63193,7 +63193,7 @@
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
@@ -66789,7 +66789,7 @@
       </c>
       <c r="B1071" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1071" s="2" t="inlineStr">
@@ -69703,7 +69703,7 @@
       </c>
       <c r="B1118" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1118" s="2" t="inlineStr">
@@ -70261,7 +70261,7 @@
       </c>
       <c r="B1127" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1127" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -71687,7 +71687,7 @@
       </c>
       <c r="B1150" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1150" s="2" t="inlineStr">
@@ -74663,7 +74663,7 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
@@ -74725,7 +74725,7 @@
       </c>
       <c r="B1199" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1199" s="2" t="inlineStr">
@@ -76213,7 +76213,7 @@
       </c>
       <c r="B1223" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1223" s="2" t="inlineStr">
@@ -77639,7 +77639,7 @@
       </c>
       <c r="B1246" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1246" s="2" t="inlineStr">
@@ -77701,7 +77701,7 @@
       </c>
       <c r="B1247" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1247" s="2" t="inlineStr">
@@ -78879,7 +78879,7 @@
       </c>
       <c r="B1266" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1266" s="2" t="inlineStr">
@@ -79747,7 +79747,7 @@
       </c>
       <c r="B1280" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1280" s="2" t="inlineStr">
@@ -83467,7 +83467,7 @@
       </c>
       <c r="B1340" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1340" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -84087,7 +84087,7 @@
       </c>
       <c r="B1350" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1350" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84707,7 +84707,7 @@
       </c>
       <c r="B1360" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1360" s="2" t="inlineStr">
@@ -84893,7 +84893,7 @@
       </c>
       <c r="B1363" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1363" s="2" t="inlineStr">
@@ -86629,7 +86629,7 @@
       </c>
       <c r="B1391" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1391" s="2" t="inlineStr">
@@ -87993,7 +87993,7 @@
       </c>
       <c r="B1413" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1413" s="2" t="inlineStr">
@@ -90225,7 +90225,7 @@
       </c>
       <c r="B1449" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1449" s="2" t="inlineStr">
@@ -90287,7 +90287,7 @@
       </c>
       <c r="B1450" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1450" s="2" t="inlineStr">
@@ -92643,7 +92643,7 @@
       </c>
       <c r="B1488" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1488" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
@@ -31635,7 +31635,7 @@
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
@@ -31821,7 +31821,7 @@
       </c>
       <c r="B507" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C507" s="2" t="inlineStr">
@@ -34425,7 +34425,7 @@
       </c>
       <c r="B549" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C549" s="2" t="inlineStr">
@@ -34921,7 +34921,7 @@
       </c>
       <c r="B557" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C557" s="2" t="inlineStr">
@@ -42609,7 +42609,7 @@
       </c>
       <c r="B681" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C681" s="2" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -47445,7 +47445,7 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
@@ -51413,7 +51413,7 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
@@ -51537,7 +51537,7 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -58171,7 +58171,7 @@
       </c>
       <c r="B932" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C932" s="2" t="inlineStr">
@@ -58233,7 +58233,7 @@
       </c>
       <c r="B933" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C933" s="2" t="inlineStr">
@@ -63193,7 +63193,7 @@
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -73609,7 +73609,7 @@
       </c>
       <c r="B1181" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1181" s="2" t="inlineStr">
@@ -74663,7 +74663,7 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
@@ -74725,7 +74725,7 @@
       </c>
       <c r="B1199" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1199" s="2" t="inlineStr">
@@ -74973,7 +74973,7 @@
       </c>
       <c r="B1203" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1203" s="2" t="inlineStr">
@@ -76213,7 +76213,7 @@
       </c>
       <c r="B1223" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1223" s="2" t="inlineStr">
@@ -77577,7 +77577,7 @@
       </c>
       <c r="B1245" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1245" s="2" t="inlineStr">
@@ -77639,7 +77639,7 @@
       </c>
       <c r="B1246" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1246" s="2" t="inlineStr">
@@ -77701,7 +77701,7 @@
       </c>
       <c r="B1247" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1247" s="2" t="inlineStr">
@@ -78879,7 +78879,7 @@
       </c>
       <c r="B1266" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1266" s="2" t="inlineStr">
@@ -79747,7 +79747,7 @@
       </c>
       <c r="B1280" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1280" s="2" t="inlineStr">
@@ -83467,7 +83467,7 @@
       </c>
       <c r="B1340" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1340" s="2" t="inlineStr">
@@ -83591,7 +83591,7 @@
       </c>
       <c r="B1342" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1342" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -83963,7 +83963,7 @@
       </c>
       <c r="B1348" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1348" s="2" t="inlineStr">
@@ -84707,7 +84707,7 @@
       </c>
       <c r="B1360" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1360" s="2" t="inlineStr">
@@ -87993,7 +87993,7 @@
       </c>
       <c r="B1413" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1413" s="2" t="inlineStr">
@@ -88551,7 +88551,7 @@
       </c>
       <c r="B1422" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1422" s="2" t="inlineStr">
@@ -90225,7 +90225,7 @@
       </c>
       <c r="B1449" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1449" s="2" t="inlineStr">
@@ -90287,7 +90287,7 @@
       </c>
       <c r="B1450" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1450" s="2" t="inlineStr">
@@ -90349,7 +90349,7 @@
       </c>
       <c r="B1451" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1451" s="2" t="inlineStr">
@@ -92643,7 +92643,7 @@
       </c>
       <c r="B1488" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1488" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
@@ -28411,7 +28411,7 @@
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
@@ -31635,7 +31635,7 @@
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
@@ -31821,7 +31821,7 @@
       </c>
       <c r="B507" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C507" s="2" t="inlineStr">
@@ -34921,7 +34921,7 @@
       </c>
       <c r="B557" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C557" s="2" t="inlineStr">
@@ -35541,7 +35541,7 @@
       </c>
       <c r="B567" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C567" s="2" t="inlineStr">
@@ -37897,7 +37897,7 @@
       </c>
       <c r="B605" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C605" s="2" t="inlineStr">
@@ -40315,7 +40315,7 @@
       </c>
       <c r="B644" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C644" s="2" t="inlineStr">
@@ -42485,7 +42485,7 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -51041,7 +51041,7 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
@@ -51537,7 +51537,7 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="B971" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C971" s="2" t="inlineStr">
@@ -63193,7 +63193,7 @@
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
@@ -70261,7 +70261,7 @@
       </c>
       <c r="B1127" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1127" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -71687,7 +71687,7 @@
       </c>
       <c r="B1150" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1150" s="2" t="inlineStr">
@@ -71749,7 +71749,7 @@
       </c>
       <c r="B1151" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1151" s="2" t="inlineStr">
@@ -73609,7 +73609,7 @@
       </c>
       <c r="B1181" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1181" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -74973,7 +74973,7 @@
       </c>
       <c r="B1203" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1203" s="2" t="inlineStr">
@@ -77577,7 +77577,7 @@
       </c>
       <c r="B1245" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1245" s="2" t="inlineStr">
@@ -83591,7 +83591,7 @@
       </c>
       <c r="B1342" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1342" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84769,7 +84769,7 @@
       </c>
       <c r="B1361" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1361" s="2" t="inlineStr">
@@ -84893,7 +84893,7 @@
       </c>
       <c r="B1363" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1363" s="2" t="inlineStr">
@@ -86629,7 +86629,7 @@
       </c>
       <c r="B1391" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1391" s="2" t="inlineStr">
@@ -87931,7 +87931,7 @@
       </c>
       <c r="B1412" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1412" s="2" t="inlineStr">
@@ -88551,7 +88551,7 @@
       </c>
       <c r="B1422" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1422" s="2" t="inlineStr">
@@ -90349,7 +90349,7 @@
       </c>
       <c r="B1451" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1451" s="2" t="inlineStr">
@@ -91031,7 +91031,7 @@
       </c>
       <c r="B1462" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1462" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">
@@ -92643,7 +92643,7 @@
       </c>
       <c r="B1488" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1488" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -28411,7 +28411,7 @@
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
@@ -31635,7 +31635,7 @@
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
@@ -33185,7 +33185,7 @@
       </c>
       <c r="B529" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C529" s="2" t="inlineStr">
@@ -34921,7 +34921,7 @@
       </c>
       <c r="B557" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C557" s="2" t="inlineStr">
@@ -35665,7 +35665,7 @@
       </c>
       <c r="B569" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C569" s="2" t="inlineStr">
@@ -37897,7 +37897,7 @@
       </c>
       <c r="B605" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C605" s="2" t="inlineStr">
@@ -40315,7 +40315,7 @@
       </c>
       <c r="B644" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C644" s="2" t="inlineStr">
@@ -42485,7 +42485,7 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
@@ -42981,7 +42981,7 @@
       </c>
       <c r="B687" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C687" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -48933,7 +48933,7 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
@@ -51413,7 +51413,7 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
@@ -51599,7 +51599,7 @@
       </c>
       <c r="B826" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C826" s="2" t="inlineStr">
@@ -56001,7 +56001,7 @@
       </c>
       <c r="B897" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C897" s="2" t="inlineStr">
@@ -58171,7 +58171,7 @@
       </c>
       <c r="B932" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C932" s="2" t="inlineStr">
@@ -58233,7 +58233,7 @@
       </c>
       <c r="B933" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C933" s="2" t="inlineStr">
@@ -70261,7 +70261,7 @@
       </c>
       <c r="B1127" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1127" s="2" t="inlineStr">
@@ -71191,7 +71191,7 @@
       </c>
       <c r="B1142" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1142" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -71749,7 +71749,7 @@
       </c>
       <c r="B1151" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1151" s="2" t="inlineStr">
@@ -74725,7 +74725,7 @@
       </c>
       <c r="B1199" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1199" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -74973,7 +74973,7 @@
       </c>
       <c r="B1203" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1203" s="2" t="inlineStr">
@@ -75035,7 +75035,7 @@
       </c>
       <c r="B1204" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1204" s="2" t="inlineStr">
@@ -76213,7 +76213,7 @@
       </c>
       <c r="B1223" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1223" s="2" t="inlineStr">
@@ -77701,7 +77701,7 @@
       </c>
       <c r="B1247" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1247" s="2" t="inlineStr">
@@ -78879,7 +78879,7 @@
       </c>
       <c r="B1266" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1266" s="2" t="inlineStr">
@@ -79561,7 +79561,7 @@
       </c>
       <c r="B1277" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1277" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -84273,7 +84273,7 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84707,7 +84707,7 @@
       </c>
       <c r="B1360" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1360" s="2" t="inlineStr">
@@ -84769,7 +84769,7 @@
       </c>
       <c r="B1361" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1361" s="2" t="inlineStr">
@@ -84893,7 +84893,7 @@
       </c>
       <c r="B1363" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1363" s="2" t="inlineStr">
@@ -88489,7 +88489,7 @@
       </c>
       <c r="B1421" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1421" s="2" t="inlineStr">
@@ -88551,7 +88551,7 @@
       </c>
       <c r="B1422" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1422" s="2" t="inlineStr">
@@ -90225,7 +90225,7 @@
       </c>
       <c r="B1449" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1449" s="2" t="inlineStr">
@@ -90349,7 +90349,7 @@
       </c>
       <c r="B1451" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1451" s="2" t="inlineStr">
@@ -91031,7 +91031,7 @@
       </c>
       <c r="B1462" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1462" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
@@ -31635,7 +31635,7 @@
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
@@ -32937,7 +32937,7 @@
       </c>
       <c r="B525" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C525" s="2" t="inlineStr">
@@ -33185,7 +33185,7 @@
       </c>
       <c r="B529" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C529" s="2" t="inlineStr">
@@ -34921,7 +34921,7 @@
       </c>
       <c r="B557" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C557" s="2" t="inlineStr">
@@ -35541,7 +35541,7 @@
       </c>
       <c r="B567" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C567" s="2" t="inlineStr">
@@ -35665,7 +35665,7 @@
       </c>
       <c r="B569" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C569" s="2" t="inlineStr">
@@ -37897,7 +37897,7 @@
       </c>
       <c r="B605" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C605" s="2" t="inlineStr">
@@ -38331,7 +38331,7 @@
       </c>
       <c r="B612" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C612" s="2" t="inlineStr">
@@ -40315,7 +40315,7 @@
       </c>
       <c r="B644" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C644" s="2" t="inlineStr">
@@ -42485,7 +42485,7 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -48933,7 +48933,7 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
@@ -51599,7 +51599,7 @@
       </c>
       <c r="B826" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C826" s="2" t="inlineStr">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="B971" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C971" s="2" t="inlineStr">
@@ -66789,7 +66789,7 @@
       </c>
       <c r="B1071" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1071" s="2" t="inlineStr">
@@ -69703,7 +69703,7 @@
       </c>
       <c r="B1118" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1118" s="2" t="inlineStr">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
@@ -71191,7 +71191,7 @@
       </c>
       <c r="B1142" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1142" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -71687,7 +71687,7 @@
       </c>
       <c r="B1150" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1150" s="2" t="inlineStr">
@@ -74725,7 +74725,7 @@
       </c>
       <c r="B1199" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1199" s="2" t="inlineStr">
@@ -74973,7 +74973,7 @@
       </c>
       <c r="B1203" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1203" s="2" t="inlineStr">
@@ -77639,7 +77639,7 @@
       </c>
       <c r="B1246" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1246" s="2" t="inlineStr">
@@ -77701,7 +77701,7 @@
       </c>
       <c r="B1247" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1247" s="2" t="inlineStr">
@@ -78879,7 +78879,7 @@
       </c>
       <c r="B1266" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1266" s="2" t="inlineStr">
@@ -79747,7 +79747,7 @@
       </c>
       <c r="B1280" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1280" s="2" t="inlineStr">
@@ -83467,7 +83467,7 @@
       </c>
       <c r="B1340" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1340" s="2" t="inlineStr">
@@ -83591,7 +83591,7 @@
       </c>
       <c r="B1342" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1342" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -84087,7 +84087,7 @@
       </c>
       <c r="B1350" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1350" s="2" t="inlineStr">
@@ -84273,7 +84273,7 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
@@ -84397,7 +84397,7 @@
       </c>
       <c r="B1355" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1355" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84769,7 +84769,7 @@
       </c>
       <c r="B1361" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1361" s="2" t="inlineStr">
@@ -84831,7 +84831,7 @@
       </c>
       <c r="B1362" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1362" s="2" t="inlineStr">
@@ -84893,7 +84893,7 @@
       </c>
       <c r="B1363" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1363" s="2" t="inlineStr">
@@ -87931,7 +87931,7 @@
       </c>
       <c r="B1412" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1412" s="2" t="inlineStr">
@@ -87993,7 +87993,7 @@
       </c>
       <c r="B1413" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1413" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
@@ -32937,7 +32937,7 @@
       </c>
       <c r="B525" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C525" s="2" t="inlineStr">
@@ -33185,7 +33185,7 @@
       </c>
       <c r="B529" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C529" s="2" t="inlineStr">
@@ -34921,7 +34921,7 @@
       </c>
       <c r="B557" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C557" s="2" t="inlineStr">
@@ -35541,7 +35541,7 @@
       </c>
       <c r="B567" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C567" s="2" t="inlineStr">
@@ -37897,7 +37897,7 @@
       </c>
       <c r="B605" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C605" s="2" t="inlineStr">
@@ -42485,7 +42485,7 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -47445,7 +47445,7 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
@@ -51041,7 +51041,7 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
@@ -51413,7 +51413,7 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
@@ -51537,7 +51537,7 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -56001,7 +56001,7 @@
       </c>
       <c r="B897" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C897" s="2" t="inlineStr">
@@ -66789,7 +66789,7 @@
       </c>
       <c r="B1071" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1071" s="2" t="inlineStr">
@@ -69703,7 +69703,7 @@
       </c>
       <c r="B1118" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1118" s="2" t="inlineStr">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
@@ -70261,7 +70261,7 @@
       </c>
       <c r="B1127" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1127" s="2" t="inlineStr">
@@ -71191,7 +71191,7 @@
       </c>
       <c r="B1142" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1142" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -71687,7 +71687,7 @@
       </c>
       <c r="B1150" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1150" s="2" t="inlineStr">
@@ -74601,7 +74601,7 @@
       </c>
       <c r="B1197" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1197" s="2" t="inlineStr">
@@ -74663,7 +74663,7 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
@@ -74725,7 +74725,7 @@
       </c>
       <c r="B1199" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1199" s="2" t="inlineStr">
@@ -77577,7 +77577,7 @@
       </c>
       <c r="B1245" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1245" s="2" t="inlineStr">
@@ -77639,7 +77639,7 @@
       </c>
       <c r="B1246" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1246" s="2" t="inlineStr">
@@ -77701,7 +77701,7 @@
       </c>
       <c r="B1247" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1247" s="2" t="inlineStr">
@@ -79561,7 +79561,7 @@
       </c>
       <c r="B1277" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1277" s="2" t="inlineStr">
@@ -83467,7 +83467,7 @@
       </c>
       <c r="B1340" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1340" s="2" t="inlineStr">
@@ -84087,7 +84087,7 @@
       </c>
       <c r="B1350" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1350" s="2" t="inlineStr">
@@ -84273,7 +84273,7 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84769,7 +84769,7 @@
       </c>
       <c r="B1361" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1361" s="2" t="inlineStr">
@@ -84831,7 +84831,7 @@
       </c>
       <c r="B1362" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1362" s="2" t="inlineStr">
@@ -88551,7 +88551,7 @@
       </c>
       <c r="B1422" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1422" s="2" t="inlineStr">
@@ -90225,7 +90225,7 @@
       </c>
       <c r="B1449" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1449" s="2" t="inlineStr">
@@ -90349,7 +90349,7 @@
       </c>
       <c r="B1451" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1451" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -28411,7 +28411,7 @@
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
@@ -31573,7 +31573,7 @@
       </c>
       <c r="B503" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C503" s="2" t="inlineStr">
@@ -31635,7 +31635,7 @@
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
@@ -32937,7 +32937,7 @@
       </c>
       <c r="B525" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C525" s="2" t="inlineStr">
@@ -34425,7 +34425,7 @@
       </c>
       <c r="B549" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C549" s="2" t="inlineStr">
@@ -34921,7 +34921,7 @@
       </c>
       <c r="B557" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C557" s="2" t="inlineStr">
@@ -35541,7 +35541,7 @@
       </c>
       <c r="B567" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C567" s="2" t="inlineStr">
@@ -37897,7 +37897,7 @@
       </c>
       <c r="B605" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C605" s="2" t="inlineStr">
@@ -38331,7 +38331,7 @@
       </c>
       <c r="B612" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C612" s="2" t="inlineStr">
@@ -40315,7 +40315,7 @@
       </c>
       <c r="B644" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C644" s="2" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -47445,7 +47445,7 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
@@ -51103,7 +51103,7 @@
       </c>
       <c r="B818" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C818" s="2" t="inlineStr">
@@ -51599,7 +51599,7 @@
       </c>
       <c r="B826" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C826" s="2" t="inlineStr">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
@@ -56001,7 +56001,7 @@
       </c>
       <c r="B897" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C897" s="2" t="inlineStr">
@@ -58171,7 +58171,7 @@
       </c>
       <c r="B932" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C932" s="2" t="inlineStr">
@@ -63193,7 +63193,7 @@
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
@@ -70261,7 +70261,7 @@
       </c>
       <c r="B1127" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1127" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -71687,7 +71687,7 @@
       </c>
       <c r="B1150" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1150" s="2" t="inlineStr">
@@ -74601,7 +74601,7 @@
       </c>
       <c r="B1197" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1197" s="2" t="inlineStr">
@@ -74663,7 +74663,7 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
@@ -74725,7 +74725,7 @@
       </c>
       <c r="B1199" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1199" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -75035,7 +75035,7 @@
       </c>
       <c r="B1204" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1204" s="2" t="inlineStr">
@@ -77701,7 +77701,7 @@
       </c>
       <c r="B1247" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1247" s="2" t="inlineStr">
@@ -78879,7 +78879,7 @@
       </c>
       <c r="B1266" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1266" s="2" t="inlineStr">
@@ -79375,7 +79375,7 @@
       </c>
       <c r="B1274" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1274" s="2" t="inlineStr">
@@ -79561,7 +79561,7 @@
       </c>
       <c r="B1277" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1277" s="2" t="inlineStr">
@@ -83467,7 +83467,7 @@
       </c>
       <c r="B1340" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1340" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -83963,7 +83963,7 @@
       </c>
       <c r="B1348" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1348" s="2" t="inlineStr">
@@ -84273,7 +84273,7 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
@@ -84707,7 +84707,7 @@
       </c>
       <c r="B1360" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1360" s="2" t="inlineStr">
@@ -84831,7 +84831,7 @@
       </c>
       <c r="B1362" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1362" s="2" t="inlineStr">
@@ -87931,7 +87931,7 @@
       </c>
       <c r="B1412" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1412" s="2" t="inlineStr">
@@ -88551,7 +88551,7 @@
       </c>
       <c r="B1422" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1422" s="2" t="inlineStr">
@@ -90225,7 +90225,7 @@
       </c>
       <c r="B1449" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1449" s="2" t="inlineStr">
@@ -90287,7 +90287,7 @@
       </c>
       <c r="B1450" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1450" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">
@@ -92643,7 +92643,7 @@
       </c>
       <c r="B1488" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1488" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
@@ -30767,7 +30767,7 @@
       </c>
       <c r="B490" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C490" s="2" t="inlineStr">
@@ -31573,7 +31573,7 @@
       </c>
       <c r="B503" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C503" s="2" t="inlineStr">
@@ -32937,7 +32937,7 @@
       </c>
       <c r="B525" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C525" s="2" t="inlineStr">
@@ -33185,7 +33185,7 @@
       </c>
       <c r="B529" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C529" s="2" t="inlineStr">
@@ -34921,7 +34921,7 @@
       </c>
       <c r="B557" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C557" s="2" t="inlineStr">
@@ -35541,7 +35541,7 @@
       </c>
       <c r="B567" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C567" s="2" t="inlineStr">
@@ -35665,7 +35665,7 @@
       </c>
       <c r="B569" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C569" s="2" t="inlineStr">
@@ -37897,7 +37897,7 @@
       </c>
       <c r="B605" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C605" s="2" t="inlineStr">
@@ -42485,7 +42485,7 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -47445,7 +47445,7 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
@@ -48933,7 +48933,7 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
@@ -51041,7 +51041,7 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
@@ -51103,7 +51103,7 @@
       </c>
       <c r="B818" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C818" s="2" t="inlineStr">
@@ -51413,7 +51413,7 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
@@ -51537,7 +51537,7 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
@@ -51599,7 +51599,7 @@
       </c>
       <c r="B826" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C826" s="2" t="inlineStr">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
@@ -56001,7 +56001,7 @@
       </c>
       <c r="B897" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C897" s="2" t="inlineStr">
@@ -58171,7 +58171,7 @@
       </c>
       <c r="B932" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C932" s="2" t="inlineStr">
@@ -66789,7 +66789,7 @@
       </c>
       <c r="B1071" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1071" s="2" t="inlineStr">
@@ -69641,7 +69641,7 @@
       </c>
       <c r="B1117" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1117" s="2" t="inlineStr">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
@@ -71687,7 +71687,7 @@
       </c>
       <c r="B1150" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1150" s="2" t="inlineStr">
@@ -71749,7 +71749,7 @@
       </c>
       <c r="B1151" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1151" s="2" t="inlineStr">
@@ -74663,7 +74663,7 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
@@ -74725,7 +74725,7 @@
       </c>
       <c r="B1199" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1199" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -77701,7 +77701,7 @@
       </c>
       <c r="B1247" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1247" s="2" t="inlineStr">
@@ -78879,7 +78879,7 @@
       </c>
       <c r="B1266" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1266" s="2" t="inlineStr">
@@ -79375,7 +79375,7 @@
       </c>
       <c r="B1274" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1274" s="2" t="inlineStr">
@@ -83467,7 +83467,7 @@
       </c>
       <c r="B1340" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1340" s="2" t="inlineStr">
@@ -83963,7 +83963,7 @@
       </c>
       <c r="B1348" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1348" s="2" t="inlineStr">
@@ -84397,7 +84397,7 @@
       </c>
       <c r="B1355" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1355" s="2" t="inlineStr">
@@ -84707,7 +84707,7 @@
       </c>
       <c r="B1360" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1360" s="2" t="inlineStr">
@@ -86629,7 +86629,7 @@
       </c>
       <c r="B1391" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1391" s="2" t="inlineStr">
@@ -87931,7 +87931,7 @@
       </c>
       <c r="B1412" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1412" s="2" t="inlineStr">
@@ -87993,7 +87993,7 @@
       </c>
       <c r="B1413" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1413" s="2" t="inlineStr">
@@ -88551,7 +88551,7 @@
       </c>
       <c r="B1422" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1422" s="2" t="inlineStr">
@@ -90225,7 +90225,7 @@
       </c>
       <c r="B1449" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1449" s="2" t="inlineStr">
@@ -90287,7 +90287,7 @@
       </c>
       <c r="B1450" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1450" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">
@@ -91961,7 +91961,7 @@
       </c>
       <c r="B1477" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1477" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
@@ -33185,7 +33185,7 @@
       </c>
       <c r="B529" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C529" s="2" t="inlineStr">
@@ -35665,7 +35665,7 @@
       </c>
       <c r="B569" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C569" s="2" t="inlineStr">
@@ -37897,7 +37897,7 @@
       </c>
       <c r="B605" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C605" s="2" t="inlineStr">
@@ -40315,7 +40315,7 @@
       </c>
       <c r="B644" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C644" s="2" t="inlineStr">
@@ -42485,7 +42485,7 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
@@ -42981,7 +42981,7 @@
       </c>
       <c r="B687" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C687" s="2" t="inlineStr">
@@ -48933,7 +48933,7 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
@@ -51041,7 +51041,7 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
@@ -51103,7 +51103,7 @@
       </c>
       <c r="B818" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C818" s="2" t="inlineStr">
@@ -51413,7 +51413,7 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
@@ -51537,7 +51537,7 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
@@ -51599,7 +51599,7 @@
       </c>
       <c r="B826" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C826" s="2" t="inlineStr">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -63193,7 +63193,7 @@
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
@@ -66789,7 +66789,7 @@
       </c>
       <c r="B1071" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1071" s="2" t="inlineStr">
@@ -69703,7 +69703,7 @@
       </c>
       <c r="B1118" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1118" s="2" t="inlineStr">
@@ -71191,7 +71191,7 @@
       </c>
       <c r="B1142" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1142" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -71749,7 +71749,7 @@
       </c>
       <c r="B1151" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1151" s="2" t="inlineStr">
@@ -74663,7 +74663,7 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -74973,7 +74973,7 @@
       </c>
       <c r="B1203" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1203" s="2" t="inlineStr">
@@ -76213,7 +76213,7 @@
       </c>
       <c r="B1223" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1223" s="2" t="inlineStr">
@@ -77577,7 +77577,7 @@
       </c>
       <c r="B1245" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1245" s="2" t="inlineStr">
@@ -77701,7 +77701,7 @@
       </c>
       <c r="B1247" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1247" s="2" t="inlineStr">
@@ -79375,7 +79375,7 @@
       </c>
       <c r="B1274" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1274" s="2" t="inlineStr">
@@ -79747,7 +79747,7 @@
       </c>
       <c r="B1280" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1280" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -84273,7 +84273,7 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84707,7 +84707,7 @@
       </c>
       <c r="B1360" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1360" s="2" t="inlineStr">
@@ -84831,7 +84831,7 @@
       </c>
       <c r="B1362" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1362" s="2" t="inlineStr">
@@ -84893,7 +84893,7 @@
       </c>
       <c r="B1363" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1363" s="2" t="inlineStr">
@@ -86629,7 +86629,7 @@
       </c>
       <c r="B1391" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1391" s="2" t="inlineStr">
@@ -87931,7 +87931,7 @@
       </c>
       <c r="B1412" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1412" s="2" t="inlineStr">
@@ -88489,7 +88489,7 @@
       </c>
       <c r="B1421" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1421" s="2" t="inlineStr">
@@ -90287,7 +90287,7 @@
       </c>
       <c r="B1450" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1450" s="2" t="inlineStr">
@@ -92643,7 +92643,7 @@
       </c>
       <c r="B1488" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1488" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -28411,7 +28411,7 @@
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
@@ -34425,7 +34425,7 @@
       </c>
       <c r="B549" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C549" s="2" t="inlineStr">
@@ -35665,7 +35665,7 @@
       </c>
       <c r="B569" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C569" s="2" t="inlineStr">
@@ -38331,7 +38331,7 @@
       </c>
       <c r="B612" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C612" s="2" t="inlineStr">
@@ -42485,7 +42485,7 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
@@ -42609,7 +42609,7 @@
       </c>
       <c r="B681" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C681" s="2" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
@@ -42919,7 +42919,7 @@
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
@@ -42981,7 +42981,7 @@
       </c>
       <c r="B687" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C687" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -47445,7 +47445,7 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
@@ -51103,7 +51103,7 @@
       </c>
       <c r="B818" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C818" s="2" t="inlineStr">
@@ -51413,7 +51413,7 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
@@ -56001,7 +56001,7 @@
       </c>
       <c r="B897" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C897" s="2" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="B971" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C971" s="2" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
@@ -71687,7 +71687,7 @@
       </c>
       <c r="B1150" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1150" s="2" t="inlineStr">
@@ -74663,7 +74663,7 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
@@ -74725,7 +74725,7 @@
       </c>
       <c r="B1199" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1199" s="2" t="inlineStr">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
@@ -74973,7 +74973,7 @@
       </c>
       <c r="B1203" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1203" s="2" t="inlineStr">
@@ -75035,7 +75035,7 @@
       </c>
       <c r="B1204" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1204" s="2" t="inlineStr">
@@ -76213,7 +76213,7 @@
       </c>
       <c r="B1223" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1223" s="2" t="inlineStr">
@@ -77577,7 +77577,7 @@
       </c>
       <c r="B1245" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1245" s="2" t="inlineStr">
@@ -77639,7 +77639,7 @@
       </c>
       <c r="B1246" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1246" s="2" t="inlineStr">
@@ -77701,7 +77701,7 @@
       </c>
       <c r="B1247" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1247" s="2" t="inlineStr">
@@ -78879,7 +78879,7 @@
       </c>
       <c r="B1266" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1266" s="2" t="inlineStr">
@@ -79375,7 +79375,7 @@
       </c>
       <c r="B1274" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1274" s="2" t="inlineStr">
@@ -83591,7 +83591,7 @@
       </c>
       <c r="B1342" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1342" s="2" t="inlineStr">
@@ -83653,7 +83653,7 @@
       </c>
       <c r="B1343" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1343" s="2" t="inlineStr">
@@ -83963,7 +83963,7 @@
       </c>
       <c r="B1348" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1348" s="2" t="inlineStr">
@@ -84087,7 +84087,7 @@
       </c>
       <c r="B1350" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1350" s="2" t="inlineStr">
@@ -84273,7 +84273,7 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
@@ -84707,7 +84707,7 @@
       </c>
       <c r="B1360" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1360" s="2" t="inlineStr">
@@ -84893,7 +84893,7 @@
       </c>
       <c r="B1363" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1363" s="2" t="inlineStr">
@@ -87931,7 +87931,7 @@
       </c>
       <c r="B1412" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1412" s="2" t="inlineStr">
@@ -88489,7 +88489,7 @@
       </c>
       <c r="B1421" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1421" s="2" t="inlineStr">
@@ -88551,7 +88551,7 @@
       </c>
       <c r="B1422" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1422" s="2" t="inlineStr">
@@ -90225,7 +90225,7 @@
       </c>
       <c r="B1449" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1449" s="2" t="inlineStr">
@@ -90287,7 +90287,7 @@
       </c>
       <c r="B1450" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1450" s="2" t="inlineStr">
@@ -90349,7 +90349,7 @@
       </c>
       <c r="B1451" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1451" s="2" t="inlineStr">
@@ -91961,7 +91961,7 @@
       </c>
       <c r="B1477" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1477" s="2" t="inlineStr">
@@ -92643,7 +92643,7 @@
       </c>
       <c r="B1488" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1488" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -31821,7 +31821,7 @@
       </c>
       <c r="B507" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C507" s="2" t="inlineStr">
@@ -37897,7 +37897,7 @@
       </c>
       <c r="B605" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C605" s="2" t="inlineStr">
@@ -38331,7 +38331,7 @@
       </c>
       <c r="B612" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C612" s="2" t="inlineStr">
@@ -40315,7 +40315,7 @@
       </c>
       <c r="B644" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C644" s="2" t="inlineStr">
@@ -42485,7 +42485,7 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
@@ -47445,7 +47445,7 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
@@ -51041,7 +51041,7 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
@@ -51661,7 +51661,7 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -56001,7 +56001,7 @@
       </c>
       <c r="B897" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C897" s="2" t="inlineStr">
@@ -58233,7 +58233,7 @@
       </c>
       <c r="B933" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C933" s="2" t="inlineStr">
@@ -69579,7 +69579,7 @@
       </c>
       <c r="B1116" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1116" s="2" t="inlineStr">
@@ -69765,7 +69765,7 @@
       </c>
       <c r="B1119" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1119" s="2" t="inlineStr">
@@ -70137,7 +70137,7 @@
       </c>
       <c r="B1125" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1125" s="2" t="inlineStr">
@@ -70385,7 +70385,7 @@
       </c>
       <c r="B1129" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1129" s="2" t="inlineStr">
@@ -71315,7 +71315,7 @@
       </c>
       <c r="B1144" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1144" s="2" t="inlineStr">
@@ -71687,7 +71687,7 @@
       </c>
       <c r="B1150" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1150" s="2" t="inlineStr">
@@ -73733,7 +73733,7 @@
       </c>
       <c r="B1183" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1183" s="2" t="inlineStr">
@@ -74911,7 +74911,7 @@
       </c>
       <c r="B1202" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1202" s="2" t="inlineStr">
@@ -76337,7 +76337,7 @@
       </c>
       <c r="B1225" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1225" s="2" t="inlineStr">
@@ -77701,7 +77701,7 @@
       </c>
       <c r="B1247" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1247" s="2" t="inlineStr">
@@ -77763,7 +77763,7 @@
       </c>
       <c r="B1248" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1248" s="2" t="inlineStr">
@@ -79003,7 +79003,7 @@
       </c>
       <c r="B1268" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1268" s="2" t="inlineStr">
@@ -79685,7 +79685,7 @@
       </c>
       <c r="B1279" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1279" s="2" t="inlineStr">
@@ -79871,7 +79871,7 @@
       </c>
       <c r="B1282" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1282" s="2" t="inlineStr">
@@ -83715,7 +83715,7 @@
       </c>
       <c r="B1344" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1344" s="2" t="inlineStr">
@@ -84087,7 +84087,7 @@
       </c>
       <c r="B1350" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1350" s="2" t="inlineStr">
@@ -84397,7 +84397,7 @@
       </c>
       <c r="B1355" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1355" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84955,7 +84955,7 @@
       </c>
       <c r="B1364" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1364" s="2" t="inlineStr">
@@ -86753,7 +86753,7 @@
       </c>
       <c r="B1393" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1393" s="2" t="inlineStr">
@@ -88613,7 +88613,7 @@
       </c>
       <c r="B1423" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1423" s="2" t="inlineStr">
@@ -88675,7 +88675,7 @@
       </c>
       <c r="B1424" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1424" s="2" t="inlineStr">
@@ -90349,7 +90349,7 @@
       </c>
       <c r="B1451" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1451" s="2" t="inlineStr">
@@ -92767,7 +92767,7 @@
       </c>
       <c r="B1490" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1490" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analítico" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analítico'!$A$1:$L$1503</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analítico'!$A$1:$L$1505</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1503"/>
+  <dimension ref="A1:L1505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7455,7 +7455,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -29341,7 +29341,7 @@
       </c>
       <c r="B467" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C467" s="2" t="inlineStr">
@@ -31945,7 +31945,7 @@
       </c>
       <c r="B509" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C509" s="2" t="inlineStr">
@@ -35231,7 +35231,7 @@
       </c>
       <c r="B562" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C562" s="2" t="inlineStr">
@@ -35851,7 +35851,7 @@
       </c>
       <c r="B572" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C572" s="2" t="inlineStr">
@@ -38207,7 +38207,7 @@
       </c>
       <c r="B610" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C610" s="2" t="inlineStr">
@@ -40625,7 +40625,7 @@
       </c>
       <c r="B649" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C649" s="2" t="inlineStr">
@@ -43105,7 +43105,7 @@
       </c>
       <c r="B689" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C689" s="2" t="inlineStr">
@@ -44097,7 +44097,7 @@
       </c>
       <c r="B705" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C705" s="2" t="inlineStr">
@@ -44717,7 +44717,7 @@
       </c>
       <c r="B715" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C715" s="2" t="inlineStr">
@@ -47755,7 +47755,7 @@
       </c>
       <c r="B764" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C764" s="2" t="inlineStr">
@@ -49243,7 +49243,7 @@
       </c>
       <c r="B788" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C788" s="2" t="inlineStr">
@@ -51909,7 +51909,7 @@
       </c>
       <c r="B831" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C831" s="2" t="inlineStr">
@@ -52033,7 +52033,7 @@
       </c>
       <c r="B833" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C833" s="2" t="inlineStr">
@@ -58543,7 +58543,7 @@
       </c>
       <c r="B938" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C938" s="2" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="B971" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C971" s="2" t="inlineStr">
@@ -60713,7 +60713,7 @@
       </c>
       <c r="B973" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C973" s="2" t="inlineStr">
@@ -67223,7 +67223,7 @@
       </c>
       <c r="B1078" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1078" s="2" t="inlineStr">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
@@ -70199,7 +70199,7 @@
       </c>
       <c r="B1126" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1126" s="2" t="inlineStr">
@@ -70261,7 +70261,7 @@
       </c>
       <c r="B1127" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1127" s="2" t="inlineStr">
@@ -71749,7 +71749,7 @@
       </c>
       <c r="B1151" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1151" s="2" t="inlineStr">
@@ -72121,7 +72121,7 @@
       </c>
       <c r="B1157" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1157" s="2" t="inlineStr">
@@ -72245,7 +72245,7 @@
       </c>
       <c r="B1159" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1159" s="2" t="inlineStr">
@@ -75283,7 +75283,7 @@
       </c>
       <c r="B1208" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1208" s="2" t="inlineStr">
@@ -75345,7 +75345,7 @@
       </c>
       <c r="B1209" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1209" s="2" t="inlineStr">
@@ -76771,7 +76771,7 @@
       </c>
       <c r="B1232" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1232" s="2" t="inlineStr">
@@ -78135,7 +78135,7 @@
       </c>
       <c r="B1254" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1254" s="2" t="inlineStr">
@@ -78197,7 +78197,7 @@
       </c>
       <c r="B1255" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1255" s="2" t="inlineStr">
@@ -79127,7 +79127,7 @@
       </c>
       <c r="B1270" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1270" s="2" t="inlineStr">
@@ -79189,7 +79189,7 @@
       </c>
       <c r="B1271" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1271" s="2" t="inlineStr">
@@ -80305,27 +80305,27 @@
       </c>
       <c r="B1289" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1289" s="2" t="inlineStr">
         <is>
-          <t>556427</t>
+          <t>567167</t>
         </is>
       </c>
       <c r="D1289" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="E1289" s="2" t="inlineStr">
         <is>
-          <t>A8174</t>
+          <t>A9323</t>
         </is>
       </c>
       <c r="F1289" s="2" t="inlineStr">
         <is>
-          <t>00019200000012726788</t>
+          <t>00019200000014266067</t>
         </is>
       </c>
       <c r="G1289" s="2" t="inlineStr">
@@ -80335,12 +80335,12 @@
       </c>
       <c r="H1289" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026 08:20</t>
+          <t>13/09/2026 00:30</t>
         </is>
       </c>
       <c r="I1289" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026 13:30</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J1289" s="2" t="inlineStr">
@@ -80350,7 +80350,7 @@
       </c>
       <c r="K1289" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13/09/2026 00:30</t>
         </is>
       </c>
       <c r="L1289" s="2" t="inlineStr">
@@ -80367,27 +80367,27 @@
       </c>
       <c r="B1290" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1290" s="2" t="inlineStr">
         <is>
-          <t>556427</t>
+          <t>567167</t>
         </is>
       </c>
       <c r="D1290" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="E1290" s="2" t="inlineStr">
         <is>
-          <t>A4607</t>
+          <t>A5077</t>
         </is>
       </c>
       <c r="F1290" s="2" t="inlineStr">
         <is>
-          <t>00019200000012901067</t>
+          <t>00019200000014266075</t>
         </is>
       </c>
       <c r="G1290" s="2" t="inlineStr">
@@ -80397,12 +80397,12 @@
       </c>
       <c r="H1290" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026 08:20</t>
+          <t>13/09/2026 00:30</t>
         </is>
       </c>
       <c r="I1290" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026 13:30</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J1290" s="2" t="inlineStr">
@@ -80412,7 +80412,7 @@
       </c>
       <c r="K1290" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13/09/2026 00:30</t>
         </is>
       </c>
       <c r="L1290" s="2" t="inlineStr">
@@ -80434,7 +80434,7 @@
       </c>
       <c r="C1291" s="2" t="inlineStr">
         <is>
-          <t>559096</t>
+          <t>556427</t>
         </is>
       </c>
       <c r="D1291" s="2" t="inlineStr">
@@ -80444,12 +80444,12 @@
       </c>
       <c r="E1291" s="2" t="inlineStr">
         <is>
-          <t>A6393</t>
+          <t>A8174</t>
         </is>
       </c>
       <c r="F1291" s="2" t="inlineStr">
         <is>
-          <t>00019200000013248332</t>
+          <t>00019200000012726788</t>
         </is>
       </c>
       <c r="G1291" s="2" t="inlineStr">
@@ -80459,12 +80459,12 @@
       </c>
       <c r="H1291" s="2" t="inlineStr">
         <is>
-          <t>29/06/2026 05:40</t>
+          <t>10/06/2026 08:20</t>
         </is>
       </c>
       <c r="I1291" s="2" t="inlineStr">
         <is>
-          <t>30/06/2026 15:00</t>
+          <t>11/06/2026 13:30</t>
         </is>
       </c>
       <c r="J1291" s="2" t="inlineStr">
@@ -80474,12 +80474,12 @@
       </c>
       <c r="K1291" s="2" t="inlineStr">
         <is>
-          <t>29/06/2026 05:40</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L1291" s="2" t="inlineStr">
         <is>
-          <t>30/06/2026 15:00</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -80491,12 +80491,12 @@
       </c>
       <c r="B1292" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1292" s="2" t="inlineStr">
         <is>
-          <t>559925</t>
+          <t>556427</t>
         </is>
       </c>
       <c r="D1292" s="2" t="inlineStr">
@@ -80506,12 +80506,12 @@
       </c>
       <c r="E1292" s="2" t="inlineStr">
         <is>
-          <t>A7594</t>
+          <t>A4607</t>
         </is>
       </c>
       <c r="F1292" s="2" t="inlineStr">
         <is>
-          <t>00019200000013419137</t>
+          <t>00019200000012901067</t>
         </is>
       </c>
       <c r="G1292" s="2" t="inlineStr">
@@ -80521,12 +80521,12 @@
       </c>
       <c r="H1292" s="2" t="inlineStr">
         <is>
-          <t>07/07/2026 06:51</t>
+          <t>10/06/2026 08:20</t>
         </is>
       </c>
       <c r="I1292" s="2" t="inlineStr">
         <is>
-          <t>09/07/2026 13:09</t>
+          <t>11/06/2026 13:30</t>
         </is>
       </c>
       <c r="J1292" s="2" t="inlineStr">
@@ -80536,12 +80536,12 @@
       </c>
       <c r="K1292" s="2" t="inlineStr">
         <is>
-          <t>07/07/2026 06:51</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L1292" s="2" t="inlineStr">
         <is>
-          <t>09/07/2026 13:09</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -80553,12 +80553,12 @@
       </c>
       <c r="B1293" s="2" t="inlineStr">
         <is>
-          <t>-90 C a -60 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1293" s="2" t="inlineStr">
         <is>
-          <t>560574</t>
+          <t>559096</t>
         </is>
       </c>
       <c r="D1293" s="2" t="inlineStr">
@@ -80568,12 +80568,12 @@
       </c>
       <c r="E1293" s="2" t="inlineStr">
         <is>
-          <t>AS-0499</t>
+          <t>A6393</t>
         </is>
       </c>
       <c r="F1293" s="2" t="inlineStr">
         <is>
-          <t>00019200000013463969</t>
+          <t>00019200000013248332</t>
         </is>
       </c>
       <c r="G1293" s="2" t="inlineStr">
@@ -80583,12 +80583,12 @@
       </c>
       <c r="H1293" s="2" t="inlineStr">
         <is>
-          <t>21/07/2026 22:28</t>
+          <t>29/06/2026 05:40</t>
         </is>
       </c>
       <c r="I1293" s="2" t="inlineStr">
         <is>
-          <t>23/07/2026 15:00</t>
+          <t>30/06/2026 15:00</t>
         </is>
       </c>
       <c r="J1293" s="2" t="inlineStr">
@@ -80598,12 +80598,12 @@
       </c>
       <c r="K1293" s="2" t="inlineStr">
         <is>
-          <t>21/07/2026 22:28</t>
+          <t>29/06/2026 05:40</t>
         </is>
       </c>
       <c r="L1293" s="2" t="inlineStr">
         <is>
-          <t>23/07/2026 13:15</t>
+          <t>30/06/2026 15:00</t>
         </is>
       </c>
     </row>
@@ -80615,12 +80615,12 @@
       </c>
       <c r="B1294" s="2" t="inlineStr">
         <is>
-          <t>-90 C a -60 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1294" s="2" t="inlineStr">
         <is>
-          <t>560574</t>
+          <t>559925</t>
         </is>
       </c>
       <c r="D1294" s="2" t="inlineStr">
@@ -80630,12 +80630,12 @@
       </c>
       <c r="E1294" s="2" t="inlineStr">
         <is>
-          <t>AS-0683</t>
+          <t>A7594</t>
         </is>
       </c>
       <c r="F1294" s="2" t="inlineStr">
         <is>
-          <t>00019200000013463977</t>
+          <t>00019200000013419137</t>
         </is>
       </c>
       <c r="G1294" s="2" t="inlineStr">
@@ -80645,12 +80645,12 @@
       </c>
       <c r="H1294" s="2" t="inlineStr">
         <is>
-          <t>21/07/2026 22:28</t>
+          <t>07/07/2026 06:51</t>
         </is>
       </c>
       <c r="I1294" s="2" t="inlineStr">
         <is>
-          <t>23/07/2026 15:00</t>
+          <t>09/07/2026 13:09</t>
         </is>
       </c>
       <c r="J1294" s="2" t="inlineStr">
@@ -80660,12 +80660,12 @@
       </c>
       <c r="K1294" s="2" t="inlineStr">
         <is>
-          <t>21/07/2026 22:28</t>
+          <t>07/07/2026 06:51</t>
         </is>
       </c>
       <c r="L1294" s="2" t="inlineStr">
         <is>
-          <t>23/07/2026 13:15</t>
+          <t>09/07/2026 13:09</t>
         </is>
       </c>
     </row>
@@ -80692,12 +80692,12 @@
       </c>
       <c r="E1295" s="2" t="inlineStr">
         <is>
-          <t>AS-0426</t>
+          <t>AS-0499</t>
         </is>
       </c>
       <c r="F1295" s="2" t="inlineStr">
         <is>
-          <t>00019200000013463985</t>
+          <t>00019200000013463969</t>
         </is>
       </c>
       <c r="G1295" s="2" t="inlineStr">
@@ -80754,12 +80754,12 @@
       </c>
       <c r="E1296" s="2" t="inlineStr">
         <is>
-          <t>AS-0702</t>
+          <t>AS-0683</t>
         </is>
       </c>
       <c r="F1296" s="2" t="inlineStr">
         <is>
-          <t>00019200000013463993</t>
+          <t>00019200000013463977</t>
         </is>
       </c>
       <c r="G1296" s="2" t="inlineStr">
@@ -80816,12 +80816,12 @@
       </c>
       <c r="E1297" s="2" t="inlineStr">
         <is>
-          <t>AS-0869</t>
+          <t>AS-0426</t>
         </is>
       </c>
       <c r="F1297" s="2" t="inlineStr">
         <is>
-          <t>00019200000013464019</t>
+          <t>00019200000013463985</t>
         </is>
       </c>
       <c r="G1297" s="2" t="inlineStr">
@@ -80878,12 +80878,12 @@
       </c>
       <c r="E1298" s="2" t="inlineStr">
         <is>
-          <t>AS-0837</t>
+          <t>AS-0702</t>
         </is>
       </c>
       <c r="F1298" s="2" t="inlineStr">
         <is>
-          <t>00019200000013464027</t>
+          <t>00019200000013463993</t>
         </is>
       </c>
       <c r="G1298" s="2" t="inlineStr">
@@ -80940,12 +80940,12 @@
       </c>
       <c r="E1299" s="2" t="inlineStr">
         <is>
-          <t>AS-0201</t>
+          <t>AS-0869</t>
         </is>
       </c>
       <c r="F1299" s="2" t="inlineStr">
         <is>
-          <t>00019200000013464035</t>
+          <t>00019200000013464019</t>
         </is>
       </c>
       <c r="G1299" s="2" t="inlineStr">
@@ -80975,7 +80975,7 @@
       </c>
       <c r="L1299" s="2" t="inlineStr">
         <is>
-          <t>23/07/2026 15:00</t>
+          <t>23/07/2026 13:15</t>
         </is>
       </c>
     </row>
@@ -81002,12 +81002,12 @@
       </c>
       <c r="E1300" s="2" t="inlineStr">
         <is>
-          <t>AS-0487</t>
+          <t>AS-0837</t>
         </is>
       </c>
       <c r="F1300" s="2" t="inlineStr">
         <is>
-          <t>00019200000013464043</t>
+          <t>00019200000013464027</t>
         </is>
       </c>
       <c r="G1300" s="2" t="inlineStr">
@@ -81064,12 +81064,12 @@
       </c>
       <c r="E1301" s="2" t="inlineStr">
         <is>
-          <t>AS-0356</t>
+          <t>AS-0201</t>
         </is>
       </c>
       <c r="F1301" s="2" t="inlineStr">
         <is>
-          <t>00019200000013464051</t>
+          <t>00019200000013464035</t>
         </is>
       </c>
       <c r="G1301" s="2" t="inlineStr">
@@ -81126,12 +81126,12 @@
       </c>
       <c r="E1302" s="2" t="inlineStr">
         <is>
-          <t>AS-0414</t>
+          <t>AS-0487</t>
         </is>
       </c>
       <c r="F1302" s="2" t="inlineStr">
         <is>
-          <t>00019200000013464078</t>
+          <t>00019200000013464043</t>
         </is>
       </c>
       <c r="G1302" s="2" t="inlineStr">
@@ -81188,12 +81188,12 @@
       </c>
       <c r="E1303" s="2" t="inlineStr">
         <is>
-          <t>AS-0078</t>
+          <t>AS-0356</t>
         </is>
       </c>
       <c r="F1303" s="2" t="inlineStr">
         <is>
-          <t>00019200000013464086</t>
+          <t>00019200000013464051</t>
         </is>
       </c>
       <c r="G1303" s="2" t="inlineStr">
@@ -81250,12 +81250,12 @@
       </c>
       <c r="E1304" s="2" t="inlineStr">
         <is>
-          <t>AS-0019</t>
+          <t>AS-0414</t>
         </is>
       </c>
       <c r="F1304" s="2" t="inlineStr">
         <is>
-          <t>00019200000013464094</t>
+          <t>00019200000013464078</t>
         </is>
       </c>
       <c r="G1304" s="2" t="inlineStr">
@@ -81285,7 +81285,7 @@
       </c>
       <c r="L1304" s="2" t="inlineStr">
         <is>
-          <t>23/07/2026 15:00</t>
+          <t>23/07/2026 13:15</t>
         </is>
       </c>
     </row>
@@ -81312,12 +81312,12 @@
       </c>
       <c r="E1305" s="2" t="inlineStr">
         <is>
-          <t>AS-0252</t>
+          <t>AS-0078</t>
         </is>
       </c>
       <c r="F1305" s="2" t="inlineStr">
         <is>
-          <t>00019200000013464108</t>
+          <t>00019200000013464086</t>
         </is>
       </c>
       <c r="G1305" s="2" t="inlineStr">
@@ -81374,12 +81374,12 @@
       </c>
       <c r="E1306" s="2" t="inlineStr">
         <is>
-          <t>AS-0160</t>
+          <t>AS-0019</t>
         </is>
       </c>
       <c r="F1306" s="2" t="inlineStr">
         <is>
-          <t>00019200000013464116</t>
+          <t>00019200000013464094</t>
         </is>
       </c>
       <c r="G1306" s="2" t="inlineStr">
@@ -81436,12 +81436,12 @@
       </c>
       <c r="E1307" s="2" t="inlineStr">
         <is>
-          <t>AS-0513</t>
+          <t>AS-0252</t>
         </is>
       </c>
       <c r="F1307" s="2" t="inlineStr">
         <is>
-          <t>00019200000013464124</t>
+          <t>00019200000013464108</t>
         </is>
       </c>
       <c r="G1307" s="2" t="inlineStr">
@@ -81471,7 +81471,7 @@
       </c>
       <c r="L1307" s="2" t="inlineStr">
         <is>
-          <t>23/07/2026 13:15</t>
+          <t>23/07/2026 15:00</t>
         </is>
       </c>
     </row>
@@ -81498,12 +81498,12 @@
       </c>
       <c r="E1308" s="2" t="inlineStr">
         <is>
-          <t>AS-0234</t>
+          <t>AS-0160</t>
         </is>
       </c>
       <c r="F1308" s="2" t="inlineStr">
         <is>
-          <t>00019200000013464132</t>
+          <t>00019200000013464116</t>
         </is>
       </c>
       <c r="G1308" s="2" t="inlineStr">
@@ -81560,12 +81560,12 @@
       </c>
       <c r="E1309" s="2" t="inlineStr">
         <is>
-          <t>AS-0494</t>
+          <t>AS-0513</t>
         </is>
       </c>
       <c r="F1309" s="2" t="inlineStr">
         <is>
-          <t>00019200000013464140</t>
+          <t>00019200000013464124</t>
         </is>
       </c>
       <c r="G1309" s="2" t="inlineStr">
@@ -81595,7 +81595,7 @@
       </c>
       <c r="L1309" s="2" t="inlineStr">
         <is>
-          <t>23/07/2026 15:00</t>
+          <t>23/07/2026 13:15</t>
         </is>
       </c>
     </row>
@@ -81622,12 +81622,12 @@
       </c>
       <c r="E1310" s="2" t="inlineStr">
         <is>
-          <t>AS-0850</t>
+          <t>AS-0234</t>
         </is>
       </c>
       <c r="F1310" s="2" t="inlineStr">
         <is>
-          <t>00019200000013464159</t>
+          <t>00019200000013464132</t>
         </is>
       </c>
       <c r="G1310" s="2" t="inlineStr">
@@ -81684,12 +81684,12 @@
       </c>
       <c r="E1311" s="2" t="inlineStr">
         <is>
-          <t>AS-0107</t>
+          <t>AS-0494</t>
         </is>
       </c>
       <c r="F1311" s="2" t="inlineStr">
         <is>
-          <t>00019200000013464167</t>
+          <t>00019200000013464140</t>
         </is>
       </c>
       <c r="G1311" s="2" t="inlineStr">
@@ -81746,12 +81746,12 @@
       </c>
       <c r="E1312" s="2" t="inlineStr">
         <is>
-          <t>AS-0845</t>
+          <t>AS-0850</t>
         </is>
       </c>
       <c r="F1312" s="2" t="inlineStr">
         <is>
-          <t>00019200000013464175</t>
+          <t>00019200000013464159</t>
         </is>
       </c>
       <c r="G1312" s="2" t="inlineStr">
@@ -81808,12 +81808,12 @@
       </c>
       <c r="E1313" s="2" t="inlineStr">
         <is>
-          <t>AS-0511</t>
+          <t>AS-0107</t>
         </is>
       </c>
       <c r="F1313" s="2" t="inlineStr">
         <is>
-          <t>00019200000013464183</t>
+          <t>00019200000013464167</t>
         </is>
       </c>
       <c r="G1313" s="2" t="inlineStr">
@@ -81870,12 +81870,12 @@
       </c>
       <c r="E1314" s="2" t="inlineStr">
         <is>
-          <t>AS-0363</t>
+          <t>AS-0845</t>
         </is>
       </c>
       <c r="F1314" s="2" t="inlineStr">
         <is>
-          <t>00019200000013464191</t>
+          <t>00019200000013464175</t>
         </is>
       </c>
       <c r="G1314" s="2" t="inlineStr">
@@ -81905,7 +81905,7 @@
       </c>
       <c r="L1314" s="2" t="inlineStr">
         <is>
-          <t>23/07/2026 13:15</t>
+          <t>23/07/2026 15:00</t>
         </is>
       </c>
     </row>
@@ -81932,12 +81932,12 @@
       </c>
       <c r="E1315" s="2" t="inlineStr">
         <is>
-          <t>AS-0269</t>
+          <t>AS-0511</t>
         </is>
       </c>
       <c r="F1315" s="2" t="inlineStr">
         <is>
-          <t>00019200000013464205</t>
+          <t>00019200000013464183</t>
         </is>
       </c>
       <c r="G1315" s="2" t="inlineStr">
@@ -81967,7 +81967,7 @@
       </c>
       <c r="L1315" s="2" t="inlineStr">
         <is>
-          <t>23/07/2026 13:15</t>
+          <t>23/07/2026 15:00</t>
         </is>
       </c>
     </row>
@@ -81994,12 +81994,12 @@
       </c>
       <c r="E1316" s="2" t="inlineStr">
         <is>
-          <t>AS-0643</t>
+          <t>AS-0363</t>
         </is>
       </c>
       <c r="F1316" s="2" t="inlineStr">
         <is>
-          <t>00019200000013464213</t>
+          <t>00019200000013464191</t>
         </is>
       </c>
       <c r="G1316" s="2" t="inlineStr">
@@ -82056,12 +82056,12 @@
       </c>
       <c r="E1317" s="2" t="inlineStr">
         <is>
-          <t>AS-0263</t>
+          <t>AS-0269</t>
         </is>
       </c>
       <c r="F1317" s="2" t="inlineStr">
         <is>
-          <t>00019200000013464221</t>
+          <t>00019200000013464205</t>
         </is>
       </c>
       <c r="G1317" s="2" t="inlineStr">
@@ -82103,12 +82103,12 @@
       </c>
       <c r="B1318" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-90 C a -60 C</t>
         </is>
       </c>
       <c r="C1318" s="2" t="inlineStr">
         <is>
-          <t>560688</t>
+          <t>560574</t>
         </is>
       </c>
       <c r="D1318" s="2" t="inlineStr">
@@ -82118,42 +82118,42 @@
       </c>
       <c r="E1318" s="2" t="inlineStr">
         <is>
-          <t>A5913</t>
+          <t>AS-0643</t>
         </is>
       </c>
       <c r="F1318" s="2" t="inlineStr">
         <is>
-          <t>00019200000013694359</t>
+          <t>00019200000013464213</t>
         </is>
       </c>
       <c r="G1318" s="2" t="inlineStr">
         <is>
-          <t>Rodoviário</t>
+          <t>MultiModal</t>
         </is>
       </c>
       <c r="H1318" s="2" t="inlineStr">
         <is>
-          <t>27/07/2026 06:04</t>
+          <t>21/07/2026 22:28</t>
         </is>
       </c>
       <c r="I1318" s="2" t="inlineStr">
         <is>
-          <t>29/07/2026 10:36</t>
+          <t>23/07/2026 15:00</t>
         </is>
       </c>
       <c r="J1318" s="2" t="inlineStr">
         <is>
-          <t>29/07/2026 09:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K1318" s="2" t="inlineStr">
         <is>
-          <t>27/07/2026 06:04</t>
+          <t>21/07/2026 22:28</t>
         </is>
       </c>
       <c r="L1318" s="2" t="inlineStr">
         <is>
-          <t>29/07/2026 10:23</t>
+          <t>23/07/2026 13:15</t>
         </is>
       </c>
     </row>
@@ -82170,7 +82170,7 @@
       </c>
       <c r="C1319" s="2" t="inlineStr">
         <is>
-          <t>561641</t>
+          <t>560574</t>
         </is>
       </c>
       <c r="D1319" s="2" t="inlineStr">
@@ -82180,12 +82180,12 @@
       </c>
       <c r="E1319" s="2" t="inlineStr">
         <is>
-          <t>869170034872433</t>
+          <t>AS-0263</t>
         </is>
       </c>
       <c r="F1319" s="2" t="inlineStr">
         <is>
-          <t>00019200000013789848</t>
+          <t>00019200000013464221</t>
         </is>
       </c>
       <c r="G1319" s="2" t="inlineStr">
@@ -82195,12 +82195,12 @@
       </c>
       <c r="H1319" s="2" t="inlineStr">
         <is>
-          <t>03/08/2026 04:37</t>
+          <t>21/07/2026 22:28</t>
         </is>
       </c>
       <c r="I1319" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026 11:10</t>
+          <t>23/07/2026 15:00</t>
         </is>
       </c>
       <c r="J1319" s="2" t="inlineStr">
@@ -82210,12 +82210,12 @@
       </c>
       <c r="K1319" s="2" t="inlineStr">
         <is>
-          <t>03/08/2026 04:37</t>
+          <t>21/07/2026 22:28</t>
         </is>
       </c>
       <c r="L1319" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026 11:10</t>
+          <t>23/07/2026 13:15</t>
         </is>
       </c>
     </row>
@@ -82227,12 +82227,12 @@
       </c>
       <c r="B1320" s="2" t="inlineStr">
         <is>
-          <t>-90 C a -60 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1320" s="2" t="inlineStr">
         <is>
-          <t>561641</t>
+          <t>560688</t>
         </is>
       </c>
       <c r="D1320" s="2" t="inlineStr">
@@ -82242,42 +82242,42 @@
       </c>
       <c r="E1320" s="2" t="inlineStr">
         <is>
-          <t>869170035510362</t>
+          <t>A5913</t>
         </is>
       </c>
       <c r="F1320" s="2" t="inlineStr">
         <is>
-          <t>00019200000013836790</t>
+          <t>00019200000013694359</t>
         </is>
       </c>
       <c r="G1320" s="2" t="inlineStr">
         <is>
-          <t>MultiModal</t>
+          <t>Rodoviário</t>
         </is>
       </c>
       <c r="H1320" s="2" t="inlineStr">
         <is>
-          <t>03/08/2026 04:37</t>
+          <t>27/07/2026 06:04</t>
         </is>
       </c>
       <c r="I1320" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026 11:10</t>
+          <t>29/07/2026 10:36</t>
         </is>
       </c>
       <c r="J1320" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>29/07/2026 09:00</t>
         </is>
       </c>
       <c r="K1320" s="2" t="inlineStr">
         <is>
-          <t>03/08/2026 04:37</t>
+          <t>27/07/2026 06:04</t>
         </is>
       </c>
       <c r="L1320" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026 11:10</t>
+          <t>29/07/2026 10:23</t>
         </is>
       </c>
     </row>
@@ -82304,12 +82304,12 @@
       </c>
       <c r="E1321" s="2" t="inlineStr">
         <is>
-          <t>869170035513457</t>
+          <t>869170034872433</t>
         </is>
       </c>
       <c r="F1321" s="2" t="inlineStr">
         <is>
-          <t>00019200000013836803</t>
+          <t>00019200000013789848</t>
         </is>
       </c>
       <c r="G1321" s="2" t="inlineStr">
@@ -82366,12 +82366,12 @@
       </c>
       <c r="E1322" s="2" t="inlineStr">
         <is>
-          <t>869170034888512</t>
+          <t>869170035510362</t>
         </is>
       </c>
       <c r="F1322" s="2" t="inlineStr">
         <is>
-          <t>00019200000013836811</t>
+          <t>00019200000013836790</t>
         </is>
       </c>
       <c r="G1322" s="2" t="inlineStr">
@@ -82396,7 +82396,7 @@
       </c>
       <c r="K1322" s="2" t="inlineStr">
         <is>
-          <t>03/08/2026 05:05</t>
+          <t>03/08/2026 04:37</t>
         </is>
       </c>
       <c r="L1322" s="2" t="inlineStr">
@@ -82428,12 +82428,12 @@
       </c>
       <c r="E1323" s="2" t="inlineStr">
         <is>
-          <t>869170035512301</t>
+          <t>869170035513457</t>
         </is>
       </c>
       <c r="F1323" s="2" t="inlineStr">
         <is>
-          <t>00019200000013836820</t>
+          <t>00019200000013836803</t>
         </is>
       </c>
       <c r="G1323" s="2" t="inlineStr">
@@ -82458,7 +82458,7 @@
       </c>
       <c r="K1323" s="2" t="inlineStr">
         <is>
-          <t>03/08/2026 05:05</t>
+          <t>03/08/2026 04:37</t>
         </is>
       </c>
       <c r="L1323" s="2" t="inlineStr">
@@ -82490,12 +82490,12 @@
       </c>
       <c r="E1324" s="2" t="inlineStr">
         <is>
-          <t>869170035514208</t>
+          <t>869170034888512</t>
         </is>
       </c>
       <c r="F1324" s="2" t="inlineStr">
         <is>
-          <t>00019200000013836838</t>
+          <t>00019200000013836811</t>
         </is>
       </c>
       <c r="G1324" s="2" t="inlineStr">
@@ -82552,12 +82552,12 @@
       </c>
       <c r="E1325" s="2" t="inlineStr">
         <is>
-          <t>869170035502492</t>
+          <t>869170035512301</t>
         </is>
       </c>
       <c r="F1325" s="2" t="inlineStr">
         <is>
-          <t>00019200000013836846</t>
+          <t>00019200000013836820</t>
         </is>
       </c>
       <c r="G1325" s="2" t="inlineStr">
@@ -82614,12 +82614,12 @@
       </c>
       <c r="E1326" s="2" t="inlineStr">
         <is>
-          <t>869170035511394</t>
+          <t>869170035514208</t>
         </is>
       </c>
       <c r="F1326" s="2" t="inlineStr">
         <is>
-          <t>00019200000013836854</t>
+          <t>00019200000013836838</t>
         </is>
       </c>
       <c r="G1326" s="2" t="inlineStr">
@@ -82644,7 +82644,7 @@
       </c>
       <c r="K1326" s="2" t="inlineStr">
         <is>
-          <t>03/08/2026 04:37</t>
+          <t>03/08/2026 05:05</t>
         </is>
       </c>
       <c r="L1326" s="2" t="inlineStr">
@@ -82676,12 +82676,12 @@
       </c>
       <c r="E1327" s="2" t="inlineStr">
         <is>
-          <t>869170034877770</t>
+          <t>869170035502492</t>
         </is>
       </c>
       <c r="F1327" s="2" t="inlineStr">
         <is>
-          <t>00019200000013836862</t>
+          <t>00019200000013836846</t>
         </is>
       </c>
       <c r="G1327" s="2" t="inlineStr">
@@ -82738,12 +82738,12 @@
       </c>
       <c r="E1328" s="2" t="inlineStr">
         <is>
-          <t>869170034887449</t>
+          <t>869170035511394</t>
         </is>
       </c>
       <c r="F1328" s="2" t="inlineStr">
         <is>
-          <t>00019200000013836870</t>
+          <t>00019200000013836854</t>
         </is>
       </c>
       <c r="G1328" s="2" t="inlineStr">
@@ -82800,12 +82800,12 @@
       </c>
       <c r="E1329" s="2" t="inlineStr">
         <is>
-          <t>869170035503821</t>
+          <t>869170034877770</t>
         </is>
       </c>
       <c r="F1329" s="2" t="inlineStr">
         <is>
-          <t>00019200000013836889</t>
+          <t>00019200000013836862</t>
         </is>
       </c>
       <c r="G1329" s="2" t="inlineStr">
@@ -82862,12 +82862,12 @@
       </c>
       <c r="E1330" s="2" t="inlineStr">
         <is>
-          <t>869170035501585</t>
+          <t>869170034887449</t>
         </is>
       </c>
       <c r="F1330" s="2" t="inlineStr">
         <is>
-          <t>00019200000013836897</t>
+          <t>00019200000013836870</t>
         </is>
       </c>
       <c r="G1330" s="2" t="inlineStr">
@@ -82924,12 +82924,12 @@
       </c>
       <c r="E1331" s="2" t="inlineStr">
         <is>
-          <t>869170034872243</t>
+          <t>869170035503821</t>
         </is>
       </c>
       <c r="F1331" s="2" t="inlineStr">
         <is>
-          <t>00019200000013836900</t>
+          <t>00019200000013836889</t>
         </is>
       </c>
       <c r="G1331" s="2" t="inlineStr">
@@ -82986,12 +82986,12 @@
       </c>
       <c r="E1332" s="2" t="inlineStr">
         <is>
-          <t>869170034872110</t>
+          <t>869170035501585</t>
         </is>
       </c>
       <c r="F1332" s="2" t="inlineStr">
         <is>
-          <t>00019200000013836919</t>
+          <t>00019200000013836897</t>
         </is>
       </c>
       <c r="G1332" s="2" t="inlineStr">
@@ -83048,12 +83048,12 @@
       </c>
       <c r="E1333" s="2" t="inlineStr">
         <is>
-          <t>869170034886797</t>
+          <t>869170034872243</t>
         </is>
       </c>
       <c r="F1333" s="2" t="inlineStr">
         <is>
-          <t>00019200000013836927</t>
+          <t>00019200000013836900</t>
         </is>
       </c>
       <c r="G1333" s="2" t="inlineStr">
@@ -83078,7 +83078,7 @@
       </c>
       <c r="K1333" s="2" t="inlineStr">
         <is>
-          <t>03/08/2026 04:37</t>
+          <t>03/08/2026 05:05</t>
         </is>
       </c>
       <c r="L1333" s="2" t="inlineStr">
@@ -83110,12 +83110,12 @@
       </c>
       <c r="E1334" s="2" t="inlineStr">
         <is>
-          <t>869170035503680</t>
+          <t>869170034872110</t>
         </is>
       </c>
       <c r="F1334" s="2" t="inlineStr">
         <is>
-          <t>00019200000013836935</t>
+          <t>00019200000013836919</t>
         </is>
       </c>
       <c r="G1334" s="2" t="inlineStr">
@@ -83172,12 +83172,12 @@
       </c>
       <c r="E1335" s="2" t="inlineStr">
         <is>
-          <t>869170034882598</t>
+          <t>869170034886797</t>
         </is>
       </c>
       <c r="F1335" s="2" t="inlineStr">
         <is>
-          <t>00019200000013836943</t>
+          <t>00019200000013836927</t>
         </is>
       </c>
       <c r="G1335" s="2" t="inlineStr">
@@ -83202,7 +83202,7 @@
       </c>
       <c r="K1335" s="2" t="inlineStr">
         <is>
-          <t>03/08/2026 05:05</t>
+          <t>03/08/2026 04:37</t>
         </is>
       </c>
       <c r="L1335" s="2" t="inlineStr">
@@ -83234,12 +83234,12 @@
       </c>
       <c r="E1336" s="2" t="inlineStr">
         <is>
-          <t>869170034871666</t>
+          <t>869170035503680</t>
         </is>
       </c>
       <c r="F1336" s="2" t="inlineStr">
         <is>
-          <t>00019200000013836951</t>
+          <t>00019200000013836935</t>
         </is>
       </c>
       <c r="G1336" s="2" t="inlineStr">
@@ -83264,7 +83264,7 @@
       </c>
       <c r="K1336" s="2" t="inlineStr">
         <is>
-          <t>03/08/2026 05:05</t>
+          <t>03/08/2026 04:37</t>
         </is>
       </c>
       <c r="L1336" s="2" t="inlineStr">
@@ -83296,12 +83296,12 @@
       </c>
       <c r="E1337" s="2" t="inlineStr">
         <is>
-          <t>869170035514240</t>
+          <t>869170034882598</t>
         </is>
       </c>
       <c r="F1337" s="2" t="inlineStr">
         <is>
-          <t>00019200000013836960</t>
+          <t>00019200000013836943</t>
         </is>
       </c>
       <c r="G1337" s="2" t="inlineStr">
@@ -83358,12 +83358,12 @@
       </c>
       <c r="E1338" s="2" t="inlineStr">
         <is>
-          <t>869170034890153</t>
+          <t>869170034871666</t>
         </is>
       </c>
       <c r="F1338" s="2" t="inlineStr">
         <is>
-          <t>00019200000013836978</t>
+          <t>00019200000013836951</t>
         </is>
       </c>
       <c r="G1338" s="2" t="inlineStr">
@@ -83420,12 +83420,12 @@
       </c>
       <c r="E1339" s="2" t="inlineStr">
         <is>
-          <t>V541018C</t>
+          <t>869170035514240</t>
         </is>
       </c>
       <c r="F1339" s="2" t="inlineStr">
         <is>
-          <t>00019200000013836986</t>
+          <t>00019200000013836960</t>
         </is>
       </c>
       <c r="G1339" s="2" t="inlineStr">
@@ -83450,7 +83450,7 @@
       </c>
       <c r="K1339" s="2" t="inlineStr">
         <is>
-          <t>03/08/2026 04:37</t>
+          <t>03/08/2026 05:05</t>
         </is>
       </c>
       <c r="L1339" s="2" t="inlineStr">
@@ -83482,12 +83482,12 @@
       </c>
       <c r="E1340" s="2" t="inlineStr">
         <is>
-          <t>869170035501478</t>
+          <t>869170034890153</t>
         </is>
       </c>
       <c r="F1340" s="2" t="inlineStr">
         <is>
-          <t>00019200000013837010</t>
+          <t>00019200000013836978</t>
         </is>
       </c>
       <c r="G1340" s="2" t="inlineStr">
@@ -83544,12 +83544,12 @@
       </c>
       <c r="E1341" s="2" t="inlineStr">
         <is>
-          <t>869170035518829</t>
+          <t>V541018C</t>
         </is>
       </c>
       <c r="F1341" s="2" t="inlineStr">
         <is>
-          <t>00019200000013837028</t>
+          <t>00019200000013836986</t>
         </is>
       </c>
       <c r="G1341" s="2" t="inlineStr">
@@ -83574,7 +83574,7 @@
       </c>
       <c r="K1341" s="2" t="inlineStr">
         <is>
-          <t>03/08/2026 05:05</t>
+          <t>03/08/2026 04:37</t>
         </is>
       </c>
       <c r="L1341" s="2" t="inlineStr">
@@ -83606,12 +83606,12 @@
       </c>
       <c r="E1342" s="2" t="inlineStr">
         <is>
-          <t>869170035513879</t>
+          <t>869170035501478</t>
         </is>
       </c>
       <c r="F1342" s="2" t="inlineStr">
         <is>
-          <t>00019200000013837036</t>
+          <t>00019200000013837010</t>
         </is>
       </c>
       <c r="G1342" s="2" t="inlineStr">
@@ -83636,7 +83636,7 @@
       </c>
       <c r="K1342" s="2" t="inlineStr">
         <is>
-          <t>03/08/2026 04:37</t>
+          <t>03/08/2026 05:05</t>
         </is>
       </c>
       <c r="L1342" s="2" t="inlineStr">
@@ -83668,12 +83668,12 @@
       </c>
       <c r="E1343" s="2" t="inlineStr">
         <is>
-          <t>869170034872250</t>
+          <t>869170035518829</t>
         </is>
       </c>
       <c r="F1343" s="2" t="inlineStr">
         <is>
-          <t>00019200000013837044</t>
+          <t>00019200000013837028</t>
         </is>
       </c>
       <c r="G1343" s="2" t="inlineStr">
@@ -83698,7 +83698,7 @@
       </c>
       <c r="K1343" s="2" t="inlineStr">
         <is>
-          <t>03/08/2026 04:37</t>
+          <t>03/08/2026 05:05</t>
         </is>
       </c>
       <c r="L1343" s="2" t="inlineStr">
@@ -83730,12 +83730,12 @@
       </c>
       <c r="E1344" s="2" t="inlineStr">
         <is>
-          <t>869170034886946</t>
+          <t>869170035513879</t>
         </is>
       </c>
       <c r="F1344" s="2" t="inlineStr">
         <is>
-          <t>00019200000013837052</t>
+          <t>00019200000013837036</t>
         </is>
       </c>
       <c r="G1344" s="2" t="inlineStr">
@@ -83760,7 +83760,7 @@
       </c>
       <c r="K1344" s="2" t="inlineStr">
         <is>
-          <t>03/08/2026 05:05</t>
+          <t>03/08/2026 04:37</t>
         </is>
       </c>
       <c r="L1344" s="2" t="inlineStr">
@@ -83792,12 +83792,12 @@
       </c>
       <c r="E1345" s="2" t="inlineStr">
         <is>
-          <t>869170034887373</t>
+          <t>869170034872250</t>
         </is>
       </c>
       <c r="F1345" s="2" t="inlineStr">
         <is>
-          <t>00019200000013837060</t>
+          <t>00019200000013837044</t>
         </is>
       </c>
       <c r="G1345" s="2" t="inlineStr">
@@ -83822,7 +83822,7 @@
       </c>
       <c r="K1345" s="2" t="inlineStr">
         <is>
-          <t>03/08/2026 05:05</t>
+          <t>03/08/2026 04:37</t>
         </is>
       </c>
       <c r="L1345" s="2" t="inlineStr">
@@ -83854,12 +83854,12 @@
       </c>
       <c r="E1346" s="2" t="inlineStr">
         <is>
-          <t>869170035512582</t>
+          <t>869170034886946</t>
         </is>
       </c>
       <c r="F1346" s="2" t="inlineStr">
         <is>
-          <t>00019200000013837079</t>
+          <t>00019200000013837052</t>
         </is>
       </c>
       <c r="G1346" s="2" t="inlineStr">
@@ -83884,7 +83884,7 @@
       </c>
       <c r="K1346" s="2" t="inlineStr">
         <is>
-          <t>03/08/2026 04:37</t>
+          <t>03/08/2026 05:05</t>
         </is>
       </c>
       <c r="L1346" s="2" t="inlineStr">
@@ -83916,12 +83916,12 @@
       </c>
       <c r="E1347" s="2" t="inlineStr">
         <is>
-          <t>869170034884032</t>
+          <t>869170034887373</t>
         </is>
       </c>
       <c r="F1347" s="2" t="inlineStr">
         <is>
-          <t>00019200000013837087</t>
+          <t>00019200000013837060</t>
         </is>
       </c>
       <c r="G1347" s="2" t="inlineStr">
@@ -83946,7 +83946,7 @@
       </c>
       <c r="K1347" s="2" t="inlineStr">
         <is>
-          <t>03/08/2026 04:37</t>
+          <t>03/08/2026 05:05</t>
         </is>
       </c>
       <c r="L1347" s="2" t="inlineStr">
@@ -83978,12 +83978,12 @@
       </c>
       <c r="E1348" s="2" t="inlineStr">
         <is>
-          <t>869170034889643</t>
+          <t>869170035512582</t>
         </is>
       </c>
       <c r="F1348" s="2" t="inlineStr">
         <is>
-          <t>00019200000013837095</t>
+          <t>00019200000013837079</t>
         </is>
       </c>
       <c r="G1348" s="2" t="inlineStr">
@@ -84040,12 +84040,12 @@
       </c>
       <c r="E1349" s="2" t="inlineStr">
         <is>
-          <t>869170034885856</t>
+          <t>869170034884032</t>
         </is>
       </c>
       <c r="F1349" s="2" t="inlineStr">
         <is>
-          <t>00019200000013837109</t>
+          <t>00019200000013837087</t>
         </is>
       </c>
       <c r="G1349" s="2" t="inlineStr">
@@ -84102,12 +84102,12 @@
       </c>
       <c r="E1350" s="2" t="inlineStr">
         <is>
-          <t>869170035502823</t>
+          <t>869170034889643</t>
         </is>
       </c>
       <c r="F1350" s="2" t="inlineStr">
         <is>
-          <t>00019200000013837117</t>
+          <t>00019200000013837095</t>
         </is>
       </c>
       <c r="G1350" s="2" t="inlineStr">
@@ -84132,7 +84132,7 @@
       </c>
       <c r="K1350" s="2" t="inlineStr">
         <is>
-          <t>03/08/2026 05:05</t>
+          <t>03/08/2026 04:37</t>
         </is>
       </c>
       <c r="L1350" s="2" t="inlineStr">
@@ -84149,12 +84149,12 @@
       </c>
       <c r="B1351" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-90 C a -60 C</t>
         </is>
       </c>
       <c r="C1351" s="2" t="inlineStr">
         <is>
-          <t>562154</t>
+          <t>561641</t>
         </is>
       </c>
       <c r="D1351" s="2" t="inlineStr">
@@ -84164,12 +84164,12 @@
       </c>
       <c r="E1351" s="2" t="inlineStr">
         <is>
-          <t>A4440</t>
+          <t>869170034885856</t>
         </is>
       </c>
       <c r="F1351" s="2" t="inlineStr">
         <is>
-          <t>00019200000013778293</t>
+          <t>00019200000013837109</t>
         </is>
       </c>
       <c r="G1351" s="2" t="inlineStr">
@@ -84179,12 +84179,12 @@
       </c>
       <c r="H1351" s="2" t="inlineStr">
         <is>
-          <t>28/07/2026 03:39</t>
+          <t>03/08/2026 04:37</t>
         </is>
       </c>
       <c r="I1351" s="2" t="inlineStr">
         <is>
-          <t>31/07/2026 11:28</t>
+          <t>04/08/2026 11:10</t>
         </is>
       </c>
       <c r="J1351" s="2" t="inlineStr">
@@ -84194,12 +84194,12 @@
       </c>
       <c r="K1351" s="2" t="inlineStr">
         <is>
-          <t>28/07/2026 03:39</t>
+          <t>03/08/2026 04:37</t>
         </is>
       </c>
       <c r="L1351" s="2" t="inlineStr">
         <is>
-          <t>31/07/2026 11:28</t>
+          <t>04/08/2026 11:10</t>
         </is>
       </c>
     </row>
@@ -84211,12 +84211,12 @@
       </c>
       <c r="B1352" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-90 C a -60 C</t>
         </is>
       </c>
       <c r="C1352" s="2" t="inlineStr">
         <is>
-          <t>563189</t>
+          <t>561641</t>
         </is>
       </c>
       <c r="D1352" s="2" t="inlineStr">
@@ -84226,12 +84226,12 @@
       </c>
       <c r="E1352" s="2" t="inlineStr">
         <is>
-          <t>A0204</t>
+          <t>869170035502823</t>
         </is>
       </c>
       <c r="F1352" s="2" t="inlineStr">
         <is>
-          <t>00019200000013853376</t>
+          <t>00019200000013837117</t>
         </is>
       </c>
       <c r="G1352" s="2" t="inlineStr">
@@ -84241,12 +84241,12 @@
       </c>
       <c r="H1352" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026 23:26</t>
+          <t>03/08/2026 04:37</t>
         </is>
       </c>
       <c r="I1352" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026 13:45</t>
+          <t>04/08/2026 11:10</t>
         </is>
       </c>
       <c r="J1352" s="2" t="inlineStr">
@@ -84256,12 +84256,12 @@
       </c>
       <c r="K1352" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026 23:26</t>
+          <t>03/08/2026 05:05</t>
         </is>
       </c>
       <c r="L1352" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026 13:45</t>
+          <t>04/08/2026 11:10</t>
         </is>
       </c>
     </row>
@@ -84273,12 +84273,12 @@
       </c>
       <c r="B1353" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1353" s="2" t="inlineStr">
         <is>
-          <t>563189</t>
+          <t>562154</t>
         </is>
       </c>
       <c r="D1353" s="2" t="inlineStr">
@@ -84288,12 +84288,12 @@
       </c>
       <c r="E1353" s="2" t="inlineStr">
         <is>
-          <t>A2981</t>
+          <t>A4440</t>
         </is>
       </c>
       <c r="F1353" s="2" t="inlineStr">
         <is>
-          <t>00019200000013853384</t>
+          <t>00019200000013778293</t>
         </is>
       </c>
       <c r="G1353" s="2" t="inlineStr">
@@ -84303,12 +84303,12 @@
       </c>
       <c r="H1353" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026 23:26</t>
+          <t>28/07/2026 03:39</t>
         </is>
       </c>
       <c r="I1353" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026 13:45</t>
+          <t>31/07/2026 11:28</t>
         </is>
       </c>
       <c r="J1353" s="2" t="inlineStr">
@@ -84318,12 +84318,12 @@
       </c>
       <c r="K1353" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026 23:26</t>
+          <t>28/07/2026 03:39</t>
         </is>
       </c>
       <c r="L1353" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026 13:45</t>
+          <t>31/07/2026 11:28</t>
         </is>
       </c>
     </row>
@@ -84340,7 +84340,7 @@
       </c>
       <c r="C1354" s="2" t="inlineStr">
         <is>
-          <t>565596</t>
+          <t>563189</t>
         </is>
       </c>
       <c r="D1354" s="2" t="inlineStr">
@@ -84350,12 +84350,12 @@
       </c>
       <c r="E1354" s="2" t="inlineStr">
         <is>
-          <t>A4277</t>
+          <t>A0204</t>
         </is>
       </c>
       <c r="F1354" s="2" t="inlineStr">
         <is>
-          <t>00019200000014019752</t>
+          <t>00019200000013853376</t>
         </is>
       </c>
       <c r="G1354" s="2" t="inlineStr">
@@ -84365,12 +84365,12 @@
       </c>
       <c r="H1354" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026 05:09</t>
+          <t>04/08/2026 23:26</t>
         </is>
       </c>
       <c r="I1354" s="2" t="inlineStr">
         <is>
-          <t>28/08/2026 08:30</t>
+          <t>06/08/2026 13:45</t>
         </is>
       </c>
       <c r="J1354" s="2" t="inlineStr">
@@ -84380,12 +84380,12 @@
       </c>
       <c r="K1354" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026 05:09</t>
+          <t>04/08/2026 23:26</t>
         </is>
       </c>
       <c r="L1354" s="2" t="inlineStr">
         <is>
-          <t>28/08/2026 08:30</t>
+          <t>06/08/2026 13:45</t>
         </is>
       </c>
     </row>
@@ -84397,12 +84397,12 @@
       </c>
       <c r="B1355" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1355" s="2" t="inlineStr">
         <is>
-          <t>567156</t>
+          <t>563189</t>
         </is>
       </c>
       <c r="D1355" s="2" t="inlineStr">
@@ -84412,12 +84412,12 @@
       </c>
       <c r="E1355" s="2" t="inlineStr">
         <is>
-          <t>0741700980</t>
+          <t>A2981</t>
         </is>
       </c>
       <c r="F1355" s="2" t="inlineStr">
         <is>
-          <t>00019200000014229650</t>
+          <t>00019200000013853384</t>
         </is>
       </c>
       <c r="G1355" s="2" t="inlineStr">
@@ -84427,12 +84427,12 @@
       </c>
       <c r="H1355" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026 13:08</t>
+          <t>04/08/2026 23:26</t>
         </is>
       </c>
       <c r="I1355" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026 16:00</t>
+          <t>06/08/2026 13:45</t>
         </is>
       </c>
       <c r="J1355" s="2" t="inlineStr">
@@ -84442,12 +84442,12 @@
       </c>
       <c r="K1355" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026 13:08</t>
+          <t>04/08/2026 23:26</t>
         </is>
       </c>
       <c r="L1355" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026 16:00</t>
+          <t>06/08/2026 13:45</t>
         </is>
       </c>
     </row>
@@ -84464,22 +84464,22 @@
       </c>
       <c r="C1356" s="2" t="inlineStr">
         <is>
-          <t>556409</t>
+          <t>565596</t>
         </is>
       </c>
       <c r="D1356" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E1356" s="2" t="inlineStr">
         <is>
-          <t>A5875</t>
+          <t>A4277</t>
         </is>
       </c>
       <c r="F1356" s="2" t="inlineStr">
         <is>
-          <t>00019200000012729590</t>
+          <t>00019200000014019752</t>
         </is>
       </c>
       <c r="G1356" s="2" t="inlineStr">
@@ -84489,12 +84489,12 @@
       </c>
       <c r="H1356" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026 06:40</t>
+          <t>26/08/2026 05:09</t>
         </is>
       </c>
       <c r="I1356" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026 17:18</t>
+          <t>28/08/2026 08:30</t>
         </is>
       </c>
       <c r="J1356" s="2" t="inlineStr">
@@ -84504,12 +84504,12 @@
       </c>
       <c r="K1356" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>26/08/2026 05:09</t>
         </is>
       </c>
       <c r="L1356" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>28/08/2026 08:30</t>
         </is>
       </c>
     </row>
@@ -84521,27 +84521,27 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
         <is>
-          <t>557176</t>
+          <t>567156</t>
         </is>
       </c>
       <c r="D1357" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E1357" s="2" t="inlineStr">
         <is>
-          <t>A6058</t>
+          <t>0741700980</t>
         </is>
       </c>
       <c r="F1357" s="2" t="inlineStr">
         <is>
-          <t>00019200000012684520</t>
+          <t>00019200000014229650</t>
         </is>
       </c>
       <c r="G1357" s="2" t="inlineStr">
@@ -84551,12 +84551,12 @@
       </c>
       <c r="H1357" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026 10:11</t>
+          <t>10/09/2026 13:08</t>
         </is>
       </c>
       <c r="I1357" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026 13:40</t>
+          <t>11/09/2026 16:00</t>
         </is>
       </c>
       <c r="J1357" s="2" t="inlineStr">
@@ -84566,12 +84566,12 @@
       </c>
       <c r="K1357" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026 10:11</t>
+          <t>10/09/2026 13:08</t>
         </is>
       </c>
       <c r="L1357" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026 13:40</t>
+          <t>11/09/2026 16:00</t>
         </is>
       </c>
     </row>
@@ -84583,12 +84583,12 @@
       </c>
       <c r="B1358" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1358" s="2" t="inlineStr">
         <is>
-          <t>557176</t>
+          <t>556409</t>
         </is>
       </c>
       <c r="D1358" s="2" t="inlineStr">
@@ -84598,12 +84598,12 @@
       </c>
       <c r="E1358" s="2" t="inlineStr">
         <is>
-          <t>A4203</t>
+          <t>A5875</t>
         </is>
       </c>
       <c r="F1358" s="2" t="inlineStr">
         <is>
-          <t>00019200000012684538</t>
+          <t>00019200000012729590</t>
         </is>
       </c>
       <c r="G1358" s="2" t="inlineStr">
@@ -84613,12 +84613,12 @@
       </c>
       <c r="H1358" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026 10:11</t>
+          <t>10/06/2026 06:40</t>
         </is>
       </c>
       <c r="I1358" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026 13:40</t>
+          <t>11/06/2026 17:18</t>
         </is>
       </c>
       <c r="J1358" s="2" t="inlineStr">
@@ -84628,12 +84628,12 @@
       </c>
       <c r="K1358" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026 10:11</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L1358" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026 13:40</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -84645,12 +84645,12 @@
       </c>
       <c r="B1359" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1359" s="2" t="inlineStr">
         <is>
-          <t>559423</t>
+          <t>557176</t>
         </is>
       </c>
       <c r="D1359" s="2" t="inlineStr">
@@ -84660,12 +84660,12 @@
       </c>
       <c r="E1359" s="2" t="inlineStr">
         <is>
-          <t>A8271</t>
+          <t>A6058</t>
         </is>
       </c>
       <c r="F1359" s="2" t="inlineStr">
         <is>
-          <t>00019200000013202294</t>
+          <t>00019200000012684520</t>
         </is>
       </c>
       <c r="G1359" s="2" t="inlineStr">
@@ -84675,12 +84675,12 @@
       </c>
       <c r="H1359" s="2" t="inlineStr">
         <is>
-          <t>29/06/2026 05:35</t>
+          <t>15/06/2026 10:11</t>
         </is>
       </c>
       <c r="I1359" s="2" t="inlineStr">
         <is>
-          <t>30/06/2026 14:52</t>
+          <t>16/06/2026 13:40</t>
         </is>
       </c>
       <c r="J1359" s="2" t="inlineStr">
@@ -84690,12 +84690,12 @@
       </c>
       <c r="K1359" s="2" t="inlineStr">
         <is>
-          <t>29/06/2026 05:35</t>
+          <t>15/06/2026 10:11</t>
         </is>
       </c>
       <c r="L1359" s="2" t="inlineStr">
         <is>
-          <t>30/06/2026 14:52</t>
+          <t>16/06/2026 13:40</t>
         </is>
       </c>
     </row>
@@ -84707,12 +84707,12 @@
       </c>
       <c r="B1360" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1360" s="2" t="inlineStr">
         <is>
-          <t>559880</t>
+          <t>557176</t>
         </is>
       </c>
       <c r="D1360" s="2" t="inlineStr">
@@ -84722,12 +84722,12 @@
       </c>
       <c r="E1360" s="2" t="inlineStr">
         <is>
-          <t>A8482</t>
+          <t>A4203</t>
         </is>
       </c>
       <c r="F1360" s="2" t="inlineStr">
         <is>
-          <t>00019200000013407147</t>
+          <t>00019200000012684538</t>
         </is>
       </c>
       <c r="G1360" s="2" t="inlineStr">
@@ -84737,12 +84737,12 @@
       </c>
       <c r="H1360" s="2" t="inlineStr">
         <is>
-          <t>09/07/2026 05:48</t>
+          <t>15/06/2026 10:11</t>
         </is>
       </c>
       <c r="I1360" s="2" t="inlineStr">
         <is>
-          <t>10/07/2026 17:00</t>
+          <t>16/06/2026 13:40</t>
         </is>
       </c>
       <c r="J1360" s="2" t="inlineStr">
@@ -84752,12 +84752,12 @@
       </c>
       <c r="K1360" s="2" t="inlineStr">
         <is>
-          <t>09/07/2026 05:48</t>
+          <t>15/06/2026 10:11</t>
         </is>
       </c>
       <c r="L1360" s="2" t="inlineStr">
         <is>
-          <t>10/07/2026 17:00</t>
+          <t>16/06/2026 13:40</t>
         </is>
       </c>
     </row>
@@ -84774,7 +84774,7 @@
       </c>
       <c r="C1361" s="2" t="inlineStr">
         <is>
-          <t>559880</t>
+          <t>559423</t>
         </is>
       </c>
       <c r="D1361" s="2" t="inlineStr">
@@ -84784,12 +84784,12 @@
       </c>
       <c r="E1361" s="2" t="inlineStr">
         <is>
-          <t>A4021</t>
+          <t>A8271</t>
         </is>
       </c>
       <c r="F1361" s="2" t="inlineStr">
         <is>
-          <t>00019200000013407180</t>
+          <t>00019200000013202294</t>
         </is>
       </c>
       <c r="G1361" s="2" t="inlineStr">
@@ -84799,12 +84799,12 @@
       </c>
       <c r="H1361" s="2" t="inlineStr">
         <is>
-          <t>09/07/2026 05:48</t>
+          <t>29/06/2026 05:35</t>
         </is>
       </c>
       <c r="I1361" s="2" t="inlineStr">
         <is>
-          <t>10/07/2026 17:00</t>
+          <t>30/06/2026 14:52</t>
         </is>
       </c>
       <c r="J1361" s="2" t="inlineStr">
@@ -84814,12 +84814,12 @@
       </c>
       <c r="K1361" s="2" t="inlineStr">
         <is>
-          <t>09/07/2026 05:48</t>
+          <t>29/06/2026 05:35</t>
         </is>
       </c>
       <c r="L1361" s="2" t="inlineStr">
         <is>
-          <t>10/07/2026 17:00</t>
+          <t>30/06/2026 14:52</t>
         </is>
       </c>
     </row>
@@ -84846,12 +84846,12 @@
       </c>
       <c r="E1362" s="2" t="inlineStr">
         <is>
-          <t>A7212</t>
+          <t>A8482</t>
         </is>
       </c>
       <c r="F1362" s="2" t="inlineStr">
         <is>
-          <t>00019200000013407198</t>
+          <t>00019200000013407147</t>
         </is>
       </c>
       <c r="G1362" s="2" t="inlineStr">
@@ -84893,7 +84893,7 @@
       </c>
       <c r="B1363" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1363" s="2" t="inlineStr">
@@ -84908,12 +84908,12 @@
       </c>
       <c r="E1363" s="2" t="inlineStr">
         <is>
-          <t>A3672</t>
+          <t>A4021</t>
         </is>
       </c>
       <c r="F1363" s="2" t="inlineStr">
         <is>
-          <t>00019200000013407201</t>
+          <t>00019200000013407180</t>
         </is>
       </c>
       <c r="G1363" s="2" t="inlineStr">
@@ -84955,7 +84955,7 @@
       </c>
       <c r="B1364" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1364" s="2" t="inlineStr">
@@ -84970,12 +84970,12 @@
       </c>
       <c r="E1364" s="2" t="inlineStr">
         <is>
-          <t>TA0241</t>
+          <t>A7212</t>
         </is>
       </c>
       <c r="F1364" s="2" t="inlineStr">
         <is>
-          <t>00019200000013407210</t>
+          <t>00019200000013407198</t>
         </is>
       </c>
       <c r="G1364" s="2" t="inlineStr">
@@ -85017,12 +85017,12 @@
       </c>
       <c r="B1365" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1365" s="2" t="inlineStr">
         <is>
-          <t>563153</t>
+          <t>559880</t>
         </is>
       </c>
       <c r="D1365" s="2" t="inlineStr">
@@ -85032,12 +85032,12 @@
       </c>
       <c r="E1365" s="2" t="inlineStr">
         <is>
-          <t>A0372</t>
+          <t>A3672</t>
         </is>
       </c>
       <c r="F1365" s="2" t="inlineStr">
         <is>
-          <t>00019200000013852965</t>
+          <t>00019200000013407201</t>
         </is>
       </c>
       <c r="G1365" s="2" t="inlineStr">
@@ -85047,12 +85047,12 @@
       </c>
       <c r="H1365" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026 23:33</t>
+          <t>09/07/2026 05:48</t>
         </is>
       </c>
       <c r="I1365" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026 17:00</t>
+          <t>10/07/2026 17:00</t>
         </is>
       </c>
       <c r="J1365" s="2" t="inlineStr">
@@ -85062,12 +85062,12 @@
       </c>
       <c r="K1365" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026 23:33</t>
+          <t>09/07/2026 05:48</t>
         </is>
       </c>
       <c r="L1365" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026 17:00</t>
+          <t>10/07/2026 17:00</t>
         </is>
       </c>
     </row>
@@ -85084,7 +85084,7 @@
       </c>
       <c r="C1366" s="2" t="inlineStr">
         <is>
-          <t>563153</t>
+          <t>559880</t>
         </is>
       </c>
       <c r="D1366" s="2" t="inlineStr">
@@ -85094,12 +85094,12 @@
       </c>
       <c r="E1366" s="2" t="inlineStr">
         <is>
-          <t>A8300</t>
+          <t>TA0241</t>
         </is>
       </c>
       <c r="F1366" s="2" t="inlineStr">
         <is>
-          <t>00019200000013852973</t>
+          <t>00019200000013407210</t>
         </is>
       </c>
       <c r="G1366" s="2" t="inlineStr">
@@ -85109,12 +85109,12 @@
       </c>
       <c r="H1366" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026 23:33</t>
+          <t>09/07/2026 05:48</t>
         </is>
       </c>
       <c r="I1366" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026 17:00</t>
+          <t>10/07/2026 17:00</t>
         </is>
       </c>
       <c r="J1366" s="2" t="inlineStr">
@@ -85124,12 +85124,12 @@
       </c>
       <c r="K1366" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026 23:33</t>
+          <t>09/07/2026 05:48</t>
         </is>
       </c>
       <c r="L1366" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026 17:00</t>
+          <t>10/07/2026 17:00</t>
         </is>
       </c>
     </row>
@@ -85141,7 +85141,7 @@
       </c>
       <c r="B1367" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1367" s="2" t="inlineStr">
@@ -85156,12 +85156,12 @@
       </c>
       <c r="E1367" s="2" t="inlineStr">
         <is>
-          <t>TA0920</t>
+          <t>A0372</t>
         </is>
       </c>
       <c r="F1367" s="2" t="inlineStr">
         <is>
-          <t>00019200000013852981</t>
+          <t>00019200000013852965</t>
         </is>
       </c>
       <c r="G1367" s="2" t="inlineStr">
@@ -85218,12 +85218,12 @@
       </c>
       <c r="E1368" s="2" t="inlineStr">
         <is>
-          <t>TA0004</t>
+          <t>A8300</t>
         </is>
       </c>
       <c r="F1368" s="2" t="inlineStr">
         <is>
-          <t>00019200000013852990</t>
+          <t>00019200000013852973</t>
         </is>
       </c>
       <c r="G1368" s="2" t="inlineStr">
@@ -85265,7 +85265,7 @@
       </c>
       <c r="B1369" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1369" s="2" t="inlineStr">
@@ -85280,12 +85280,12 @@
       </c>
       <c r="E1369" s="2" t="inlineStr">
         <is>
-          <t>A8425</t>
+          <t>TA0920</t>
         </is>
       </c>
       <c r="F1369" s="2" t="inlineStr">
         <is>
-          <t>00019200000013856740</t>
+          <t>00019200000013852981</t>
         </is>
       </c>
       <c r="G1369" s="2" t="inlineStr">
@@ -85327,12 +85327,12 @@
       </c>
       <c r="B1370" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1370" s="2" t="inlineStr">
         <is>
-          <t>563886</t>
+          <t>563153</t>
         </is>
       </c>
       <c r="D1370" s="2" t="inlineStr">
@@ -85342,12 +85342,12 @@
       </c>
       <c r="E1370" s="2" t="inlineStr">
         <is>
-          <t>TA0472</t>
+          <t>TA0004</t>
         </is>
       </c>
       <c r="F1370" s="2" t="inlineStr">
         <is>
-          <t>00019200000013868470</t>
+          <t>00019200000013852990</t>
         </is>
       </c>
       <c r="G1370" s="2" t="inlineStr">
@@ -85357,12 +85357,12 @@
       </c>
       <c r="H1370" s="2" t="inlineStr">
         <is>
-          <t>10/08/2026 22:36</t>
+          <t>04/08/2026 23:33</t>
         </is>
       </c>
       <c r="I1370" s="2" t="inlineStr">
         <is>
-          <t>12/08/2026 15:55</t>
+          <t>06/08/2026 17:00</t>
         </is>
       </c>
       <c r="J1370" s="2" t="inlineStr">
@@ -85372,12 +85372,12 @@
       </c>
       <c r="K1370" s="2" t="inlineStr">
         <is>
-          <t>10/08/2026 22:36</t>
+          <t>04/08/2026 23:33</t>
         </is>
       </c>
       <c r="L1370" s="2" t="inlineStr">
         <is>
-          <t>12/08/2026 15:55</t>
+          <t>06/08/2026 17:00</t>
         </is>
       </c>
     </row>
@@ -85394,7 +85394,7 @@
       </c>
       <c r="C1371" s="2" t="inlineStr">
         <is>
-          <t>563932</t>
+          <t>563153</t>
         </is>
       </c>
       <c r="D1371" s="2" t="inlineStr">
@@ -85404,12 +85404,12 @@
       </c>
       <c r="E1371" s="2" t="inlineStr">
         <is>
-          <t>A8979</t>
+          <t>A8425</t>
         </is>
       </c>
       <c r="F1371" s="2" t="inlineStr">
         <is>
-          <t>00019200000013868489</t>
+          <t>00019200000013856740</t>
         </is>
       </c>
       <c r="G1371" s="2" t="inlineStr">
@@ -85419,12 +85419,12 @@
       </c>
       <c r="H1371" s="2" t="inlineStr">
         <is>
-          <t>10/08/2026 22:38</t>
+          <t>04/08/2026 23:33</t>
         </is>
       </c>
       <c r="I1371" s="2" t="inlineStr">
         <is>
-          <t>12/08/2026 15:55</t>
+          <t>06/08/2026 17:00</t>
         </is>
       </c>
       <c r="J1371" s="2" t="inlineStr">
@@ -85434,12 +85434,12 @@
       </c>
       <c r="K1371" s="2" t="inlineStr">
         <is>
-          <t>10/08/2026 22:38</t>
+          <t>04/08/2026 23:33</t>
         </is>
       </c>
       <c r="L1371" s="2" t="inlineStr">
         <is>
-          <t>12/08/2026 15:55</t>
+          <t>06/08/2026 17:00</t>
         </is>
       </c>
     </row>
@@ -85451,12 +85451,12 @@
       </c>
       <c r="B1372" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1372" s="2" t="inlineStr">
         <is>
-          <t>567134</t>
+          <t>563886</t>
         </is>
       </c>
       <c r="D1372" s="2" t="inlineStr">
@@ -85466,12 +85466,12 @@
       </c>
       <c r="E1372" s="2" t="inlineStr">
         <is>
-          <t>0741700314</t>
+          <t>TA0472</t>
         </is>
       </c>
       <c r="F1372" s="2" t="inlineStr">
         <is>
-          <t>00019200000014229390</t>
+          <t>00019200000013868470</t>
         </is>
       </c>
       <c r="G1372" s="2" t="inlineStr">
@@ -85481,12 +85481,12 @@
       </c>
       <c r="H1372" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026 13:12</t>
+          <t>10/08/2026 22:36</t>
         </is>
       </c>
       <c r="I1372" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026 17:29</t>
+          <t>12/08/2026 15:55</t>
         </is>
       </c>
       <c r="J1372" s="2" t="inlineStr">
@@ -85496,12 +85496,12 @@
       </c>
       <c r="K1372" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026 13:12</t>
+          <t>10/08/2026 22:36</t>
         </is>
       </c>
       <c r="L1372" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026 17:29</t>
+          <t>12/08/2026 15:55</t>
         </is>
       </c>
     </row>
@@ -85513,12 +85513,12 @@
       </c>
       <c r="B1373" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1373" s="2" t="inlineStr">
         <is>
-          <t>567134</t>
+          <t>563932</t>
         </is>
       </c>
       <c r="D1373" s="2" t="inlineStr">
@@ -85528,12 +85528,12 @@
       </c>
       <c r="E1373" s="2" t="inlineStr">
         <is>
-          <t>0741700259</t>
+          <t>A8979</t>
         </is>
       </c>
       <c r="F1373" s="2" t="inlineStr">
         <is>
-          <t>00019200000014229404</t>
+          <t>00019200000013868489</t>
         </is>
       </c>
       <c r="G1373" s="2" t="inlineStr">
@@ -85543,12 +85543,12 @@
       </c>
       <c r="H1373" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026 13:12</t>
+          <t>10/08/2026 22:38</t>
         </is>
       </c>
       <c r="I1373" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026 17:29</t>
+          <t>12/08/2026 15:55</t>
         </is>
       </c>
       <c r="J1373" s="2" t="inlineStr">
@@ -85558,12 +85558,12 @@
       </c>
       <c r="K1373" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026 13:12</t>
+          <t>10/08/2026 22:38</t>
         </is>
       </c>
       <c r="L1373" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026 17:29</t>
+          <t>12/08/2026 15:55</t>
         </is>
       </c>
     </row>
@@ -85575,7 +85575,7 @@
       </c>
       <c r="B1374" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1374" s="2" t="inlineStr">
@@ -85590,12 +85590,12 @@
       </c>
       <c r="E1374" s="2" t="inlineStr">
         <is>
-          <t>0741700428</t>
+          <t>0741700314</t>
         </is>
       </c>
       <c r="F1374" s="2" t="inlineStr">
         <is>
-          <t>00019200000014229412</t>
+          <t>00019200000014229390</t>
         </is>
       </c>
       <c r="G1374" s="2" t="inlineStr">
@@ -85637,7 +85637,7 @@
       </c>
       <c r="B1375" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1375" s="2" t="inlineStr">
@@ -85652,12 +85652,12 @@
       </c>
       <c r="E1375" s="2" t="inlineStr">
         <is>
-          <t>0741700280</t>
+          <t>0741700259</t>
         </is>
       </c>
       <c r="F1375" s="2" t="inlineStr">
         <is>
-          <t>00019200000014229420</t>
+          <t>00019200000014229404</t>
         </is>
       </c>
       <c r="G1375" s="2" t="inlineStr">
@@ -85704,7 +85704,7 @@
       </c>
       <c r="C1376" s="2" t="inlineStr">
         <is>
-          <t>567783</t>
+          <t>567134</t>
         </is>
       </c>
       <c r="D1376" s="2" t="inlineStr">
@@ -85714,12 +85714,12 @@
       </c>
       <c r="E1376" s="2" t="inlineStr">
         <is>
-          <t>0741700346</t>
+          <t>0741700428</t>
         </is>
       </c>
       <c r="F1376" s="2" t="inlineStr">
         <is>
-          <t>00019200000014232146</t>
+          <t>00019200000014229412</t>
         </is>
       </c>
       <c r="G1376" s="2" t="inlineStr">
@@ -85729,12 +85729,12 @@
       </c>
       <c r="H1376" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026 08:36</t>
+          <t>10/09/2026 13:12</t>
         </is>
       </c>
       <c r="I1376" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026 17:27</t>
+          <t>11/09/2026 17:29</t>
         </is>
       </c>
       <c r="J1376" s="2" t="inlineStr">
@@ -85744,12 +85744,12 @@
       </c>
       <c r="K1376" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026 08:36</t>
+          <t>10/09/2026 13:12</t>
         </is>
       </c>
       <c r="L1376" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026 17:27</t>
+          <t>11/09/2026 17:29</t>
         </is>
       </c>
     </row>
@@ -85761,27 +85761,27 @@
       </c>
       <c r="B1377" s="2" t="inlineStr">
         <is>
-          <t>-90 C a -60 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1377" s="2" t="inlineStr">
         <is>
-          <t>557500</t>
+          <t>567134</t>
         </is>
       </c>
       <c r="D1377" s="2" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E1377" s="2" t="inlineStr">
         <is>
-          <t>AS-0259</t>
+          <t>0741700280</t>
         </is>
       </c>
       <c r="F1377" s="2" t="inlineStr">
         <is>
-          <t>00019200000012614947</t>
+          <t>00019200000014229420</t>
         </is>
       </c>
       <c r="G1377" s="2" t="inlineStr">
@@ -85791,12 +85791,12 @@
       </c>
       <c r="H1377" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026 00:48</t>
+          <t>10/09/2026 13:12</t>
         </is>
       </c>
       <c r="I1377" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026 15:00</t>
+          <t>11/09/2026 17:29</t>
         </is>
       </c>
       <c r="J1377" s="2" t="inlineStr">
@@ -85806,12 +85806,12 @@
       </c>
       <c r="K1377" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026 00:48</t>
+          <t>10/09/2026 13:12</t>
         </is>
       </c>
       <c r="L1377" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026 15:00</t>
+          <t>11/09/2026 17:29</t>
         </is>
       </c>
     </row>
@@ -85823,27 +85823,27 @@
       </c>
       <c r="B1378" s="2" t="inlineStr">
         <is>
-          <t>-90 C a -60 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1378" s="2" t="inlineStr">
         <is>
-          <t>557500</t>
+          <t>567783</t>
         </is>
       </c>
       <c r="D1378" s="2" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E1378" s="2" t="inlineStr">
         <is>
-          <t>869170034875337</t>
+          <t>0741700346</t>
         </is>
       </c>
       <c r="F1378" s="2" t="inlineStr">
         <is>
-          <t>00019200000012614955</t>
+          <t>00019200000014232146</t>
         </is>
       </c>
       <c r="G1378" s="2" t="inlineStr">
@@ -85853,12 +85853,12 @@
       </c>
       <c r="H1378" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026 00:48</t>
+          <t>10/09/2026 08:36</t>
         </is>
       </c>
       <c r="I1378" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026 15:00</t>
+          <t>11/09/2026 17:27</t>
         </is>
       </c>
       <c r="J1378" s="2" t="inlineStr">
@@ -85868,12 +85868,12 @@
       </c>
       <c r="K1378" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026 00:48</t>
+          <t>10/09/2026 08:36</t>
         </is>
       </c>
       <c r="L1378" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026 15:00</t>
+          <t>11/09/2026 17:27</t>
         </is>
       </c>
     </row>
@@ -85900,12 +85900,12 @@
       </c>
       <c r="E1379" s="2" t="inlineStr">
         <is>
-          <t>869170035502047</t>
+          <t>AS-0259</t>
         </is>
       </c>
       <c r="F1379" s="2" t="inlineStr">
         <is>
-          <t>00019200000012614963</t>
+          <t>00019200000012614947</t>
         </is>
       </c>
       <c r="G1379" s="2" t="inlineStr">
@@ -85962,12 +85962,12 @@
       </c>
       <c r="E1380" s="2" t="inlineStr">
         <is>
-          <t>869170035520544</t>
+          <t>869170034875337</t>
         </is>
       </c>
       <c r="F1380" s="2" t="inlineStr">
         <is>
-          <t>00019200000012614980</t>
+          <t>00019200000012614955</t>
         </is>
       </c>
       <c r="G1380" s="2" t="inlineStr">
@@ -86024,12 +86024,12 @@
       </c>
       <c r="E1381" s="2" t="inlineStr">
         <is>
-          <t>869170034875469</t>
+          <t>869170035502047</t>
         </is>
       </c>
       <c r="F1381" s="2" t="inlineStr">
         <is>
-          <t>00019200000012614998</t>
+          <t>00019200000012614963</t>
         </is>
       </c>
       <c r="G1381" s="2" t="inlineStr">
@@ -86086,12 +86086,12 @@
       </c>
       <c r="E1382" s="2" t="inlineStr">
         <is>
-          <t>869170034878802</t>
+          <t>869170035520544</t>
         </is>
       </c>
       <c r="F1382" s="2" t="inlineStr">
         <is>
-          <t>00019200000013313916</t>
+          <t>00019200000012614980</t>
         </is>
       </c>
       <c r="G1382" s="2" t="inlineStr">
@@ -86148,12 +86148,12 @@
       </c>
       <c r="E1383" s="2" t="inlineStr">
         <is>
-          <t>869170035502203</t>
+          <t>869170034875469</t>
         </is>
       </c>
       <c r="F1383" s="2" t="inlineStr">
         <is>
-          <t>00019200000013314920</t>
+          <t>00019200000012614998</t>
         </is>
       </c>
       <c r="G1383" s="2" t="inlineStr">
@@ -86210,12 +86210,12 @@
       </c>
       <c r="E1384" s="2" t="inlineStr">
         <is>
-          <t>869170034872755</t>
+          <t>869170034878802</t>
         </is>
       </c>
       <c r="F1384" s="2" t="inlineStr">
         <is>
-          <t>00019200000013314939</t>
+          <t>00019200000013313916</t>
         </is>
       </c>
       <c r="G1384" s="2" t="inlineStr">
@@ -86272,12 +86272,12 @@
       </c>
       <c r="E1385" s="2" t="inlineStr">
         <is>
-          <t>869170034883687</t>
+          <t>869170035502203</t>
         </is>
       </c>
       <c r="F1385" s="2" t="inlineStr">
         <is>
-          <t>00019200000013314947</t>
+          <t>00019200000013314920</t>
         </is>
       </c>
       <c r="G1385" s="2" t="inlineStr">
@@ -86334,12 +86334,12 @@
       </c>
       <c r="E1386" s="2" t="inlineStr">
         <is>
-          <t>869170034873043</t>
+          <t>869170034872755</t>
         </is>
       </c>
       <c r="F1386" s="2" t="inlineStr">
         <is>
-          <t>00019200000013314955</t>
+          <t>00019200000013314939</t>
         </is>
       </c>
       <c r="G1386" s="2" t="inlineStr">
@@ -86396,12 +86396,12 @@
       </c>
       <c r="E1387" s="2" t="inlineStr">
         <is>
-          <t>869170034879339</t>
+          <t>869170034883687</t>
         </is>
       </c>
       <c r="F1387" s="2" t="inlineStr">
         <is>
-          <t>00019200000013314963</t>
+          <t>00019200000013314947</t>
         </is>
       </c>
       <c r="G1387" s="2" t="inlineStr">
@@ -86458,12 +86458,12 @@
       </c>
       <c r="E1388" s="2" t="inlineStr">
         <is>
-          <t>869170034886797</t>
+          <t>869170034873043</t>
         </is>
       </c>
       <c r="F1388" s="2" t="inlineStr">
         <is>
-          <t>00019200000013314971</t>
+          <t>00019200000013314955</t>
         </is>
       </c>
       <c r="G1388" s="2" t="inlineStr">
@@ -86520,12 +86520,12 @@
       </c>
       <c r="E1389" s="2" t="inlineStr">
         <is>
-          <t>869170034885807</t>
+          <t>869170034879339</t>
         </is>
       </c>
       <c r="F1389" s="2" t="inlineStr">
         <is>
-          <t>00019200000013314980</t>
+          <t>00019200000013314963</t>
         </is>
       </c>
       <c r="G1389" s="2" t="inlineStr">
@@ -86582,12 +86582,12 @@
       </c>
       <c r="E1390" s="2" t="inlineStr">
         <is>
-          <t>869170035501999</t>
+          <t>869170034886797</t>
         </is>
       </c>
       <c r="F1390" s="2" t="inlineStr">
         <is>
-          <t>00019200000013314998</t>
+          <t>00019200000013314971</t>
         </is>
       </c>
       <c r="G1390" s="2" t="inlineStr">
@@ -86644,12 +86644,12 @@
       </c>
       <c r="E1391" s="2" t="inlineStr">
         <is>
-          <t>869170034886243</t>
+          <t>869170034885807</t>
         </is>
       </c>
       <c r="F1391" s="2" t="inlineStr">
         <is>
-          <t>00019200000013315005</t>
+          <t>00019200000013314980</t>
         </is>
       </c>
       <c r="G1391" s="2" t="inlineStr">
@@ -86706,12 +86706,12 @@
       </c>
       <c r="E1392" s="2" t="inlineStr">
         <is>
-          <t>869170034887332</t>
+          <t>869170035501999</t>
         </is>
       </c>
       <c r="F1392" s="2" t="inlineStr">
         <is>
-          <t>00019200000013315013</t>
+          <t>00019200000013314998</t>
         </is>
       </c>
       <c r="G1392" s="2" t="inlineStr">
@@ -86768,12 +86768,12 @@
       </c>
       <c r="E1393" s="2" t="inlineStr">
         <is>
-          <t>AS-0695</t>
+          <t>869170034886243</t>
         </is>
       </c>
       <c r="F1393" s="2" t="inlineStr">
         <is>
-          <t>00019200000013315021</t>
+          <t>00019200000013315005</t>
         </is>
       </c>
       <c r="G1393" s="2" t="inlineStr">
@@ -86830,12 +86830,12 @@
       </c>
       <c r="E1394" s="2" t="inlineStr">
         <is>
-          <t>869170034877499</t>
+          <t>869170034887332</t>
         </is>
       </c>
       <c r="F1394" s="2" t="inlineStr">
         <is>
-          <t>00019200000013315030</t>
+          <t>00019200000013315013</t>
         </is>
       </c>
       <c r="G1394" s="2" t="inlineStr">
@@ -86892,12 +86892,12 @@
       </c>
       <c r="E1395" s="2" t="inlineStr">
         <is>
-          <t>869170034889734</t>
+          <t>AS-0695</t>
         </is>
       </c>
       <c r="F1395" s="2" t="inlineStr">
         <is>
-          <t>00019200000013315048</t>
+          <t>00019200000013315021</t>
         </is>
       </c>
       <c r="G1395" s="2" t="inlineStr">
@@ -86954,12 +86954,12 @@
       </c>
       <c r="E1396" s="2" t="inlineStr">
         <is>
-          <t>869170034886110</t>
+          <t>869170034877499</t>
         </is>
       </c>
       <c r="F1396" s="2" t="inlineStr">
         <is>
-          <t>00019200000013315056</t>
+          <t>00019200000013315030</t>
         </is>
       </c>
       <c r="G1396" s="2" t="inlineStr">
@@ -87016,12 +87016,12 @@
       </c>
       <c r="E1397" s="2" t="inlineStr">
         <is>
-          <t>869170034886235</t>
+          <t>869170034889734</t>
         </is>
       </c>
       <c r="F1397" s="2" t="inlineStr">
         <is>
-          <t>00019200000013315064</t>
+          <t>00019200000013315048</t>
         </is>
       </c>
       <c r="G1397" s="2" t="inlineStr">
@@ -87078,12 +87078,12 @@
       </c>
       <c r="E1398" s="2" t="inlineStr">
         <is>
-          <t>869170034872896</t>
+          <t>869170034886110</t>
         </is>
       </c>
       <c r="F1398" s="2" t="inlineStr">
         <is>
-          <t>00019200000013315072</t>
+          <t>00019200000013315056</t>
         </is>
       </c>
       <c r="G1398" s="2" t="inlineStr">
@@ -87140,12 +87140,12 @@
       </c>
       <c r="E1399" s="2" t="inlineStr">
         <is>
-          <t>869170034876905</t>
+          <t>869170034886235</t>
         </is>
       </c>
       <c r="F1399" s="2" t="inlineStr">
         <is>
-          <t>00019200000013315080</t>
+          <t>00019200000013315064</t>
         </is>
       </c>
       <c r="G1399" s="2" t="inlineStr">
@@ -87202,12 +87202,12 @@
       </c>
       <c r="E1400" s="2" t="inlineStr">
         <is>
-          <t>869170034881301</t>
+          <t>869170034872896</t>
         </is>
       </c>
       <c r="F1400" s="2" t="inlineStr">
         <is>
-          <t>00019200000013315099</t>
+          <t>00019200000013315072</t>
         </is>
       </c>
       <c r="G1400" s="2" t="inlineStr">
@@ -87264,12 +87264,12 @@
       </c>
       <c r="E1401" s="2" t="inlineStr">
         <is>
-          <t>869170035510388</t>
+          <t>869170034876905</t>
         </is>
       </c>
       <c r="F1401" s="2" t="inlineStr">
         <is>
-          <t>00019200000013315102</t>
+          <t>00019200000013315080</t>
         </is>
       </c>
       <c r="G1401" s="2" t="inlineStr">
@@ -87326,12 +87326,12 @@
       </c>
       <c r="E1402" s="2" t="inlineStr">
         <is>
-          <t>869170034884198</t>
+          <t>869170034881301</t>
         </is>
       </c>
       <c r="F1402" s="2" t="inlineStr">
         <is>
-          <t>00019200000013315129</t>
+          <t>00019200000013315099</t>
         </is>
       </c>
       <c r="G1402" s="2" t="inlineStr">
@@ -87373,12 +87373,12 @@
       </c>
       <c r="B1403" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-90 C a -60 C</t>
         </is>
       </c>
       <c r="C1403" s="2" t="inlineStr">
         <is>
-          <t>559876</t>
+          <t>557500</t>
         </is>
       </c>
       <c r="D1403" s="2" t="inlineStr">
@@ -87388,12 +87388,12 @@
       </c>
       <c r="E1403" s="2" t="inlineStr">
         <is>
-          <t>A1817</t>
+          <t>869170035510388</t>
         </is>
       </c>
       <c r="F1403" s="2" t="inlineStr">
         <is>
-          <t>00019200000013419021</t>
+          <t>00019200000013315102</t>
         </is>
       </c>
       <c r="G1403" s="2" t="inlineStr">
@@ -87403,12 +87403,12 @@
       </c>
       <c r="H1403" s="2" t="inlineStr">
         <is>
-          <t>07/07/2026 00:57</t>
+          <t>25/06/2026 00:48</t>
         </is>
       </c>
       <c r="I1403" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026 15:00</t>
+          <t>26/06/2026 15:00</t>
         </is>
       </c>
       <c r="J1403" s="2" t="inlineStr">
@@ -87418,12 +87418,12 @@
       </c>
       <c r="K1403" s="2" t="inlineStr">
         <is>
-          <t>07/07/2026 00:57</t>
+          <t>25/06/2026 00:48</t>
         </is>
       </c>
       <c r="L1403" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026 15:00</t>
+          <t>26/06/2026 15:00</t>
         </is>
       </c>
     </row>
@@ -87435,12 +87435,12 @@
       </c>
       <c r="B1404" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-90 C a -60 C</t>
         </is>
       </c>
       <c r="C1404" s="2" t="inlineStr">
         <is>
-          <t>560503</t>
+          <t>557500</t>
         </is>
       </c>
       <c r="D1404" s="2" t="inlineStr">
@@ -87450,12 +87450,12 @@
       </c>
       <c r="E1404" s="2" t="inlineStr">
         <is>
-          <t>A0727</t>
+          <t>869170034884198</t>
         </is>
       </c>
       <c r="F1404" s="2" t="inlineStr">
         <is>
-          <t>00019200000013454420</t>
+          <t>00019200000013315129</t>
         </is>
       </c>
       <c r="G1404" s="2" t="inlineStr">
@@ -87465,12 +87465,12 @@
       </c>
       <c r="H1404" s="2" t="inlineStr">
         <is>
-          <t>15/07/2026 23:21</t>
+          <t>25/06/2026 00:48</t>
         </is>
       </c>
       <c r="I1404" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026 12:20</t>
+          <t>26/06/2026 15:00</t>
         </is>
       </c>
       <c r="J1404" s="2" t="inlineStr">
@@ -87480,12 +87480,12 @@
       </c>
       <c r="K1404" s="2" t="inlineStr">
         <is>
-          <t>15/07/2026 23:21</t>
+          <t>25/06/2026 00:48</t>
         </is>
       </c>
       <c r="L1404" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026 12:20</t>
+          <t>26/06/2026 15:00</t>
         </is>
       </c>
     </row>
@@ -87497,12 +87497,12 @@
       </c>
       <c r="B1405" s="2" t="inlineStr">
         <is>
-          <t>-90 C a -60 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1405" s="2" t="inlineStr">
         <is>
-          <t>560566</t>
+          <t>559876</t>
         </is>
       </c>
       <c r="D1405" s="2" t="inlineStr">
@@ -87512,12 +87512,12 @@
       </c>
       <c r="E1405" s="2" t="inlineStr">
         <is>
-          <t>300044</t>
+          <t>A1817</t>
         </is>
       </c>
       <c r="F1405" s="2" t="inlineStr">
         <is>
-          <t>00019200000013784048</t>
+          <t>00019200000013419021</t>
         </is>
       </c>
       <c r="G1405" s="2" t="inlineStr">
@@ -87527,12 +87527,12 @@
       </c>
       <c r="H1405" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026 02:39</t>
+          <t>07/07/2026 00:57</t>
         </is>
       </c>
       <c r="I1405" s="2" t="inlineStr">
         <is>
-          <t>05/08/2026 11:43</t>
+          <t>17/07/2026 15:00</t>
         </is>
       </c>
       <c r="J1405" s="2" t="inlineStr">
@@ -87542,12 +87542,12 @@
       </c>
       <c r="K1405" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026 02:39</t>
+          <t>07/07/2026 00:57</t>
         </is>
       </c>
       <c r="L1405" s="2" t="inlineStr">
         <is>
-          <t>05/08/2026 11:43</t>
+          <t>17/07/2026 15:00</t>
         </is>
       </c>
     </row>
@@ -87559,12 +87559,12 @@
       </c>
       <c r="B1406" s="2" t="inlineStr">
         <is>
-          <t>-90 C a -60 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1406" s="2" t="inlineStr">
         <is>
-          <t>560566</t>
+          <t>560503</t>
         </is>
       </c>
       <c r="D1406" s="2" t="inlineStr">
@@ -87574,12 +87574,12 @@
       </c>
       <c r="E1406" s="2" t="inlineStr">
         <is>
-          <t>869170034888124</t>
+          <t>A0727</t>
         </is>
       </c>
       <c r="F1406" s="2" t="inlineStr">
         <is>
-          <t>00019200000013784056</t>
+          <t>00019200000013454420</t>
         </is>
       </c>
       <c r="G1406" s="2" t="inlineStr">
@@ -87589,12 +87589,12 @@
       </c>
       <c r="H1406" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026 02:39</t>
+          <t>15/07/2026 23:21</t>
         </is>
       </c>
       <c r="I1406" s="2" t="inlineStr">
         <is>
-          <t>05/08/2026 11:43</t>
+          <t>17/07/2026 12:20</t>
         </is>
       </c>
       <c r="J1406" s="2" t="inlineStr">
@@ -87604,12 +87604,12 @@
       </c>
       <c r="K1406" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026 02:39</t>
+          <t>15/07/2026 23:21</t>
         </is>
       </c>
       <c r="L1406" s="2" t="inlineStr">
         <is>
-          <t>05/08/2026 11:43</t>
+          <t>17/07/2026 12:20</t>
         </is>
       </c>
     </row>
@@ -87636,12 +87636,12 @@
       </c>
       <c r="E1407" s="2" t="inlineStr">
         <is>
-          <t>869170034873522</t>
+          <t>300044</t>
         </is>
       </c>
       <c r="F1407" s="2" t="inlineStr">
         <is>
-          <t>00019200000013784064</t>
+          <t>00019200000013784048</t>
         </is>
       </c>
       <c r="G1407" s="2" t="inlineStr">
@@ -87698,12 +87698,12 @@
       </c>
       <c r="E1408" s="2" t="inlineStr">
         <is>
-          <t>869170034876368</t>
+          <t>869170034888124</t>
         </is>
       </c>
       <c r="F1408" s="2" t="inlineStr">
         <is>
-          <t>00019200000013784072</t>
+          <t>00019200000013784056</t>
         </is>
       </c>
       <c r="G1408" s="2" t="inlineStr">
@@ -87760,12 +87760,12 @@
       </c>
       <c r="E1409" s="2" t="inlineStr">
         <is>
-          <t>869170034889734</t>
+          <t>869170034873522</t>
         </is>
       </c>
       <c r="F1409" s="2" t="inlineStr">
         <is>
-          <t>00019200000013784080</t>
+          <t>00019200000013784064</t>
         </is>
       </c>
       <c r="G1409" s="2" t="inlineStr">
@@ -87822,12 +87822,12 @@
       </c>
       <c r="E1410" s="2" t="inlineStr">
         <is>
-          <t>869170034871708</t>
+          <t>869170034876368</t>
         </is>
       </c>
       <c r="F1410" s="2" t="inlineStr">
         <is>
-          <t>00019200000013784099</t>
+          <t>00019200000013784072</t>
         </is>
       </c>
       <c r="G1410" s="2" t="inlineStr">
@@ -87884,12 +87884,12 @@
       </c>
       <c r="E1411" s="2" t="inlineStr">
         <is>
-          <t>300176</t>
+          <t>869170034889734</t>
         </is>
       </c>
       <c r="F1411" s="2" t="inlineStr">
         <is>
-          <t>00019200000013784102</t>
+          <t>00019200000013784080</t>
         </is>
       </c>
       <c r="G1411" s="2" t="inlineStr">
@@ -87946,12 +87946,12 @@
       </c>
       <c r="E1412" s="2" t="inlineStr">
         <is>
-          <t>300029</t>
+          <t>869170034871708</t>
         </is>
       </c>
       <c r="F1412" s="2" t="inlineStr">
         <is>
-          <t>00019200000013784110</t>
+          <t>00019200000013784099</t>
         </is>
       </c>
       <c r="G1412" s="2" t="inlineStr">
@@ -88008,12 +88008,12 @@
       </c>
       <c r="E1413" s="2" t="inlineStr">
         <is>
-          <t>300034</t>
+          <t>300176</t>
         </is>
       </c>
       <c r="F1413" s="2" t="inlineStr">
         <is>
-          <t>00019200000013784129</t>
+          <t>00019200000013784102</t>
         </is>
       </c>
       <c r="G1413" s="2" t="inlineStr">
@@ -88070,12 +88070,12 @@
       </c>
       <c r="E1414" s="2" t="inlineStr">
         <is>
-          <t>300008</t>
+          <t>300029</t>
         </is>
       </c>
       <c r="F1414" s="2" t="inlineStr">
         <is>
-          <t>00019200000013784137</t>
+          <t>00019200000013784110</t>
         </is>
       </c>
       <c r="G1414" s="2" t="inlineStr">
@@ -88132,12 +88132,12 @@
       </c>
       <c r="E1415" s="2" t="inlineStr">
         <is>
-          <t>869170034878810</t>
+          <t>300034</t>
         </is>
       </c>
       <c r="F1415" s="2" t="inlineStr">
         <is>
-          <t>00019200000013784145</t>
+          <t>00019200000013784129</t>
         </is>
       </c>
       <c r="G1415" s="2" t="inlineStr">
@@ -88194,12 +88194,12 @@
       </c>
       <c r="E1416" s="2" t="inlineStr">
         <is>
-          <t>869170035491530</t>
+          <t>300008</t>
         </is>
       </c>
       <c r="F1416" s="2" t="inlineStr">
         <is>
-          <t>00019200000013784153</t>
+          <t>00019200000013784137</t>
         </is>
       </c>
       <c r="G1416" s="2" t="inlineStr">
@@ -88256,12 +88256,12 @@
       </c>
       <c r="E1417" s="2" t="inlineStr">
         <is>
-          <t>869170034887530</t>
+          <t>869170034878810</t>
         </is>
       </c>
       <c r="F1417" s="2" t="inlineStr">
         <is>
-          <t>00019200000013784161</t>
+          <t>00019200000013784145</t>
         </is>
       </c>
       <c r="G1417" s="2" t="inlineStr">
@@ -88318,12 +88318,12 @@
       </c>
       <c r="E1418" s="2" t="inlineStr">
         <is>
-          <t>869170034872300</t>
+          <t>869170035491530</t>
         </is>
       </c>
       <c r="F1418" s="2" t="inlineStr">
         <is>
-          <t>00019200000013789937</t>
+          <t>00019200000013784153</t>
         </is>
       </c>
       <c r="G1418" s="2" t="inlineStr">
@@ -88380,12 +88380,12 @@
       </c>
       <c r="E1419" s="2" t="inlineStr">
         <is>
-          <t>869170034875378</t>
+          <t>869170034887530</t>
         </is>
       </c>
       <c r="F1419" s="2" t="inlineStr">
         <is>
-          <t>00019200000013789945</t>
+          <t>00019200000013784161</t>
         </is>
       </c>
       <c r="G1419" s="2" t="inlineStr">
@@ -88442,12 +88442,12 @@
       </c>
       <c r="E1420" s="2" t="inlineStr">
         <is>
-          <t>869170034885583</t>
+          <t>869170034872300</t>
         </is>
       </c>
       <c r="F1420" s="2" t="inlineStr">
         <is>
-          <t>00019200000013789953</t>
+          <t>00019200000013789937</t>
         </is>
       </c>
       <c r="G1420" s="2" t="inlineStr">
@@ -88504,12 +88504,12 @@
       </c>
       <c r="E1421" s="2" t="inlineStr">
         <is>
-          <t>869170034886110</t>
+          <t>869170034875378</t>
         </is>
       </c>
       <c r="F1421" s="2" t="inlineStr">
         <is>
-          <t>00019200000013789961</t>
+          <t>00019200000013789945</t>
         </is>
       </c>
       <c r="G1421" s="2" t="inlineStr">
@@ -88566,12 +88566,12 @@
       </c>
       <c r="E1422" s="2" t="inlineStr">
         <is>
-          <t>869170034874447</t>
+          <t>869170034885583</t>
         </is>
       </c>
       <c r="F1422" s="2" t="inlineStr">
         <is>
-          <t>00019200000013789970</t>
+          <t>00019200000013789953</t>
         </is>
       </c>
       <c r="G1422" s="2" t="inlineStr">
@@ -88628,12 +88628,12 @@
       </c>
       <c r="E1423" s="2" t="inlineStr">
         <is>
-          <t>869170035510388</t>
+          <t>869170034886110</t>
         </is>
       </c>
       <c r="F1423" s="2" t="inlineStr">
         <is>
-          <t>00019200000013789988</t>
+          <t>00019200000013789961</t>
         </is>
       </c>
       <c r="G1423" s="2" t="inlineStr">
@@ -88675,12 +88675,12 @@
       </c>
       <c r="B1424" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-90 C a -60 C</t>
         </is>
       </c>
       <c r="C1424" s="2" t="inlineStr">
         <is>
-          <t>563130</t>
+          <t>560566</t>
         </is>
       </c>
       <c r="D1424" s="2" t="inlineStr">
@@ -88690,12 +88690,12 @@
       </c>
       <c r="E1424" s="2" t="inlineStr">
         <is>
-          <t>A9555</t>
+          <t>869170034874447</t>
         </is>
       </c>
       <c r="F1424" s="2" t="inlineStr">
         <is>
-          <t>00019200000013864106</t>
+          <t>00019200000013789970</t>
         </is>
       </c>
       <c r="G1424" s="2" t="inlineStr">
@@ -88705,12 +88705,12 @@
       </c>
       <c r="H1424" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026 23:39</t>
+          <t>04/08/2026 02:39</t>
         </is>
       </c>
       <c r="I1424" s="2" t="inlineStr">
         <is>
-          <t>05/08/2026 16:25</t>
+          <t>05/08/2026 11:43</t>
         </is>
       </c>
       <c r="J1424" s="2" t="inlineStr">
@@ -88720,12 +88720,12 @@
       </c>
       <c r="K1424" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026 23:39</t>
+          <t>04/08/2026 02:39</t>
         </is>
       </c>
       <c r="L1424" s="2" t="inlineStr">
         <is>
-          <t>05/08/2026 16:02</t>
+          <t>05/08/2026 11:43</t>
         </is>
       </c>
     </row>
@@ -88737,12 +88737,12 @@
       </c>
       <c r="B1425" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-90 C a -60 C</t>
         </is>
       </c>
       <c r="C1425" s="2" t="inlineStr">
         <is>
-          <t>563130</t>
+          <t>560566</t>
         </is>
       </c>
       <c r="D1425" s="2" t="inlineStr">
@@ -88752,12 +88752,12 @@
       </c>
       <c r="E1425" s="2" t="inlineStr">
         <is>
-          <t>A6073</t>
+          <t>869170035510388</t>
         </is>
       </c>
       <c r="F1425" s="2" t="inlineStr">
         <is>
-          <t>00019200000013864114</t>
+          <t>00019200000013789988</t>
         </is>
       </c>
       <c r="G1425" s="2" t="inlineStr">
@@ -88767,12 +88767,12 @@
       </c>
       <c r="H1425" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026 23:39</t>
+          <t>04/08/2026 02:39</t>
         </is>
       </c>
       <c r="I1425" s="2" t="inlineStr">
         <is>
-          <t>05/08/2026 16:25</t>
+          <t>05/08/2026 11:43</t>
         </is>
       </c>
       <c r="J1425" s="2" t="inlineStr">
@@ -88782,12 +88782,12 @@
       </c>
       <c r="K1425" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026 23:39</t>
+          <t>04/08/2026 02:39</t>
         </is>
       </c>
       <c r="L1425" s="2" t="inlineStr">
         <is>
-          <t>05/08/2026 16:02</t>
+          <t>05/08/2026 11:43</t>
         </is>
       </c>
     </row>
@@ -88799,12 +88799,12 @@
       </c>
       <c r="B1426" s="2" t="inlineStr">
         <is>
-          <t>-90 C a -60 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1426" s="2" t="inlineStr">
         <is>
-          <t>564098</t>
+          <t>563130</t>
         </is>
       </c>
       <c r="D1426" s="2" t="inlineStr">
@@ -88814,12 +88814,12 @@
       </c>
       <c r="E1426" s="2" t="inlineStr">
         <is>
-          <t>AS-0511</t>
+          <t>A9555</t>
         </is>
       </c>
       <c r="F1426" s="2" t="inlineStr">
         <is>
-          <t>00019200000014046407</t>
+          <t>00019200000013864106</t>
         </is>
       </c>
       <c r="G1426" s="2" t="inlineStr">
@@ -88829,12 +88829,12 @@
       </c>
       <c r="H1426" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026 22:28</t>
+          <t>04/08/2026 23:39</t>
         </is>
       </c>
       <c r="I1426" s="2" t="inlineStr">
         <is>
-          <t>25/08/2026 16:10</t>
+          <t>05/08/2026 16:25</t>
         </is>
       </c>
       <c r="J1426" s="2" t="inlineStr">
@@ -88844,12 +88844,12 @@
       </c>
       <c r="K1426" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026 22:28</t>
+          <t>04/08/2026 23:39</t>
         </is>
       </c>
       <c r="L1426" s="2" t="inlineStr">
         <is>
-          <t>25/08/2026 16:10</t>
+          <t>05/08/2026 16:02</t>
         </is>
       </c>
     </row>
@@ -88861,12 +88861,12 @@
       </c>
       <c r="B1427" s="2" t="inlineStr">
         <is>
-          <t>-90 C a -60 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1427" s="2" t="inlineStr">
         <is>
-          <t>564098</t>
+          <t>563130</t>
         </is>
       </c>
       <c r="D1427" s="2" t="inlineStr">
@@ -88876,12 +88876,12 @@
       </c>
       <c r="E1427" s="2" t="inlineStr">
         <is>
-          <t>AS-0426</t>
+          <t>A6073</t>
         </is>
       </c>
       <c r="F1427" s="2" t="inlineStr">
         <is>
-          <t>00019200000014046415</t>
+          <t>00019200000013864114</t>
         </is>
       </c>
       <c r="G1427" s="2" t="inlineStr">
@@ -88891,12 +88891,12 @@
       </c>
       <c r="H1427" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026 22:28</t>
+          <t>04/08/2026 23:39</t>
         </is>
       </c>
       <c r="I1427" s="2" t="inlineStr">
         <is>
-          <t>25/08/2026 16:10</t>
+          <t>05/08/2026 16:25</t>
         </is>
       </c>
       <c r="J1427" s="2" t="inlineStr">
@@ -88906,12 +88906,12 @@
       </c>
       <c r="K1427" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026 22:28</t>
+          <t>04/08/2026 23:39</t>
         </is>
       </c>
       <c r="L1427" s="2" t="inlineStr">
         <is>
-          <t>25/08/2026 16:10</t>
+          <t>05/08/2026 16:02</t>
         </is>
       </c>
     </row>
@@ -88938,12 +88938,12 @@
       </c>
       <c r="E1428" s="2" t="inlineStr">
         <is>
-          <t>300075</t>
+          <t>AS-0511</t>
         </is>
       </c>
       <c r="F1428" s="2" t="inlineStr">
         <is>
-          <t>00019200000014046423</t>
+          <t>00019200000014046407</t>
         </is>
       </c>
       <c r="G1428" s="2" t="inlineStr">
@@ -89000,12 +89000,12 @@
       </c>
       <c r="E1429" s="2" t="inlineStr">
         <is>
-          <t>AS-0616</t>
+          <t>AS-0426</t>
         </is>
       </c>
       <c r="F1429" s="2" t="inlineStr">
         <is>
-          <t>00019200000014046431</t>
+          <t>00019200000014046415</t>
         </is>
       </c>
       <c r="G1429" s="2" t="inlineStr">
@@ -89047,12 +89047,12 @@
       </c>
       <c r="B1430" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-90 C a -60 C</t>
         </is>
       </c>
       <c r="C1430" s="2" t="inlineStr">
         <is>
-          <t>567132</t>
+          <t>564098</t>
         </is>
       </c>
       <c r="D1430" s="2" t="inlineStr">
@@ -89062,12 +89062,12 @@
       </c>
       <c r="E1430" s="2" t="inlineStr">
         <is>
-          <t>A6358</t>
+          <t>300075</t>
         </is>
       </c>
       <c r="F1430" s="2" t="inlineStr">
         <is>
-          <t>00019200000014266300</t>
+          <t>00019200000014046423</t>
         </is>
       </c>
       <c r="G1430" s="2" t="inlineStr">
@@ -89077,12 +89077,12 @@
       </c>
       <c r="H1430" s="2" t="inlineStr">
         <is>
-          <t>13/09/2026 00:16</t>
+          <t>24/08/2026 22:28</t>
         </is>
       </c>
       <c r="I1430" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>25/08/2026 16:10</t>
         </is>
       </c>
       <c r="J1430" s="2" t="inlineStr">
@@ -89092,12 +89092,12 @@
       </c>
       <c r="K1430" s="2" t="inlineStr">
         <is>
-          <t>13/09/2026 00:16</t>
+          <t>24/08/2026 22:28</t>
         </is>
       </c>
       <c r="L1430" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>25/08/2026 16:10</t>
         </is>
       </c>
     </row>
@@ -89109,12 +89109,12 @@
       </c>
       <c r="B1431" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-90 C a -60 C</t>
         </is>
       </c>
       <c r="C1431" s="2" t="inlineStr">
         <is>
-          <t>567132</t>
+          <t>564098</t>
         </is>
       </c>
       <c r="D1431" s="2" t="inlineStr">
@@ -89124,12 +89124,12 @@
       </c>
       <c r="E1431" s="2" t="inlineStr">
         <is>
-          <t>A7142</t>
+          <t>AS-0616</t>
         </is>
       </c>
       <c r="F1431" s="2" t="inlineStr">
         <is>
-          <t>00019200000014266334</t>
+          <t>00019200000014046431</t>
         </is>
       </c>
       <c r="G1431" s="2" t="inlineStr">
@@ -89139,12 +89139,12 @@
       </c>
       <c r="H1431" s="2" t="inlineStr">
         <is>
-          <t>13/09/2026 00:16</t>
+          <t>24/08/2026 22:28</t>
         </is>
       </c>
       <c r="I1431" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>25/08/2026 16:10</t>
         </is>
       </c>
       <c r="J1431" s="2" t="inlineStr">
@@ -89154,12 +89154,12 @@
       </c>
       <c r="K1431" s="2" t="inlineStr">
         <is>
-          <t>13/09/2026 00:16</t>
+          <t>24/08/2026 22:28</t>
         </is>
       </c>
       <c r="L1431" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>25/08/2026 16:10</t>
         </is>
       </c>
     </row>
@@ -89171,42 +89171,42 @@
       </c>
       <c r="B1432" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1432" s="2" t="inlineStr">
         <is>
-          <t>556179</t>
+          <t>567132</t>
         </is>
       </c>
       <c r="D1432" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="E1432" s="2" t="inlineStr">
         <is>
-          <t>S1241</t>
+          <t>A6358</t>
         </is>
       </c>
       <c r="F1432" s="2" t="inlineStr">
         <is>
-          <t>00019200000012717746</t>
+          <t>00019200000014266300</t>
         </is>
       </c>
       <c r="G1432" s="2" t="inlineStr">
         <is>
-          <t>Rodoviário</t>
+          <t>MultiModal</t>
         </is>
       </c>
       <c r="H1432" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 04:02</t>
+          <t>13/09/2026 00:16</t>
         </is>
       </c>
       <c r="I1432" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026 13:13</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J1432" s="2" t="inlineStr">
@@ -89216,12 +89216,12 @@
       </c>
       <c r="K1432" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 04:02</t>
+          <t>13/09/2026 00:16</t>
         </is>
       </c>
       <c r="L1432" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026 13:13</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -89238,37 +89238,37 @@
       </c>
       <c r="C1433" s="2" t="inlineStr">
         <is>
-          <t>556179</t>
+          <t>567132</t>
         </is>
       </c>
       <c r="D1433" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="E1433" s="2" t="inlineStr">
         <is>
-          <t>S1104</t>
+          <t>A7142</t>
         </is>
       </c>
       <c r="F1433" s="2" t="inlineStr">
         <is>
-          <t>00019200000012717754</t>
+          <t>00019200000014266334</t>
         </is>
       </c>
       <c r="G1433" s="2" t="inlineStr">
         <is>
-          <t>Rodoviário</t>
+          <t>MultiModal</t>
         </is>
       </c>
       <c r="H1433" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 04:02</t>
+          <t>13/09/2026 00:16</t>
         </is>
       </c>
       <c r="I1433" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026 13:13</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J1433" s="2" t="inlineStr">
@@ -89278,12 +89278,12 @@
       </c>
       <c r="K1433" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 04:02</t>
+          <t>13/09/2026 00:16</t>
         </is>
       </c>
       <c r="L1433" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026 13:13</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -89295,12 +89295,12 @@
       </c>
       <c r="B1434" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1434" s="2" t="inlineStr">
         <is>
-          <t>556298</t>
+          <t>556179</t>
         </is>
       </c>
       <c r="D1434" s="2" t="inlineStr">
@@ -89310,12 +89310,12 @@
       </c>
       <c r="E1434" s="2" t="inlineStr">
         <is>
-          <t>S0799</t>
+          <t>S1241</t>
         </is>
       </c>
       <c r="F1434" s="2" t="inlineStr">
         <is>
-          <t>00019200000012902039</t>
+          <t>00019200000012717746</t>
         </is>
       </c>
       <c r="G1434" s="2" t="inlineStr">
@@ -89325,12 +89325,12 @@
       </c>
       <c r="H1434" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 04:26</t>
+          <t>18/06/2026 04:02</t>
         </is>
       </c>
       <c r="I1434" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 14:58</t>
+          <t>22/06/2026 13:13</t>
         </is>
       </c>
       <c r="J1434" s="2" t="inlineStr">
@@ -89340,12 +89340,12 @@
       </c>
       <c r="K1434" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 04:26</t>
+          <t>18/06/2026 04:02</t>
         </is>
       </c>
       <c r="L1434" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 14:58</t>
+          <t>22/06/2026 13:13</t>
         </is>
       </c>
     </row>
@@ -89357,12 +89357,12 @@
       </c>
       <c r="B1435" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1435" s="2" t="inlineStr">
         <is>
-          <t>556298</t>
+          <t>556179</t>
         </is>
       </c>
       <c r="D1435" s="2" t="inlineStr">
@@ -89372,12 +89372,12 @@
       </c>
       <c r="E1435" s="2" t="inlineStr">
         <is>
-          <t>A5190</t>
+          <t>S1104</t>
         </is>
       </c>
       <c r="F1435" s="2" t="inlineStr">
         <is>
-          <t>00019200000012902047</t>
+          <t>00019200000012717754</t>
         </is>
       </c>
       <c r="G1435" s="2" t="inlineStr">
@@ -89387,12 +89387,12 @@
       </c>
       <c r="H1435" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 04:26</t>
+          <t>18/06/2026 04:02</t>
         </is>
       </c>
       <c r="I1435" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 14:58</t>
+          <t>22/06/2026 13:13</t>
         </is>
       </c>
       <c r="J1435" s="2" t="inlineStr">
@@ -89402,12 +89402,12 @@
       </c>
       <c r="K1435" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 04:26</t>
+          <t>18/06/2026 04:02</t>
         </is>
       </c>
       <c r="L1435" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 14:58</t>
+          <t>22/06/2026 13:13</t>
         </is>
       </c>
     </row>
@@ -89434,12 +89434,12 @@
       </c>
       <c r="E1436" s="2" t="inlineStr">
         <is>
-          <t>A6396</t>
+          <t>S0799</t>
         </is>
       </c>
       <c r="F1436" s="2" t="inlineStr">
         <is>
-          <t>00019200000012902250</t>
+          <t>00019200000012902039</t>
         </is>
       </c>
       <c r="G1436" s="2" t="inlineStr">
@@ -89481,12 +89481,12 @@
       </c>
       <c r="B1437" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1437" s="2" t="inlineStr">
         <is>
-          <t>556589</t>
+          <t>556298</t>
         </is>
       </c>
       <c r="D1437" s="2" t="inlineStr">
@@ -89496,12 +89496,12 @@
       </c>
       <c r="E1437" s="2" t="inlineStr">
         <is>
-          <t>S1581</t>
+          <t>A5190</t>
         </is>
       </c>
       <c r="F1437" s="2" t="inlineStr">
         <is>
-          <t>00019200000012920509</t>
+          <t>00019200000012902047</t>
         </is>
       </c>
       <c r="G1437" s="2" t="inlineStr">
@@ -89511,12 +89511,12 @@
       </c>
       <c r="H1437" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 04:02</t>
+          <t>18/06/2026 04:26</t>
         </is>
       </c>
       <c r="I1437" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 09:51</t>
+          <t>18/06/2026 14:58</t>
         </is>
       </c>
       <c r="J1437" s="2" t="inlineStr">
@@ -89526,12 +89526,12 @@
       </c>
       <c r="K1437" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 04:02</t>
+          <t>18/06/2026 04:26</t>
         </is>
       </c>
       <c r="L1437" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 09:51</t>
+          <t>18/06/2026 14:58</t>
         </is>
       </c>
     </row>
@@ -89543,12 +89543,12 @@
       </c>
       <c r="B1438" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1438" s="2" t="inlineStr">
         <is>
-          <t>556589</t>
+          <t>556298</t>
         </is>
       </c>
       <c r="D1438" s="2" t="inlineStr">
@@ -89558,12 +89558,12 @@
       </c>
       <c r="E1438" s="2" t="inlineStr">
         <is>
-          <t>S1148</t>
+          <t>A6396</t>
         </is>
       </c>
       <c r="F1438" s="2" t="inlineStr">
         <is>
-          <t>00019200000012920517</t>
+          <t>00019200000012902250</t>
         </is>
       </c>
       <c r="G1438" s="2" t="inlineStr">
@@ -89573,12 +89573,12 @@
       </c>
       <c r="H1438" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 04:02</t>
+          <t>18/06/2026 04:26</t>
         </is>
       </c>
       <c r="I1438" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 09:51</t>
+          <t>18/06/2026 14:58</t>
         </is>
       </c>
       <c r="J1438" s="2" t="inlineStr">
@@ -89588,12 +89588,12 @@
       </c>
       <c r="K1438" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 04:02</t>
+          <t>18/06/2026 04:26</t>
         </is>
       </c>
       <c r="L1438" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 09:51</t>
+          <t>18/06/2026 14:58</t>
         </is>
       </c>
     </row>
@@ -89620,12 +89620,12 @@
       </c>
       <c r="E1439" s="2" t="inlineStr">
         <is>
-          <t>S1240</t>
+          <t>S1581</t>
         </is>
       </c>
       <c r="F1439" s="2" t="inlineStr">
         <is>
-          <t>00019200000012920525</t>
+          <t>00019200000012920509</t>
         </is>
       </c>
       <c r="G1439" s="2" t="inlineStr">
@@ -89672,7 +89672,7 @@
       </c>
       <c r="C1440" s="2" t="inlineStr">
         <is>
-          <t>556709</t>
+          <t>556589</t>
         </is>
       </c>
       <c r="D1440" s="2" t="inlineStr">
@@ -89682,12 +89682,12 @@
       </c>
       <c r="E1440" s="2" t="inlineStr">
         <is>
-          <t>A8669</t>
+          <t>S1148</t>
         </is>
       </c>
       <c r="F1440" s="2" t="inlineStr">
         <is>
-          <t>00019200000012697516</t>
+          <t>00019200000012920517</t>
         </is>
       </c>
       <c r="G1440" s="2" t="inlineStr">
@@ -89697,12 +89697,12 @@
       </c>
       <c r="H1440" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026 07:53</t>
+          <t>18/06/2026 04:02</t>
         </is>
       </c>
       <c r="I1440" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026 17:21</t>
+          <t>18/06/2026 09:51</t>
         </is>
       </c>
       <c r="J1440" s="2" t="inlineStr">
@@ -89712,12 +89712,12 @@
       </c>
       <c r="K1440" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026 07:53</t>
+          <t>18/06/2026 04:02</t>
         </is>
       </c>
       <c r="L1440" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026 17:21</t>
+          <t>18/06/2026 09:51</t>
         </is>
       </c>
     </row>
@@ -89734,7 +89734,7 @@
       </c>
       <c r="C1441" s="2" t="inlineStr">
         <is>
-          <t>556717</t>
+          <t>556589</t>
         </is>
       </c>
       <c r="D1441" s="2" t="inlineStr">
@@ -89744,12 +89744,12 @@
       </c>
       <c r="E1441" s="2" t="inlineStr">
         <is>
-          <t>S0867</t>
+          <t>S1240</t>
         </is>
       </c>
       <c r="F1441" s="2" t="inlineStr">
         <is>
-          <t>00019200000012698873</t>
+          <t>00019200000012920525</t>
         </is>
       </c>
       <c r="G1441" s="2" t="inlineStr">
@@ -89759,12 +89759,12 @@
       </c>
       <c r="H1441" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 04:28</t>
+          <t>18/06/2026 04:02</t>
         </is>
       </c>
       <c r="I1441" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 14:12</t>
+          <t>18/06/2026 09:51</t>
         </is>
       </c>
       <c r="J1441" s="2" t="inlineStr">
@@ -89774,12 +89774,12 @@
       </c>
       <c r="K1441" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 04:28</t>
+          <t>18/06/2026 04:02</t>
         </is>
       </c>
       <c r="L1441" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 14:12</t>
+          <t>18/06/2026 09:51</t>
         </is>
       </c>
     </row>
@@ -89796,7 +89796,7 @@
       </c>
       <c r="C1442" s="2" t="inlineStr">
         <is>
-          <t>556830</t>
+          <t>556709</t>
         </is>
       </c>
       <c r="D1442" s="2" t="inlineStr">
@@ -89806,12 +89806,12 @@
       </c>
       <c r="E1442" s="2" t="inlineStr">
         <is>
-          <t>A9259</t>
+          <t>A8669</t>
         </is>
       </c>
       <c r="F1442" s="2" t="inlineStr">
         <is>
-          <t>00019200000012700339</t>
+          <t>00019200000012697516</t>
         </is>
       </c>
       <c r="G1442" s="2" t="inlineStr">
@@ -89821,12 +89821,12 @@
       </c>
       <c r="H1442" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 06:51</t>
+          <t>16/06/2026 07:53</t>
         </is>
       </c>
       <c r="I1442" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 11:06</t>
+          <t>16/06/2026 17:21</t>
         </is>
       </c>
       <c r="J1442" s="2" t="inlineStr">
@@ -89836,12 +89836,12 @@
       </c>
       <c r="K1442" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 06:51</t>
+          <t>16/06/2026 07:53</t>
         </is>
       </c>
       <c r="L1442" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 11:06</t>
+          <t>16/06/2026 17:21</t>
         </is>
       </c>
     </row>
@@ -89858,7 +89858,7 @@
       </c>
       <c r="C1443" s="2" t="inlineStr">
         <is>
-          <t>556830</t>
+          <t>556717</t>
         </is>
       </c>
       <c r="D1443" s="2" t="inlineStr">
@@ -89868,12 +89868,12 @@
       </c>
       <c r="E1443" s="2" t="inlineStr">
         <is>
-          <t>A7875</t>
+          <t>S0867</t>
         </is>
       </c>
       <c r="F1443" s="2" t="inlineStr">
         <is>
-          <t>00019200000012700347</t>
+          <t>00019200000012698873</t>
         </is>
       </c>
       <c r="G1443" s="2" t="inlineStr">
@@ -89883,12 +89883,12 @@
       </c>
       <c r="H1443" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 06:51</t>
+          <t>18/06/2026 04:28</t>
         </is>
       </c>
       <c r="I1443" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 11:06</t>
+          <t>18/06/2026 14:12</t>
         </is>
       </c>
       <c r="J1443" s="2" t="inlineStr">
@@ -89898,12 +89898,12 @@
       </c>
       <c r="K1443" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 06:51</t>
+          <t>18/06/2026 04:28</t>
         </is>
       </c>
       <c r="L1443" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 11:06</t>
+          <t>18/06/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -89930,12 +89930,12 @@
       </c>
       <c r="E1444" s="2" t="inlineStr">
         <is>
-          <t>A3534</t>
+          <t>A9259</t>
         </is>
       </c>
       <c r="F1444" s="2" t="inlineStr">
         <is>
-          <t>00019200000012700355</t>
+          <t>00019200000012700339</t>
         </is>
       </c>
       <c r="G1444" s="2" t="inlineStr">
@@ -89992,12 +89992,12 @@
       </c>
       <c r="E1445" s="2" t="inlineStr">
         <is>
-          <t>A9236</t>
+          <t>A7875</t>
         </is>
       </c>
       <c r="F1445" s="2" t="inlineStr">
         <is>
-          <t>00019200000012700363</t>
+          <t>00019200000012700347</t>
         </is>
       </c>
       <c r="G1445" s="2" t="inlineStr">
@@ -90054,12 +90054,12 @@
       </c>
       <c r="E1446" s="2" t="inlineStr">
         <is>
-          <t>TA1031</t>
+          <t>A3534</t>
         </is>
       </c>
       <c r="F1446" s="2" t="inlineStr">
         <is>
-          <t>00019200000012700371</t>
+          <t>00019200000012700355</t>
         </is>
       </c>
       <c r="G1446" s="2" t="inlineStr">
@@ -90116,12 +90116,12 @@
       </c>
       <c r="E1447" s="2" t="inlineStr">
         <is>
-          <t>A7551</t>
+          <t>A9236</t>
         </is>
       </c>
       <c r="F1447" s="2" t="inlineStr">
         <is>
-          <t>00019200000012700380</t>
+          <t>00019200000012700363</t>
         </is>
       </c>
       <c r="G1447" s="2" t="inlineStr">
@@ -90178,12 +90178,12 @@
       </c>
       <c r="E1448" s="2" t="inlineStr">
         <is>
-          <t>A6780</t>
+          <t>TA1031</t>
         </is>
       </c>
       <c r="F1448" s="2" t="inlineStr">
         <is>
-          <t>00019200000012919772</t>
+          <t>00019200000012700371</t>
         </is>
       </c>
       <c r="G1448" s="2" t="inlineStr">
@@ -90240,12 +90240,12 @@
       </c>
       <c r="E1449" s="2" t="inlineStr">
         <is>
-          <t>A2410</t>
+          <t>A7551</t>
         </is>
       </c>
       <c r="F1449" s="2" t="inlineStr">
         <is>
-          <t>00019200000012919780</t>
+          <t>00019200000012700380</t>
         </is>
       </c>
       <c r="G1449" s="2" t="inlineStr">
@@ -90302,12 +90302,12 @@
       </c>
       <c r="E1450" s="2" t="inlineStr">
         <is>
-          <t>A4901</t>
+          <t>A6780</t>
         </is>
       </c>
       <c r="F1450" s="2" t="inlineStr">
         <is>
-          <t>00019200000012919799</t>
+          <t>00019200000012919772</t>
         </is>
       </c>
       <c r="G1450" s="2" t="inlineStr">
@@ -90364,12 +90364,12 @@
       </c>
       <c r="E1451" s="2" t="inlineStr">
         <is>
-          <t>A3268</t>
+          <t>A2410</t>
         </is>
       </c>
       <c r="F1451" s="2" t="inlineStr">
         <is>
-          <t>00019200000012919802</t>
+          <t>00019200000012919780</t>
         </is>
       </c>
       <c r="G1451" s="2" t="inlineStr">
@@ -90426,12 +90426,12 @@
       </c>
       <c r="E1452" s="2" t="inlineStr">
         <is>
-          <t>TA0999</t>
+          <t>A4901</t>
         </is>
       </c>
       <c r="F1452" s="2" t="inlineStr">
         <is>
-          <t>00019200000012919810</t>
+          <t>00019200000012919799</t>
         </is>
       </c>
       <c r="G1452" s="2" t="inlineStr">
@@ -90488,12 +90488,12 @@
       </c>
       <c r="E1453" s="2" t="inlineStr">
         <is>
-          <t>A6294</t>
+          <t>A3268</t>
         </is>
       </c>
       <c r="F1453" s="2" t="inlineStr">
         <is>
-          <t>00019200000012919829</t>
+          <t>00019200000012919802</t>
         </is>
       </c>
       <c r="G1453" s="2" t="inlineStr">
@@ -90550,12 +90550,12 @@
       </c>
       <c r="E1454" s="2" t="inlineStr">
         <is>
-          <t>A5228</t>
+          <t>TA0999</t>
         </is>
       </c>
       <c r="F1454" s="2" t="inlineStr">
         <is>
-          <t>00019200000012919837</t>
+          <t>00019200000012919810</t>
         </is>
       </c>
       <c r="G1454" s="2" t="inlineStr">
@@ -90612,12 +90612,12 @@
       </c>
       <c r="E1455" s="2" t="inlineStr">
         <is>
-          <t>A3522</t>
+          <t>A6294</t>
         </is>
       </c>
       <c r="F1455" s="2" t="inlineStr">
         <is>
-          <t>00019200000012919845</t>
+          <t>00019200000012919829</t>
         </is>
       </c>
       <c r="G1455" s="2" t="inlineStr">
@@ -90674,12 +90674,12 @@
       </c>
       <c r="E1456" s="2" t="inlineStr">
         <is>
-          <t>A4356</t>
+          <t>A5228</t>
         </is>
       </c>
       <c r="F1456" s="2" t="inlineStr">
         <is>
-          <t>00019200000012919853</t>
+          <t>00019200000012919837</t>
         </is>
       </c>
       <c r="G1456" s="2" t="inlineStr">
@@ -90736,12 +90736,12 @@
       </c>
       <c r="E1457" s="2" t="inlineStr">
         <is>
-          <t>A6501</t>
+          <t>A3522</t>
         </is>
       </c>
       <c r="F1457" s="2" t="inlineStr">
         <is>
-          <t>00019200000012919861</t>
+          <t>00019200000012919845</t>
         </is>
       </c>
       <c r="G1457" s="2" t="inlineStr">
@@ -90798,12 +90798,12 @@
       </c>
       <c r="E1458" s="2" t="inlineStr">
         <is>
-          <t>TA0769</t>
+          <t>A4356</t>
         </is>
       </c>
       <c r="F1458" s="2" t="inlineStr">
         <is>
-          <t>00019200000012919870</t>
+          <t>00019200000012919853</t>
         </is>
       </c>
       <c r="G1458" s="2" t="inlineStr">
@@ -90860,12 +90860,12 @@
       </c>
       <c r="E1459" s="2" t="inlineStr">
         <is>
-          <t>TA0286</t>
+          <t>A6501</t>
         </is>
       </c>
       <c r="F1459" s="2" t="inlineStr">
         <is>
-          <t>00019200000012919888</t>
+          <t>00019200000012919861</t>
         </is>
       </c>
       <c r="G1459" s="2" t="inlineStr">
@@ -90912,7 +90912,7 @@
       </c>
       <c r="C1460" s="2" t="inlineStr">
         <is>
-          <t>557178</t>
+          <t>556830</t>
         </is>
       </c>
       <c r="D1460" s="2" t="inlineStr">
@@ -90922,12 +90922,12 @@
       </c>
       <c r="E1460" s="2" t="inlineStr">
         <is>
-          <t>S0656</t>
+          <t>TA0769</t>
         </is>
       </c>
       <c r="F1460" s="2" t="inlineStr">
         <is>
-          <t>00019200000012685836</t>
+          <t>00019200000012919870</t>
         </is>
       </c>
       <c r="G1460" s="2" t="inlineStr">
@@ -90937,12 +90937,12 @@
       </c>
       <c r="H1460" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 06:54</t>
+          <t>18/06/2026 06:51</t>
         </is>
       </c>
       <c r="I1460" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 14:56</t>
+          <t>18/06/2026 11:06</t>
         </is>
       </c>
       <c r="J1460" s="2" t="inlineStr">
@@ -90952,12 +90952,12 @@
       </c>
       <c r="K1460" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 06:54</t>
+          <t>18/06/2026 06:51</t>
         </is>
       </c>
       <c r="L1460" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 14:56</t>
+          <t>18/06/2026 11:06</t>
         </is>
       </c>
     </row>
@@ -90969,12 +90969,12 @@
       </c>
       <c r="B1461" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1461" s="2" t="inlineStr">
         <is>
-          <t>559319</t>
+          <t>556830</t>
         </is>
       </c>
       <c r="D1461" s="2" t="inlineStr">
@@ -90984,12 +90984,12 @@
       </c>
       <c r="E1461" s="2" t="inlineStr">
         <is>
-          <t>A8356</t>
+          <t>TA0286</t>
         </is>
       </c>
       <c r="F1461" s="2" t="inlineStr">
         <is>
-          <t>00019200000013247638</t>
+          <t>00019200000012919888</t>
         </is>
       </c>
       <c r="G1461" s="2" t="inlineStr">
@@ -90999,12 +90999,12 @@
       </c>
       <c r="H1461" s="2" t="inlineStr">
         <is>
-          <t>01/07/2026 03:55</t>
+          <t>18/06/2026 06:51</t>
         </is>
       </c>
       <c r="I1461" s="2" t="inlineStr">
         <is>
-          <t>01/07/2026 13:54</t>
+          <t>18/06/2026 11:06</t>
         </is>
       </c>
       <c r="J1461" s="2" t="inlineStr">
@@ -91014,12 +91014,12 @@
       </c>
       <c r="K1461" s="2" t="inlineStr">
         <is>
-          <t>01/07/2026 03:55</t>
+          <t>18/06/2026 06:51</t>
         </is>
       </c>
       <c r="L1461" s="2" t="inlineStr">
         <is>
-          <t>01/07/2026 13:54</t>
+          <t>18/06/2026 11:06</t>
         </is>
       </c>
     </row>
@@ -91031,12 +91031,12 @@
       </c>
       <c r="B1462" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1462" s="2" t="inlineStr">
         <is>
-          <t>559697</t>
+          <t>557178</t>
         </is>
       </c>
       <c r="D1462" s="2" t="inlineStr">
@@ -91046,12 +91046,12 @@
       </c>
       <c r="E1462" s="2" t="inlineStr">
         <is>
-          <t>A5033</t>
+          <t>S0656</t>
         </is>
       </c>
       <c r="F1462" s="2" t="inlineStr">
         <is>
-          <t>00019200000013422723</t>
+          <t>00019200000012685836</t>
         </is>
       </c>
       <c r="G1462" s="2" t="inlineStr">
@@ -91061,12 +91061,12 @@
       </c>
       <c r="H1462" s="2" t="inlineStr">
         <is>
-          <t>03/07/2026 05:14</t>
+          <t>18/06/2026 06:54</t>
         </is>
       </c>
       <c r="I1462" s="2" t="inlineStr">
         <is>
-          <t>03/07/2026 12:42</t>
+          <t>18/06/2026 14:56</t>
         </is>
       </c>
       <c r="J1462" s="2" t="inlineStr">
@@ -91076,12 +91076,12 @@
       </c>
       <c r="K1462" s="2" t="inlineStr">
         <is>
-          <t>03/07/2026 05:14</t>
+          <t>18/06/2026 06:54</t>
         </is>
       </c>
       <c r="L1462" s="2" t="inlineStr">
         <is>
-          <t>03/07/2026 12:42</t>
+          <t>18/06/2026 14:56</t>
         </is>
       </c>
     </row>
@@ -91098,7 +91098,7 @@
       </c>
       <c r="C1463" s="2" t="inlineStr">
         <is>
-          <t>559870</t>
+          <t>559319</t>
         </is>
       </c>
       <c r="D1463" s="2" t="inlineStr">
@@ -91108,12 +91108,12 @@
       </c>
       <c r="E1463" s="2" t="inlineStr">
         <is>
-          <t>A5209</t>
+          <t>A8356</t>
         </is>
       </c>
       <c r="F1463" s="2" t="inlineStr">
         <is>
-          <t>00019200000013415280</t>
+          <t>00019200000013247638</t>
         </is>
       </c>
       <c r="G1463" s="2" t="inlineStr">
@@ -91123,12 +91123,12 @@
       </c>
       <c r="H1463" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026 04:54</t>
+          <t>01/07/2026 03:55</t>
         </is>
       </c>
       <c r="I1463" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026 10:18</t>
+          <t>01/07/2026 13:54</t>
         </is>
       </c>
       <c r="J1463" s="2" t="inlineStr">
@@ -91138,12 +91138,12 @@
       </c>
       <c r="K1463" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026 04:54</t>
+          <t>01/07/2026 03:55</t>
         </is>
       </c>
       <c r="L1463" s="2" t="inlineStr">
         <is>
-          <t>20/07/2026 14:05</t>
+          <t>01/07/2026 13:54</t>
         </is>
       </c>
     </row>
@@ -91155,12 +91155,12 @@
       </c>
       <c r="B1464" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1464" s="2" t="inlineStr">
         <is>
-          <t>559870</t>
+          <t>559697</t>
         </is>
       </c>
       <c r="D1464" s="2" t="inlineStr">
@@ -91170,12 +91170,12 @@
       </c>
       <c r="E1464" s="2" t="inlineStr">
         <is>
-          <t>A4755</t>
+          <t>A5033</t>
         </is>
       </c>
       <c r="F1464" s="2" t="inlineStr">
         <is>
-          <t>00019200000013415298</t>
+          <t>00019200000013422723</t>
         </is>
       </c>
       <c r="G1464" s="2" t="inlineStr">
@@ -91185,12 +91185,12 @@
       </c>
       <c r="H1464" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026 04:54</t>
+          <t>03/07/2026 05:14</t>
         </is>
       </c>
       <c r="I1464" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026 10:18</t>
+          <t>03/07/2026 12:42</t>
         </is>
       </c>
       <c r="J1464" s="2" t="inlineStr">
@@ -91200,12 +91200,12 @@
       </c>
       <c r="K1464" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026 04:54</t>
+          <t>03/07/2026 05:14</t>
         </is>
       </c>
       <c r="L1464" s="2" t="inlineStr">
         <is>
-          <t>20/07/2026 14:05</t>
+          <t>03/07/2026 12:42</t>
         </is>
       </c>
     </row>
@@ -91217,7 +91217,7 @@
       </c>
       <c r="B1465" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1465" s="2" t="inlineStr">
@@ -91232,12 +91232,12 @@
       </c>
       <c r="E1465" s="2" t="inlineStr">
         <is>
-          <t>A4555</t>
+          <t>A5209</t>
         </is>
       </c>
       <c r="F1465" s="2" t="inlineStr">
         <is>
-          <t>00019200000013415301</t>
+          <t>00019200000013415280</t>
         </is>
       </c>
       <c r="G1465" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">
@@ -91294,12 +91294,12 @@
       </c>
       <c r="E1466" s="2" t="inlineStr">
         <is>
-          <t>A4843</t>
+          <t>A4755</t>
         </is>
       </c>
       <c r="F1466" s="2" t="inlineStr">
         <is>
-          <t>00019200000013415310</t>
+          <t>00019200000013415298</t>
         </is>
       </c>
       <c r="G1466" s="2" t="inlineStr">
@@ -91346,7 +91346,7 @@
       </c>
       <c r="C1467" s="2" t="inlineStr">
         <is>
-          <t>560113</t>
+          <t>559870</t>
         </is>
       </c>
       <c r="D1467" s="2" t="inlineStr">
@@ -91356,12 +91356,12 @@
       </c>
       <c r="E1467" s="2" t="inlineStr">
         <is>
-          <t>A3818</t>
+          <t>A4555</t>
         </is>
       </c>
       <c r="F1467" s="2" t="inlineStr">
         <is>
-          <t>00019200000013451758</t>
+          <t>00019200000013415301</t>
         </is>
       </c>
       <c r="G1467" s="2" t="inlineStr">
@@ -91371,12 +91371,12 @@
       </c>
       <c r="H1467" s="2" t="inlineStr">
         <is>
-          <t>15/07/2026 02:34</t>
+          <t>17/07/2026 04:54</t>
         </is>
       </c>
       <c r="I1467" s="2" t="inlineStr">
         <is>
-          <t>15/07/2026 10:05</t>
+          <t>17/07/2026 10:18</t>
         </is>
       </c>
       <c r="J1467" s="2" t="inlineStr">
@@ -91386,12 +91386,12 @@
       </c>
       <c r="K1467" s="2" t="inlineStr">
         <is>
-          <t>15/07/2026 02:34</t>
+          <t>17/07/2026 04:54</t>
         </is>
       </c>
       <c r="L1467" s="2" t="inlineStr">
         <is>
-          <t>15/07/2026 10:05</t>
+          <t>20/07/2026 14:05</t>
         </is>
       </c>
     </row>
@@ -91403,12 +91403,12 @@
       </c>
       <c r="B1468" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1468" s="2" t="inlineStr">
         <is>
-          <t>561125</t>
+          <t>559870</t>
         </is>
       </c>
       <c r="D1468" s="2" t="inlineStr">
@@ -91418,12 +91418,12 @@
       </c>
       <c r="E1468" s="2" t="inlineStr">
         <is>
-          <t>A8303</t>
+          <t>A4843</t>
         </is>
       </c>
       <c r="F1468" s="2" t="inlineStr">
         <is>
-          <t>00019200000013478745</t>
+          <t>00019200000013415310</t>
         </is>
       </c>
       <c r="G1468" s="2" t="inlineStr">
@@ -91433,12 +91433,12 @@
       </c>
       <c r="H1468" s="2" t="inlineStr">
         <is>
-          <t>16/07/2026 01:43</t>
+          <t>17/07/2026 04:54</t>
         </is>
       </c>
       <c r="I1468" s="2" t="inlineStr">
         <is>
-          <t>16/07/2026 09:34</t>
+          <t>17/07/2026 10:18</t>
         </is>
       </c>
       <c r="J1468" s="2" t="inlineStr">
@@ -91448,12 +91448,12 @@
       </c>
       <c r="K1468" s="2" t="inlineStr">
         <is>
-          <t>16/07/2026 01:43</t>
+          <t>17/07/2026 04:54</t>
         </is>
       </c>
       <c r="L1468" s="2" t="inlineStr">
         <is>
-          <t>16/07/2026 09:34</t>
+          <t>20/07/2026 14:05</t>
         </is>
       </c>
     </row>
@@ -91465,12 +91465,12 @@
       </c>
       <c r="B1469" s="2" t="inlineStr">
         <is>
-          <t>-90 C a -60 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1469" s="2" t="inlineStr">
         <is>
-          <t>561435</t>
+          <t>560113</t>
         </is>
       </c>
       <c r="D1469" s="2" t="inlineStr">
@@ -91480,12 +91480,12 @@
       </c>
       <c r="E1469" s="2" t="inlineStr">
         <is>
-          <t>869170035491621</t>
+          <t>A3818</t>
         </is>
       </c>
       <c r="F1469" s="2" t="inlineStr">
         <is>
-          <t>00019200000013751824</t>
+          <t>00019200000013451758</t>
         </is>
       </c>
       <c r="G1469" s="2" t="inlineStr">
@@ -91495,27 +91495,27 @@
       </c>
       <c r="H1469" s="2" t="inlineStr">
         <is>
-          <t>27/07/2026 01:06</t>
+          <t>15/07/2026 02:34</t>
         </is>
       </c>
       <c r="I1469" s="2" t="inlineStr">
         <is>
-          <t>27/07/2026 09:08</t>
+          <t>15/07/2026 10:05</t>
         </is>
       </c>
       <c r="J1469" s="2" t="inlineStr">
         <is>
-          <t>27/07/2026 07:58</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K1469" s="2" t="inlineStr">
         <is>
-          <t>27/07/2026 01:06</t>
+          <t>15/07/2026 02:34</t>
         </is>
       </c>
       <c r="L1469" s="2" t="inlineStr">
         <is>
-          <t>27/07/2026 09:11</t>
+          <t>15/07/2026 10:05</t>
         </is>
       </c>
     </row>
@@ -91527,12 +91527,12 @@
       </c>
       <c r="B1470" s="2" t="inlineStr">
         <is>
-          <t>-90 C a -60 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1470" s="2" t="inlineStr">
         <is>
-          <t>561435</t>
+          <t>561125</t>
         </is>
       </c>
       <c r="D1470" s="2" t="inlineStr">
@@ -91542,12 +91542,12 @@
       </c>
       <c r="E1470" s="2" t="inlineStr">
         <is>
-          <t>869170034887332</t>
+          <t>A8303</t>
         </is>
       </c>
       <c r="F1470" s="2" t="inlineStr">
         <is>
-          <t>00019200000013751832</t>
+          <t>00019200000013478745</t>
         </is>
       </c>
       <c r="G1470" s="2" t="inlineStr">
@@ -91557,27 +91557,27 @@
       </c>
       <c r="H1470" s="2" t="inlineStr">
         <is>
-          <t>27/07/2026 01:06</t>
+          <t>16/07/2026 01:43</t>
         </is>
       </c>
       <c r="I1470" s="2" t="inlineStr">
         <is>
-          <t>27/07/2026 09:08</t>
+          <t>16/07/2026 09:34</t>
         </is>
       </c>
       <c r="J1470" s="2" t="inlineStr">
         <is>
-          <t>27/07/2026 07:58</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K1470" s="2" t="inlineStr">
         <is>
-          <t>27/07/2026 01:06</t>
+          <t>16/07/2026 01:43</t>
         </is>
       </c>
       <c r="L1470" s="2" t="inlineStr">
         <is>
-          <t>27/07/2026 09:11</t>
+          <t>16/07/2026 09:34</t>
         </is>
       </c>
     </row>
@@ -91604,12 +91604,12 @@
       </c>
       <c r="E1471" s="2" t="inlineStr">
         <is>
-          <t>869170034874710</t>
+          <t>869170035491621</t>
         </is>
       </c>
       <c r="F1471" s="2" t="inlineStr">
         <is>
-          <t>00019200000013751840</t>
+          <t>00019200000013751824</t>
         </is>
       </c>
       <c r="G1471" s="2" t="inlineStr">
@@ -91666,12 +91666,12 @@
       </c>
       <c r="E1472" s="2" t="inlineStr">
         <is>
-          <t>869170035511287</t>
+          <t>869170034887332</t>
         </is>
       </c>
       <c r="F1472" s="2" t="inlineStr">
         <is>
-          <t>00019200000013751859</t>
+          <t>00019200000013751832</t>
         </is>
       </c>
       <c r="G1472" s="2" t="inlineStr">
@@ -91728,12 +91728,12 @@
       </c>
       <c r="E1473" s="2" t="inlineStr">
         <is>
-          <t>869170035511360</t>
+          <t>869170034874710</t>
         </is>
       </c>
       <c r="F1473" s="2" t="inlineStr">
         <is>
-          <t>00019200000013751867</t>
+          <t>00019200000013751840</t>
         </is>
       </c>
       <c r="G1473" s="2" t="inlineStr">
@@ -91790,12 +91790,12 @@
       </c>
       <c r="E1474" s="2" t="inlineStr">
         <is>
-          <t>869170035518605</t>
+          <t>869170035511287</t>
         </is>
       </c>
       <c r="F1474" s="2" t="inlineStr">
         <is>
-          <t>00019200000013751875</t>
+          <t>00019200000013751859</t>
         </is>
       </c>
       <c r="G1474" s="2" t="inlineStr">
@@ -91837,12 +91837,12 @@
       </c>
       <c r="B1475" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-90 C a -60 C</t>
         </is>
       </c>
       <c r="C1475" s="2" t="inlineStr">
         <is>
-          <t>562000</t>
+          <t>561435</t>
         </is>
       </c>
       <c r="D1475" s="2" t="inlineStr">
@@ -91852,12 +91852,12 @@
       </c>
       <c r="E1475" s="2" t="inlineStr">
         <is>
-          <t>A3766</t>
+          <t>869170035511360</t>
         </is>
       </c>
       <c r="F1475" s="2" t="inlineStr">
         <is>
-          <t>00019200000013595202</t>
+          <t>00019200000013751867</t>
         </is>
       </c>
       <c r="G1475" s="2" t="inlineStr">
@@ -91867,27 +91867,27 @@
       </c>
       <c r="H1475" s="2" t="inlineStr">
         <is>
-          <t>23/07/2026 03:21</t>
+          <t>27/07/2026 01:06</t>
         </is>
       </c>
       <c r="I1475" s="2" t="inlineStr">
         <is>
-          <t>23/07/2026 12:49</t>
+          <t>27/07/2026 09:08</t>
         </is>
       </c>
       <c r="J1475" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>27/07/2026 07:58</t>
         </is>
       </c>
       <c r="K1475" s="2" t="inlineStr">
         <is>
-          <t>23/07/2026 03:21</t>
+          <t>27/07/2026 01:06</t>
         </is>
       </c>
       <c r="L1475" s="2" t="inlineStr">
         <is>
-          <t>23/07/2026 12:49</t>
+          <t>27/07/2026 09:11</t>
         </is>
       </c>
     </row>
@@ -91899,12 +91899,12 @@
       </c>
       <c r="B1476" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-90 C a -60 C</t>
         </is>
       </c>
       <c r="C1476" s="2" t="inlineStr">
         <is>
-          <t>563123</t>
+          <t>561435</t>
         </is>
       </c>
       <c r="D1476" s="2" t="inlineStr">
@@ -91914,12 +91914,12 @@
       </c>
       <c r="E1476" s="2" t="inlineStr">
         <is>
-          <t>A6644</t>
+          <t>869170035518605</t>
         </is>
       </c>
       <c r="F1476" s="2" t="inlineStr">
         <is>
-          <t>00019200000013870300</t>
+          <t>00019200000013751875</t>
         </is>
       </c>
       <c r="G1476" s="2" t="inlineStr">
@@ -91929,27 +91929,27 @@
       </c>
       <c r="H1476" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026 04:44</t>
+          <t>27/07/2026 01:06</t>
         </is>
       </c>
       <c r="I1476" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026 10:49</t>
+          <t>27/07/2026 09:08</t>
         </is>
       </c>
       <c r="J1476" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>27/07/2026 07:58</t>
         </is>
       </c>
       <c r="K1476" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026 05:06</t>
+          <t>27/07/2026 01:06</t>
         </is>
       </c>
       <c r="L1476" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026 12:33</t>
+          <t>27/07/2026 09:11</t>
         </is>
       </c>
     </row>
@@ -91961,12 +91961,12 @@
       </c>
       <c r="B1477" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1477" s="2" t="inlineStr">
         <is>
-          <t>563123</t>
+          <t>562000</t>
         </is>
       </c>
       <c r="D1477" s="2" t="inlineStr">
@@ -91976,12 +91976,12 @@
       </c>
       <c r="E1477" s="2" t="inlineStr">
         <is>
-          <t>A5521</t>
+          <t>A3766</t>
         </is>
       </c>
       <c r="F1477" s="2" t="inlineStr">
         <is>
-          <t>00019200000013870319</t>
+          <t>00019200000013595202</t>
         </is>
       </c>
       <c r="G1477" s="2" t="inlineStr">
@@ -91991,12 +91991,12 @@
       </c>
       <c r="H1477" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026 04:44</t>
+          <t>23/07/2026 03:21</t>
         </is>
       </c>
       <c r="I1477" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026 10:49</t>
+          <t>23/07/2026 12:49</t>
         </is>
       </c>
       <c r="J1477" s="2" t="inlineStr">
@@ -92006,12 +92006,12 @@
       </c>
       <c r="K1477" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026 05:06</t>
+          <t>23/07/2026 03:21</t>
         </is>
       </c>
       <c r="L1477" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026 12:33</t>
+          <t>23/07/2026 12:49</t>
         </is>
       </c>
     </row>
@@ -92038,12 +92038,12 @@
       </c>
       <c r="E1478" s="2" t="inlineStr">
         <is>
-          <t>A7760</t>
+          <t>A6644</t>
         </is>
       </c>
       <c r="F1478" s="2" t="inlineStr">
         <is>
-          <t>00019200000013870327</t>
+          <t>00019200000013870300</t>
         </is>
       </c>
       <c r="G1478" s="2" t="inlineStr">
@@ -92085,7 +92085,7 @@
       </c>
       <c r="B1479" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1479" s="2" t="inlineStr">
@@ -92100,12 +92100,12 @@
       </c>
       <c r="E1479" s="2" t="inlineStr">
         <is>
-          <t>TA0579</t>
+          <t>A5521</t>
         </is>
       </c>
       <c r="F1479" s="2" t="inlineStr">
         <is>
-          <t>00019200000013870335</t>
+          <t>00019200000013870319</t>
         </is>
       </c>
       <c r="G1479" s="2" t="inlineStr">
@@ -92147,7 +92147,7 @@
       </c>
       <c r="B1480" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1480" s="2" t="inlineStr">
@@ -92162,12 +92162,12 @@
       </c>
       <c r="E1480" s="2" t="inlineStr">
         <is>
-          <t>A8174</t>
+          <t>A7760</t>
         </is>
       </c>
       <c r="F1480" s="2" t="inlineStr">
         <is>
-          <t>00019200000013870343</t>
+          <t>00019200000013870327</t>
         </is>
       </c>
       <c r="G1480" s="2" t="inlineStr">
@@ -92214,7 +92214,7 @@
       </c>
       <c r="C1481" s="2" t="inlineStr">
         <is>
-          <t>563671</t>
+          <t>563123</t>
         </is>
       </c>
       <c r="D1481" s="2" t="inlineStr">
@@ -92224,12 +92224,12 @@
       </c>
       <c r="E1481" s="2" t="inlineStr">
         <is>
-          <t>A1954</t>
+          <t>TA0579</t>
         </is>
       </c>
       <c r="F1481" s="2" t="inlineStr">
         <is>
-          <t>00019200000013854470</t>
+          <t>00019200000013870335</t>
         </is>
       </c>
       <c r="G1481" s="2" t="inlineStr">
@@ -92239,27 +92239,27 @@
       </c>
       <c r="H1481" s="2" t="inlineStr">
         <is>
-          <t>07/08/2026 01:38</t>
+          <t>06/08/2026 04:44</t>
         </is>
       </c>
       <c r="I1481" s="2" t="inlineStr">
         <is>
-          <t>07/08/2026 14:25</t>
+          <t>06/08/2026 10:49</t>
         </is>
       </c>
       <c r="J1481" s="2" t="inlineStr">
         <is>
-          <t>07/08/2026 14:25</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K1481" s="2" t="inlineStr">
         <is>
-          <t>07/08/2026 01:38</t>
+          <t>06/08/2026 05:06</t>
         </is>
       </c>
       <c r="L1481" s="2" t="inlineStr">
         <is>
-          <t>07/08/2026 14:28</t>
+          <t>06/08/2026 12:33</t>
         </is>
       </c>
     </row>
@@ -92276,7 +92276,7 @@
       </c>
       <c r="C1482" s="2" t="inlineStr">
         <is>
-          <t>563673</t>
+          <t>563123</t>
         </is>
       </c>
       <c r="D1482" s="2" t="inlineStr">
@@ -92286,12 +92286,12 @@
       </c>
       <c r="E1482" s="2" t="inlineStr">
         <is>
-          <t>A4613</t>
+          <t>A8174</t>
         </is>
       </c>
       <c r="F1482" s="2" t="inlineStr">
         <is>
-          <t>00019200000013854488</t>
+          <t>00019200000013870343</t>
         </is>
       </c>
       <c r="G1482" s="2" t="inlineStr">
@@ -92301,27 +92301,27 @@
       </c>
       <c r="H1482" s="2" t="inlineStr">
         <is>
-          <t>07/08/2026 03:59</t>
+          <t>06/08/2026 04:44</t>
         </is>
       </c>
       <c r="I1482" s="2" t="inlineStr">
         <is>
-          <t>07/08/2026 08:17</t>
+          <t>06/08/2026 10:49</t>
         </is>
       </c>
       <c r="J1482" s="2" t="inlineStr">
         <is>
-          <t>07/08/2026 07:40</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K1482" s="2" t="inlineStr">
         <is>
-          <t>07/08/2026 03:59</t>
+          <t>06/08/2026 05:06</t>
         </is>
       </c>
       <c r="L1482" s="2" t="inlineStr">
         <is>
-          <t>07/08/2026 08:23</t>
+          <t>06/08/2026 12:33</t>
         </is>
       </c>
     </row>
@@ -92338,7 +92338,7 @@
       </c>
       <c r="C1483" s="2" t="inlineStr">
         <is>
-          <t>564524</t>
+          <t>563671</t>
         </is>
       </c>
       <c r="D1483" s="2" t="inlineStr">
@@ -92348,12 +92348,12 @@
       </c>
       <c r="E1483" s="2" t="inlineStr">
         <is>
-          <t>A4777</t>
+          <t>A1954</t>
         </is>
       </c>
       <c r="F1483" s="2" t="inlineStr">
         <is>
-          <t>00019200000013969552</t>
+          <t>00019200000013854470</t>
         </is>
       </c>
       <c r="G1483" s="2" t="inlineStr">
@@ -92363,27 +92363,27 @@
       </c>
       <c r="H1483" s="2" t="inlineStr">
         <is>
-          <t>18/08/2026 04:52</t>
+          <t>07/08/2026 01:38</t>
         </is>
       </c>
       <c r="I1483" s="2" t="inlineStr">
         <is>
-          <t>18/08/2026 11:56</t>
+          <t>07/08/2026 14:25</t>
         </is>
       </c>
       <c r="J1483" s="2" t="inlineStr">
         <is>
-          <t>18/08/2026 11:56</t>
+          <t>07/08/2026 14:25</t>
         </is>
       </c>
       <c r="K1483" s="2" t="inlineStr">
         <is>
-          <t>18/08/2026 04:52</t>
+          <t>07/08/2026 01:38</t>
         </is>
       </c>
       <c r="L1483" s="2" t="inlineStr">
         <is>
-          <t>18/08/2026 12:02</t>
+          <t>07/08/2026 14:28</t>
         </is>
       </c>
     </row>
@@ -92400,7 +92400,7 @@
       </c>
       <c r="C1484" s="2" t="inlineStr">
         <is>
-          <t>564524</t>
+          <t>563673</t>
         </is>
       </c>
       <c r="D1484" s="2" t="inlineStr">
@@ -92410,12 +92410,12 @@
       </c>
       <c r="E1484" s="2" t="inlineStr">
         <is>
-          <t>A7751</t>
+          <t>A4613</t>
         </is>
       </c>
       <c r="F1484" s="2" t="inlineStr">
         <is>
-          <t>00019200000013969560</t>
+          <t>00019200000013854488</t>
         </is>
       </c>
       <c r="G1484" s="2" t="inlineStr">
@@ -92425,27 +92425,27 @@
       </c>
       <c r="H1484" s="2" t="inlineStr">
         <is>
-          <t>18/08/2026 04:52</t>
+          <t>07/08/2026 03:59</t>
         </is>
       </c>
       <c r="I1484" s="2" t="inlineStr">
         <is>
-          <t>18/08/2026 11:56</t>
+          <t>07/08/2026 08:17</t>
         </is>
       </c>
       <c r="J1484" s="2" t="inlineStr">
         <is>
-          <t>18/08/2026 11:56</t>
+          <t>07/08/2026 07:40</t>
         </is>
       </c>
       <c r="K1484" s="2" t="inlineStr">
         <is>
-          <t>18/08/2026 04:52</t>
+          <t>07/08/2026 03:59</t>
         </is>
       </c>
       <c r="L1484" s="2" t="inlineStr">
         <is>
-          <t>18/08/2026 12:02</t>
+          <t>07/08/2026 08:23</t>
         </is>
       </c>
     </row>
@@ -92462,7 +92462,7 @@
       </c>
       <c r="C1485" s="2" t="inlineStr">
         <is>
-          <t>565995</t>
+          <t>564524</t>
         </is>
       </c>
       <c r="D1485" s="2" t="inlineStr">
@@ -92472,12 +92472,12 @@
       </c>
       <c r="E1485" s="2" t="inlineStr">
         <is>
-          <t>A4837</t>
+          <t>A4777</t>
         </is>
       </c>
       <c r="F1485" s="2" t="inlineStr">
         <is>
-          <t>00019200000014013282</t>
+          <t>00019200000013969552</t>
         </is>
       </c>
       <c r="G1485" s="2" t="inlineStr">
@@ -92487,27 +92487,27 @@
       </c>
       <c r="H1485" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026 04:06</t>
+          <t>18/08/2026 04:52</t>
         </is>
       </c>
       <c r="I1485" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026 12:50</t>
+          <t>18/08/2026 11:56</t>
         </is>
       </c>
       <c r="J1485" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026 12:50</t>
+          <t>18/08/2026 11:56</t>
         </is>
       </c>
       <c r="K1485" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026 04:06</t>
+          <t>18/08/2026 04:52</t>
         </is>
       </c>
       <c r="L1485" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026 12:53</t>
+          <t>18/08/2026 12:02</t>
         </is>
       </c>
     </row>
@@ -92524,7 +92524,7 @@
       </c>
       <c r="C1486" s="2" t="inlineStr">
         <is>
-          <t>565995</t>
+          <t>564524</t>
         </is>
       </c>
       <c r="D1486" s="2" t="inlineStr">
@@ -92534,12 +92534,12 @@
       </c>
       <c r="E1486" s="2" t="inlineStr">
         <is>
-          <t>A0312</t>
+          <t>A7751</t>
         </is>
       </c>
       <c r="F1486" s="2" t="inlineStr">
         <is>
-          <t>00019200000014013290</t>
+          <t>00019200000013969560</t>
         </is>
       </c>
       <c r="G1486" s="2" t="inlineStr">
@@ -92549,27 +92549,27 @@
       </c>
       <c r="H1486" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026 04:06</t>
+          <t>18/08/2026 04:52</t>
         </is>
       </c>
       <c r="I1486" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026 12:50</t>
+          <t>18/08/2026 11:56</t>
         </is>
       </c>
       <c r="J1486" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026 12:50</t>
+          <t>18/08/2026 11:56</t>
         </is>
       </c>
       <c r="K1486" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026 04:06</t>
+          <t>18/08/2026 04:52</t>
         </is>
       </c>
       <c r="L1486" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026 12:53</t>
+          <t>18/08/2026 12:02</t>
         </is>
       </c>
     </row>
@@ -92586,7 +92586,7 @@
       </c>
       <c r="C1487" s="2" t="inlineStr">
         <is>
-          <t>567764</t>
+          <t>565995</t>
         </is>
       </c>
       <c r="D1487" s="2" t="inlineStr">
@@ -92596,12 +92596,12 @@
       </c>
       <c r="E1487" s="2" t="inlineStr">
         <is>
-          <t>0741700606</t>
+          <t>A4837</t>
         </is>
       </c>
       <c r="F1487" s="2" t="inlineStr">
         <is>
-          <t>00019200000014235978</t>
+          <t>00019200000014013282</t>
         </is>
       </c>
       <c r="G1487" s="2" t="inlineStr">
@@ -92611,27 +92611,27 @@
       </c>
       <c r="H1487" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026 05:46</t>
+          <t>26/08/2026 04:06</t>
         </is>
       </c>
       <c r="I1487" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026 09:32</t>
+          <t>26/08/2026 12:50</t>
         </is>
       </c>
       <c r="J1487" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026 09:33</t>
+          <t>26/08/2026 12:50</t>
         </is>
       </c>
       <c r="K1487" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026 05:46</t>
+          <t>26/08/2026 04:06</t>
         </is>
       </c>
       <c r="L1487" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026 09:35</t>
+          <t>26/08/2026 12:53</t>
         </is>
       </c>
     </row>
@@ -92648,7 +92648,7 @@
       </c>
       <c r="C1488" s="2" t="inlineStr">
         <is>
-          <t>567764</t>
+          <t>565995</t>
         </is>
       </c>
       <c r="D1488" s="2" t="inlineStr">
@@ -92658,12 +92658,12 @@
       </c>
       <c r="E1488" s="2" t="inlineStr">
         <is>
-          <t>0741700626</t>
+          <t>A0312</t>
         </is>
       </c>
       <c r="F1488" s="2" t="inlineStr">
         <is>
-          <t>00019200000014236362</t>
+          <t>00019200000014013290</t>
         </is>
       </c>
       <c r="G1488" s="2" t="inlineStr">
@@ -92673,27 +92673,27 @@
       </c>
       <c r="H1488" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026 05:46</t>
+          <t>26/08/2026 04:06</t>
         </is>
       </c>
       <c r="I1488" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026 09:32</t>
+          <t>26/08/2026 12:50</t>
         </is>
       </c>
       <c r="J1488" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026 09:33</t>
+          <t>26/08/2026 12:50</t>
         </is>
       </c>
       <c r="K1488" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026 05:46</t>
+          <t>26/08/2026 04:06</t>
         </is>
       </c>
       <c r="L1488" s="2" t="inlineStr">
         <is>
-          <t>10/09/2026 09:35</t>
+          <t>26/08/2026 12:53</t>
         </is>
       </c>
     </row>
@@ -92720,12 +92720,12 @@
       </c>
       <c r="E1489" s="2" t="inlineStr">
         <is>
-          <t>0741700726</t>
+          <t>0741700606</t>
         </is>
       </c>
       <c r="F1489" s="2" t="inlineStr">
         <is>
-          <t>00019200000014236370</t>
+          <t>00019200000014235978</t>
         </is>
       </c>
       <c r="G1489" s="2" t="inlineStr">
@@ -92767,57 +92767,57 @@
       </c>
       <c r="B1490" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1490" s="2" t="inlineStr">
         <is>
-          <t>557180</t>
+          <t>567764</t>
         </is>
       </c>
       <c r="D1490" s="2" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E1490" s="2" t="inlineStr">
         <is>
-          <t>A3929</t>
+          <t>0741700626</t>
         </is>
       </c>
       <c r="F1490" s="2" t="inlineStr">
         <is>
-          <t>00019200000012685780</t>
+          <t>00019200000014236362</t>
         </is>
       </c>
       <c r="G1490" s="2" t="inlineStr">
         <is>
-          <t>MultiModal</t>
+          <t>Rodoviário</t>
         </is>
       </c>
       <c r="H1490" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026 09:37</t>
+          <t>10/09/2026 05:46</t>
         </is>
       </c>
       <c r="I1490" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026 10:00</t>
+          <t>10/09/2026 09:32</t>
         </is>
       </c>
       <c r="J1490" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10/09/2026 09:33</t>
         </is>
       </c>
       <c r="K1490" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026 09:38</t>
+          <t>10/09/2026 05:46</t>
         </is>
       </c>
       <c r="L1490" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026 10:00</t>
+          <t>10/09/2026 09:35</t>
         </is>
       </c>
     </row>
@@ -92829,57 +92829,57 @@
       </c>
       <c r="B1491" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1491" s="2" t="inlineStr">
         <is>
-          <t>559781</t>
+          <t>567764</t>
         </is>
       </c>
       <c r="D1491" s="2" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E1491" s="2" t="inlineStr">
         <is>
-          <t>A8445</t>
+          <t>0741700726</t>
         </is>
       </c>
       <c r="F1491" s="2" t="inlineStr">
         <is>
-          <t>00019200000013419129</t>
+          <t>00019200000014236370</t>
         </is>
       </c>
       <c r="G1491" s="2" t="inlineStr">
         <is>
-          <t>MultiModal</t>
+          <t>Rodoviário</t>
         </is>
       </c>
       <c r="H1491" s="2" t="inlineStr">
         <is>
-          <t>07/07/2026 01:13</t>
+          <t>10/09/2026 05:46</t>
         </is>
       </c>
       <c r="I1491" s="2" t="inlineStr">
         <is>
-          <t>08/07/2026 18:00</t>
+          <t>10/09/2026 09:32</t>
         </is>
       </c>
       <c r="J1491" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10/09/2026 09:33</t>
         </is>
       </c>
       <c r="K1491" s="2" t="inlineStr">
         <is>
-          <t>07/07/2026 01:13</t>
+          <t>10/09/2026 05:46</t>
         </is>
       </c>
       <c r="L1491" s="2" t="inlineStr">
         <is>
-          <t>08/07/2026 18:00</t>
+          <t>10/09/2026 09:35</t>
         </is>
       </c>
     </row>
@@ -92891,12 +92891,12 @@
       </c>
       <c r="B1492" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1492" s="2" t="inlineStr">
         <is>
-          <t>560364</t>
+          <t>557180</t>
         </is>
       </c>
       <c r="D1492" s="2" t="inlineStr">
@@ -92906,12 +92906,12 @@
       </c>
       <c r="E1492" s="2" t="inlineStr">
         <is>
-          <t>A8870</t>
+          <t>A3929</t>
         </is>
       </c>
       <c r="F1492" s="2" t="inlineStr">
         <is>
-          <t>00019200000013491555</t>
+          <t>00019200000012685780</t>
         </is>
       </c>
       <c r="G1492" s="2" t="inlineStr">
@@ -92921,12 +92921,12 @@
       </c>
       <c r="H1492" s="2" t="inlineStr">
         <is>
-          <t>13/07/2026 01:44</t>
+          <t>15/06/2026 09:37</t>
         </is>
       </c>
       <c r="I1492" s="2" t="inlineStr">
         <is>
-          <t>15/07/2026 17:22</t>
+          <t>16/06/2026 10:00</t>
         </is>
       </c>
       <c r="J1492" s="2" t="inlineStr">
@@ -92936,12 +92936,12 @@
       </c>
       <c r="K1492" s="2" t="inlineStr">
         <is>
-          <t>13/07/2026 01:44</t>
+          <t>15/06/2026 09:38</t>
         </is>
       </c>
       <c r="L1492" s="2" t="inlineStr">
         <is>
-          <t>15/07/2026 17:22</t>
+          <t>16/06/2026 10:00</t>
         </is>
       </c>
     </row>
@@ -92953,12 +92953,12 @@
       </c>
       <c r="B1493" s="2" t="inlineStr">
         <is>
-          <t>-90 C a -60 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1493" s="2" t="inlineStr">
         <is>
-          <t>560565</t>
+          <t>559781</t>
         </is>
       </c>
       <c r="D1493" s="2" t="inlineStr">
@@ -92968,12 +92968,12 @@
       </c>
       <c r="E1493" s="2" t="inlineStr">
         <is>
-          <t>AS-0851</t>
+          <t>A8445</t>
         </is>
       </c>
       <c r="F1493" s="2" t="inlineStr">
         <is>
-          <t>00019200000013789856</t>
+          <t>00019200000013419129</t>
         </is>
       </c>
       <c r="G1493" s="2" t="inlineStr">
@@ -92983,12 +92983,12 @@
       </c>
       <c r="H1493" s="2" t="inlineStr">
         <is>
-          <t>03/08/2026 00:41</t>
+          <t>07/07/2026 01:13</t>
         </is>
       </c>
       <c r="I1493" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026 15:00</t>
+          <t>08/07/2026 18:00</t>
         </is>
       </c>
       <c r="J1493" s="2" t="inlineStr">
@@ -92998,12 +92998,12 @@
       </c>
       <c r="K1493" s="2" t="inlineStr">
         <is>
-          <t>03/08/2026 00:41</t>
+          <t>07/07/2026 01:13</t>
         </is>
       </c>
       <c r="L1493" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026 15:00</t>
+          <t>08/07/2026 18:00</t>
         </is>
       </c>
     </row>
@@ -93015,12 +93015,12 @@
       </c>
       <c r="B1494" s="2" t="inlineStr">
         <is>
-          <t>-90 C a -60 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1494" s="2" t="inlineStr">
         <is>
-          <t>560565</t>
+          <t>560364</t>
         </is>
       </c>
       <c r="D1494" s="2" t="inlineStr">
@@ -93030,12 +93030,12 @@
       </c>
       <c r="E1494" s="2" t="inlineStr">
         <is>
-          <t>AS-0095</t>
+          <t>A8870</t>
         </is>
       </c>
       <c r="F1494" s="2" t="inlineStr">
         <is>
-          <t>00019200000013789864</t>
+          <t>00019200000013491555</t>
         </is>
       </c>
       <c r="G1494" s="2" t="inlineStr">
@@ -93045,12 +93045,12 @@
       </c>
       <c r="H1494" s="2" t="inlineStr">
         <is>
-          <t>03/08/2026 00:41</t>
+          <t>13/07/2026 01:44</t>
         </is>
       </c>
       <c r="I1494" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026 15:00</t>
+          <t>15/07/2026 17:22</t>
         </is>
       </c>
       <c r="J1494" s="2" t="inlineStr">
@@ -93060,12 +93060,12 @@
       </c>
       <c r="K1494" s="2" t="inlineStr">
         <is>
-          <t>03/08/2026 00:41</t>
+          <t>13/07/2026 01:44</t>
         </is>
       </c>
       <c r="L1494" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026 15:00</t>
+          <t>15/07/2026 17:22</t>
         </is>
       </c>
     </row>
@@ -93092,12 +93092,12 @@
       </c>
       <c r="E1495" s="2" t="inlineStr">
         <is>
-          <t>AS-0001</t>
+          <t>AS-0851</t>
         </is>
       </c>
       <c r="F1495" s="2" t="inlineStr">
         <is>
-          <t>00019200000013789872</t>
+          <t>00019200000013789856</t>
         </is>
       </c>
       <c r="G1495" s="2" t="inlineStr">
@@ -93154,12 +93154,12 @@
       </c>
       <c r="E1496" s="2" t="inlineStr">
         <is>
-          <t>AS-0259</t>
+          <t>AS-0095</t>
         </is>
       </c>
       <c r="F1496" s="2" t="inlineStr">
         <is>
-          <t>00019200000013789880</t>
+          <t>00019200000013789864</t>
         </is>
       </c>
       <c r="G1496" s="2" t="inlineStr">
@@ -93216,12 +93216,12 @@
       </c>
       <c r="E1497" s="2" t="inlineStr">
         <is>
-          <t>AS-0635</t>
+          <t>AS-0001</t>
         </is>
       </c>
       <c r="F1497" s="2" t="inlineStr">
         <is>
-          <t>00019200000013789899</t>
+          <t>00019200000013789872</t>
         </is>
       </c>
       <c r="G1497" s="2" t="inlineStr">
@@ -93278,12 +93278,12 @@
       </c>
       <c r="E1498" s="2" t="inlineStr">
         <is>
-          <t>AS-0716</t>
+          <t>AS-0259</t>
         </is>
       </c>
       <c r="F1498" s="2" t="inlineStr">
         <is>
-          <t>00019200000013789902</t>
+          <t>00019200000013789880</t>
         </is>
       </c>
       <c r="G1498" s="2" t="inlineStr">
@@ -93340,12 +93340,12 @@
       </c>
       <c r="E1499" s="2" t="inlineStr">
         <is>
-          <t>AS-0462</t>
+          <t>AS-0635</t>
         </is>
       </c>
       <c r="F1499" s="2" t="inlineStr">
         <is>
-          <t>00019200000013789910</t>
+          <t>00019200000013789899</t>
         </is>
       </c>
       <c r="G1499" s="2" t="inlineStr">
@@ -93402,12 +93402,12 @@
       </c>
       <c r="E1500" s="2" t="inlineStr">
         <is>
-          <t>AS-0182</t>
+          <t>AS-0716</t>
         </is>
       </c>
       <c r="F1500" s="2" t="inlineStr">
         <is>
-          <t>00019200000013789929</t>
+          <t>00019200000013789902</t>
         </is>
       </c>
       <c r="G1500" s="2" t="inlineStr">
@@ -93449,12 +93449,12 @@
       </c>
       <c r="B1501" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-90 C a -60 C</t>
         </is>
       </c>
       <c r="C1501" s="2" t="inlineStr">
         <is>
-          <t>563104</t>
+          <t>560565</t>
         </is>
       </c>
       <c r="D1501" s="2" t="inlineStr">
@@ -93464,12 +93464,12 @@
       </c>
       <c r="E1501" s="2" t="inlineStr">
         <is>
-          <t>A9410</t>
+          <t>AS-0462</t>
         </is>
       </c>
       <c r="F1501" s="2" t="inlineStr">
         <is>
-          <t>00019200000013863851</t>
+          <t>00019200000013789910</t>
         </is>
       </c>
       <c r="G1501" s="2" t="inlineStr">
@@ -93479,12 +93479,12 @@
       </c>
       <c r="H1501" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026 23:37</t>
+          <t>03/08/2026 00:41</t>
         </is>
       </c>
       <c r="I1501" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026 12:14</t>
+          <t>04/08/2026 15:00</t>
         </is>
       </c>
       <c r="J1501" s="2" t="inlineStr">
@@ -93494,12 +93494,12 @@
       </c>
       <c r="K1501" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026 23:37</t>
+          <t>03/08/2026 00:41</t>
         </is>
       </c>
       <c r="L1501" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026 12:14</t>
+          <t>04/08/2026 15:00</t>
         </is>
       </c>
     </row>
@@ -93511,12 +93511,12 @@
       </c>
       <c r="B1502" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-90 C a -60 C</t>
         </is>
       </c>
       <c r="C1502" s="2" t="inlineStr">
         <is>
-          <t>563104</t>
+          <t>560565</t>
         </is>
       </c>
       <c r="D1502" s="2" t="inlineStr">
@@ -93526,12 +93526,12 @@
       </c>
       <c r="E1502" s="2" t="inlineStr">
         <is>
-          <t>A6513</t>
+          <t>AS-0182</t>
         </is>
       </c>
       <c r="F1502" s="2" t="inlineStr">
         <is>
-          <t>00019200000013863860</t>
+          <t>00019200000013789929</t>
         </is>
       </c>
       <c r="G1502" s="2" t="inlineStr">
@@ -93541,12 +93541,12 @@
       </c>
       <c r="H1502" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026 23:37</t>
+          <t>03/08/2026 00:41</t>
         </is>
       </c>
       <c r="I1502" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026 12:14</t>
+          <t>04/08/2026 15:00</t>
         </is>
       </c>
       <c r="J1502" s="2" t="inlineStr">
@@ -93556,12 +93556,12 @@
       </c>
       <c r="K1502" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026 23:37</t>
+          <t>03/08/2026 00:41</t>
         </is>
       </c>
       <c r="L1502" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026 12:14</t>
+          <t>04/08/2026 15:00</t>
         </is>
       </c>
     </row>
@@ -93578,57 +93578,181 @@
       </c>
       <c r="C1503" s="2" t="inlineStr">
         <is>
+          <t>563104</t>
+        </is>
+      </c>
+      <c r="D1503" s="2" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="E1503" s="2" t="inlineStr">
+        <is>
+          <t>A9410</t>
+        </is>
+      </c>
+      <c r="F1503" s="2" t="inlineStr">
+        <is>
+          <t>00019200000013863851</t>
+        </is>
+      </c>
+      <c r="G1503" s="2" t="inlineStr">
+        <is>
+          <t>MultiModal</t>
+        </is>
+      </c>
+      <c r="H1503" s="2" t="inlineStr">
+        <is>
+          <t>04/08/2026 23:37</t>
+        </is>
+      </c>
+      <c r="I1503" s="2" t="inlineStr">
+        <is>
+          <t>06/08/2026 12:14</t>
+        </is>
+      </c>
+      <c r="J1503" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K1503" s="2" t="inlineStr">
+        <is>
+          <t>04/08/2026 23:37</t>
+        </is>
+      </c>
+      <c r="L1503" s="2" t="inlineStr">
+        <is>
+          <t>06/08/2026 12:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" s="2" t="inlineStr">
+        <is>
+          <t>CAIXA 42L</t>
+        </is>
+      </c>
+      <c r="B1504" s="2" t="inlineStr">
+        <is>
+          <t>-30 C a -15 C</t>
+        </is>
+      </c>
+      <c r="C1504" s="2" t="inlineStr">
+        <is>
+          <t>563104</t>
+        </is>
+      </c>
+      <c r="D1504" s="2" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="E1504" s="2" t="inlineStr">
+        <is>
+          <t>A6513</t>
+        </is>
+      </c>
+      <c r="F1504" s="2" t="inlineStr">
+        <is>
+          <t>00019200000013863860</t>
+        </is>
+      </c>
+      <c r="G1504" s="2" t="inlineStr">
+        <is>
+          <t>MultiModal</t>
+        </is>
+      </c>
+      <c r="H1504" s="2" t="inlineStr">
+        <is>
+          <t>04/08/2026 23:37</t>
+        </is>
+      </c>
+      <c r="I1504" s="2" t="inlineStr">
+        <is>
+          <t>06/08/2026 12:14</t>
+        </is>
+      </c>
+      <c r="J1504" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K1504" s="2" t="inlineStr">
+        <is>
+          <t>04/08/2026 23:37</t>
+        </is>
+      </c>
+      <c r="L1504" s="2" t="inlineStr">
+        <is>
+          <t>06/08/2026 12:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" s="2" t="inlineStr">
+        <is>
+          <t>CAIXA 42L</t>
+        </is>
+      </c>
+      <c r="B1505" s="2" t="inlineStr">
+        <is>
+          <t>-30 C a -15 C</t>
+        </is>
+      </c>
+      <c r="C1505" s="2" t="inlineStr">
+        <is>
           <t>567060</t>
         </is>
       </c>
-      <c r="D1503" s="2" t="inlineStr">
+      <c r="D1505" s="2" t="inlineStr">
         <is>
           <t>TO</t>
         </is>
       </c>
-      <c r="E1503" s="2" t="inlineStr">
+      <c r="E1505" s="2" t="inlineStr">
         <is>
           <t>TA0038</t>
         </is>
       </c>
-      <c r="F1503" s="2" t="inlineStr">
+      <c r="F1505" s="2" t="inlineStr">
         <is>
           <t>00019200000014263858</t>
         </is>
       </c>
-      <c r="G1503" s="2" t="inlineStr">
-        <is>
-          <t>MultiModal</t>
-        </is>
-      </c>
-      <c r="H1503" s="2" t="inlineStr">
+      <c r="G1505" s="2" t="inlineStr">
+        <is>
+          <t>MultiModal</t>
+        </is>
+      </c>
+      <c r="H1505" s="2" t="inlineStr">
         <is>
           <t>12/09/2026 23:59</t>
         </is>
       </c>
-      <c r="I1503" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J1503" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K1503" s="2" t="inlineStr">
+      <c r="I1505" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J1505" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K1505" s="2" t="inlineStr">
         <is>
           <t>12/09/2026 23:59</t>
         </is>
       </c>
-      <c r="L1503" s="2" t="inlineStr">
+      <c r="L1505" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1503"/>
+  <autoFilter ref="A1:L1505"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -15453,7 +15453,7 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
@@ -22707,7 +22707,7 @@
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
@@ -28659,7 +28659,7 @@
       </c>
       <c r="B456" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C456" s="2" t="inlineStr">
@@ -28721,7 +28721,7 @@
       </c>
       <c r="B457" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C457" s="2" t="inlineStr">
@@ -31945,7 +31945,7 @@
       </c>
       <c r="B509" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C509" s="2" t="inlineStr">
@@ -35851,7 +35851,7 @@
       </c>
       <c r="B572" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C572" s="2" t="inlineStr">
@@ -38207,7 +38207,7 @@
       </c>
       <c r="B610" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C610" s="2" t="inlineStr">
@@ -40625,7 +40625,7 @@
       </c>
       <c r="B649" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C649" s="2" t="inlineStr">
@@ -42919,7 +42919,7 @@
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
@@ -43043,7 +43043,7 @@
       </c>
       <c r="B688" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C688" s="2" t="inlineStr">
@@ -43105,7 +43105,7 @@
       </c>
       <c r="B689" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C689" s="2" t="inlineStr">
@@ -44717,7 +44717,7 @@
       </c>
       <c r="B715" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C715" s="2" t="inlineStr">
@@ -47755,7 +47755,7 @@
       </c>
       <c r="B764" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C764" s="2" t="inlineStr">
@@ -51351,7 +51351,7 @@
       </c>
       <c r="B822" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C822" s="2" t="inlineStr">
@@ -51413,7 +51413,7 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
@@ -52033,7 +52033,7 @@
       </c>
       <c r="B833" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C833" s="2" t="inlineStr">
@@ -58543,7 +58543,7 @@
       </c>
       <c r="B938" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C938" s="2" t="inlineStr">
@@ -67223,7 +67223,7 @@
       </c>
       <c r="B1078" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1078" s="2" t="inlineStr">
@@ -71749,7 +71749,7 @@
       </c>
       <c r="B1151" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1151" s="2" t="inlineStr">
@@ -72121,7 +72121,7 @@
       </c>
       <c r="B1157" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1157" s="2" t="inlineStr">
@@ -72245,7 +72245,7 @@
       </c>
       <c r="B1159" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1159" s="2" t="inlineStr">
@@ -75221,7 +75221,7 @@
       </c>
       <c r="B1207" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1207" s="2" t="inlineStr">
@@ -76771,7 +76771,7 @@
       </c>
       <c r="B1232" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1232" s="2" t="inlineStr">
@@ -78135,7 +78135,7 @@
       </c>
       <c r="B1254" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1254" s="2" t="inlineStr">
@@ -78259,7 +78259,7 @@
       </c>
       <c r="B1256" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1256" s="2" t="inlineStr">
@@ -79127,7 +79127,7 @@
       </c>
       <c r="B1270" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1270" s="2" t="inlineStr">
@@ -79623,7 +79623,7 @@
       </c>
       <c r="B1278" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1278" s="2" t="inlineStr">
@@ -80119,7 +80119,7 @@
       </c>
       <c r="B1286" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1286" s="2" t="inlineStr">
@@ -80367,7 +80367,7 @@
       </c>
       <c r="B1290" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1290" s="2" t="inlineStr">
@@ -84335,7 +84335,7 @@
       </c>
       <c r="B1354" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1354" s="2" t="inlineStr">
@@ -84459,7 +84459,7 @@
       </c>
       <c r="B1356" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1356" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84583,7 +84583,7 @@
       </c>
       <c r="B1358" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1358" s="2" t="inlineStr">
@@ -85389,7 +85389,7 @@
       </c>
       <c r="B1371" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1371" s="2" t="inlineStr">
@@ -85637,7 +85637,7 @@
       </c>
       <c r="B1375" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1375" s="2" t="inlineStr">
@@ -88799,7 +88799,7 @@
       </c>
       <c r="B1426" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1426" s="2" t="inlineStr">
@@ -89543,7 +89543,7 @@
       </c>
       <c r="B1438" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1438" s="2" t="inlineStr">
@@ -91217,7 +91217,7 @@
       </c>
       <c r="B1465" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1465" s="2" t="inlineStr">
@@ -92953,7 +92953,7 @@
       </c>
       <c r="B1493" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1493" s="2" t="inlineStr">
@@ -93635,7 +93635,7 @@
       </c>
       <c r="B1504" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1504" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -22707,7 +22707,7 @@
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
@@ -28659,7 +28659,7 @@
       </c>
       <c r="B456" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C456" s="2" t="inlineStr">
@@ -28721,7 +28721,7 @@
       </c>
       <c r="B457" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C457" s="2" t="inlineStr">
@@ -31077,7 +31077,7 @@
       </c>
       <c r="B495" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C495" s="2" t="inlineStr">
@@ -34735,7 +34735,7 @@
       </c>
       <c r="B554" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C554" s="2" t="inlineStr">
@@ -42919,7 +42919,7 @@
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
@@ -43105,7 +43105,7 @@
       </c>
       <c r="B689" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C689" s="2" t="inlineStr">
@@ -43291,7 +43291,7 @@
       </c>
       <c r="B692" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C692" s="2" t="inlineStr">
@@ -44717,7 +44717,7 @@
       </c>
       <c r="B715" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C715" s="2" t="inlineStr">
@@ -51413,7 +51413,7 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
@@ -51847,7 +51847,7 @@
       </c>
       <c r="B830" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C830" s="2" t="inlineStr">
@@ -51909,7 +51909,7 @@
       </c>
       <c r="B831" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C831" s="2" t="inlineStr">
@@ -51971,7 +51971,7 @@
       </c>
       <c r="B832" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C832" s="2" t="inlineStr">
@@ -58481,7 +58481,7 @@
       </c>
       <c r="B937" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C937" s="2" t="inlineStr">
@@ -58543,7 +58543,7 @@
       </c>
       <c r="B938" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C938" s="2" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="B971" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C971" s="2" t="inlineStr">
@@ -60651,7 +60651,7 @@
       </c>
       <c r="B972" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C972" s="2" t="inlineStr">
@@ -61023,7 +61023,7 @@
       </c>
       <c r="B978" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C978" s="2" t="inlineStr">
@@ -70199,7 +70199,7 @@
       </c>
       <c r="B1126" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1126" s="2" t="inlineStr">
@@ -70819,7 +70819,7 @@
       </c>
       <c r="B1136" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1136" s="2" t="inlineStr">
@@ -71749,7 +71749,7 @@
       </c>
       <c r="B1151" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1151" s="2" t="inlineStr">
@@ -72121,7 +72121,7 @@
       </c>
       <c r="B1157" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1157" s="2" t="inlineStr">
@@ -72245,7 +72245,7 @@
       </c>
       <c r="B1159" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1159" s="2" t="inlineStr">
@@ -72307,7 +72307,7 @@
       </c>
       <c r="B1160" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1160" s="2" t="inlineStr">
@@ -75221,7 +75221,7 @@
       </c>
       <c r="B1207" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1207" s="2" t="inlineStr">
@@ -75593,7 +75593,7 @@
       </c>
       <c r="B1213" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1213" s="2" t="inlineStr">
@@ -79127,7 +79127,7 @@
       </c>
       <c r="B1270" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1270" s="2" t="inlineStr">
@@ -79623,7 +79623,7 @@
       </c>
       <c r="B1278" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1278" s="2" t="inlineStr">
@@ -80119,7 +80119,7 @@
       </c>
       <c r="B1286" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1286" s="2" t="inlineStr">
@@ -80367,7 +80367,7 @@
       </c>
       <c r="B1290" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1290" s="2" t="inlineStr">
@@ -80429,7 +80429,7 @@
       </c>
       <c r="B1291" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1291" s="2" t="inlineStr">
@@ -84335,7 +84335,7 @@
       </c>
       <c r="B1354" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1354" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84583,7 +84583,7 @@
       </c>
       <c r="B1358" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1358" s="2" t="inlineStr">
@@ -84955,7 +84955,7 @@
       </c>
       <c r="B1364" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1364" s="2" t="inlineStr">
@@ -85141,7 +85141,7 @@
       </c>
       <c r="B1367" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1367" s="2" t="inlineStr">
@@ -85389,7 +85389,7 @@
       </c>
       <c r="B1371" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1371" s="2" t="inlineStr">
@@ -85637,7 +85637,7 @@
       </c>
       <c r="B1375" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1375" s="2" t="inlineStr">
@@ -85699,7 +85699,7 @@
       </c>
       <c r="B1376" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1376" s="2" t="inlineStr">
@@ -87497,7 +87497,7 @@
       </c>
       <c r="B1405" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1405" s="2" t="inlineStr">
@@ -88799,7 +88799,7 @@
       </c>
       <c r="B1426" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1426" s="2" t="inlineStr">
@@ -88861,7 +88861,7 @@
       </c>
       <c r="B1427" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1427" s="2" t="inlineStr">
@@ -89171,7 +89171,7 @@
       </c>
       <c r="B1432" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1432" s="2" t="inlineStr">
@@ -89543,7 +89543,7 @@
       </c>
       <c r="B1438" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1438" s="2" t="inlineStr">
@@ -91217,7 +91217,7 @@
       </c>
       <c r="B1465" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1465" s="2" t="inlineStr">
@@ -91341,7 +91341,7 @@
       </c>
       <c r="B1467" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1467" s="2" t="inlineStr">
@@ -92271,7 +92271,7 @@
       </c>
       <c r="B1482" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1482" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -15453,7 +15453,7 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
@@ -28659,7 +28659,7 @@
       </c>
       <c r="B456" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C456" s="2" t="inlineStr">
@@ -28721,7 +28721,7 @@
       </c>
       <c r="B457" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C457" s="2" t="inlineStr">
@@ -29341,7 +29341,7 @@
       </c>
       <c r="B467" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C467" s="2" t="inlineStr">
@@ -33247,7 +33247,7 @@
       </c>
       <c r="B530" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C530" s="2" t="inlineStr">
@@ -34735,7 +34735,7 @@
       </c>
       <c r="B554" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C554" s="2" t="inlineStr">
@@ -35851,7 +35851,7 @@
       </c>
       <c r="B572" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C572" s="2" t="inlineStr">
@@ -35975,7 +35975,7 @@
       </c>
       <c r="B574" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C574" s="2" t="inlineStr">
@@ -38207,7 +38207,7 @@
       </c>
       <c r="B610" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C610" s="2" t="inlineStr">
@@ -38641,7 +38641,7 @@
       </c>
       <c r="B617" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C617" s="2" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -42919,7 +42919,7 @@
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
@@ -43043,7 +43043,7 @@
       </c>
       <c r="B688" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C688" s="2" t="inlineStr">
@@ -44097,7 +44097,7 @@
       </c>
       <c r="B705" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C705" s="2" t="inlineStr">
@@ -44717,7 +44717,7 @@
       </c>
       <c r="B715" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C715" s="2" t="inlineStr">
@@ -47755,7 +47755,7 @@
       </c>
       <c r="B764" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C764" s="2" t="inlineStr">
@@ -49243,7 +49243,7 @@
       </c>
       <c r="B788" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C788" s="2" t="inlineStr">
@@ -51847,7 +51847,7 @@
       </c>
       <c r="B830" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C830" s="2" t="inlineStr">
@@ -52033,7 +52033,7 @@
       </c>
       <c r="B833" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C833" s="2" t="inlineStr">
@@ -58543,7 +58543,7 @@
       </c>
       <c r="B938" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C938" s="2" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="B971" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C971" s="2" t="inlineStr">
@@ -61023,7 +61023,7 @@
       </c>
       <c r="B978" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C978" s="2" t="inlineStr">
@@ -63627,7 +63627,7 @@
       </c>
       <c r="B1020" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1020" s="2" t="inlineStr">
@@ -67223,7 +67223,7 @@
       </c>
       <c r="B1078" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1078" s="2" t="inlineStr">
@@ -70199,7 +70199,7 @@
       </c>
       <c r="B1126" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1126" s="2" t="inlineStr">
@@ -70571,7 +70571,7 @@
       </c>
       <c r="B1132" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1132" s="2" t="inlineStr">
@@ -70819,7 +70819,7 @@
       </c>
       <c r="B1136" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1136" s="2" t="inlineStr">
@@ -71749,7 +71749,7 @@
       </c>
       <c r="B1151" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1151" s="2" t="inlineStr">
@@ -72121,7 +72121,7 @@
       </c>
       <c r="B1157" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1157" s="2" t="inlineStr">
@@ -72307,7 +72307,7 @@
       </c>
       <c r="B1160" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1160" s="2" t="inlineStr">
@@ -74167,7 +74167,7 @@
       </c>
       <c r="B1190" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1190" s="2" t="inlineStr">
@@ -75221,7 +75221,7 @@
       </c>
       <c r="B1207" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1207" s="2" t="inlineStr">
@@ -75283,7 +75283,7 @@
       </c>
       <c r="B1208" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1208" s="2" t="inlineStr">
@@ -78197,7 +78197,7 @@
       </c>
       <c r="B1255" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1255" s="2" t="inlineStr">
@@ -78259,7 +78259,7 @@
       </c>
       <c r="B1256" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1256" s="2" t="inlineStr">
@@ -79127,7 +79127,7 @@
       </c>
       <c r="B1270" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1270" s="2" t="inlineStr">
@@ -80119,7 +80119,7 @@
       </c>
       <c r="B1286" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1286" s="2" t="inlineStr">
@@ -80305,7 +80305,7 @@
       </c>
       <c r="B1289" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1289" s="2" t="inlineStr">
@@ -80429,7 +80429,7 @@
       </c>
       <c r="B1291" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1291" s="2" t="inlineStr">
@@ -84335,7 +84335,7 @@
       </c>
       <c r="B1354" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1354" s="2" t="inlineStr">
@@ -84459,7 +84459,7 @@
       </c>
       <c r="B1356" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1356" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84831,7 +84831,7 @@
       </c>
       <c r="B1362" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1362" s="2" t="inlineStr">
@@ -85141,7 +85141,7 @@
       </c>
       <c r="B1367" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1367" s="2" t="inlineStr">
@@ -85265,7 +85265,7 @@
       </c>
       <c r="B1369" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1369" s="2" t="inlineStr">
@@ -85637,7 +85637,7 @@
       </c>
       <c r="B1375" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1375" s="2" t="inlineStr">
@@ -87497,7 +87497,7 @@
       </c>
       <c r="B1405" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1405" s="2" t="inlineStr">
@@ -88861,7 +88861,7 @@
       </c>
       <c r="B1427" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1427" s="2" t="inlineStr">
@@ -89171,7 +89171,7 @@
       </c>
       <c r="B1432" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1432" s="2" t="inlineStr">
@@ -91341,7 +91341,7 @@
       </c>
       <c r="B1467" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1467" s="2" t="inlineStr">
@@ -92023,7 +92023,7 @@
       </c>
       <c r="B1478" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1478" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -15453,7 +15453,7 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
@@ -22459,7 +22459,7 @@
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
@@ -28659,7 +28659,7 @@
       </c>
       <c r="B456" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C456" s="2" t="inlineStr">
@@ -31077,7 +31077,7 @@
       </c>
       <c r="B495" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C495" s="2" t="inlineStr">
@@ -31945,7 +31945,7 @@
       </c>
       <c r="B509" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C509" s="2" t="inlineStr">
@@ -32131,7 +32131,7 @@
       </c>
       <c r="B512" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C512" s="2" t="inlineStr">
@@ -33247,7 +33247,7 @@
       </c>
       <c r="B530" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C530" s="2" t="inlineStr">
@@ -34735,7 +34735,7 @@
       </c>
       <c r="B554" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C554" s="2" t="inlineStr">
@@ -35851,7 +35851,7 @@
       </c>
       <c r="B572" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C572" s="2" t="inlineStr">
@@ -42919,7 +42919,7 @@
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
@@ -43043,7 +43043,7 @@
       </c>
       <c r="B688" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C688" s="2" t="inlineStr">
@@ -43105,7 +43105,7 @@
       </c>
       <c r="B689" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C689" s="2" t="inlineStr">
@@ -44717,7 +44717,7 @@
       </c>
       <c r="B715" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C715" s="2" t="inlineStr">
@@ -47755,7 +47755,7 @@
       </c>
       <c r="B764" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C764" s="2" t="inlineStr">
@@ -49243,7 +49243,7 @@
       </c>
       <c r="B788" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C788" s="2" t="inlineStr">
@@ -51351,7 +51351,7 @@
       </c>
       <c r="B822" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C822" s="2" t="inlineStr">
@@ -51847,7 +51847,7 @@
       </c>
       <c r="B830" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C830" s="2" t="inlineStr">
@@ -51971,7 +51971,7 @@
       </c>
       <c r="B832" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C832" s="2" t="inlineStr">
@@ -52033,7 +52033,7 @@
       </c>
       <c r="B833" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C833" s="2" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="B971" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C971" s="2" t="inlineStr">
@@ -60651,7 +60651,7 @@
       </c>
       <c r="B972" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C972" s="2" t="inlineStr">
@@ -61023,7 +61023,7 @@
       </c>
       <c r="B978" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C978" s="2" t="inlineStr">
@@ -63627,7 +63627,7 @@
       </c>
       <c r="B1020" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1020" s="2" t="inlineStr">
@@ -70571,7 +70571,7 @@
       </c>
       <c r="B1132" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1132" s="2" t="inlineStr">
@@ -70819,7 +70819,7 @@
       </c>
       <c r="B1136" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1136" s="2" t="inlineStr">
@@ -71749,7 +71749,7 @@
       </c>
       <c r="B1151" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1151" s="2" t="inlineStr">
@@ -72121,7 +72121,7 @@
       </c>
       <c r="B1157" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1157" s="2" t="inlineStr">
@@ -72245,7 +72245,7 @@
       </c>
       <c r="B1159" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1159" s="2" t="inlineStr">
@@ -75283,7 +75283,7 @@
       </c>
       <c r="B1208" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1208" s="2" t="inlineStr">
@@ -75345,7 +75345,7 @@
       </c>
       <c r="B1209" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1209" s="2" t="inlineStr">
@@ -75593,7 +75593,7 @@
       </c>
       <c r="B1213" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1213" s="2" t="inlineStr">
@@ -78259,7 +78259,7 @@
       </c>
       <c r="B1256" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1256" s="2" t="inlineStr">
@@ -79127,7 +79127,7 @@
       </c>
       <c r="B1270" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1270" s="2" t="inlineStr">
@@ -80119,7 +80119,7 @@
       </c>
       <c r="B1286" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1286" s="2" t="inlineStr">
@@ -84459,7 +84459,7 @@
       </c>
       <c r="B1356" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1356" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84831,7 +84831,7 @@
       </c>
       <c r="B1362" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1362" s="2" t="inlineStr">
@@ -84955,7 +84955,7 @@
       </c>
       <c r="B1364" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1364" s="2" t="inlineStr">
@@ -85141,7 +85141,7 @@
       </c>
       <c r="B1367" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1367" s="2" t="inlineStr">
@@ -85575,7 +85575,7 @@
       </c>
       <c r="B1374" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1374" s="2" t="inlineStr">
@@ -85637,7 +85637,7 @@
       </c>
       <c r="B1375" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1375" s="2" t="inlineStr">
@@ -87497,7 +87497,7 @@
       </c>
       <c r="B1405" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1405" s="2" t="inlineStr">
@@ -88861,7 +88861,7 @@
       </c>
       <c r="B1427" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1427" s="2" t="inlineStr">
@@ -89171,7 +89171,7 @@
       </c>
       <c r="B1432" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1432" s="2" t="inlineStr">
@@ -89543,7 +89543,7 @@
       </c>
       <c r="B1438" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1438" s="2" t="inlineStr">
@@ -92023,7 +92023,7 @@
       </c>
       <c r="B1478" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1478" s="2" t="inlineStr">
@@ -92953,7 +92953,7 @@
       </c>
       <c r="B1493" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1493" s="2" t="inlineStr">
@@ -93635,7 +93635,7 @@
       </c>
       <c r="B1504" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1504" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -7455,7 +7455,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -15453,7 +15453,7 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
@@ -28659,7 +28659,7 @@
       </c>
       <c r="B456" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C456" s="2" t="inlineStr">
@@ -30023,7 +30023,7 @@
       </c>
       <c r="B478" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C478" s="2" t="inlineStr">
@@ -31945,7 +31945,7 @@
       </c>
       <c r="B509" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C509" s="2" t="inlineStr">
@@ -32131,7 +32131,7 @@
       </c>
       <c r="B512" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C512" s="2" t="inlineStr">
@@ -34735,7 +34735,7 @@
       </c>
       <c r="B554" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C554" s="2" t="inlineStr">
@@ -38641,7 +38641,7 @@
       </c>
       <c r="B617" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C617" s="2" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -43043,7 +43043,7 @@
       </c>
       <c r="B688" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C688" s="2" t="inlineStr">
@@ -43291,7 +43291,7 @@
       </c>
       <c r="B692" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C692" s="2" t="inlineStr">
@@ -44717,7 +44717,7 @@
       </c>
       <c r="B715" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C715" s="2" t="inlineStr">
@@ -51413,7 +51413,7 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -51847,7 +51847,7 @@
       </c>
       <c r="B830" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C830" s="2" t="inlineStr">
@@ -51909,7 +51909,7 @@
       </c>
       <c r="B831" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C831" s="2" t="inlineStr">
@@ -51971,7 +51971,7 @@
       </c>
       <c r="B832" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C832" s="2" t="inlineStr">
@@ -52033,7 +52033,7 @@
       </c>
       <c r="B833" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C833" s="2" t="inlineStr">
@@ -60651,7 +60651,7 @@
       </c>
       <c r="B972" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C972" s="2" t="inlineStr">
@@ -61023,7 +61023,7 @@
       </c>
       <c r="B978" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C978" s="2" t="inlineStr">
@@ -63627,7 +63627,7 @@
       </c>
       <c r="B1020" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1020" s="2" t="inlineStr">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
@@ -70199,7 +70199,7 @@
       </c>
       <c r="B1126" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1126" s="2" t="inlineStr">
@@ -70261,7 +70261,7 @@
       </c>
       <c r="B1127" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1127" s="2" t="inlineStr">
@@ -70819,7 +70819,7 @@
       </c>
       <c r="B1136" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1136" s="2" t="inlineStr">
@@ -72121,7 +72121,7 @@
       </c>
       <c r="B1157" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1157" s="2" t="inlineStr">
@@ -72245,7 +72245,7 @@
       </c>
       <c r="B1159" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1159" s="2" t="inlineStr">
@@ -74167,7 +74167,7 @@
       </c>
       <c r="B1190" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1190" s="2" t="inlineStr">
@@ -75221,7 +75221,7 @@
       </c>
       <c r="B1207" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1207" s="2" t="inlineStr">
@@ -75345,7 +75345,7 @@
       </c>
       <c r="B1209" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1209" s="2" t="inlineStr">
@@ -75593,7 +75593,7 @@
       </c>
       <c r="B1213" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1213" s="2" t="inlineStr">
@@ -79127,7 +79127,7 @@
       </c>
       <c r="B1270" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1270" s="2" t="inlineStr">
@@ -79189,7 +79189,7 @@
       </c>
       <c r="B1271" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1271" s="2" t="inlineStr">
@@ -79623,7 +79623,7 @@
       </c>
       <c r="B1278" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1278" s="2" t="inlineStr">
@@ -80429,7 +80429,7 @@
       </c>
       <c r="B1291" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1291" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84831,7 +84831,7 @@
       </c>
       <c r="B1362" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1362" s="2" t="inlineStr">
@@ -84955,7 +84955,7 @@
       </c>
       <c r="B1364" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1364" s="2" t="inlineStr">
@@ -85265,7 +85265,7 @@
       </c>
       <c r="B1369" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1369" s="2" t="inlineStr">
@@ -85389,7 +85389,7 @@
       </c>
       <c r="B1371" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1371" s="2" t="inlineStr">
@@ -85575,7 +85575,7 @@
       </c>
       <c r="B1374" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1374" s="2" t="inlineStr">
@@ -85699,7 +85699,7 @@
       </c>
       <c r="B1376" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1376" s="2" t="inlineStr">
@@ -87497,7 +87497,7 @@
       </c>
       <c r="B1405" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1405" s="2" t="inlineStr">
@@ -88861,7 +88861,7 @@
       </c>
       <c r="B1427" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1427" s="2" t="inlineStr">
@@ -89543,7 +89543,7 @@
       </c>
       <c r="B1438" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1438" s="2" t="inlineStr">
@@ -91217,7 +91217,7 @@
       </c>
       <c r="B1465" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1465" s="2" t="inlineStr">
@@ -92271,7 +92271,7 @@
       </c>
       <c r="B1482" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1482" s="2" t="inlineStr">
@@ -93635,7 +93635,7 @@
       </c>
       <c r="B1504" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1504" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7455,7 +7455,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -15453,7 +15453,7 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
@@ -22459,7 +22459,7 @@
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
@@ -28659,7 +28659,7 @@
       </c>
       <c r="B456" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C456" s="2" t="inlineStr">
@@ -28721,7 +28721,7 @@
       </c>
       <c r="B457" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C457" s="2" t="inlineStr">
@@ -29341,7 +29341,7 @@
       </c>
       <c r="B467" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C467" s="2" t="inlineStr">
@@ -30023,7 +30023,7 @@
       </c>
       <c r="B478" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C478" s="2" t="inlineStr">
@@ -31077,7 +31077,7 @@
       </c>
       <c r="B495" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C495" s="2" t="inlineStr">
@@ -32131,7 +32131,7 @@
       </c>
       <c r="B512" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C512" s="2" t="inlineStr">
@@ -35851,7 +35851,7 @@
       </c>
       <c r="B572" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C572" s="2" t="inlineStr">
@@ -35975,7 +35975,7 @@
       </c>
       <c r="B574" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C574" s="2" t="inlineStr">
@@ -40625,7 +40625,7 @@
       </c>
       <c r="B649" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C649" s="2" t="inlineStr">
@@ -42919,7 +42919,7 @@
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
@@ -43043,7 +43043,7 @@
       </c>
       <c r="B688" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C688" s="2" t="inlineStr">
@@ -43105,7 +43105,7 @@
       </c>
       <c r="B689" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C689" s="2" t="inlineStr">
@@ -43291,7 +43291,7 @@
       </c>
       <c r="B692" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C692" s="2" t="inlineStr">
@@ -44097,7 +44097,7 @@
       </c>
       <c r="B705" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C705" s="2" t="inlineStr">
@@ -51413,7 +51413,7 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
@@ -51847,7 +51847,7 @@
       </c>
       <c r="B830" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C830" s="2" t="inlineStr">
@@ -51971,7 +51971,7 @@
       </c>
       <c r="B832" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C832" s="2" t="inlineStr">
@@ -52033,7 +52033,7 @@
       </c>
       <c r="B833" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C833" s="2" t="inlineStr">
@@ -56311,7 +56311,7 @@
       </c>
       <c r="B902" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C902" s="2" t="inlineStr">
@@ -58481,7 +58481,7 @@
       </c>
       <c r="B937" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C937" s="2" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="B971" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C971" s="2" t="inlineStr">
@@ -60651,7 +60651,7 @@
       </c>
       <c r="B972" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C972" s="2" t="inlineStr">
@@ -61023,7 +61023,7 @@
       </c>
       <c r="B978" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C978" s="2" t="inlineStr">
@@ -70199,7 +70199,7 @@
       </c>
       <c r="B1126" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1126" s="2" t="inlineStr">
@@ -70571,7 +70571,7 @@
       </c>
       <c r="B1132" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1132" s="2" t="inlineStr">
@@ -72121,7 +72121,7 @@
       </c>
       <c r="B1157" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1157" s="2" t="inlineStr">
@@ -74167,7 +74167,7 @@
       </c>
       <c r="B1190" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1190" s="2" t="inlineStr">
@@ -75221,7 +75221,7 @@
       </c>
       <c r="B1207" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1207" s="2" t="inlineStr">
@@ -75345,7 +75345,7 @@
       </c>
       <c r="B1209" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1209" s="2" t="inlineStr">
@@ -78197,7 +78197,7 @@
       </c>
       <c r="B1255" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1255" s="2" t="inlineStr">
@@ -78321,7 +78321,7 @@
       </c>
       <c r="B1257" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1257" s="2" t="inlineStr">
@@ -79189,7 +79189,7 @@
       </c>
       <c r="B1271" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1271" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84583,7 +84583,7 @@
       </c>
       <c r="B1358" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1358" s="2" t="inlineStr">
@@ -84831,7 +84831,7 @@
       </c>
       <c r="B1362" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1362" s="2" t="inlineStr">
@@ -84955,7 +84955,7 @@
       </c>
       <c r="B1364" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1364" s="2" t="inlineStr">
@@ -85141,7 +85141,7 @@
       </c>
       <c r="B1367" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1367" s="2" t="inlineStr">
@@ -85575,7 +85575,7 @@
       </c>
       <c r="B1374" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1374" s="2" t="inlineStr">
@@ -85637,7 +85637,7 @@
       </c>
       <c r="B1375" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1375" s="2" t="inlineStr">
@@ -85699,7 +85699,7 @@
       </c>
       <c r="B1376" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1376" s="2" t="inlineStr">
@@ -85761,7 +85761,7 @@
       </c>
       <c r="B1377" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1377" s="2" t="inlineStr">
@@ -89543,7 +89543,7 @@
       </c>
       <c r="B1438" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1438" s="2" t="inlineStr">
@@ -91217,7 +91217,7 @@
       </c>
       <c r="B1465" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1465" s="2" t="inlineStr">
@@ -92023,7 +92023,7 @@
       </c>
       <c r="B1478" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1478" s="2" t="inlineStr">
@@ -92271,7 +92271,7 @@
       </c>
       <c r="B1482" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1482" s="2" t="inlineStr">
@@ -93635,7 +93635,7 @@
       </c>
       <c r="B1504" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1504" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -28721,7 +28721,7 @@
       </c>
       <c r="B457" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C457" s="2" t="inlineStr">
@@ -30023,7 +30023,7 @@
       </c>
       <c r="B478" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C478" s="2" t="inlineStr">
@@ -31077,7 +31077,7 @@
       </c>
       <c r="B495" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C495" s="2" t="inlineStr">
@@ -31945,7 +31945,7 @@
       </c>
       <c r="B509" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C509" s="2" t="inlineStr">
@@ -32131,7 +32131,7 @@
       </c>
       <c r="B512" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C512" s="2" t="inlineStr">
@@ -33247,7 +33247,7 @@
       </c>
       <c r="B530" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C530" s="2" t="inlineStr">
@@ -35851,7 +35851,7 @@
       </c>
       <c r="B572" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C572" s="2" t="inlineStr">
@@ -38207,7 +38207,7 @@
       </c>
       <c r="B610" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C610" s="2" t="inlineStr">
@@ -38641,7 +38641,7 @@
       </c>
       <c r="B617" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C617" s="2" t="inlineStr">
@@ -40625,7 +40625,7 @@
       </c>
       <c r="B649" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C649" s="2" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -43043,7 +43043,7 @@
       </c>
       <c r="B688" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C688" s="2" t="inlineStr">
@@ -43291,7 +43291,7 @@
       </c>
       <c r="B692" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C692" s="2" t="inlineStr">
@@ -44717,7 +44717,7 @@
       </c>
       <c r="B715" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C715" s="2" t="inlineStr">
@@ -47755,7 +47755,7 @@
       </c>
       <c r="B764" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C764" s="2" t="inlineStr">
@@ -49243,7 +49243,7 @@
       </c>
       <c r="B788" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C788" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -51847,7 +51847,7 @@
       </c>
       <c r="B830" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C830" s="2" t="inlineStr">
@@ -51909,7 +51909,7 @@
       </c>
       <c r="B831" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C831" s="2" t="inlineStr">
@@ -51971,7 +51971,7 @@
       </c>
       <c r="B832" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C832" s="2" t="inlineStr">
@@ -52033,7 +52033,7 @@
       </c>
       <c r="B833" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C833" s="2" t="inlineStr">
@@ -56311,7 +56311,7 @@
       </c>
       <c r="B902" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C902" s="2" t="inlineStr">
@@ -58481,7 +58481,7 @@
       </c>
       <c r="B937" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C937" s="2" t="inlineStr">
@@ -58543,7 +58543,7 @@
       </c>
       <c r="B938" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C938" s="2" t="inlineStr">
@@ -61023,7 +61023,7 @@
       </c>
       <c r="B978" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C978" s="2" t="inlineStr">
@@ -63627,7 +63627,7 @@
       </c>
       <c r="B1020" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1020" s="2" t="inlineStr">
@@ -67223,7 +67223,7 @@
       </c>
       <c r="B1078" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1078" s="2" t="inlineStr">
@@ -70199,7 +70199,7 @@
       </c>
       <c r="B1126" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1126" s="2" t="inlineStr">
@@ -70261,7 +70261,7 @@
       </c>
       <c r="B1127" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1127" s="2" t="inlineStr">
@@ -72121,7 +72121,7 @@
       </c>
       <c r="B1157" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1157" s="2" t="inlineStr">
@@ -74167,7 +74167,7 @@
       </c>
       <c r="B1190" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1190" s="2" t="inlineStr">
@@ -75221,7 +75221,7 @@
       </c>
       <c r="B1207" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1207" s="2" t="inlineStr">
@@ -75531,7 +75531,7 @@
       </c>
       <c r="B1212" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1212" s="2" t="inlineStr">
@@ -75593,7 +75593,7 @@
       </c>
       <c r="B1213" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1213" s="2" t="inlineStr">
@@ -78259,7 +78259,7 @@
       </c>
       <c r="B1256" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1256" s="2" t="inlineStr">
@@ -78321,7 +78321,7 @@
       </c>
       <c r="B1257" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1257" s="2" t="inlineStr">
@@ -79189,7 +79189,7 @@
       </c>
       <c r="B1271" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1271" s="2" t="inlineStr">
@@ -80119,7 +80119,7 @@
       </c>
       <c r="B1286" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1286" s="2" t="inlineStr">
@@ -80305,7 +80305,7 @@
       </c>
       <c r="B1289" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1289" s="2" t="inlineStr">
@@ -80367,7 +80367,7 @@
       </c>
       <c r="B1290" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1290" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84831,7 +84831,7 @@
       </c>
       <c r="B1362" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1362" s="2" t="inlineStr">
@@ -85265,7 +85265,7 @@
       </c>
       <c r="B1369" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1369" s="2" t="inlineStr">
@@ -85637,7 +85637,7 @@
       </c>
       <c r="B1375" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1375" s="2" t="inlineStr">
@@ -85761,7 +85761,7 @@
       </c>
       <c r="B1377" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1377" s="2" t="inlineStr">
@@ -88799,7 +88799,7 @@
       </c>
       <c r="B1426" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1426" s="2" t="inlineStr">
@@ -88861,7 +88861,7 @@
       </c>
       <c r="B1427" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1427" s="2" t="inlineStr">
@@ -89171,7 +89171,7 @@
       </c>
       <c r="B1432" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1432" s="2" t="inlineStr">
@@ -89233,7 +89233,7 @@
       </c>
       <c r="B1433" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1433" s="2" t="inlineStr">
@@ -89481,7 +89481,7 @@
       </c>
       <c r="B1437" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1437" s="2" t="inlineStr">
@@ -91217,7 +91217,7 @@
       </c>
       <c r="B1465" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1465" s="2" t="inlineStr">
@@ -91341,7 +91341,7 @@
       </c>
       <c r="B1467" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1467" s="2" t="inlineStr">
@@ -92023,7 +92023,7 @@
       </c>
       <c r="B1478" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1478" s="2" t="inlineStr">
@@ -92271,7 +92271,7 @@
       </c>
       <c r="B1482" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1482" s="2" t="inlineStr">
@@ -92953,7 +92953,7 @@
       </c>
       <c r="B1493" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1493" s="2" t="inlineStr">
@@ -93635,7 +93635,7 @@
       </c>
       <c r="B1504" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1504" s="2" t="inlineStr">
@@ -93697,7 +93697,7 @@
       </c>
       <c r="B1505" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1505" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -22707,7 +22707,7 @@
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
@@ -28659,7 +28659,7 @@
       </c>
       <c r="B456" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C456" s="2" t="inlineStr">
@@ -28721,7 +28721,7 @@
       </c>
       <c r="B457" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C457" s="2" t="inlineStr">
@@ -29341,7 +29341,7 @@
       </c>
       <c r="B467" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C467" s="2" t="inlineStr">
@@ -30023,7 +30023,7 @@
       </c>
       <c r="B478" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C478" s="2" t="inlineStr">
@@ -31945,7 +31945,7 @@
       </c>
       <c r="B509" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C509" s="2" t="inlineStr">
@@ -33247,7 +33247,7 @@
       </c>
       <c r="B530" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C530" s="2" t="inlineStr">
@@ -35231,7 +35231,7 @@
       </c>
       <c r="B562" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C562" s="2" t="inlineStr">
@@ -38207,7 +38207,7 @@
       </c>
       <c r="B610" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C610" s="2" t="inlineStr">
@@ -40625,7 +40625,7 @@
       </c>
       <c r="B649" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C649" s="2" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
@@ -43105,7 +43105,7 @@
       </c>
       <c r="B689" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C689" s="2" t="inlineStr">
@@ -44097,7 +44097,7 @@
       </c>
       <c r="B705" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C705" s="2" t="inlineStr">
@@ -44717,7 +44717,7 @@
       </c>
       <c r="B715" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C715" s="2" t="inlineStr">
@@ -47755,7 +47755,7 @@
       </c>
       <c r="B764" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C764" s="2" t="inlineStr">
@@ -49243,7 +49243,7 @@
       </c>
       <c r="B788" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C788" s="2" t="inlineStr">
@@ -51351,7 +51351,7 @@
       </c>
       <c r="B822" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C822" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -52033,7 +52033,7 @@
       </c>
       <c r="B833" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C833" s="2" t="inlineStr">
@@ -58481,7 +58481,7 @@
       </c>
       <c r="B937" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C937" s="2" t="inlineStr">
@@ -58543,7 +58543,7 @@
       </c>
       <c r="B938" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C938" s="2" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="B971" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C971" s="2" t="inlineStr">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
@@ -70199,7 +70199,7 @@
       </c>
       <c r="B1126" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1126" s="2" t="inlineStr">
@@ -71749,7 +71749,7 @@
       </c>
       <c r="B1151" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1151" s="2" t="inlineStr">
@@ -72245,7 +72245,7 @@
       </c>
       <c r="B1159" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1159" s="2" t="inlineStr">
@@ -75221,7 +75221,7 @@
       </c>
       <c r="B1207" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1207" s="2" t="inlineStr">
@@ -75345,7 +75345,7 @@
       </c>
       <c r="B1209" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1209" s="2" t="inlineStr">
@@ -75531,7 +75531,7 @@
       </c>
       <c r="B1212" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1212" s="2" t="inlineStr">
@@ -76771,7 +76771,7 @@
       </c>
       <c r="B1232" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1232" s="2" t="inlineStr">
@@ -78135,7 +78135,7 @@
       </c>
       <c r="B1254" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1254" s="2" t="inlineStr">
@@ -78197,7 +78197,7 @@
       </c>
       <c r="B1255" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1255" s="2" t="inlineStr">
@@ -78259,7 +78259,7 @@
       </c>
       <c r="B1256" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1256" s="2" t="inlineStr">
@@ -78321,7 +78321,7 @@
       </c>
       <c r="B1257" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1257" s="2" t="inlineStr">
@@ -79623,7 +79623,7 @@
       </c>
       <c r="B1278" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1278" s="2" t="inlineStr">
@@ -80305,7 +80305,7 @@
       </c>
       <c r="B1289" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1289" s="2" t="inlineStr">
@@ -80367,7 +80367,7 @@
       </c>
       <c r="B1290" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1290" s="2" t="inlineStr">
@@ -80429,7 +80429,7 @@
       </c>
       <c r="B1291" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1291" s="2" t="inlineStr">
@@ -80615,7 +80615,7 @@
       </c>
       <c r="B1294" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1294" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84831,7 +84831,7 @@
       </c>
       <c r="B1362" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1362" s="2" t="inlineStr">
@@ -84955,7 +84955,7 @@
       </c>
       <c r="B1364" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1364" s="2" t="inlineStr">
@@ -85141,7 +85141,7 @@
       </c>
       <c r="B1367" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1367" s="2" t="inlineStr">
@@ -85265,7 +85265,7 @@
       </c>
       <c r="B1369" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1369" s="2" t="inlineStr">
@@ -85575,7 +85575,7 @@
       </c>
       <c r="B1374" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1374" s="2" t="inlineStr">
@@ -85637,7 +85637,7 @@
       </c>
       <c r="B1375" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1375" s="2" t="inlineStr">
@@ -85699,7 +85699,7 @@
       </c>
       <c r="B1376" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1376" s="2" t="inlineStr">
@@ -87497,7 +87497,7 @@
       </c>
       <c r="B1405" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1405" s="2" t="inlineStr">
@@ -88799,7 +88799,7 @@
       </c>
       <c r="B1426" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1426" s="2" t="inlineStr">
@@ -89171,7 +89171,7 @@
       </c>
       <c r="B1432" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1432" s="2" t="inlineStr">
@@ -89233,7 +89233,7 @@
       </c>
       <c r="B1433" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1433" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">
@@ -91341,7 +91341,7 @@
       </c>
       <c r="B1467" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1467" s="2" t="inlineStr">
@@ -92023,7 +92023,7 @@
       </c>
       <c r="B1478" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1478" s="2" t="inlineStr">
@@ -92953,7 +92953,7 @@
       </c>
       <c r="B1493" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1493" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -22707,7 +22707,7 @@
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
@@ -34735,7 +34735,7 @@
       </c>
       <c r="B554" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C554" s="2" t="inlineStr">
@@ -35231,7 +35231,7 @@
       </c>
       <c r="B562" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C562" s="2" t="inlineStr">
@@ -38641,7 +38641,7 @@
       </c>
       <c r="B617" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C617" s="2" t="inlineStr">
@@ -40625,7 +40625,7 @@
       </c>
       <c r="B649" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C649" s="2" t="inlineStr">
@@ -43105,7 +43105,7 @@
       </c>
       <c r="B689" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C689" s="2" t="inlineStr">
@@ -43291,7 +43291,7 @@
       </c>
       <c r="B692" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C692" s="2" t="inlineStr">
@@ -49243,7 +49243,7 @@
       </c>
       <c r="B788" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C788" s="2" t="inlineStr">
@@ -52033,7 +52033,7 @@
       </c>
       <c r="B833" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C833" s="2" t="inlineStr">
@@ -58481,7 +58481,7 @@
       </c>
       <c r="B937" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C937" s="2" t="inlineStr">
@@ -58543,7 +58543,7 @@
       </c>
       <c r="B938" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C938" s="2" t="inlineStr">
@@ -60651,7 +60651,7 @@
       </c>
       <c r="B972" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C972" s="2" t="inlineStr">
@@ -61023,7 +61023,7 @@
       </c>
       <c r="B978" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C978" s="2" t="inlineStr">
@@ -63627,7 +63627,7 @@
       </c>
       <c r="B1020" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C1020" s="2" t="inlineStr">
@@ -70199,7 +70199,7 @@
       </c>
       <c r="B1126" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1126" s="2" t="inlineStr">
@@ -70261,7 +70261,7 @@
       </c>
       <c r="B1127" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1127" s="2" t="inlineStr">
@@ -72121,7 +72121,7 @@
       </c>
       <c r="B1157" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1157" s="2" t="inlineStr">
@@ -72245,7 +72245,7 @@
       </c>
       <c r="B1159" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1159" s="2" t="inlineStr">
@@ -75221,7 +75221,7 @@
       </c>
       <c r="B1207" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1207" s="2" t="inlineStr">
@@ -75345,7 +75345,7 @@
       </c>
       <c r="B1209" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1209" s="2" t="inlineStr">
@@ -75593,7 +75593,7 @@
       </c>
       <c r="B1213" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1213" s="2" t="inlineStr">
@@ -76771,7 +76771,7 @@
       </c>
       <c r="B1232" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1232" s="2" t="inlineStr">
@@ -78135,7 +78135,7 @@
       </c>
       <c r="B1254" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1254" s="2" t="inlineStr">
@@ -78197,7 +78197,7 @@
       </c>
       <c r="B1255" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1255" s="2" t="inlineStr">
@@ -78321,7 +78321,7 @@
       </c>
       <c r="B1257" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1257" s="2" t="inlineStr">
@@ -79127,7 +79127,7 @@
       </c>
       <c r="B1270" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C1270" s="2" t="inlineStr">
@@ -80119,7 +80119,7 @@
       </c>
       <c r="B1286" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1286" s="2" t="inlineStr">
@@ -80367,7 +80367,7 @@
       </c>
       <c r="B1290" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1290" s="2" t="inlineStr">
@@ -84459,7 +84459,7 @@
       </c>
       <c r="B1356" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1356" s="2" t="inlineStr">
@@ -84521,7 +84521,7 @@
       </c>
       <c r="B1357" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1357" s="2" t="inlineStr">
@@ -84831,7 +84831,7 @@
       </c>
       <c r="B1362" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1362" s="2" t="inlineStr">
@@ -84955,7 +84955,7 @@
       </c>
       <c r="B1364" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1364" s="2" t="inlineStr">
@@ -85699,7 +85699,7 @@
       </c>
       <c r="B1376" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1376" s="2" t="inlineStr">
@@ -85761,7 +85761,7 @@
       </c>
       <c r="B1377" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1377" s="2" t="inlineStr">
@@ -87497,7 +87497,7 @@
       </c>
       <c r="B1405" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1405" s="2" t="inlineStr">
@@ -88861,7 +88861,7 @@
       </c>
       <c r="B1427" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1427" s="2" t="inlineStr">
@@ -89481,7 +89481,7 @@
       </c>
       <c r="B1437" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1437" s="2" t="inlineStr">
@@ -91217,7 +91217,7 @@
       </c>
       <c r="B1465" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1465" s="2" t="inlineStr">
@@ -91279,7 +91279,7 @@
       </c>
       <c r="B1466" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1466" s="2" t="inlineStr">
@@ -91341,7 +91341,7 @@
       </c>
       <c r="B1467" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1467" s="2" t="inlineStr">
@@ -92271,7 +92271,7 @@
       </c>
       <c r="B1482" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1482" s="2" t="inlineStr">
@@ -93635,7 +93635,7 @@
       </c>
       <c r="B1504" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1504" s="2" t="inlineStr">
@@ -93697,7 +93697,7 @@
       </c>
       <c r="B1505" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1505" s="2" t="inlineStr">

--- a/relatorio_analitico_caixa_42l.xlsx
+++ b/relatorio_analitico_caixa_42l.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -15453,7 +15453,7 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
@@ -22707,7 +22707,7 @@
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
@@ -28659,7 +28659,7 @@
       </c>
       <c r="B456" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C456" s="2" t="inlineStr">
@@ -32131,7 +32131,7 @@
       </c>
       <c r="B512" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C512" s="2" t="inlineStr">
@@ -33495,7 +33495,7 @@
       </c>
       <c r="B534" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C534" s="2" t="inlineStr">
@@ -40625,7 +40625,7 @@
       </c>
       <c r="B649" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C649" s="2" t="inlineStr">
@@ -43043,7 +43043,7 @@
       </c>
       <c r="B688" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C688" s="2" t="inlineStr">
@@ -43105,7 +43105,7 @@
       </c>
       <c r="B689" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>2 C a 8 C</t>
         </is>
       </c>
       <c r="C689" s="2" t="inlineStr">
@@ -44097,7 +44097,7 @@
       </c>
       <c r="B705" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C705" s="2" t="inlineStr">
@@ -44717,7 +44717,7 @@
       </c>
       <c r="B715" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C715" s="2" t="inlineStr">
@@ -47755,7 +47755,7 @@
       </c>
       <c r="B764" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C764" s="2" t="inlineStr">
@@ -51351,7 +51351,7 @@
       </c>
       <c r="B822" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C822" s="2" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
@@ -51847,7 +51847,7 @@
       </c>
       <c r="B830" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C830" s="2" t="inlineStr">
@@ -51909,7 +51909,7 @@
       </c>
       <c r="B831" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C831" s="2" t="inlineStr">
@@ -51971,7 +51971,7 @@
       </c>
       <c r="B832" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C832" s="2" t="inlineStr">
@@ -52033,7 +52033,7 @@
       </c>
       <c r="B833" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C833" s="2" t="inlineStr">
@@ -54203,7 +54203,7 @@
       </c>
       <c r="B868" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-15 C a -30 C</t>
         </is>
       </c>
       <c r="C868" s="2" t="inlineStr">
@@ -58605,7 +58605,7 @@
       </c>
       <c r="B939" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C939" s="2" t="inlineStr">
@@ -58667,7 +58667,7 @@
       </c>
       <c r="B940" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C940" s="2" t="inlineStr">
@@ -60713,7 +60713,7 @@
       </c>
       <c r="B973" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C973" s="2" t="inlineStr">
@@ -60775,7 +60775,7 @@
       </c>
       <c r="B974" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C974" s="2" t="inlineStr">
@@ -61147,7 +61147,7 @@
       </c>
       <c r="B980" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C980" s="2" t="inlineStr">
@@ -63751,7 +63751,7 @@
       </c>
       <c r="B1022" s="2" t="inlineStr">
         <is>
-          <t>-15 C a -30 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1022" s="2" t="inlineStr">
@@ -70075,7 +70075,7 @@
       </c>
       <c r="B1124" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1124" s="2" t="inlineStr">
@@ -70385,7 +70385,7 @@
       </c>
       <c r="B1129" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1129" s="2" t="inlineStr">
@@ -72369,7 +72369,7 @@
       </c>
       <c r="B1161" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1161" s="2" t="inlineStr">
@@ -75283,7 +75283,7 @@
       </c>
       <c r="B1208" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1208" s="2" t="inlineStr">
@@ -75407,7 +75407,7 @@
       </c>
       <c r="B1210" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1210" s="2" t="inlineStr">
@@ -75717,7 +75717,7 @@
       </c>
       <c r="B1215" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1215" s="2" t="inlineStr">
@@ -76895,7 +76895,7 @@
       </c>
       <c r="B1234" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1234" s="2" t="inlineStr">
@@ -78321,7 +78321,7 @@
       </c>
       <c r="B1257" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1257" s="2" t="inlineStr">
@@ -78383,7 +78383,7 @@
       </c>
       <c r="B1258" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1258" s="2" t="inlineStr">
@@ -80243,7 +80243,7 @@
       </c>
       <c r="B1288" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1288" s="2" t="inlineStr">
@@ -80429,7 +80429,7 @@
       </c>
       <c r="B1291" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1291" s="2" t="inlineStr">
@@ -80553,7 +80553,7 @@
       </c>
       <c r="B1293" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1293" s="2" t="inlineStr">
@@ -84583,7 +84583,7 @@
       </c>
       <c r="B1358" s="2" t="inlineStr">
         <is>
-          <t>-35 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1358" s="2" t="inlineStr">
@@ -84645,7 +84645,7 @@
       </c>
       <c r="B1359" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1359" s="2" t="inlineStr">
@@ -84955,7 +84955,7 @@
       </c>
       <c r="B1364" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1364" s="2" t="inlineStr">
@@ -85389,7 +85389,7 @@
       </c>
       <c r="B1371" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1371" s="2" t="inlineStr">
@@ -85761,7 +85761,7 @@
       </c>
       <c r="B1377" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1377" s="2" t="inlineStr">
@@ -85823,7 +85823,7 @@
       </c>
       <c r="B1378" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1378" s="2" t="inlineStr">
@@ -89295,7 +89295,7 @@
       </c>
       <c r="B1434" s="2" t="inlineStr">
         <is>
-          <t>-25 C a -15 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1434" s="2" t="inlineStr">
@@ -89357,7 +89357,7 @@
       </c>
       <c r="B1435" s="2" t="inlineStr">
         <is>
-          <t>2 C a 8 C</t>
+          <t>-30 C a -15 C</t>
         </is>
       </c>
       <c r="C1435" s="2" t="inlineStr">
@@ -91403,7 +91403,7 @@
       </c>
       <c r="B1468" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1468" s="2" t="inlineStr">
@@ -92147,7 +92147,7 @@
       </c>
       <c r="B1480" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-25 C a -15 C</t>
         </is>
       </c>
       <c r="C1480" s="2" t="inlineStr">
@@ -93821,7 +93821,7 @@
       </c>
       <c r="B1507" s="2" t="inlineStr">
         <is>
-          <t>-30 C a -15 C</t>
+          <t>-35 C a -15 C</t>
         </is>
       </c>
       <c r="C1507" s="2" t="inlineStr">
